--- a/leads/Genuine_NM_100_Clients.xlsx
+++ b/leads/Genuine_NM_100_Clients.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:Q152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -444,9 +444,12 @@
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,15 +510,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Email Subject</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email Body</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WhatsApp Message</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>WhatsApp Link</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Email Link</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -571,15 +589,52 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918779385489?text=Hi%20Renu%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Harshis%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Harshis%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Harshis: I checked harshis.in</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>mailto:renugujari@gmail.com?subject=Harshis%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Renu%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Harshis.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20site%20intermittently%20errors%20%28500%20observed%29%3B%20template%20leftovers%20%28needhelp%40floens.com%20/%20fake%20support%20number%29%3B%20thin%20menu%20and%20no%20online%20order%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Harshis%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Renu,
+I opened https://harshis.in/ while looking at bakery businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Your website sometimes opens an error page (I got a 500) instead of your homepage
+• Leftover template / fake contact details are still showing on the site — not your real number or email
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Harshis this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Hi Renu,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://harshis.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Your website sometimes opens an error page (I got a 500) instead of your homepage
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Harshis this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918779385489?text=Hi%20Renu%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//harshis.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Harshis%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>mailto:renugujari@gmail.com?subject=Harshis%3A%20I%20checked%20harshis.in&amp;body=Dear%20Renu%2C%0A%0AI%20opened%20https%3A//harshis.in/%20while%20looking%20at%20bakery%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20Leftover%20template%20/%20fake%20contact%20details%20are%20still%20showing%20on%20the%20site%20%E2%80%94%20not%20your%20real%20number%20or%20email%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Harshis%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -639,15 +694,52 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917738334040?text=Hi%20Nikhil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20%28Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Copyright%20frozen%20at%202021%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Pacific Diagnostics &amp; Multispeciality Dental Clinic: I checked pacificddk.com</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>mailto:pacificddk@gmail.com?subject=Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Nikhil%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0ACopyright%20frozen%20at%202021%3B%20Gmail-only%20contact%3B%20generic%20Endurance%20Tech%20template%20look%3B%20mixed%20diagnostics%20%2B%20dental%20messaging%20dilutes%20specialty%20positioning%0A%0APanvel%20diagnostics-dental%20hybrid%20needs%20clearer%20dual-service%20website%20to%20convert%20implant%20and%20scan%20walk-ins.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Nikhil,
+I opened https://pacificddk.com/ while looking at dental businesses in Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• The copyright year on the site is old, so it looks abandoned
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Pacific Diagnostics &amp; Multispeciality Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nikhil,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pacificddk.com/) and a couple of things stood out:
+• The copyright year on the site is old, so it looks abandoned
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Pacific Diagnostics &amp; Multispeciality Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917738334040?text=Hi%20Nikhil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pacificddk.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>mailto:pacificddk@gmail.com?subject=Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%3A%20I%20checked%20pacificddk.com&amp;body=Dear%20Nikhil%2C%0A%0AI%20opened%20https%3A//pacificddk.com/%20while%20looking%20at%20dental%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>https://pacificddk.com/</t>
         </is>
@@ -707,15 +799,52 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919022759022?text=Hi%20Rohit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sparsh%20Superspeciality%20Hospital%20%28Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Homepage%20counters%20stuck%20at%200%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sparsh%20Superspeciality%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Sparsh Superspeciality Hospital: I checked sparshhospital.in</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>mailto:sparsh.tpa@gmail.com?subject=Sparsh%20Superspeciality%20Hospital%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Rohit%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Sparsh%20Superspeciality%20Hospital.%0A%0ASpecific%20issues%20I%20found%3A%0AHomepage%20counters%20stuck%20at%200%3B%20typos%20%28%27Confortable%20care%27%2C%20%27Heart%20Valce%27%29%3B%20Gmail%20TPA%20email%20as%20primary%20contact%3B%20template%20hospital%20design%20with%20weak%20specialty%20storytelling%0A%0A24x7%20Panvel%20trauma/ortho%20hospital%20whose%20broken%20stats%20and%20typos%20undermine%20emergency%20trust.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Sparsh%20Superspeciality%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Rohit,
+I opened https://sparshhospital.in/ while looking at healthcare businesses in Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• There are typos on the homepage (e.g. 'Confortable care') that look unprofessional
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Sparsh Superspeciality Hospital this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Hi Rohit,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sparshhospital.in/) and a couple of things stood out:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• There are typos on the homepage (e.g. 'Confortable care') that look unprofessional
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Sparsh Superspeciality Hospital this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919022759022?text=Hi%20Rohit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sparshhospital.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Confortable%20care%27%29%20that%20look%20unprofessional%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sparsh%20Superspeciality%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sparsh.tpa@gmail.com?subject=Sparsh%20Superspeciality%20Hospital%3A%20I%20checked%20sparshhospital.in&amp;body=Dear%20Rohit%2C%0A%0AI%20opened%20https%3A//sparshhospital.in/%20while%20looking%20at%20healthcare%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Confortable%20care%27%29%20that%20look%20unprofessional%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sparsh%20Superspeciality%20Hospital%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>https://sparshhospital.in/</t>
         </is>
@@ -775,15 +904,52 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917021761628?text=Hi%20Jagruti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Gmail-only%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr. Jagruti Skin and Hair Clinic: I checked drjagrutiskinclinic.com</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>mailto:drjagruti97@gmail.com?subject=Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Jagruti%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20contact%3B%20generic%20aesthetic%20clinic%20template%3B%20two-location%20footer%20dilutes%20local%20Vashi%20focus%3B%20limited%20treatment%20detail%20depth%20for%20laser/hair%20packages%0A%0ASector%2017%20Vashi%20skin%20clinic%20that%20can%20win%20more%20clients%20with%20a%20sharper%20local%20booking%20funnel%20and%20branded%20email.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Jagruti,
+I opened https://drjagrutiskinclinic.com/ while looking at healthcare businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The site looks like a generic template rather than your brand
+• Two-location footer dilutes local Vashi focus
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr. Jagruti Skin and Hair Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jagruti,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drjagrutiskinclinic.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The site looks like a generic template rather than your brand
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr. Jagruti Skin and Hair Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917021761628?text=Hi%20Jagruti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drjagrutiskinclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>mailto:drjagruti97@gmail.com?subject=Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%3A%20I%20checked%20drjagrutiskinclinic.com&amp;body=Dear%20Jagruti%2C%0A%0AI%20opened%20https%3A//drjagrutiskinclinic.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Two-location%20footer%20dilutes%20local%20Vashi%20focus%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>https://drjagrutiskinclinic.com/</t>
         </is>
@@ -843,15 +1009,52 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917045011188?text=Hi%20Jatin%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Jairaj%27s%20Hospital%20%28CBD%20Belapur%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Gmail-only%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Jairaj%27s%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr. Jairaj's Hospital: I checked drjairajshospital.com</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>mailto:jairajhospital@gmail.com?subject=Dr.%20Jairaj%27s%20Hospital%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Jatin%2C%0A%0AWhile%20reviewing%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dr.%20Jairaj%27s%20Hospital.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20contact%3B%20thin%20service%20pages%20with%20generic%20wellness%20copy%3B%20limited%20doctor%20detail%3B%20basic%20template%20look%20for%20a%20multispeciality%20hospital%0A%0ABelapur%20maternity/ortho%20hospital%20with%20good%20local%20reviews%20but%20thin%20website%20fails%20to%20convert%20specialty%20searches.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr.%20Jairaj%27s%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Jatin,
+I opened https://drjairajshospital.com/ while looking at healthcare businesses in CBD Belapur, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+• Limited doctor detail
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr. Jairaj's Hospital this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jatin,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drjairajshospital.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr. Jairaj's Hospital this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917045011188?text=Hi%20Jatin%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drjairajshospital.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jairaj%27s%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>mailto:jairajhospital@gmail.com?subject=Dr.%20Jairaj%27s%20Hospital%3A%20I%20checked%20drjairajshospital.com&amp;body=Dear%20Jatin%2C%0A%0AI%20opened%20https%3A//drjairajshospital.com/%20while%20looking%20at%20healthcare%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Limited%20doctor%20detail%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Jairaj%27s%20Hospital%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>https://drjairajshospital.com/</t>
         </is>
@@ -911,15 +1114,52 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918850610990?text=Hi%20Rita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Rita%27s%20Beauty%20Hub%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Old%20static%20multi-page%20HTML%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Rita%27s%20Beauty%20Hub%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Rita's Beauty Hub: I checked www.ritasbeautyhub.in</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>mailto:ritasbeautyhub@gmail.com?subject=Rita%27s%20Beauty%20Hub%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Rita%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Rita%27s%20Beauty%20Hub.%0A%0ASpecific%20issues%20I%20found%3A%0AOld%20static%20multi-page%20HTML%3B%20heavy%20keyword%20stuffing%20in%20title%3B%20typos%20in%20testimonials%20%28%27Amonymous%27%2C%20%27Testimoinials%27%29%3B%20Gmail%20contact%3B%20weak%20mobile%20UX%0A%0ASalon%20traffic%20is%20mobile-first%20%E2%80%94%20replacing%20the%20dated%20static%20site%20with%20a%20booking-led%20redesign%20recovers%20lost%20walk-in%20enquiries.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Rita%27s%20Beauty%20Hub%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Rita,
+I opened https://www.ritasbeautyhub.in/ while looking at salon businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Old static multi-page HTML
+• Heavy keyword stuffing in title
+• There are typos on the homepage (e.g. 'Amonymous') that look unprofessional
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Rita's Beauty Hub this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Hi Rita,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.ritasbeautyhub.in/) and a couple of things stood out:
+• Old static multi-page HTML
+• Heavy keyword stuffing in title
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Rita's Beauty Hub this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918850610990?text=Hi%20Rita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.ritasbeautyhub.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Old%20static%20multi-page%20HTML%0A%E2%80%A2%20Heavy%20keyword%20stuffing%20in%20title%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Rita%27s%20Beauty%20Hub%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>mailto:ritasbeautyhub@gmail.com?subject=Rita%27s%20Beauty%20Hub%3A%20I%20checked%20www.ritasbeautyhub.in&amp;body=Dear%20Rita%2C%0A%0AI%20opened%20https%3A//www.ritasbeautyhub.in/%20while%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Old%20static%20multi-page%20HTML%0A%E2%80%A2%20Heavy%20keyword%20stuffing%20in%20title%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Amonymous%27%29%20that%20look%20unprofessional%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Rita%27s%20Beauty%20Hub%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>https://www.ritasbeautyhub.in/index.html</t>
         </is>
@@ -975,15 +1215,52 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967661337?text=Hi%20Rutuparn%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sasane%20Dental%20Clinic%20%28Panvel%29%20and%20noticed%3A%20Gmail-only%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sasane%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Sasane Dental Clinic: I checked sasanedental.com</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>mailto:sasanedentalclinic@gmail.com?subject=Sasane%20Dental%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Rutuparn%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%2C%20I%20looked%20at%20Sasane%20Dental%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20email%3B%20homepage%20counters%20show%200%2B%3B%20dual-brand%20%28Tooth%20Legacy%29%20messaging%20can%20confuse%3B%20agency-built%20template%20feel%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Sasane%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Rutuparn,
+I opened https://sasanedental.com/ while looking at dental businesses in Panvel.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• Dual-brand (Tooth Legacy) messaging can confuse
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Sasane Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Hi Rutuparn,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sasanedental.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Sasane Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919967661337?text=Hi%20Rutuparn%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sasanedental.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sasane%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sasanedentalclinic@gmail.com?subject=Sasane%20Dental%20Clinic%3A%20I%20checked%20sasanedental.com&amp;body=Dear%20Rutuparn%2C%0A%0AI%20opened%20https%3A//sasanedental.com/%20while%20looking%20at%20dental%20businesses%20in%20Panvel.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20Dual-brand%20%28Tooth%20Legacy%29%20messaging%20can%20confuse%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sasane%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -1039,15 +1316,52 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004120002?text=Hi%20Harshil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dentkraft%20Dental%20Clinics%20%28Kharghar%29%20and%20noticed%3A%20Gmail-only%20primary%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dentkraft%20Dental%20Clinics%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dentkraft Dental Clinics: I checked dentkraftdentalclinics.com</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>mailto:dr.harshil@gmail.com?subject=Dentkraft%20Dental%20Clinics%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Harshil%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20I%20looked%20at%20Dentkraft%20Dental%20Clinics.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20primary%20email%3B%20dated%20multi-page%20template%20design%3B%20thin%20modern%20UX%3B%20contact%20form%20heavy%20vs%20clear%20CTA%20hierarchy%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dentkraft%20Dental%20Clinics%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Harshil,
+I opened https://dentkraftdentalclinics.com/ while looking at dental businesses in Kharghar.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Dentkraft Dental Clinics this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Hi Harshil,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://dentkraftdentalclinics.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Dentkraft Dental Clinics this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919004120002?text=Hi%20Harshil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//dentkraftdentalclinics.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dentkraft%20Dental%20Clinics%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>mailto:dr.harshil@gmail.com?subject=Dentkraft%20Dental%20Clinics%3A%20I%20checked%20dentkraftdentalclinics.com&amp;body=Dear%20Harshil%2C%0A%0AI%20opened%20https%3A//dentkraftdentalclinics.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dentkraft%20Dental%20Clinics%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -1107,15 +1421,52 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918108973790?text=Hi%20Ganesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Gmail-only%20professional%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr. Bhandari's Dental Clinic &amp; Implant Centre: I checked drgbdentalclinic.com</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>mailto:drbhandarisdentalclinic@gmail.com?subject=Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Ganesh%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20professional%20contact%3B%20contact%20form%20requires%20JavaScript%20and%20looks%20incomplete%3B%20thin%20contact%20page%3B%20no%20prominent%20WhatsApp%20booking%20CTA%0A%0AStrong%20implant%20reviews%20and%20a%20real%20landline%2C%20but%20the%20site%20under-sells%20a%20specialist%20prosthodontist%20practice.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Ganesh,
+I opened https://drgbdentalclinic.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Contact form requires JavaScript and looks incomplete
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Dr. Bhandari's Dental Clinic &amp; Implant Centre this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ganesh,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drgbdentalclinic.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Contact form requires JavaScript and looks incomplete
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Dr. Bhandari's Dental Clinic &amp; Implant Centre this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918108973790?text=Hi%20Ganesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drgbdentalclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Contact%20form%20requires%20JavaScript%20and%20looks%20incomplete%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>mailto:drbhandarisdentalclinic@gmail.com?subject=Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%3A%20I%20checked%20drgbdentalclinic.com&amp;body=Dear%20Ganesh%2C%0A%0AI%20opened%20https%3A//drgbdentalclinic.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Contact%20form%20requires%20JavaScript%20and%20looks%20incomplete%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>https://drgbdentalclinic.com/</t>
         </is>
@@ -1171,15 +1522,52 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919892850651?text=Hi%20Amit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Orosmyle%20Dental%20Clinic%20%28Kamothe%29%20and%20noticed%3A%20Gmail-only%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Orosmyle%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Orosmyle Dental Clinic: I checked orosmyle.com</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>mailto:orosmyle@gmail.com?subject=Orosmyle%20Dental%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Amit%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kamothe%2C%20I%20looked%20at%20Orosmyle%20Dental%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20email%3B%20homepage%20counters%20stuck%20at%200%3B%20template%20dental%20theme%3B%20thin%20about/team%20depth%20on%20main%20page%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Orosmyle%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Amit,
+I opened https://orosmyle.com/ while looking at dental businesses in Kamothe.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Orosmyle Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Hi Amit,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://orosmyle.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Orosmyle Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919892850651?text=Hi%20Amit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//orosmyle.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Orosmyle%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>mailto:orosmyle@gmail.com?subject=Orosmyle%20Dental%20Clinic%3A%20I%20checked%20orosmyle.com&amp;body=Dear%20Amit%2C%0A%0AI%20opened%20https%3A//orosmyle.com/%20while%20looking%20at%20dental%20businesses%20in%20Kamothe.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Orosmyle%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -1235,15 +1623,52 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917045859333?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Ratnakokan%20Restaurant%20%28Sanpada%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Outdated/broken%20homepage%20presentation%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Ratnakokan%20Restaurant%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Ratnakokan Restaurant: I checked ratnakokan.com</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>mailto:mail@ratnakokan.com?subject=Ratnakokan%20Restaurant%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sanjay%2C%0A%0AWhile%20reviewing%20businesses%20in%20Sanpada%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Ratnakokan%20Restaurant.%0A%0ASpecific%20issues%20I%20found%3A%0AOutdated/broken%20homepage%20presentation%3B%20no%20online%20order%20cart%3B%20multi-branch%20phones%20listed%20but%20weak%20conversion%20CTAs%3B%20Swiggy/Zomato%20reliant%20for%20delivery%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Ratnakokan%20Restaurant%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sanjay,
+I opened https://ratnakokan.com/ while looking at restaurant businesses in Sanpada, Navi Mumbai.
+Here's what a customer would notice today:
+• The pages look dated and thin — visitors don't get enough proof to call
+• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+• Multi-branch phones listed but weak conversion CTAs
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Ratnakokan Restaurant this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sanjay,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ratnakokan.com/) and a couple of things stood out:
+• The pages look dated and thin — visitors don't get enough proof to call
+• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Ratnakokan Restaurant this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917045859333?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ratnakokan.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ratnakokan%20Restaurant%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>mailto:mail@ratnakokan.com?subject=Ratnakokan%20Restaurant%3A%20I%20checked%20ratnakokan.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20opened%20https%3A//ratnakokan.com/%20while%20looking%20at%20restaurant%20businesses%20in%20Sanpada%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%E2%80%A2%20Multi-branch%20phones%20listed%20but%20weak%20conversion%20CTAs%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Ratnakokan%20Restaurant%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -1299,15 +1724,52 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919021621337?text=Hi%20Rutuparn%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20%28Panvel%29%20and%20noticed%3A%20New%20Panvel%20brand%20nested%20under%20Old%20Panvel%20site%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Sasane Dental / Tooth Legacy Dental &amp; Implant Center: I checked sasanedental.com/contact-us</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>mailto:sasanedentalclinic@gmail.com?subject=Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Rutuparn%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%2C%20I%20looked%20at%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center.%0A%0ASpecific%20issues%20I%20found%3A%0ANew%20Panvel%20brand%20nested%20under%20Old%20Panvel%20site%3B%20Gmail-only%20email%3B%20dual-location%20confusion%3B%20agency%20template%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Rutuparn,
+I opened https://sasanedental.com/contact-us/ while looking at dental businesses in Panvel.
+Here's what a customer would notice today:
+• New Panvel brand nested under Old Panvel site
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Dual-location confusion
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Sasane Dental / Tooth Legacy Dental &amp; Implant Center this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Hi Rutuparn,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sasanedental.com/contact-us/) and a couple of things stood out:
+• New Panvel brand nested under Old Panvel site
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Sasane Dental / Tooth Legacy Dental &amp; Implant Center this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919021621337?text=Hi%20Rutuparn%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sasanedental.com/contact-us/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20New%20Panvel%20brand%20nested%20under%20Old%20Panvel%20site%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sasanedentalclinic@gmail.com?subject=Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%3A%20I%20checked%20sasanedental.com/contact-us&amp;body=Dear%20Rutuparn%2C%0A%0AI%20opened%20https%3A//sasanedental.com/contact-us/%20while%20looking%20at%20dental%20businesses%20in%20Panvel.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20New%20Panvel%20brand%20nested%20under%20Old%20Panvel%20site%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Dual-location%20confusion%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -1363,15 +1825,52 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137208535?text=Hi%20Sharad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20%28Nerul%29%20and%20noticed%3A%20Branch%20page%20shares%20parent%20site%20template%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Smile Please Super Speciality Dental Clinic (Nerul): I checked www.smiileplease.com/nerulbranch</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>mailto:shharrad@gmail.com?subject=Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sharad%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%2C%20I%20looked%20at%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29.%0A%0ASpecific%20issues%20I%20found%3A%0ABranch%20page%20shares%20parent%20site%20template%3B%20Gmail-only%20email%3B%20dated%20design%3B%20booking%20still%20phone-centric%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sharad,
+I opened https://www.smiileplease.com/nerulbranch/ while looking at dental businesses in Nerul.
+Here's what a customer would notice today:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Smile Please Super Speciality Dental Clinic (Nerul) this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sharad,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smiileplease.com/nerulbranch/) and a couple of things stood out:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Smile Please Super Speciality Dental Clinic (Nerul) this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919137208535?text=Hi%20Sharad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smiileplease.com/nerulbranch/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>mailto:shharrad@gmail.com?subject=Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%3A%20I%20checked%20www.smiileplease.com/nerulbranch&amp;body=Dear%20Sharad%2C%0A%0AI%20opened%20https%3A//www.smiileplease.com/nerulbranch/%20while%20looking%20at%20dental%20businesses%20in%20Nerul.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -1431,15 +1930,49 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967044547?text=Hi%20CA%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Yash%20A.%20Jain%20%26%20Associates%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Broken%20animated%20counters%20stuck%20at%200%2B%2C%20Gmail%20contact%2C%20template%20CA%20layout%2C%20limited%20service%20detail%20beyond%20buzzwords%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Yash%20A.%20Jain%20%26%20Associates%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Yash A. Jain &amp; Associates: I checked www.cayashjain.com</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>mailto:yjassociates12@gmail.com?subject=Yash%20A.%20Jain%20%26%20Associates%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20CA%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Yash%20A.%20Jain%20%26%20Associates.%0A%0ASpecific%20issues%20I%20found%3A%0ABroken%20animated%20counters%20stuck%20at%200%2B%2C%20Gmail%20contact%2C%20template%20CA%20layout%2C%20limited%20service%20detail%20beyond%20buzzwords%0A%0ASME%20clients%20in%20Vashi%20shortlist%20CAs%20via%20Google%3B%20a%20credible%20service/booking%20site%20would%20win%20filings%20season%20traffic.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Yash%20A.%20Jain%20%26%20Associates%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Yash,
+I opened https://www.cayashjain.com/ while looking at ca firm businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
+I can share a free concept page for Yash A. Jain &amp; Associates this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Hi Yash,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.cayashjain.com/) and a couple of things stood out:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
+I can send a free one-page concept for Yash A. Jain &amp; Associates this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919967044547?text=Hi%20Yash%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.cayashjain.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Yash%20A.%20Jain%20%26%20Associates%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>mailto:yjassociates12@gmail.com?subject=Yash%20A.%20Jain%20%26%20Associates%3A%20I%20checked%20www.cayashjain.com&amp;body=Dear%20Yash%2C%0A%0AI%20opened%20https%3A//www.cayashjain.com/%20while%20looking%20at%20ca%20firm%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Yash%20A.%20Jain%20%26%20Associates%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>https://www.cayashjain.com/</t>
         </is>
@@ -1495,15 +2028,52 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917304577281?text=Hi%20Monika%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20ALLDENT%20Dental%20Clinic%20%28Ulwe%29%20and%20noticed%3A%20Gmail-only%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20ALLDENT%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>ALLDENT Dental Clinic: I checked www.alldentcliniculwe.com</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>mailto:alldentulwe@gmail.com?subject=ALLDENT%20Dental%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Monika%2C%0A%0AWhile%20reviewing%20businesses%20in%20Ulwe%2C%20I%20looked%20at%20ALLDENT%20Dental%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20email%3B%20phone%20not%20on%20homepage%20%28only%20booking%20page%29%3B%20thin%20treatment%20descriptions%3B%20WhatsApp-first%20contact%20pattern%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20ALLDENT%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Monika,
+I opened https://www.alldentcliniculwe.com/ while looking at dental businesses in Ulwe.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The phone number is missing from the homepage — people can't call you from the first screen
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for ALLDENT Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Hi Monika,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.alldentcliniculwe.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The phone number is missing from the homepage — people can't call you from the first screen
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for ALLDENT Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917304577281?text=Hi%20Monika%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.alldentcliniculwe.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20ALLDENT%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>mailto:alldentulwe@gmail.com?subject=ALLDENT%20Dental%20Clinic%3A%20I%20checked%20www.alldentcliniculwe.com&amp;body=Dear%20Monika%2C%0A%0AI%20opened%20https%3A//www.alldentcliniculwe.com/%20while%20looking%20at%20dental%20businesses%20in%20Ulwe.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20ALLDENT%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -1563,15 +2133,51 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917715888551?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Avneesh%20Diagnostics%20%26%20Healthcare%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Avneesh%20Diagnostics%20%26%20Healthcare%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Avneesh Diagnostics &amp; Healthcare: I checked avneeshdiagnostics.com</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@avneeshdiagnostics.com?subject=Avneesh%20Diagnostics%20%26%20Healthcare%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sanjay%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Avneesh%20Diagnostics%20%26%20Healthcare.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%3B%20No%20WhatsApp%20click-to-chat%20CTA%3B%20No%20clear%20online%20booking/order%20path%20on%20homepage%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Avneesh%20Diagnostics%20%26%20Healthcare%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sanjay,
+I opened https://avneeshdiagnostics.com/ while looking at diagnostics businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Avneesh Diagnostics &amp; Healthcare this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sanjay,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://avneeshdiagnostics.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Avneesh Diagnostics &amp; Healthcare this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917715888551?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//avneeshdiagnostics.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Avneesh%20Diagnostics%20%26%20Healthcare%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@avneeshdiagnostics.com?subject=Avneesh%20Diagnostics%20%26%20Healthcare%3A%20I%20checked%20avneeshdiagnostics.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20opened%20https%3A//avneeshdiagnostics.com/%20while%20looking%20at%20diagnostics%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Avneesh%20Diagnostics%20%26%20Healthcare%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>https://avneeshdiagnostics.com/</t>
         </is>
@@ -1631,15 +2237,52 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918433589999?text=Hi%20Govind%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20CoreGym%20Kharghar%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Copyright%20year%20looks%20outdated%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20CoreGym%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>CoreGym Kharghar: I checked coregym.co.in/home</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>mailto:impallari@gmail.com?subject=CoreGym%20Kharghar%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Govind%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20CoreGym%20Kharghar.%0A%0ASpecific%20issues%20I%20found%3A%0ACopyright%20year%20looks%20outdated%3B%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%3B%20No%20clear%20online%20booking/order%20path%20on%20homepage%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20CoreGym%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Govind,
+I opened https://coregym.co.in/home while looking at fitness businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The copyright year on the site is old, so it looks abandoned
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for CoreGym Kharghar this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Hi Govind,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://coregym.co.in/home) and a couple of things stood out:
+• The copyright year on the site is old, so it looks abandoned
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for CoreGym Kharghar this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918433589999?text=Hi%20Govind%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//coregym.co.in/home%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20CoreGym%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>mailto:impallari@gmail.com?subject=CoreGym%20Kharghar%3A%20I%20checked%20coregym.co.in/home&amp;body=Dear%20Govind%2C%0A%0AI%20opened%20https%3A//coregym.co.in/home%20while%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20CoreGym%20Kharghar%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>https://coregym.co.in/home</t>
         </is>
@@ -1695,15 +2338,52 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919136298251?text=Hi%20Belokar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20%28Kharghar%29%20and%20noticed%3A%20Outdated%20copyright%20%282020-24%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr Belokar Dental Clinic and Implant Center: I checked drbelokars.com</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>mailto:dentist@drbelokars.com?subject=Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Belokar%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20I%20looked%20at%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center.%0A%0ASpecific%20issues%20I%20found%3A%0AOutdated%20copyright%20%282020-24%29%3B%20dense%20SEO%20keyword%20stuffing%3B%20generic%20multi-specialty%20template%20look%3B%20limited%20clear%20booking%20CTA%20beyond%20phone%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Belokar,
+I opened https://drbelokars.com/ while looking at dental businesses in Kharghar.
+Here's what a customer would notice today:
+• The copyright year on the site is old, so it looks abandoned
+• Dense SEO keyword stuffing
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Dr Belokar Dental Clinic and Implant Center this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Hi Belokar,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drbelokars.com/) and a couple of things stood out:
+• The copyright year on the site is old, so it looks abandoned
+• Dense SEO keyword stuffing
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Dr Belokar Dental Clinic and Implant Center this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919136298251?text=Hi%20Belokar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drbelokars.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20Dense%20SEO%20keyword%20stuffing%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>mailto:dentist@drbelokars.com?subject=Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%3A%20I%20checked%20drbelokars.com&amp;body=Dear%20Belokar%2C%0A%0AI%20opened%20https%3A//drbelokars.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20Dense%20SEO%20keyword%20stuffing%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -1763,15 +2443,52 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967752407?text=Hi%20Vaishali%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Copyright%20still%20shows%202023%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic: I checked entvaishalisangole.com</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@vaishalisangole.com?subject=Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Vaishali%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0ACopyright%20still%20shows%202023%3B%20repeated%20generic%20treatment%20blurbs%3B%20typo%20%27Ontology%20Service%27%20instead%20of%20Otology%3B%20appointment%20is%20WhatsApp-script%20driven%20rather%20than%20proper%20online%20booking%0A%0ANiche%20vertigo%20specialist%20clinic%20that%20should%20dominate%20local%20search%2C%20but%20weak%20content%20quality%20reduces%20perceived%20expertise.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Vaishali,
+I opened https://entvaishalisangole.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Copyright still shows 2023
+• Repeated generic treatment blurbs
+• There are typos on the homepage (e.g. 'Ontology Service') that look unprofessional
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Hi Vaishali,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://entvaishalisangole.com/) and a couple of things stood out:
+• Copyright still shows 2023
+• Repeated generic treatment blurbs
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919967752407?text=Hi%20Vaishali%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//entvaishalisangole.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Copyright%20still%20shows%202023%0A%E2%80%A2%20Repeated%20generic%20treatment%20blurbs%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@vaishalisangole.com?subject=Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%3A%20I%20checked%20entvaishalisangole.com&amp;body=Dear%20Vaishali%2C%0A%0AI%20opened%20https%3A//entvaishalisangole.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Copyright%20still%20shows%202023%0A%E2%80%A2%20Repeated%20generic%20treatment%20blurbs%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Ontology%20Service%27%29%20that%20look%20unprofessional%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>https://entvaishalisangole.com/</t>
         </is>
@@ -1827,11 +2544,48 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967064548?text=Hi%20R.R.%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Jairaj%27s%20Diagnostic%20Centre%20%28CBD%20Belapur%20/%20Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Site%20still%20on%20HTTP%20%28no%20HTTPS%20trust%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Jairaj%27s%20Diagnostic%20Centre%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>Dr. Jairaj's Diagnostic Centre: I checked jairajdiagnostics.com</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened http://jairajdiagnostics.com/ while looking at diagnostics businesses in CBD Belapur / Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site still opens on HTTP (no lock/HTTPS), which browsers flag as not secure
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+• The site is hard to use on a phone — it doesn't fit the screen properly
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr. Jairaj's Diagnostic Centre this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (http://jairajdiagnostics.com/) and a couple of things stood out:
+• The site still opens on HTTP (no lock/HTTPS), which browsers flag as not secure
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr. Jairaj's Diagnostic Centre this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919967064548?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28http%3A//jairajdiagnostics.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20opens%20on%20HTTP%20%28no%20lock/HTTPS%29%2C%20which%20browsers%20flag%20as%20not%20secure%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jairaj%27s%20Diagnostic%20Centre%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>http://jairajdiagnostics.com/(S(51xpl1akqci52oxrq1b1jw0i))/ExternalSite/index.aspx</t>
         </is>
@@ -1887,15 +2641,52 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919619944888?text=Hi%20Harshvardhan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20The%20Dental%20House%20%28Kopar%20Khairane%29%20and%20noticed%3A%20Outdated%20copyright/footer%20incomplete%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20The%20Dental%20House%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>The Dental House: I checked dentalhousemumbai.com</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@dentalhousemumbai.com?subject=The%20Dental%20House%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Harshvardhan%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kopar%20Khairane%2C%20I%20looked%20at%20The%20Dental%20House.%0A%0ASpecific%20issues%20I%20found%3A%0AOutdated%20copyright/footer%20incomplete%3B%20encoding%20glitches%20in%20reviews%3B%20thin%20SEO%20doorway%20pages%3B%20dated%20template%20design%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20The%20Dental%20House%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Harshvardhan,
+I opened https://dentalhousemumbai.com/ while looking at dental businesses in Kopar Khairane.
+Here's what a customer would notice today:
+• The copyright year on the site is old, so it looks abandoned
+• Reviews/text on the site show broken characters, so it looks unmaintained
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for The Dental House this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Hi Harshvardhan,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://dentalhousemumbai.com/) and a couple of things stood out:
+• The copyright year on the site is old, so it looks abandoned
+• Reviews/text on the site show broken characters, so it looks unmaintained
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for The Dental House this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919619944888?text=Hi%20Harshvardhan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//dentalhousemumbai.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20Reviews/text%20on%20the%20site%20show%20broken%20characters%2C%20so%20it%20looks%20unmaintained%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20House%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@dentalhousemumbai.com?subject=The%20Dental%20House%3A%20I%20checked%20dentalhousemumbai.com&amp;body=Dear%20Harshvardhan%2C%0A%0AI%20opened%20https%3A//dentalhousemumbai.com/%20while%20looking%20at%20dental%20businesses%20in%20Kopar%20Khairane.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20Reviews/text%20on%20the%20site%20show%20broken%20characters%2C%20so%20it%20looks%20unmaintained%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20Dental%20House%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -1955,15 +2746,52 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919323464302?text=Hi%20Sohil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Travellers%20World%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Severely%20outdated%20site%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Travellers%20World%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Travellers World: I checked travellersworld.co.in</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>mailto:sohilthakkar123@gmail.com?subject=Travellers%20World%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sohil%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Travellers%20World.%0A%0ASpecific%20issues%20I%20found%3A%0ASeverely%20outdated%20site%3B%20package%20offers%20still%20labelled%20valid%20till%2031%20March%202012%3B%20table-based%202010s%20layout%3B%20Gmail%20contact%3B%20landline%20formatting%20broken%20%28%27%2B91%2022%204974424%27%29%0A%0AA%20travel%20agency%20still%20advertising%202012%20package%20validity%20is%20a%20textbook%20redesign%20prospect%20with%20clear%20ROI.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Travellers%20World%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sohil,
+I opened https://travellersworld.co.in/ while looking at travel agent businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The pages look dated and thin — visitors don't get enough proof to call
+• Old offers are still live on the site (one still says valid till 2012) — it looks abandoned
+• Table-based 2010s layout
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Travellers World this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sohil,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://travellersworld.co.in/) and a couple of things stood out:
+• The pages look dated and thin — visitors don't get enough proof to call
+• Old offers are still live on the site (one still says valid till 2012) — it looks abandoned
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Travellers World this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919323464302?text=Hi%20Sohil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//travellersworld.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Old%20offers%20are%20still%20live%20on%20the%20site%20%28one%20still%20says%20valid%20till%202012%29%20%E2%80%94%20it%20looks%20abandoned%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Travellers%20World%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sohilthakkar123@gmail.com?subject=Travellers%20World%3A%20I%20checked%20travellersworld.co.in&amp;body=Dear%20Sohil%2C%0A%0AI%20opened%20https%3A//travellersworld.co.in/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Old%20offers%20are%20still%20live%20on%20the%20site%20%28one%20still%20says%20valid%20till%202012%29%20%E2%80%94%20it%20looks%20abandoned%0A%E2%80%A2%20Table-based%202010s%20layout%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Travellers%20World%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>https://travellersworld.co.in/contactus.html</t>
         </is>
@@ -2023,15 +2851,49 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591828081?text=Hi%20Pranali%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Pranali%20Bane%20Interior%20Design%27s%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Template%20marketing%20site%20mimicking%20big-brand%20interior%20funnels%2C%20limited%20authentic%20project%20case%20studies%2C%20Zoho%20free-mail%20branding%2C%20weak%20trust%20for%20turnkey%20claims%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Pranali%20Bane%20Interior%20Design%27s%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Pranali Bane Interior Design's: I checked pranalibaneinteriordesign.com</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>mailto:Pb.design@zohomail.in?subject=Pranali%20Bane%20Interior%20Design%27s%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Pranali%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Pranali%20Bane%20Interior%20Design%27s.%0A%0ASpecific%20issues%20I%20found%3A%0ATemplate%20marketing%20site%20mimicking%20big-brand%20interior%20funnels%2C%20limited%20authentic%20project%20case%20studies%2C%20Zoho%20free-mail%20branding%2C%20weak%20trust%20for%20turnkey%20claims%0A%0APrime%20Mall%20location%20clients%20expect%20polished%20portfolio%20proof%20before%20site%20visit.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Pranali%20Bane%20Interior%20Design%27s%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Pranali,
+I opened https://pranalibaneinteriordesign.com/ while looking at interior design businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like SEO/template pages rather than a real project portfolio
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for Pranali Bane Interior Design's this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Hi Pranali,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pranalibaneinteriordesign.com/) and a couple of things stood out:
+• The site looks like SEO/template pages rather than a real project portfolio
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for Pranali Bane Interior Design's this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918591828081?text=Hi%20Pranali%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pranalibaneinteriordesign.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pranali%20Bane%20Interior%20Design%27s%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>mailto:Pb.design@zohomail.in?subject=Pranali%20Bane%20Interior%20Design%27s%3A%20I%20checked%20pranalibaneinteriordesign.com&amp;body=Dear%20Pranali%2C%0A%0AI%20opened%20https%3A//pranalibaneinteriordesign.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pranali%20Bane%20Interior%20Design%27s%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>https://pranalibaneinteriordesign.com/</t>
         </is>
@@ -2091,15 +2953,52 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591365551?text=Hi%20Rita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Ramp%20Salon%20%26%20Academy%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20SEO-stuffed%20duplicate%20service%20blocks%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Ramp%20Salon%20%26%20Academy%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Ramp Salon &amp; Academy: I checked www.rampsalonandacademy.com</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>mailto:rampsalonacademy@gmail.com?subject=Ramp%20Salon%20%26%20Academy%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Rita%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Ramp%20Salon%20%26%20Academy.%0A%0ASpecific%20issues%20I%20found%3A%0ASEO-stuffed%20duplicate%20service%20blocks%3B%20Gmail%20primary%20contact%3B%20hours%20listed%20oddly%20as%20Mon-Fri%20only%20while%20salon%20likely%20needs%20weekend%20booking%20clarity%0A%0ABridal/salon%20buyers%20book%20from%20phones%20%E2%80%94%20a%20cleaner%20service%20%2B%20WhatsApp%20booking%20page%20converts%20more%20Kharghar%20enquiries.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Ramp%20Salon%20%26%20Academy%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Rita,
+I opened https://www.rampsalonandacademy.com/ while looking at salon businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• SEO-stuffed duplicate service blocks
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Hours listed oddly as Mon-Fri only while salon likely needs weekend booking clarity
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Ramp Salon &amp; Academy this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Hi Rita,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.rampsalonandacademy.com/) and a couple of things stood out:
+• SEO-stuffed duplicate service blocks
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Ramp Salon &amp; Academy this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918591365551?text=Hi%20Rita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.rampsalonandacademy.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20SEO-stuffed%20duplicate%20service%20blocks%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ramp%20Salon%20%26%20Academy%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>mailto:rampsalonacademy@gmail.com?subject=Ramp%20Salon%20%26%20Academy%3A%20I%20checked%20www.rampsalonandacademy.com&amp;body=Dear%20Rita%2C%0A%0AI%20opened%20https%3A//www.rampsalonandacademy.com/%20while%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20SEO-stuffed%20duplicate%20service%20blocks%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Hours%20listed%20oddly%20as%20Mon-Fri%20only%20while%20salon%20likely%20needs%20weekend%20booking%20clarity%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Ramp%20Salon%20%26%20Academy%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>https://www.rampsalonandacademy.com/</t>
         </is>
@@ -2159,15 +3058,52 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919324774567?text=Hi%20Priti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Peacock%20Salon%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20About%20page%20incorrectly%20references%20%27Luxe%20Haven%27%20brand%20name%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Peacock%20Salon%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Peacock Salon: I checked peacocksalon.in</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>mailto:vashi.peacock@gmail.com?subject=Peacock%20Salon%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Priti%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Peacock%20Salon.%0A%0ASpecific%20issues%20I%20found%3A%0AAbout%20page%20incorrectly%20references%20%27Luxe%20Haven%27%20brand%20name%3B%20stats%20widgets%20show%200%2B%3B%20product%20ratings%20show%200%3B%20Gmail%20contact%3B%20booking%20CTA%20buried%0A%0AA%20long-running%20Vashi%20salon%20still%20looks%20inconsistent%20online%20%E2%80%94%20fixing%20brand%20mismatches%20and%20booking%20flow%20lifts%20appointment%20calls.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Peacock%20Salon%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Priti,
+I opened https://peacocksalon.in/ while looking at salon businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The site still has leftover template branding that isn't yours
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• Product ratings show 0
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Peacock Salon this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Hi Priti,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://peacocksalon.in/) and a couple of things stood out:
+• The site still has leftover template branding that isn't yours
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Peacock Salon this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919324774567?text=Hi%20Priti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//peacocksalon.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20has%20leftover%20template%20branding%20that%20isn%27t%20yours%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Peacock%20Salon%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>mailto:vashi.peacock@gmail.com?subject=Peacock%20Salon%3A%20I%20checked%20peacocksalon.in&amp;body=Dear%20Priti%2C%0A%0AI%20opened%20https%3A//peacocksalon.in/%20while%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20still%20has%20leftover%20template%20branding%20that%20isn%27t%20yours%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20Product%20ratings%20show%200%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Peacock%20Salon%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>https://peacocksalon.in/contact-us</t>
         </is>
@@ -2227,15 +3163,49 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919035010503?text=Hi%20Pankaj%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20SLK%20Foundation%20Guest%20House%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Room%20amenity%20lists%20contradict%20room%20types%2C%20email-only%20booking%2C%20Gmail%20alias%2C%20weak%20rate/availability%20UX%20for%20ACTREC%20visitor%20niche%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20SLK%20Foundation%20Guest%20House%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>SLK Foundation Guest House: I checked www.slkfoundation.in/guest-house</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>mailto:slkfoundation.in@gmail.com?subject=SLK%20Foundation%20Guest%20House%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Pankaj%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20SLK%20Foundation%20Guest%20House.%0A%0ASpecific%20issues%20I%20found%3A%0ARoom%20amenity%20lists%20contradict%20room%20types%2C%20email-only%20booking%2C%20Gmail%20alias%2C%20weak%20rate/availability%20UX%20for%20ACTREC%20visitor%20niche%0A%0ACancer-patient%20family%20stays%20need%20frictionless%20booking%3B%20clearer%20rates%20and%20WhatsApp%20booking%20would%20fill%20rooms.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20SLK%20Foundation%20Guest%20House%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Pankaj,
+I opened https://www.slkfoundation.in/guest-house/ while looking at hotel businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for SLK Foundation Guest House this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Hi Pankaj,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.slkfoundation.in/guest-house/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for SLK Foundation Guest House this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919035010503?text=Hi%20Pankaj%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.slkfoundation.in/guest-house/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20SLK%20Foundation%20Guest%20House%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>mailto:slkfoundation.in@gmail.com?subject=SLK%20Foundation%20Guest%20House%3A%20I%20checked%20www.slkfoundation.in/guest-house&amp;body=Dear%20Pankaj%2C%0A%0AI%20opened%20https%3A//www.slkfoundation.in/guest-house/%20while%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20SLK%20Foundation%20Guest%20House%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>https://www.slkfoundation.in/guest-house/</t>
         </is>
@@ -2291,15 +3261,52 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137777030?text=Hi%20Gunjan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20%28Kopar%20Khairane%29%20and%20noticed%3A%20Multiple%20phone%20numbers%20across%20pages%20%289137777030%20/%209930562407%29%20create%20confusion%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Splendid Smiles Dental Clinic &amp; Implant Center: I checked www.splendidsmilesdentalclinic.com</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>mailto:help@splendidsmilesdentalclinic.com?subject=Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Gunjan%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kopar%20Khairane%2C%20I%20looked%20at%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center.%0A%0ASpecific%20issues%20I%20found%3A%0AMultiple%20phone%20numbers%20across%20pages%20%289137777030%20/%209930562407%29%20create%20confusion%3B%20generic%20premium%20template%3B%20limited%20local%20content%20depth%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Gunjan,
+I opened https://www.splendidsmilesdentalclinic.com/ while looking at dental businesses in Kopar Khairane.
+Here's what a customer would notice today:
+• Multiple phone numbers across pages (9137777030 / 9930562407) create confusion
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Limited local content depth
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Splendid Smiles Dental Clinic &amp; Implant Center this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Hi Gunjan,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.splendidsmilesdentalclinic.com/) and a couple of things stood out:
+• Multiple phone numbers across pages (9137777030 / 9930562407) create confusion
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Splendid Smiles Dental Clinic &amp; Implant Center this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919137777030?text=Hi%20Gunjan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.splendidsmilesdentalclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Multiple%20phone%20numbers%20across%20pages%20%289137777030%20/%209930562407%29%20create%20confusion%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>mailto:help@splendidsmilesdentalclinic.com?subject=Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%3A%20I%20checked%20www.splendidsmilesdentalclinic.com&amp;body=Dear%20Gunjan%2C%0A%0AI%20opened%20https%3A//www.splendidsmilesdentalclinic.com/%20while%20looking%20at%20dental%20businesses%20in%20Kopar%20Khairane.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Multiple%20phone%20numbers%20across%20pages%20%289137777030%20/%209930562407%29%20create%20confusion%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Limited%20local%20content%20depth%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -2359,15 +3366,52 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917208390300?text=Hi%20Tejas%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Veer%20Multispecialty%20Hospital%20%28Panvel%20%28Khanda%20Colony%29%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Broken%20English/placeholder%20copy%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Veer%20Multispecialty%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Veer Multispecialty Hospital: I checked veericupanvel.com</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>mailto:veerhospital50@gmail.com?subject=Veer%20Multispecialty%20Hospital%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Tejas%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%20%28Khanda%20Colony%29%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Veer%20Multispecialty%20Hospital.%0A%0ASpecific%20issues%20I%20found%3A%0ABroken%20English/placeholder%20copy%3B%20Gmail-only%20contact%3B%20duplicate%20specialty%20sections%3B%20form%20validation/error%20states%20visible%20on%20page%0A%0AOwner-operated%20Panvel%20hospital%20with%20real%20reviews%2C%20but%20unfinished%20website%20likely%20loses%20emergency%20and%20OPD%20enquiries.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Veer%20Multispecialty%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Tejas,
+I opened https://veericupanvel.com/ while looking at healthcare businesses in Panvel (Khanda Colony), Navi Mumbai.
+Here's what a customer would notice today:
+• Broken English/placeholder copy
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Duplicate specialty sections
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Veer Multispecialty Hospital this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tejas,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://veericupanvel.com/) and a couple of things stood out:
+• Broken English/placeholder copy
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Veer Multispecialty Hospital this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917208390300?text=Hi%20Tejas%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//veericupanvel.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Broken%20English/placeholder%20copy%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Veer%20Multispecialty%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>mailto:veerhospital50@gmail.com?subject=Veer%20Multispecialty%20Hospital%3A%20I%20checked%20veericupanvel.com&amp;body=Dear%20Tejas%2C%0A%0AI%20opened%20https%3A//veericupanvel.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Panvel%20%28Khanda%20Colony%29%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Broken%20English/placeholder%20copy%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Duplicate%20specialty%20sections%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Veer%20Multispecialty%20Hospital%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>https://veericupanvel.com/</t>
         </is>
@@ -2427,15 +3471,51 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919326674310?text=Hi%20Husain%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Alpha%20Study%20%28Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Alpha%20Study%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Alpha Study: I checked alphagogy.com</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>mailto:alphastudy.nerul@gmail.com?subject=Alpha%20Study%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Husain%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Alpha%20Study.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%3B%20No%20clear%20online%20booking/order%20path%20on%20homepage%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Alpha%20Study%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Husain,
+I opened https://alphagogy.com/ while looking at education businesses in Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can share a free concept page for Alpha Study this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Hi Husain,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://alphagogy.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can send a free one-page concept for Alpha Study this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919326674310?text=Hi%20Husain%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//alphagogy.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Alpha%20Study%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>mailto:alphastudy.nerul@gmail.com?subject=Alpha%20Study%3A%20I%20checked%20alphagogy.com&amp;body=Dear%20Husain%2C%0A%0AI%20opened%20https%3A//alphagogy.com/%20while%20looking%20at%20education%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Alpha%20Study%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>https://alphagogy.com/</t>
         </is>
@@ -2495,15 +3575,52 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919699356306?text=Hi%20Sweta%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20%28Airoli%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Cure Dental Clinic (Dr. Sweta Alapuria): I checked www.drswetaalapuria.com</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>mailto:shweta.doc.2207@gmail.com?subject=Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sweta%2C%0A%0AWhile%20reviewing%20businesses%20in%20Airoli%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20phone-first%20booking%3B%20thin%20conversion%20hierarchy%20for%20implants/aligners%0A%0ADoctor-branded%20Airoli%20clinic%20%E2%80%94%20booking%20funnel%20converts%20Google%20searches.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sweta,
+I opened https://www.drswetaalapuria.com/ while looking at dental businesses in Airoli, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Cure Dental Clinic (Dr. Sweta Alapuria) this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sweta,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.drswetaalapuria.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Cure Dental Clinic (Dr. Sweta Alapuria) this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919699356306?text=Hi%20Sweta%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.drswetaalapuria.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>mailto:shweta.doc.2207@gmail.com?subject=Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%3A%20I%20checked%20www.drswetaalapuria.com&amp;body=Dear%20Sweta%2C%0A%0AI%20opened%20https%3A//www.drswetaalapuria.com/%20while%20looking%20at%20dental%20businesses%20in%20Airoli%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>https://www.drswetaalapuria.com/</t>
         </is>
@@ -2563,15 +3680,52 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919869369029?text=Hi%20Nandini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr. Nandini's Skin and Hair Care Clinic: I checked www.drnandiniskincare.com</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>mailto:drnandinisskinhaircare@gmail.com?subject=Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Nandini%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20dated%20clinic%20CMS%20feel%3B%20laser/cosmetology%20booking%20path%20not%20conversion-sharp%0A%0A18-year%20dermatologist%20in%20Sector%2020%20%E2%80%94%20modern%20booking%20site%20matches%20catchment%20spend.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Nandini,
+I opened https://www.drnandiniskincare.com/ while looking at dermatology businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+• Laser/cosmetology booking path not conversion-sharp
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr. Nandini's Skin and Hair Care Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nandini,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.drnandiniskincare.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr. Nandini's Skin and Hair Care Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919869369029?text=Hi%20Nandini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.drnandiniskincare.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>mailto:drnandinisskinhaircare@gmail.com?subject=Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%3A%20I%20checked%20www.drnandiniskincare.com&amp;body=Dear%20Nandini%2C%0A%0AI%20opened%20https%3A//www.drnandiniskincare.com/%20while%20looking%20at%20dermatology%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Laser/cosmetology%20booking%20path%20not%20conversion-sharp%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>https://www.drnandiniskincare.com/</t>
         </is>
@@ -2627,15 +3781,52 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919324303057?text=Hi%20Nitin%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Kokan%20Swad%20Seawoods%20%28Seawoods%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Enquiry-form%20led%20%28no%20direct%20online%20order%20on%20branch%20page%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Kokan%20Swad%20Seawoods%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Kokan Swad Seawoods: I checked kokanswad.restaurant/branches/seawoods</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>mailto:sales@kokanswad.restaurant?subject=Kokan%20Swad%20Seawoods%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Nitin%2C%0A%0AWhile%20reviewing%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Kokan%20Swad%20Seawoods.%0A%0ASpecific%20issues%20I%20found%3A%0AEnquiry-form%20led%20%28no%20direct%20online%20order%20on%20branch%20page%29%3B%20multi-outlet%20brand%20site%20dilutes%20local%20conversion%3B%20WhatsApp%20present%20but%20secondary%20to%20form%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Kokan%20Swad%20Seawoods%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Nitin,
+I opened https://kokanswad.restaurant/branches/seawoods/ while looking at restaurant businesses in Seawoods, Navi Mumbai.
+Here's what a customer would notice today:
+• Enquiry-form led (no direct online order on branch page)
+• Multi-outlet brand site dilutes local conversion
+• WhatsApp present but secondary to form
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Kokan Swad Seawoods this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nitin,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://kokanswad.restaurant/branches/seawoods/) and a couple of things stood out:
+• Enquiry-form led (no direct online order on branch page)
+• Multi-outlet brand site dilutes local conversion
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Kokan Swad Seawoods this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919324303057?text=Hi%20Nitin%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//kokanswad.restaurant/branches/seawoods/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Enquiry-form%20led%20%28no%20direct%20online%20order%20on%20branch%20page%29%0A%E2%80%A2%20Multi-outlet%20brand%20site%20dilutes%20local%20conversion%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Kokan%20Swad%20Seawoods%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sales@kokanswad.restaurant?subject=Kokan%20Swad%20Seawoods%3A%20I%20checked%20kokanswad.restaurant/branches/seawoods&amp;body=Dear%20Nitin%2C%0A%0AI%20opened%20https%3A//kokanswad.restaurant/branches/seawoods/%20while%20looking%20at%20restaurant%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Enquiry-form%20led%20%28no%20direct%20online%20order%20on%20branch%20page%29%0A%E2%80%A2%20Multi-outlet%20brand%20site%20dilutes%20local%20conversion%0A%E2%80%A2%20WhatsApp%20present%20but%20secondary%20to%20form%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Kokan%20Swad%20Seawoods%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -2695,15 +3886,52 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919820536312?text=Hi%20Mahesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Mahesh%20Pade%20%26%20Associates%20%28Nerul%20/%20Seawoods%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Stat%20counters%20stuck%20at%200%2B%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Mahesh%20Pade%20%26%20Associates%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Mahesh Pade &amp; Associates: I checked www.maheshpade.com</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@maheshpade.com?subject=Mahesh%20Pade%20%26%20Associates%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Mahesh%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%20/%20Seawoods%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Mahesh%20Pade%20%26%20Associates.%0A%0ASpecific%20issues%20I%20found%3A%0AStat%20counters%20stuck%20at%200%2B%3B%20dated%20HubTech-built%20template%20look%3B%20weak%20project-case%20presentation%20for%20a%20studio%20since%202003%0A%0ASenior%20designers%20with%20long%20track%20records%20still%20underperform%20online%20when%20the%20site%20looks%20frozen%20in%20an%20old%20template%20era.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Mahesh%20Pade%20%26%20Associates%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Mahesh,
+I opened https://www.maheshpade.com/ while looking at interior design businesses in Nerul / Seawoods, Navi Mumbai.
+Here's what a customer would notice today:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• The site looks like SEO/template pages rather than a real project portfolio
+• Weak project-case presentation for a studio since 2003
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for Mahesh Pade &amp; Associates this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mahesh,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.maheshpade.com/) and a couple of things stood out:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• The site looks like SEO/template pages rather than a real project portfolio
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for Mahesh Pade &amp; Associates this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919820536312?text=Hi%20Mahesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.maheshpade.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Mahesh%20Pade%20%26%20Associates%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@maheshpade.com?subject=Mahesh%20Pade%20%26%20Associates%3A%20I%20checked%20www.maheshpade.com&amp;body=Dear%20Mahesh%2C%0A%0AI%20opened%20https%3A//www.maheshpade.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Nerul%20/%20Seawoods%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%E2%80%A2%20Weak%20project-case%20presentation%20for%20a%20studio%20since%202003%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Mahesh%20Pade%20%26%20Associates%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>https://www.maheshpade.com/</t>
         </is>
@@ -2759,15 +3987,52 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919867113900?text=Hi%20Nafisa%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Moi%20Doughssier%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Still%20pushes%20Swiggy/Zomato%20alongside%20direct%20order%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Moi%20Doughssier%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Moi Doughssier: I checked www.moidoughssier.com</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>mailto:nafisa@moidoughssier.com?subject=Moi%20Doughssier%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Nafisa%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Moi%20Doughssier.%0A%0ASpecific%20issues%20I%20found%3A%0AStill%20pushes%20Swiggy/Zomato%20alongside%20direct%20order%3B%20custom%20cakes%20WhatsApp-only%3B%20site%20is%20strong%20but%20reservation/table%20booking%20for%20cafe%20seating%20is%20weak%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Moi%20Doughssier%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Nafisa,
+I opened https://www.moidoughssier.com/ while looking at bakery businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The site still pushes people to Swiggy/Zomato instead of letting them order/book with you directly
+• Custom cakes WhatsApp-only
+• Site is strong but reservation/table booking for cafe seating is weak
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Moi Doughssier this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nafisa,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.moidoughssier.com/) and a couple of things stood out:
+• The site still pushes people to Swiggy/Zomato instead of letting them order/book with you directly
+• Custom cakes WhatsApp-only
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Moi Doughssier this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919867113900?text=Hi%20Nafisa%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.moidoughssier.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20pushes%20people%20to%20Swiggy/Zomato%20instead%20of%20letting%20them%20order/book%20with%20you%20directly%0A%E2%80%A2%20Custom%20cakes%20WhatsApp-only%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Moi%20Doughssier%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>mailto:nafisa@moidoughssier.com?subject=Moi%20Doughssier%3A%20I%20checked%20www.moidoughssier.com&amp;body=Dear%20Nafisa%2C%0A%0AI%20opened%20https%3A//www.moidoughssier.com/%20while%20looking%20at%20bakery%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20still%20pushes%20people%20to%20Swiggy/Zomato%20instead%20of%20letting%20them%20order/book%20with%20you%20directly%0A%E2%80%A2%20Custom%20cakes%20WhatsApp-only%0A%E2%80%A2%20Site%20is%20strong%20but%20reservation/table%20booking%20for%20cafe%20seating%20is%20weak%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Moi%20Doughssier%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -2827,15 +4092,51 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004366342?text=Hi%20Sreekumar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20%28Sanpada%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Panikar's Centre for Advanced Dentistry: I checked www.panikarsdentistry.com</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>mailto:panikarsdentistry@gmail.com?subject=Panikar%27s%20Centre%20for%20Advanced%20Dentistry%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sreekumar%2C%0A%0AWhile%20reviewing%20businesses%20in%20Sanpada%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20award%20messaging%20strong%20but%20appointment%20path%20is%20call-heavy%20vs%20modern%20implant%20clinics%0A%0ASince%202011%20Sanpada%20implant%20practice%20%E2%80%94%20booking%20UX%20converts%20family%20%2B%20implant%20demand.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sreekumar,
+I opened https://www.panikarsdentistry.com/ while looking at dental businesses in Sanpada, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Award messaging strong but appointment path is call-heavy vs modern implant clinics
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Panikar's Centre for Advanced Dentistry this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sreekumar,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.panikarsdentistry.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Award messaging strong but appointment path is call-heavy vs modern implant clinics
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Panikar's Centre for Advanced Dentistry this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919004366342?text=Hi%20Sreekumar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.panikarsdentistry.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Award%20messaging%20strong%20but%20appointment%20path%20is%20call-heavy%20vs%20modern%20implant%20clinics%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>mailto:panikarsdentistry@gmail.com?subject=Panikar%27s%20Centre%20for%20Advanced%20Dentistry%3A%20I%20checked%20www.panikarsdentistry.com&amp;body=Dear%20Sreekumar%2C%0A%0AI%20opened%20https%3A//www.panikarsdentistry.com/%20while%20looking%20at%20dental%20businesses%20in%20Sanpada%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Award%20messaging%20strong%20but%20appointment%20path%20is%20call-heavy%20vs%20modern%20implant%20clinics%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>https://www.panikarsdentistry.com/contact.html</t>
         </is>
@@ -2895,15 +4196,49 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919322268989?text=Hi%20Sudip%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sai%20Saya%20Principal%20Consultants%20%28Airoli%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Thin%20about-led%20site%20for%20a%2030-year%20Airoli%20practice%2C%20Gmail%20contact%2C%20limited%20property%20showcase/search%20UX%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sai%20Saya%20Principal%20Consultants%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Sai Saya Principal Consultants: I checked saisayaprincipalconsultant.com</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>mailto:saisaya89@gmail.com?subject=Sai%20Saya%20Principal%20Consultants%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sudip%2C%0A%0AWhile%20reviewing%20businesses%20in%20Airoli%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Sai%20Saya%20Principal%20Consultants.%0A%0ASpecific%20issues%20I%20found%3A%0AThin%20about-led%20site%20for%20a%2030-year%20Airoli%20practice%2C%20Gmail%20contact%2C%20limited%20property%20showcase/search%20UX%0A%0AAiroli%20end-users%20still%20Google%20brokers%3B%20inventory-led%20site%20would%20reduce%20dependence%20on%20referrals%20alone.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Sai%20Saya%20Principal%20Consultants%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sudip,
+I opened https://saisayaprincipalconsultant.com/ while looking at real estate broker businesses in Airoli, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Sai Saya Principal Consultants this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sudip,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://saisayaprincipalconsultant.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Sai Saya Principal Consultants this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919322268989?text=Hi%20Sudip%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//saisayaprincipalconsultant.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sai%20Saya%20Principal%20Consultants%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>mailto:saisaya89@gmail.com?subject=Sai%20Saya%20Principal%20Consultants%3A%20I%20checked%20saisayaprincipalconsultant.com&amp;body=Dear%20Sudip%2C%0A%0AI%20opened%20https%3A//saisayaprincipalconsultant.com/%20while%20looking%20at%20real%20estate%20broker%20businesses%20in%20Airoli%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sai%20Saya%20Principal%20Consultants%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>https://saisayaprincipalconsultant.com/about</t>
         </is>
@@ -2959,15 +4294,52 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918291883844?text=Hi%20Satish%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20%28Airoli%29%20and%20noticed%3A%20Gmail-only%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>SK Smile Dental Clinic and Implant Center: I checked sksmiledental.com</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>mailto:sksmiledental@gmail.com?subject=SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Satish%2C%0A%0AWhile%20reviewing%20businesses%20in%20Airoli%2C%20I%20looked%20at%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20email%3B%20thin%20homepage%20content%3B%20generic%20WordPress%20look%3B%20dual-location%20contact%20not%20well%20structured%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Satish,
+I opened https://sksmiledental.com/ while looking at dental businesses in Airoli.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+• Generic WordPress look
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for SK Smile Dental Clinic and Implant Center this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Hi Satish,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sksmiledental.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for SK Smile Dental Clinic and Implant Center this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918291883844?text=Hi%20Satish%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sksmiledental.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sksmiledental@gmail.com?subject=SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%3A%20I%20checked%20sksmiledental.com&amp;body=Dear%20Satish%2C%0A%0AI%20opened%20https%3A//sksmiledental.com/%20while%20looking%20at%20dental%20businesses%20in%20Airoli.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Generic%20WordPress%20look%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -3027,15 +4399,51 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917777005606?text=Hi%20Kiran%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Skin%20Science%20Clinic%20%28Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Skin%20Science%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Skin Science Clinic: I checked skinsciencemumbai.com</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>mailto:skinscienceclinics@gmail.com?subject=Skin%20Science%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Kiran%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Skin%20Science%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20aesthetic%20clinic%20booking%20can%20be%20sharper%20for%20Seawoods/Nerul%20high%20ARPU%20treatments%0A%0AFounder%20dermatologists%20near%20Seawoods%20%E2%80%94%20booking%20UX%20converts%20Instagram%20interest%20into%20consultations.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Skin%20Science%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Kiran,
+I opened https://skinsciencemumbai.com/ while looking at dermatology businesses in Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Aesthetic clinic booking can be sharper for Seawoods/Nerul high ARPU treatments
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Skin Science Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kiran,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://skinsciencemumbai.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Aesthetic clinic booking can be sharper for Seawoods/Nerul high ARPU treatments
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Skin Science Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917777005606?text=Hi%20Kiran%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//skinsciencemumbai.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Aesthetic%20clinic%20booking%20can%20be%20sharper%20for%20Seawoods/Nerul%20high%20ARPU%20treatments%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Skin%20Science%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>mailto:skinscienceclinics@gmail.com?subject=Skin%20Science%20Clinic%3A%20I%20checked%20skinsciencemumbai.com&amp;body=Dear%20Kiran%2C%0A%0AI%20opened%20https%3A//skinsciencemumbai.com/%20while%20looking%20at%20dermatology%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Aesthetic%20clinic%20booking%20can%20be%20sharper%20for%20Seawoods/Nerul%20high%20ARPU%20treatments%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Skin%20Science%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>https://skinsciencemumbai.com/</t>
         </is>
@@ -3091,15 +4499,52 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652628813?text=Hi%20Umesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20%28Airoli%29%20and%20noticed%3A%20Yahoo%20email%20%28dated%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Smile Care Dental Clinic &amp; Implant Center: I checked www.smilecareairoli.com</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>mailto:smilecaredentalclinic@yahoo.com?subject=Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Umesh%2C%0A%0AWhile%20reviewing%20businesses%20in%20Airoli%2C%20I%20looked%20at%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center.%0A%0ASpecific%20issues%20I%20found%3A%0AYahoo%20email%20%28dated%29%3B%20homepage%20lacks%20prominent%20phone%3B%20basic%20template%20layout%3B%20limited%20modern%20booking%20UX%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Umesh,
+I opened https://www.smilecareairoli.com/ while looking at dental businesses in Airoli.
+Here's what a customer would notice today:
+• The public email on the site is a Yahoo address — that looks dated to customers
+• The phone number is missing from the homepage — people can't call you from the first screen
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Smile Care Dental Clinic &amp; Implant Center this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Hi Umesh,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smilecareairoli.com/) and a couple of things stood out:
+• The public email on the site is a Yahoo address — that looks dated to customers
+• The phone number is missing from the homepage — people can't call you from the first screen
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Smile Care Dental Clinic &amp; Implant Center this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918652628813?text=Hi%20Umesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smilecareairoli.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Yahoo%20address%20%E2%80%94%20that%20looks%20dated%20to%20customers%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>mailto:smilecaredentalclinic@yahoo.com?subject=Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%3A%20I%20checked%20www.smilecareairoli.com&amp;body=Dear%20Umesh%2C%0A%0AI%20opened%20https%3A//www.smilecareairoli.com/%20while%20looking%20at%20dental%20businesses%20in%20Airoli.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Yahoo%20address%20%E2%80%94%20that%20looks%20dated%20to%20customers%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -3155,15 +4600,51 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919869912382?text=Hi%20Vinothini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Smilekraft%20Dental%20Clinic%20%28Seawoods%29%20and%20noticed%3A%20Gmail-only%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Smilekraft%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Smilekraft Dental Clinic: I checked www.smilekraftclinic.com</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>mailto:smilekraftclinic@gmail.com?subject=Smilekraft%20Dental%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Vinothini%2C%0A%0AWhile%20reviewing%20businesses%20in%20Seawoods%2C%20I%20looked%20at%20Smilekraft%20Dental%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20email%3B%20long-form%20SEO%20page%20density%3B%20limited%20secondary%20contact%20channels%20beyond%20phone/Gmail%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Smilekraft%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Vinothini,
+I opened https://www.smilekraftclinic.com/ while looking at dental businesses in Seawoods.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Long-form SEO page density
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Smilekraft Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Hi Vinothini,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smilekraftclinic.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Long-form SEO page density
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Smilekraft Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919869912382?text=Hi%20Vinothini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smilekraftclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Long-form%20SEO%20page%20density%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smilekraft%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>mailto:smilekraftclinic@gmail.com?subject=Smilekraft%20Dental%20Clinic%3A%20I%20checked%20www.smilekraftclinic.com&amp;body=Dear%20Vinothini%2C%0A%0AI%20opened%20https%3A//www.smilekraftclinic.com/%20while%20looking%20at%20dental%20businesses%20in%20Seawoods.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Long-form%20SEO%20page%20density%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Smilekraft%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -3223,15 +4704,52 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967485808?text=Hi%20Sandeep%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20%28Airoli%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Gmail%20as%20primary%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>The Ashtanga Institute of Yoga &amp; Naturopathy: I checked theashtangainstitute.com</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>mailto:theashtangainstitute@gmail.com?subject=The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sandeep%2C%0A%0AWhile%20reviewing%20businesses%20in%20Airoli%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail%20as%20primary%20email%3B%20animated%20counters%20stuck%20at%200%2B%3B%20dated%20layout%20and%20weak%20course-enquiry%20funnel%0A%0AYoga/naturopathy%20institutes%20with%20strong%20founders%20still%20lose%20enquiries%20when%20the%20site%20looks%20dated%20versus%20newer%20studios.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sandeep,
+I opened https://theashtangainstitute.com/ while looking at gym businesses in Airoli, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• The pages look dated and thin — visitors don't get enough proof to call
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for The Ashtanga Institute of Yoga &amp; Naturopathy this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sandeep,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://theashtangainstitute.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for The Ashtanga Institute of Yoga &amp; Naturopathy this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919967485808?text=Hi%20Sandeep%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//theashtangainstitute.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>mailto:theashtangainstitute@gmail.com?subject=The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%3A%20I%20checked%20theashtangainstitute.com&amp;body=Dear%20Sandeep%2C%0A%0AI%20opened%20https%3A//theashtangainstitute.com/%20while%20looking%20at%20gym%20businesses%20in%20Airoli%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>https://theashtangainstitute.com/</t>
         </is>
@@ -3291,15 +4809,51 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919867063446?text=Hi%20Shalini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Aaroh%20Academy%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20structure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Aaroh%20Academy%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Aaroh Academy: I checked aarohacademy.com</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@aarohacademy.com?subject=Aaroh%20Academy%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Shalini%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Aaroh%20Academy.%0A%0ASpecific%20issues%20I%20found%3A%0AGeneric%20template%20structure%3B%20weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Aaroh%20Academy%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Shalini,
+I opened https://aarohacademy.com/ while looking at education businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• Weak conversion hierarchy vs modern competitors
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can share a free concept page for Aaroh Academy this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Hi Shalini,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://aarohacademy.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• Weak conversion hierarchy vs modern competitors
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can send a free one-page concept for Aaroh Academy this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919867063446?text=Hi%20Shalini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//aarohacademy.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Aaroh%20Academy%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@aarohacademy.com?subject=Aaroh%20Academy%3A%20I%20checked%20aarohacademy.com&amp;body=Dear%20Shalini%2C%0A%0AI%20opened%20https%3A//aarohacademy.com/%20while%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Aaroh%20Academy%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>https://aarohacademy.com/</t>
         </is>
@@ -3359,15 +4913,51 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004229269?text=Hi%20Ashok%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Meritorious%20Tutorials%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20structure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Meritorious%20Tutorials%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Meritorious Tutorials: I checked meritorious.co.in</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@meritorious.co.in?subject=Meritorious%20Tutorials%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Ashok%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Meritorious%20Tutorials.%0A%0ASpecific%20issues%20I%20found%3A%0AGeneric%20template%20structure%3B%20weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Meritorious%20Tutorials%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Ashok,
+I opened https://meritorious.co.in/ while looking at education businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• Weak conversion hierarchy vs modern competitors
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can share a free concept page for Meritorious Tutorials this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ashok,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://meritorious.co.in/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• Weak conversion hierarchy vs modern competitors
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can send a free one-page concept for Meritorious Tutorials this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919004229269?text=Hi%20Ashok%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//meritorious.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Meritorious%20Tutorials%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@meritorious.co.in?subject=Meritorious%20Tutorials%3A%20I%20checked%20meritorious.co.in&amp;body=Dear%20Ashok%2C%0A%0AI%20opened%20https%3A//meritorious.co.in/%20while%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Meritorious%20Tutorials%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>https://meritorious.co.in/</t>
         </is>
@@ -3427,15 +5017,51 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917875617480?text=Hi%20Prerna%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Ora%20Care%20Dental%20Studio%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20structure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Ora%20Care%20Dental%20Studio%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Ora Care Dental Studio: I checked oracaredentalstudio.com</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>mailto:your@email.com?subject=Ora%20Care%20Dental%20Studio%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Prerna%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Ora%20Care%20Dental%20Studio.%0A%0ASpecific%20issues%20I%20found%3A%0AGeneric%20template%20structure%3B%20weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Ora%20Care%20Dental%20Studio%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Prerna,
+I opened https://oracaredentalstudio.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak conversion hierarchy vs modern competitors
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Ora Care Dental Studio this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Hi Prerna,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://oracaredentalstudio.com/) and a couple of things stood out:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak conversion hierarchy vs modern competitors
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Ora Care Dental Studio this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917875617480?text=Hi%20Prerna%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//oracaredentalstudio.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ora%20Care%20Dental%20Studio%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>mailto:your@email.com?subject=Ora%20Care%20Dental%20Studio%3A%20I%20checked%20oracaredentalstudio.com&amp;body=Dear%20Prerna%2C%0A%0AI%20opened%20https%3A//oracaredentalstudio.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Ora%20Care%20Dental%20Studio%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>https://oracaredentalstudio.com/</t>
         </is>
@@ -3491,15 +5117,52 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833862548?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Ratnakokan%20Seawoods%20%28Seawoods%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Shared%20thin%20multi-branch%20site%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Ratnakokan%20Seawoods%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Ratnakokan Seawoods: I checked ratnakokan.com</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>mailto:mail@ratnakokan.com?subject=Ratnakokan%20Seawoods%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sanjay%2C%0A%0AWhile%20reviewing%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Ratnakokan%20Seawoods.%0A%0ASpecific%20issues%20I%20found%3A%0AShared%20thin%20multi-branch%20site%3B%20no%20branch-specific%20menu/order%20flow%3B%20no%20WhatsApp%20CTA%3B%20delivery%20discovery%20via%20aggregators%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Ratnakokan%20Seawoods%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sanjay,
+I opened https://ratnakokan.com/ while looking at restaurant businesses in Seawoods, Navi Mumbai.
+Here's what a customer would notice today:
+• The pages look dated and thin — visitors don't get enough proof to call
+• No branch-specific menu/order flow
+• There's no Order Online / Book a table button on the homepage
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Ratnakokan Seawoods this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sanjay,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ratnakokan.com/) and a couple of things stood out:
+• The pages look dated and thin — visitors don't get enough proof to call
+• No branch-specific menu/order flow
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Ratnakokan Seawoods this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919833862548?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ratnakokan.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20No%20branch-specific%20menu/order%20flow%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ratnakokan%20Seawoods%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>mailto:mail@ratnakokan.com?subject=Ratnakokan%20Seawoods%3A%20I%20checked%20ratnakokan.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20opened%20https%3A//ratnakokan.com/%20while%20looking%20at%20restaurant%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20No%20branch-specific%20menu/order%20flow%0A%E2%80%A2%20There%27s%20no%20Order%20Online%20/%20Book%20a%20table%20button%20on%20the%20homepage%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Ratnakokan%20Seawoods%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -3555,15 +5218,52 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918850192774?text=Hi%20Prasad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20%28Kharghar%29%20and%20noticed%3A%20Homepage%20intermittently%20returns%20500%20errors%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Smile Matters Multispeciality Dental Clinic: I checked smilemattersgroup.com</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>mailto:drprasad@smilemattersgroup.com?subject=Smile%20Matters%20Multispeciality%20Dental%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Prasad%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20I%20looked%20at%20Smile%20Matters%20Multispeciality%20Dental%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AHomepage%20intermittently%20returns%20500%20errors%3B%20thin%20branding%20differentiation%3B%20booking%20depends%20mainly%20on%20phone/WhatsApp%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Prasad,
+I opened https://smilemattersgroup.com/ while looking at dental businesses in Kharghar.
+Here's what a customer would notice today:
+• Your website sometimes opens an error page (I got a 500) instead of your homepage
+• The pages look dated and thin — visitors don't get enough proof to call
+• Booking depends mainly on phone/WhatsApp
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Smile Matters Multispeciality Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Hi Prasad,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://smilemattersgroup.com/) and a couple of things stood out:
+• Your website sometimes opens an error page (I got a 500) instead of your homepage
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Smile Matters Multispeciality Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918850192774?text=Hi%20Prasad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//smilemattersgroup.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>mailto:drprasad@smilemattersgroup.com?subject=Smile%20Matters%20Multispeciality%20Dental%20Clinic%3A%20I%20checked%20smilemattersgroup.com&amp;body=Dear%20Prasad%2C%0A%0AI%20opened%20https%3A//smilemattersgroup.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Booking%20depends%20mainly%20on%20phone/WhatsApp%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -3623,15 +5323,49 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918928785788?text=Hi%20Anup%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Agrawal%20Diagnostics%20Center%20Ulwe%20%28Ulwe%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Agrawal%20Diagnostics%20Center%20Ulwe%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Agrawal Diagnostics Center Ulwe: I checked agrawaldiagnosticsulwe.com</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>mailto:anup3356@gmail.com?subject=Agrawal%20Diagnostics%20Center%20Ulwe%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Anup%2C%0A%0AWhile%20reviewing%20businesses%20in%20Ulwe%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Agrawal%20Diagnostics%20Center%20Ulwe.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Agrawal%20Diagnostics%20Center%20Ulwe%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Anup,
+I opened https://agrawaldiagnosticsulwe.com/ while looking at diagnostics businesses in Ulwe, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Agrawal Diagnostics Center Ulwe this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Hi Anup,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://agrawaldiagnosticsulwe.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Agrawal Diagnostics Center Ulwe this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918928785788?text=Hi%20Anup%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//agrawaldiagnosticsulwe.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Agrawal%20Diagnostics%20Center%20Ulwe%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>mailto:anup3356@gmail.com?subject=Agrawal%20Diagnostics%20Center%20Ulwe%3A%20I%20checked%20agrawaldiagnosticsulwe.com&amp;body=Dear%20Anup%2C%0A%0AI%20opened%20https%3A//agrawaldiagnosticsulwe.com/%20while%20looking%20at%20diagnostics%20businesses%20in%20Ulwe%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Agrawal%20Diagnostics%20Center%20Ulwe%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>https://agrawaldiagnosticsulwe.com/</t>
         </is>
@@ -3691,15 +5425,49 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918823529411?text=Hi%20Archana%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Janugade%20Ayurvedic%20Clinic%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Janugade%20Ayurvedic%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr. Janugade Ayurvedic Clinic: I checked www.drjanugades.com</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>mailto:drjanugades@gmail.com?subject=Dr.%20Janugade%20Ayurvedic%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Archana%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dr.%20Janugade%20Ayurvedic%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr.%20Janugade%20Ayurvedic%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Archana,
+I opened https://www.drjanugades.com/ while looking at healthcare businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr. Janugade Ayurvedic Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Hi Archana,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.drjanugades.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr. Janugade Ayurvedic Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918823529411?text=Hi%20Archana%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.drjanugades.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Janugade%20Ayurvedic%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>mailto:drjanugades@gmail.com?subject=Dr.%20Janugade%20Ayurvedic%20Clinic%3A%20I%20checked%20www.drjanugades.com&amp;body=Dear%20Archana%2C%0A%0AI%20opened%20https%3A//www.drjanugades.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Janugade%20Ayurvedic%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>https://www.drjanugades.com/</t>
         </is>
@@ -3759,15 +5527,49 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591420077?text=Hi%20Sambhaji%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20%28Nerul%20/%20Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr. Sambhaji Patil Skin Care Clinic: I checked drsambhajipatil.com</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>mailto:drsambhajipatil.com@gmail.com?subject=Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Sambhaji%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%20/%20Panvel%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Sambhaji,
+I opened https://drsambhajipatil.com/ while looking at healthcare businesses in Nerul / Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr. Sambhaji Patil Skin Care Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sambhaji,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drsambhajipatil.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr. Sambhaji Patil Skin Care Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918591420077?text=Hi%20Sambhaji%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drsambhajipatil.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>mailto:drsambhajipatil.com@gmail.com?subject=Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%3A%20I%20checked%20drsambhajipatil.com&amp;body=Dear%20Sambhaji%2C%0A%0AI%20opened%20https%3A//drsambhajipatil.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Nerul%20/%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>https://drsambhajipatil.com/</t>
         </is>
@@ -3819,15 +5621,52 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591971009?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Nakhawa%20Garden%20Restaurant%20%28Panvel%20%28Shirdhon%29%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Nakhawa%20Garden%20Restaurant%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Nakhawa Garden Restaurant: I checked nakhawagardenrestaurant.com</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>mailto:nakhawa1009@gmail.com?subject=Nakhawa%20Garden%20Restaurant%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%20%28Shirdhon%29%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Nakhawa%20Garden%20Restaurant.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20thin%20menu%20presentation%3B%20no%20online%20order%3B%20contact-led%20site%20with%20limited%20WhatsApp%20CTA%20prominence%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Nakhawa%20Garden%20Restaurant%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://nakhawagardenrestaurant.com/ while looking at restaurant businesses in Panvel (Shirdhon), Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+• Contact-led site with limited WhatsApp CTA prominence
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Nakhawa Garden Restaurant this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://nakhawagardenrestaurant.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Nakhawa Garden Restaurant this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918591971009?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//nakhawagardenrestaurant.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Nakhawa%20Garden%20Restaurant%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>mailto:nakhawa1009@gmail.com?subject=Nakhawa%20Garden%20Restaurant%3A%20I%20checked%20nakhawagardenrestaurant.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//nakhawagardenrestaurant.com/%20while%20looking%20at%20restaurant%20businesses%20in%20Panvel%20%28Shirdhon%29%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%E2%80%A2%20Contact-led%20site%20with%20limited%20WhatsApp%20CTA%20prominence%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Nakhawa%20Garden%20Restaurant%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -3887,15 +5726,49 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918989255544?text=Hi%20Himmat%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20The%20Dental%20Studio%20Kharghar%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20The%20Dental%20Studio%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>The Dental Studio Kharghar: I checked thedentalstudiokharghar.com</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>mailto:anands9@gmail.com?subject=The%20Dental%20Studio%20Kharghar%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Himmat%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20The%20Dental%20Studio%20Kharghar.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20The%20Dental%20Studio%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Himmat,
+I opened https://thedentalstudiokharghar.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for The Dental Studio Kharghar this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Hi Himmat,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thedentalstudiokharghar.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for The Dental Studio Kharghar this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918989255544?text=Hi%20Himmat%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thedentalstudiokharghar.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20Studio%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>mailto:anands9@gmail.com?subject=The%20Dental%20Studio%20Kharghar%3A%20I%20checked%20thedentalstudiokharghar.com&amp;body=Dear%20Himmat%2C%0A%0AI%20opened%20https%3A//thedentalstudiokharghar.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20Dental%20Studio%20Kharghar%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>https://thedentalstudiokharghar.com/</t>
         </is>
@@ -3955,15 +5828,49 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919930050434?text=Hi%20Bhavna%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20The%20TOOTH%20Clinic%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20The%20TOOTH%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>The TOOTH Clinic: I checked thetoothclinickharghar.co.in</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>mailto:thetoothclinic.kharghar@gmail.com?subject=The%20TOOTH%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Bhavna%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20The%20TOOTH%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20The%20TOOTH%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Bhavna,
+I opened https://thetoothclinickharghar.co.in/ while looking at dental businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for The TOOTH Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Hi Bhavna,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thetoothclinickharghar.co.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for The TOOTH Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919930050434?text=Hi%20Bhavna%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thetoothclinickharghar.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20TOOTH%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>mailto:thetoothclinic.kharghar@gmail.com?subject=The%20TOOTH%20Clinic%3A%20I%20checked%20thetoothclinickharghar.co.in&amp;body=Dear%20Bhavna%2C%0A%0AI%20opened%20https%3A//thetoothclinickharghar.co.in/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20TOOTH%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>https://thetoothclinickharghar.co.in/</t>
         </is>
@@ -4019,11 +5926,48 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652458337?text=Hi%20Archis%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Samarth%20Nethralaya%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Older%20eye-hospital%20template%20design%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Samarth%20Nethralaya%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>Samarth Nethralaya: I checked samarthnethralaya.com</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Dear Archis,
+I opened https://samarthnethralaya.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• No clear public email
+• Booking form forwards to WhatsApp rather than integrated scheduling
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Samarth Nethralaya this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Hi Archis,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://samarthnethralaya.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• No clear public email
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Samarth Nethralaya this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918652458337?text=Hi%20Archis%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//samarthnethralaya.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20No%20clear%20public%20email%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Samarth%20Nethralaya%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>https://samarthnethralaya.com/</t>
         </is>
@@ -4079,11 +6023,48 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919167550145?text=Hi%20Anand%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Art%20of%20Smiles%20by%20Citizen%20Dental%20Clinic%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Built%20on%20Wix%20with%20template%20feel%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Art%20of%20Smiles%20by%20Citizen%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>Art of Smiles by Citizen Dental Clinic: I checked www.artofsmiles.in</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Dear Anand,
+I opened https://www.artofsmiles.in/ while looking at dental businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The site is a basic Wix brochure page — it doesn't look like a serious local brand
+• The site still has leftover template branding that isn't yours
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Art of Smiles by Citizen Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Hi Anand,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.artofsmiles.in/) and a couple of things stood out:
+• The site is a basic Wix brochure page — it doesn't look like a serious local brand
+• The site still has leftover template branding that isn't yours
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Art of Smiles by Citizen Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919167550145?text=Hi%20Anand%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.artofsmiles.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%E2%80%A2%20The%20site%20still%20has%20leftover%20template%20branding%20that%20isn%27t%20yours%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Art%20of%20Smiles%20by%20Citizen%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>https://www.artofsmiles.in/</t>
         </is>
@@ -4143,15 +6124,49 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919167980919?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20J%20B%20Patel%20%26%20Associates%20%28CBD%20Belapur%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Wix-style%20brochure%20site%2C%20duplicated%20service%20tiles%2C%20grammar%20issues%2C%20contact%20form%20without%20visible%20phone/email%20on%20page%20body%2C%20thin%20trust%20for%20Belapur%20CA%20practice%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20J%20B%20Patel%20%26%20Associates%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>J B Patel &amp; Associates: I checked www.jbpassociates.in</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>mailto:tax@jbpassociates.in?subject=J%20B%20Patel%20%26%20Associates%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20J%20B%20Patel%20%26%20Associates.%0A%0ASpecific%20issues%20I%20found%3A%0AWix-style%20brochure%20site%2C%20duplicated%20service%20tiles%2C%20grammar%20issues%2C%20contact%20form%20without%20visible%20phone/email%20on%20page%20body%2C%20thin%20trust%20for%20Belapur%20CA%20practice%0A%0ARaheja%20Arcade%20location%20firms%20compete%20for%20startups%3B%20a%20sharper%20advisory%20site%20would%20improve%20inbound%20quality.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20J%20B%20Patel%20%26%20Associates%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.jbpassociates.in/ while looking at ca firm businesses in CBD Belapur, Navi Mumbai.
+Here's what a customer would notice today:
+• The site is a basic Wix brochure page — it doesn't look like a serious local brand
+People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
+I can share a free concept page for J B Patel &amp; Associates this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.jbpassociates.in/) and a couple of things stood out:
+• The site is a basic Wix brochure page — it doesn't look like a serious local brand
+People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
+I can send a free one-page concept for J B Patel &amp; Associates this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919167980919?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.jbpassociates.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20J%20B%20Patel%20%26%20Associates%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>mailto:tax@jbpassociates.in?subject=J%20B%20Patel%20%26%20Associates%3A%20I%20checked%20www.jbpassociates.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.jbpassociates.in/%20while%20looking%20at%20ca%20firm%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20J%20B%20Patel%20%26%20Associates%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>https://www.jbpassociates.in/</t>
         </is>
@@ -4211,15 +6226,51 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917903370914?text=Hi%20Vinayak%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20%28Kharghar%20/%20Belapur%20/%20Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Team%20section%20has%20leftover%20lorem-style%20text%20%28%27While%20mirth%20large%20of%20on%20front...%27%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>VAC IIT JEE NEET (Vidyotama Ashram Classes): I checked vaciit.com</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@vaciit.com?subject=VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Vinayak%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%20/%20Belapur%20/%20Nerul%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29.%0A%0ASpecific%20issues%20I%20found%3A%0ATeam%20section%20has%20leftover%20lorem-style%20text%20%28%27While%20mirth%20large%20of%20on%20front...%27%29%3B%20counters%20show%200%3B%20founder%20name%20inconsistency%20%28Prasad%20vs%20Yadav%29%0A%0AParents%20notice%20unfinished%20template%20text%20instantly%20%E2%80%94%20cleaning%20trust%20signals%20and%20lead%20capture%20lifts%20demo-class%20bookings.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Vinayak,
+I opened https://vaciit.com/ while looking at coaching institute businesses in Kharghar / Belapur / Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• Unfinished / dummy text is still visible on the live site
+• Founder name inconsistency (Prasad vs Yadav)
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can share a free concept page for VAC IIT JEE NEET (Vidyotama Ashram Classes) this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Hi Vinayak,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://vaciit.com/) and a couple of things stood out:
+• Unfinished / dummy text is still visible on the live site
+• Founder name inconsistency (Prasad vs Yadav)
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can send a free one-page concept for VAC IIT JEE NEET (Vidyotama Ashram Classes) this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917903370914?text=Hi%20Vinayak%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//vaciit.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%E2%80%A2%20Founder%20name%20inconsistency%20%28Prasad%20vs%20Yadav%29%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@vaciit.com?subject=VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%3A%20I%20checked%20vaciit.com&amp;body=Dear%20Vinayak%2C%0A%0AI%20opened%20https%3A//vaciit.com/%20while%20looking%20at%20coaching%20institute%20businesses%20in%20Kharghar%20/%20Belapur%20/%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%E2%80%A2%20Founder%20name%20inconsistency%20%28Prasad%20vs%20Yadav%29%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>https://vaciit.com/about</t>
         </is>
@@ -4279,15 +6330,52 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917977585840?text=Hi%20Nandita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Yuvani%20Aesthetic%20Clinic%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Encoding%20glitches%20in%20testimonials%20%28mojibake%20characters%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Yuvani%20Aesthetic%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Yuvani Aesthetic Clinic: I checked www.yuvaniaestheticclinic.com</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@yuvaniaestheticclinic.com?subject=Yuvani%20Aesthetic%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Nandita%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Yuvani%20Aesthetic%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AEncoding%20glitches%20in%20testimonials%20%28mojibake%20characters%29%3B%20service%20IA%20is%20more%20brochure%20than%20conversion%20funnel%3B%20limited%20structured%20online%20booking%0A%0ANiche%20aesthetic%20gynae%20%2B%20skin%20clinic%20that%20sells%20high-ticket%20procedures%20and%20needs%20cleaner%20lead/consult%20booking.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Yuvani%20Aesthetic%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Nandita,
+I opened https://www.yuvaniaestheticclinic.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Reviews/text on the site show broken characters, so it looks unmaintained
+• The site looks like a generic template rather than your brand
+• Limited structured online booking
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Yuvani Aesthetic Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nandita,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.yuvaniaestheticclinic.com/) and a couple of things stood out:
+• Reviews/text on the site show broken characters, so it looks unmaintained
+• The site looks like a generic template rather than your brand
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Yuvani Aesthetic Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917977585840?text=Hi%20Nandita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.yuvaniaestheticclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Reviews/text%20on%20the%20site%20show%20broken%20characters%2C%20so%20it%20looks%20unmaintained%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Yuvani%20Aesthetic%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@yuvaniaestheticclinic.com?subject=Yuvani%20Aesthetic%20Clinic%3A%20I%20checked%20www.yuvaniaestheticclinic.com&amp;body=Dear%20Nandita%2C%0A%0AI%20opened%20https%3A//www.yuvaniaestheticclinic.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Reviews/text%20on%20the%20site%20show%20broken%20characters%2C%20so%20it%20looks%20unmaintained%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Limited%20structured%20online%20booking%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Yuvani%20Aesthetic%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>https://www.yuvaniaestheticclinic.com/contact/</t>
         </is>
@@ -4347,15 +6435,52 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919769619932?text=Hi%20Nalini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Baking%20Magic%20%28CBD%20Belapur%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Older%20WordPress%20catalogue%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Baking%20Magic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Baking Magic: I checked bakingmagic.in</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@bakingmagic.in?subject=Baking%20Magic%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Nalini%2C%0A%0AWhile%20reviewing%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Baking%20Magic.%0A%0ASpecific%20issues%20I%20found%3A%0AOlder%20WordPress%20catalogue%3B%20contact%20page%20shows%20broken%20Instagram/Facebook%20token%20error%3B%20enquiry%20forms%20instead%20of%20modern%20checkout%0A%0ACustom%20cakes%2C%20corporate%20gifting%2C%20and%20dessert%20stations%20need%20fast%20online%20ordering%20and%20event%20RFQs.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Baking%20Magic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Nalini,
+I opened https://bakingmagic.in/ while looking at bakery businesses in CBD Belapur, Navi Mumbai.
+Here's what a customer would notice today:
+• Older WordPress catalogue
+• Social/Instagram links on the site are broken and don't open your real pages
+• Enquiry forms instead of modern checkout
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Baking Magic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nalini,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://bakingmagic.in/) and a couple of things stood out:
+• Older WordPress catalogue
+• Social/Instagram links on the site are broken and don't open your real pages
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Baking Magic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919769619932?text=Hi%20Nalini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//bakingmagic.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Older%20WordPress%20catalogue%0A%E2%80%A2%20Social/Instagram%20links%20on%20the%20site%20are%20broken%20and%20don%27t%20open%20your%20real%20pages%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Baking%20Magic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@bakingmagic.in?subject=Baking%20Magic%3A%20I%20checked%20bakingmagic.in&amp;body=Dear%20Nalini%2C%0A%0AI%20opened%20https%3A//bakingmagic.in/%20while%20looking%20at%20bakery%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Older%20WordPress%20catalogue%0A%E2%80%A2%20Social/Instagram%20links%20on%20the%20site%20are%20broken%20and%20don%27t%20open%20your%20real%20pages%0A%E2%80%A2%20Enquiry%20forms%20instead%20of%20modern%20checkout%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Baking%20Magic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
         <is>
           <t>https://bakingmagic.in/contact-us/</t>
         </is>
@@ -4415,15 +6540,52 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919920402020?text=Hi%20Bharat%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Homepage%20counters%20show%200%2B%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Neeta's Royal Trips &amp; Holidays: I checked neetasroyalholidays.com</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@neetasroyalholidays.in?subject=Neeta%27s%20Royal%20Trips%20%26%20Holidays%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Bharat%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Neeta%27s%20Royal%20Trips%20%26%20Holidays.%0A%0ASpecific%20issues%20I%20found%3A%0AHomepage%20counters%20show%200%2B%3B%20package%20cards%20feel%20thin%3B%20contact%20page%20is%20stronger%20than%20marketing%20pages%20%E2%80%94%20conversion%20hierarchy%20uneven%0A%0ATravel%20buyers%20compare%20itineraries%20online%20%E2%80%94%20a%20sharper%20package%20%2B%20quote%20funnel%20wins%20more%20Dubai/domestic%20bookings%20from%20Vashi.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Bharat,
+I opened https://neetasroyalholidays.com/ while looking at travel agent businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• The pages look dated and thin — visitors don't get enough proof to call
+• Contact page is stronger than marketing pages — conversion hierarchy uneven
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Neeta's Royal Trips &amp; Holidays this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Hi Bharat,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://neetasroyalholidays.com/) and a couple of things stood out:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• The pages look dated and thin — visitors don't get enough proof to call
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Neeta's Royal Trips &amp; Holidays this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919920402020?text=Hi%20Bharat%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//neetasroyalholidays.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@neetasroyalholidays.in?subject=Neeta%27s%20Royal%20Trips%20%26%20Holidays%3A%20I%20checked%20neetasroyalholidays.com&amp;body=Dear%20Bharat%2C%0A%0AI%20opened%20https%3A//neetasroyalholidays.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Contact%20page%20is%20stronger%20than%20marketing%20pages%20%E2%80%94%20conversion%20hierarchy%20uneven%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>https://neetasroyalholidays.com/contact-us.php</t>
         </is>
@@ -4479,11 +6641,48 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917304483530?text=Hi%20Ruchita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Physio%20Matters%20Clinic%20%26%20Sports%20Rehab%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Cardio-pulmonary%20section%20uses%20irrelevant%20%27modern%20enterprises%27%20copy%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Physio%20Matters%20Clinic%20%26%20Sports%20Rehab%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>Physio Matters Clinic &amp; Sports Rehab: I checked physiomatters.in</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Dear Ruchita,
+I opened https://physiomatters.in/ while looking at healthcare businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• Cardio-pulmonary section uses irrelevant 'modern enterprises' copy
+• Repeated 'View More' UI clutter
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Physio Matters Clinic &amp; Sports Rehab this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ruchita,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://physiomatters.in/) and a couple of things stood out:
+• Cardio-pulmonary section uses irrelevant 'modern enterprises' copy
+• Repeated 'View More' UI clutter
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Physio Matters Clinic &amp; Sports Rehab this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917304483530?text=Hi%20Ruchita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//physiomatters.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Cardio-pulmonary%20section%20uses%20irrelevant%20%27modern%20enterprises%27%20copy%0A%E2%80%A2%20Repeated%20%27View%20More%27%20UI%20clutter%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Physio%20Matters%20Clinic%20%26%20Sports%20Rehab%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>https://physiomatters.in/</t>
         </is>
@@ -4543,15 +6742,49 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919920230990?text=Hi%20CA%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Perfect%20Tutorials%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20No%20clear%20online%20booking/order%20path%20on%20homepage%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Perfect%20Tutorials%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Perfect Tutorials: I checked www.perfecttutorials.in</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>mailto:perfecttutorials@yahoo.in?subject=Perfect%20Tutorials%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20CA%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Perfect%20Tutorials.%0A%0ASpecific%20issues%20I%20found%3A%0ANo%20clear%20online%20booking/order%20path%20on%20homepage%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Perfect%20Tutorials%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Vishal,
+I opened https://www.perfecttutorials.in/ while looking at education businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can share a free concept page for Perfect Tutorials this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Hi Vishal,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.perfecttutorials.in/) and a couple of things stood out:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can send a free one-page concept for Perfect Tutorials this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919920230990?text=Hi%20Vishal%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.perfecttutorials.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Perfect%20Tutorials%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>mailto:perfecttutorials@yahoo.in?subject=Perfect%20Tutorials%3A%20I%20checked%20www.perfecttutorials.in&amp;body=Dear%20Vishal%2C%0A%0AI%20opened%20https%3A//www.perfecttutorials.in/%20while%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Perfect%20Tutorials%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
         <is>
           <t>https://www.perfecttutorials.in/</t>
         </is>
@@ -4611,15 +6844,49 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591472142?text=Hi%20Avishkar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Zellene%20Dental%20Care%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Fake/placeholder%20contact%20numbers%20visible%20on%20site%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Zellene%20Dental%20Care%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Zellene Dental Care: I checked zellenedentalcare.com</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@zellenedentalcare.com?subject=Zellene%20Dental%20Care%3A%20quick%20note%20on%20your%20website&amp;body=Dear%20Avishkar%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Zellene%20Dental%20Care.%0A%0ASpecific%20issues%20I%20found%3A%0AFake/placeholder%20contact%20numbers%20visible%20on%20site%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Zellene%20Dental%20Care%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dear Avishkar,
+I opened https://zellenedentalcare.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Leftover template / fake contact details are still showing on the site — not your real number or email
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Zellene Dental Care this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Hi Avishkar,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://zellenedentalcare.com/) and a couple of things stood out:
+• Leftover template / fake contact details are still showing on the site — not your real number or email
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Zellene Dental Care this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918591472142?text=Hi%20Avishkar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//zellenedentalcare.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Leftover%20template%20/%20fake%20contact%20details%20are%20still%20showing%20on%20the%20site%20%E2%80%94%20not%20your%20real%20number%20or%20email%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Zellene%20Dental%20Care%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@zellenedentalcare.com?subject=Zellene%20Dental%20Care%3A%20I%20checked%20zellenedentalcare.com&amp;body=Dear%20Avishkar%2C%0A%0AI%20opened%20https%3A//zellenedentalcare.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Leftover%20template%20/%20fake%20contact%20details%20are%20still%20showing%20on%20the%20site%20%E2%80%94%20not%20your%20real%20number%20or%20email%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Zellene%20Dental%20Care%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>https://zellenedentalcare.com/</t>
         </is>
@@ -4671,11 +6938,48 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918097592505?text=Hi%20Vivek%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Ardent%20Smiles%20%28Nerul%29%20and%20noticed%3A%20No%20public%20email%20listed%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Ardent%20Smiles%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>Ardent Smiles: I checked www.ardentsmiles.in</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Dear Vivek,
+I opened https://www.ardentsmiles.in/ while looking at dental businesses in Nerul.
+Here's what a customer would notice today:
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• Emoji-heavy hero copy
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Ardent Smiles this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Hi Vivek,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.ardentsmiles.in/) and a couple of things stood out:
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• Emoji-heavy hero copy
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Ardent Smiles this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918097592505?text=Hi%20Vivek%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.ardentsmiles.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%E2%80%A2%20Emoji-heavy%20hero%20copy%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ardent%20Smiles%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -4731,11 +7035,45 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919820130065?text=Hi%20Gunjan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Gunjan%20Estate%20Consultant%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Old%20India-directory%20style%20realtor%20template%2C%20country-code%20spam%20in%20enquiry%20form%2C%20thin%20property%20detail%20pages%2C%20no%20modern%20map/filters%20UX%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Gunjan%20Estate%20Consultant%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>Gunjan Estate Consultant: I checked www.gunjanestate.com</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Dear Gunjan,
+I opened https://www.gunjanestate.com/ while looking at real estate broker businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Gunjan Estate Consultant this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Hi Gunjan,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.gunjanestate.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Gunjan Estate Consultant this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919820130065?text=Hi%20Gunjan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.gunjanestate.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Gunjan%20Estate%20Consultant%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
         <is>
           <t>https://www.gunjanestate.com/</t>
         </is>
@@ -4787,11 +7125,48 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917304319909?text=Hi%20Vaibhav%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Mumbai%20Dental%20Care%20%28Ulwe%29%20and%20noticed%3A%20No%20public%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Mumbai%20Dental%20Care%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>Mumbai Dental Care: I checked www.mumbaidentalcare.in</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Dear Vaibhav,
+I opened https://www.mumbaidentalcare.in/ while looking at dental businesses in Ulwe.
+Here's what a customer would notice today:
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• Truncated service blurbs
+• Aggressive 'Fix teeth in 3 Days' marketing claims
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Mumbai Dental Care this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Hi Vaibhav,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.mumbaidentalcare.in/) and a couple of things stood out:
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• Truncated service blurbs
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Mumbai Dental Care this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917304319909?text=Hi%20Vaibhav%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.mumbaidentalcare.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%E2%80%A2%20Truncated%20service%20blurbs%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Mumbai%20Dental%20Care%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -4843,11 +7218,48 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918356049763?text=Hi%20Kanchan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dhriti%20Dent%20%27O%27%20Care%20and%20Implant%20Center%20%28Kamothe%29%20and%20noticed%3A%20Homepage%20intermittently%20500%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dhriti%20Dent%20%27O%27%20Care%20and%20Implant%20Center%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>Dhriti Dent 'O' Care and Implant Center: I checked dhritidentocare.com</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Dear Kanchan,
+I opened https://dhritidentocare.com/ while looking at dental businesses in Kamothe.
+Here's what a customer would notice today:
+• Your website sometimes opens an error page (I got a 500) instead of your homepage
+• There are typos on the homepage that look unprofessional
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Dhriti Dent 'O' Care and Implant Center this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kanchan,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://dhritidentocare.com/) and a couple of things stood out:
+• Your website sometimes opens an error page (I got a 500) instead of your homepage
+• There are typos on the homepage that look unprofessional
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Dhriti Dent 'O' Care and Implant Center this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918356049763?text=Hi%20Kanchan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//dhritidentocare.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20that%20look%20unprofessional%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dhriti%20Dent%20%27O%27%20Care%20and%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -4899,11 +7311,48 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919987158061?text=Hi%20Sonal%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Lotus%20Dental%20Care%20Clinic%20%28Vashi%29%20and%20noticed%3A%20No%20public%20email%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Lotus%20Dental%20Care%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>Lotus Dental Care Clinic: I checked lotusdentalcareclinic.com</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Dear Sonal,
+I opened https://lotusdentalcareclinic.com/ while looking at dental businesses in Vashi.
+Here's what a customer would notice today:
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• The pages look dated and thin — visitors don't get enough proof to call
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Lotus Dental Care Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sonal,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://lotusdentalcareclinic.com/) and a couple of things stood out:
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Lotus Dental Care Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919987158061?text=Hi%20Sonal%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//lotusdentalcareclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Lotus%20Dental%20Care%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -4959,11 +7408,48 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919769759944?text=Hi%20Purshottam%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Shree%20Datta%20Mohini%20Hospital%20%28Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Typos%20on%20homepage%20%28%27Weatlh%20of%20Experience%27%2C%20%27Diebetology%27%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Shree%20Datta%20Mohini%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>Shree Datta Mohini Hospital: I checked sdmhospital.in</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Dear Purshottam,
+I opened https://sdmhospital.in/ while looking at healthcare businesses in Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• There are typos on the homepage (e.g. 'Weatlh of Experience') that look unprofessional
+• No clear public email
+• Dense text-heavy design
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Shree Datta Mohini Hospital this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Hi Purshottam,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sdmhospital.in/) and a couple of things stood out:
+• There are typos on the homepage (e.g. 'Weatlh of Experience') that look unprofessional
+• No clear public email
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Shree Datta Mohini Hospital this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919769759944?text=Hi%20Purshottam%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sdmhospital.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Weatlh%20of%20Experience%27%29%20that%20look%20unprofessional%0A%E2%80%A2%20No%20clear%20public%20email%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Datta%20Mohini%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>https://sdmhospital.in/</t>
         </is>
@@ -5015,11 +7501,48 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137267173?text=Hi%20Amit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Smile%20Avenue%20Dental%20Clinic%20%28Nerul%29%20and%20noticed%3A%20Phone%20not%20prominent%20on%20homepage%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Smile%20Avenue%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>Smile Avenue Dental Clinic: I checked smileavenueclinic.com</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Dear Amit,
+I opened https://smileavenueclinic.com/ while looking at dental businesses in Nerul.
+Here's what a customer would notice today:
+• The phone number is missing from the homepage — people can't call you from the first screen
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• The site still sends patients to Practo to book, instead of capturing the appointment on your own page
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Smile Avenue Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Hi Amit,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://smileavenueclinic.com/) and a couple of things stood out:
+• The phone number is missing from the homepage — people can't call you from the first screen
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Smile Avenue Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919137267173?text=Hi%20Amit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//smileavenueclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Avenue%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -5075,11 +7598,47 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918451922257?text=Hi%20Sunny%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20The%20Dental%20Hut%20%28Airoli%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Booking%20still%20points%20patients%20to%20call/Practo/Google%20rather%20than%20a%20clear%20owned%20appointment%20CTA%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20The%20Dental%20Hut%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>The Dental Hut: I checked www.thedentalhut.com</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>Dear Sunny,
+I opened https://www.thedentalhut.com/ while looking at dental businesses in Airoli, Navi Mumbai.
+Here's what a customer would notice today:
+• The site still sends patients to Practo to book, instead of capturing the appointment on your own page
+• Weak WhatsApp click-to-chat path for Airoli families
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for The Dental Hut this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sunny,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.thedentalhut.com/) and a couple of things stood out:
+• The site still sends patients to Practo to book, instead of capturing the appointment on your own page
+• Weak WhatsApp click-to-chat path for Airoli families
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for The Dental Hut this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918451922257?text=Hi%20Sunny%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.thedentalhut.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20sends%20patients%20to%20Practo%20to%20book%2C%20instead%20of%20capturing%20the%20appointment%20on%20your%20own%20page%0A%E2%80%A2%20Weak%20WhatsApp%20click-to-chat%20path%20for%20Airoli%20families%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20Hut%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
         <is>
           <t>https://www.thedentalhut.com/</t>
         </is>
@@ -5135,11 +7694,47 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833857855?text=Hi%20Pranav%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr%20Pranav%27s%20Physiorehab%20Clinic%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Appointment%20path%20is%20phone/WhatsApp/form%20heavy%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr%20Pranav%27s%20Physiorehab%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>Dr Pranav's Physiorehab Clinic: I checked pranavphysiorehab.in</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Dear Pranav,
+I opened https://pranavphysiorehab.in/ while looking at physiotherapy businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Appointment path is phone/WhatsApp/form heavy
+• Home-visit booking CTA not sharp enough for multi-node Navi Mumbai demand
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr Pranav's Physiorehab Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Hi Pranav,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pranavphysiorehab.in/) and a couple of things stood out:
+• Appointment path is phone/WhatsApp/form heavy
+• Home-visit booking CTA not sharp enough for multi-node Navi Mumbai demand
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr Pranav's Physiorehab Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919833857855?text=Hi%20Pranav%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pranavphysiorehab.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Appointment%20path%20is%20phone/WhatsApp/form%20heavy%0A%E2%80%A2%20Home-visit%20booking%20CTA%20not%20sharp%20enough%20for%20multi-node%20Navi%20Mumbai%20demand%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Pranav%27s%20Physiorehab%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
         <is>
           <t>https://pranavphysiorehab.in/</t>
         </is>
@@ -5195,11 +7790,48 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833831389?text=Hi%20Manasi%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Manasi%20Shirke%20Interiors%20%28Navi%20Mumbai%29%20and%20noticed%3A%20No%20visible%20business%20email%20on%20site%20%28WhatsApp-first%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Manasi%20Shirke%20Interiors%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>Manasi Shirke Interiors: I checked www.manasishirke.com</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>Dear Manasi,
+I opened https://www.manasishirke.com/ while looking at interior design businesses in Navi Mumbai.
+Here's what a customer would notice today:
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• The pages look dated and thin — visitors don't get enough proof to call
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for Manasi Shirke Interiors this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Hi Manasi,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.manasishirke.com/) and a couple of things stood out:
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for Manasi Shirke Interiors this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919833831389?text=Hi%20Manasi%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.manasishirke.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Manasi%20Shirke%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>https://www.manasishirke.com/</t>
         </is>
@@ -5251,11 +7883,48 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137814191?text=Hi%20Anuradha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Shree%20Samarth%20Dental%20Clinic%20and%20Implant%20Centre%20%28Belapur%29%20and%20noticed%3A%20Homepage%20intermittently%20500%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Shree%20Samarth%20Dental%20Clinic%20and%20Implant%20Centre%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>Shree Samarth Dental Clinic and Implant Centre: I checked shreesamarthdental.com</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Dear Anuradha,
+I opened https://shreesamarthdental.com/ while looking at dental businesses in Belapur.
+Here's what a customer would notice today:
+• Your website sometimes opens an error page (I got a 500) instead of your homepage
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Shree Samarth Dental Clinic and Implant Centre this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Hi Anuradha,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://shreesamarthdental.com/) and a couple of things stood out:
+• Your website sometimes opens an error page (I got a 500) instead of your homepage
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Shree Samarth Dental Clinic and Implant Centre this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919137814191?text=Hi%20Anuradha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//shreesamarthdental.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Samarth%20Dental%20Clinic%20and%20Implant%20Centre%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -5311,11 +7980,47 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919019607843?text=Hi%20Sharad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Smile%20Please%20Dental%20Clinic%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20structure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Smile%20Please%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>Smile Please Dental Clinic: I checked www.smiileplease.com</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>Dear Sharad,
+I opened https://www.smiileplease.com/ while looking at dental businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak conversion hierarchy vs modern competitors
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Smile Please Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sharad,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smiileplease.com/) and a couple of things stood out:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak conversion hierarchy vs modern competitors
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Smile Please Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919019607843?text=Hi%20Sharad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smiileplease.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Please%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>https://www.smiileplease.com/</t>
         </is>
@@ -5371,15 +8076,49 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917304917886?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Opal%20Spa%20%26%20Salon%20Nerul%20%28Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Template%20theme%20leftovers%20%28%27Solox%27%29%2C%20placeholder%20service%20labels%20%28%27Select%20service%2001%27%29%2C%20Gmail%20contact%2C%20Facebook/Instagram%20links%20pointing%20to%20%230%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Opal%20Spa%20%26%20Salon%20Nerul%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Opal Spa &amp; Salon Nerul: I checked opalspanerul.com</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>mailto:opalspanerul2024@gmail.com?subject=Opal%20Spa%20%26%20Salon%20Nerul%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Opal%20Spa%20%26%20Salon%20Nerul.%0A%0ASpecific%20issues%20I%20found%3A%0ATemplate%20theme%20leftovers%20%28%27Solox%27%29%2C%20placeholder%20service%20labels%20%28%27Select%20service%2001%27%29%2C%20Gmail%20contact%2C%20Facebook/Instagram%20links%20pointing%20to%20%230%0A%0ALooks%20unfinished%20vs%20Seawoods/Nerul%20salon%20competition%3B%20finishing%20booking%20UX%20would%20convert%20more%20calls%20to%20appointments.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Opal%20Spa%20%26%20Salon%20Nerul%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://opalspanerul.com/ while looking at salon businesses in Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Opal Spa &amp; Salon Nerul this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://opalspanerul.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Opal Spa &amp; Salon Nerul this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917304917886?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//opalspanerul.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Opal%20Spa%20%26%20Salon%20Nerul%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>mailto:opalspanerul2024@gmail.com?subject=Opal%20Spa%20%26%20Salon%20Nerul%3A%20I%20checked%20opalspanerul.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//opalspanerul.com/%20while%20looking%20at%20salon%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Opal%20Spa%20%26%20Salon%20Nerul%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>https://opalspanerul.com/</t>
         </is>
@@ -5431,15 +8170,52 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918422012171?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sarovar%20Annexe%20%28Kamothe%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sarovar%20Annexe%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Sarovar Annexe: I checked www.sarovarannexe.com</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>mailto:sarovarannexe@gmail.com?subject=Sarovar%20Annexe%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kamothe%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Sarovar%20Annexe.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20outdated%20template%3B%20animated%20counters%20stuck%20at%20zero%3B%20no%20online%20booking%20%28OTA-listing%20reliant%29%3B%20thin%20packages/pricing%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Sarovar%20Annexe%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.sarovarannexe.com/ while looking at banquet businesses in Kamothe, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The site looks like a generic template rather than your brand
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Sarovar Annexe this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.sarovarannexe.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The site looks like a generic template rather than your brand
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Sarovar Annexe this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918422012171?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.sarovarannexe.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sarovar%20Annexe%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sarovarannexe@gmail.com?subject=Sarovar%20Annexe%3A%20I%20checked%20www.sarovarannexe.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.sarovarannexe.com/%20while%20looking%20at%20banquet%20businesses%20in%20Kamothe%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sarovar%20Annexe%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -5495,15 +8271,49 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919930810218?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dhruvatan%20Guest%20House%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Copyright%202015%20PHP%20site%2C%20HTTP-only%2C%20archaic%20reservation%20form%2C%20dated%20gallery%2C%20men-only%20positioning%20poorly%20communicated%20online%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dhruvatan%20Guest%20House%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dhruvatan Guest House: I checked dhruvatanguesthouse.com</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@dhruvatanguesthouse.com?subject=Dhruvatan%20Guest%20House%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dhruvatan%20Guest%20House.%0A%0ASpecific%20issues%20I%20found%3A%0ACopyright%202015%20PHP%20site%2C%20HTTP-only%2C%20archaic%20reservation%20form%2C%20dated%20gallery%2C%20men-only%20positioning%20poorly%20communicated%20online%0A%0AStudent/working-men%20stays%20near%20Sector%2012%20need%20mobile-first%20booking%3B%20current%20site%20looks%20abandoned.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dhruvatan%20Guest%20House%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened http://dhruvatanguesthouse.com/ while looking at hotel businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site still opens on HTTP (no lock/HTTPS), which browsers flag as not secure
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Dhruvatan Guest House this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (http://dhruvatanguesthouse.com/) and a couple of things stood out:
+• The site still opens on HTTP (no lock/HTTPS), which browsers flag as not secure
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Dhruvatan Guest House this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919930810218?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28http%3A//dhruvatanguesthouse.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20opens%20on%20HTTP%20%28no%20lock/HTTPS%29%2C%20which%20browsers%20flag%20as%20not%20secure%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dhruvatan%20Guest%20House%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@dhruvatanguesthouse.com?subject=Dhruvatan%20Guest%20House%3A%20I%20checked%20dhruvatanguesthouse.com&amp;body=Hello%2C%0A%0AI%20opened%20http%3A//dhruvatanguesthouse.com/%20while%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20still%20opens%20on%20HTTP%20%28no%20lock/HTTPS%29%2C%20which%20browsers%20flag%20as%20not%20secure%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dhruvatan%20Guest%20House%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
         <is>
           <t>http://www.dhruvatanguesthouse.com/contact.php</t>
         </is>
@@ -5559,15 +8369,52 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919594810508?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Kharghar%20Multispeciality%20Hospital%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Gmail-only%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Kharghar%20Multispeciality%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Kharghar Multispeciality Hospital: I checked khargharhospital.com</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>mailto:khargharhospital@gmail.com?subject=Kharghar%20Multispeciality%20Hospital%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Kharghar%20Multispeciality%20Hospital.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail-only%20contact%3B%20footer%20shows%20Elementor/agency%20watermarking%20and%20mixed%20copyright%20years%3B%20service%20list%20is%20a%20long%20form%20dropdown%3B%20generic%20WordPress/Elementor%20hospital%20look%0A%0ACentrally%20located%20near%20D%27Mart%20Kharghar%20but%20the%20site%20looks%20agency-assembled%20for%20a%20multispeciality%20hospital%20brand.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Kharghar%20Multispeciality%20Hospital%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://khargharhospital.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The footer still shows leftover website-builder / agency watermarks
+• Service list is a long form dropdown
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Kharghar Multispeciality Hospital this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://khargharhospital.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The footer still shows leftover website-builder / agency watermarks
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Kharghar Multispeciality Hospital this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919594810508?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//khargharhospital.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20footer%20still%20shows%20leftover%20website-builder%20/%20agency%20watermarks%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Kharghar%20Multispeciality%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>mailto:khargharhospital@gmail.com?subject=Kharghar%20Multispeciality%20Hospital%3A%20I%20checked%20khargharhospital.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//khargharhospital.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20footer%20still%20shows%20leftover%20website-builder%20/%20agency%20watermarks%0A%E2%80%A2%20Service%20list%20is%20a%20long%20form%20dropdown%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Kharghar%20Multispeciality%20Hospital%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
         <is>
           <t>https://khargharhospital.com/contact-us/</t>
         </is>
@@ -5623,15 +8470,49 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652109924?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Hotel%20Lavish%20Villa%20%28CBD%20Belapur%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Unfinished%20template%20text%20%28%27heart%20of%20%5Blocation%5D%27%29%2C%20Gmail%20enquiry%2C%20generic%20room%20copy%2C%20clone%20look%20shared%20with%20other%20hotels%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Hotel%20Lavish%20Villa%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hotel Lavish Villa: I checked hotellavishvilla.com</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>mailto:enquiryhotellavishvilla@gmail.com?subject=Hotel%20Lavish%20Villa%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Hotel%20Lavish%20Villa.%0A%0ASpecific%20issues%20I%20found%3A%0AUnfinished%20template%20text%20%28%27heart%20of%20%5Blocation%5D%27%29%2C%20Gmail%20enquiry%2C%20generic%20room%20copy%2C%20clone%20look%20shared%20with%20other%20hotels%0A%0ANear%20Belapur%20station%20travellers%20bounce%20on%20placeholder%20copy%3B%20localised%20content%20%2B%20direct%20booking%20would%20lift%20occupancy.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Hotel%20Lavish%20Villa%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://hotellavishvilla.com/ while looking at hotel businesses in CBD Belapur, Navi Mumbai.
+Here's what a customer would notice today:
+• Unfinished / dummy text is still visible on the live site
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Hotel Lavish Villa this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotellavishvilla.com/) and a couple of things stood out:
+• Unfinished / dummy text is still visible on the live site
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Hotel Lavish Villa this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918652109924?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotellavishvilla.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Lavish%20Villa%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>mailto:enquiryhotellavishvilla@gmail.com?subject=Hotel%20Lavish%20Villa%3A%20I%20checked%20hotellavishvilla.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//hotellavishvilla.com/%20while%20looking%20at%20hotel%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Lavish%20Villa%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>https://hotellavishvilla.com/</t>
         </is>
@@ -5683,15 +8564,52 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918080610202?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Pacific%20Banquets%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Pacific%20Banquets%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Pacific Banquets: I checked pacificbanquets.co.in</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>mailto:pacificbanquets@gmail.com?subject=Pacific%20Banquets%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Pacific%20Banquets.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20quote-only%20enquiry%20%28no%20online%20booking%20calendar%29%3B%20dated%20static%20pages%3B%20no%20WhatsApp%20deep-link%20CTA%20on%20contact%20copy%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Pacific%20Banquets%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://pacificbanquets.co.in/ while looking at banquet businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book Room / Check Availability button, so guests go to Booking.com instead
+• The pages look dated and thin — visitors don't get enough proof to call
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Pacific Banquets this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pacificbanquets.co.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book Room / Check Availability button, so guests go to Booking.com instead
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Pacific Banquets this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918080610202?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pacificbanquets.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Room%20/%20Check%20Availability%20button%2C%20so%20guests%20go%20to%20Booking.com%20instead%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pacific%20Banquets%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>mailto:pacificbanquets@gmail.com?subject=Pacific%20Banquets%3A%20I%20checked%20pacificbanquets.co.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//pacificbanquets.co.in/%20while%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Room%20/%20Check%20Availability%20button%2C%20so%20guests%20go%20to%20Booking.com%20instead%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pacific%20Banquets%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -5743,15 +8661,52 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652381977?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20%28New%20Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Sansmaran Banquet &amp; Fine Dine: I checked sansmaran.in</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>mailto:sansmaranfinedine@gmail.com?subject=Sansmaran%20Banquet%20%26%20Fine%20Dine%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20New%20Panvel%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Sansmaran%20Banquet%20%26%20Fine%20Dine.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20banquet%20enquiry%20is%20form-only%20%28no%20WhatsApp%20CTA%29%3B%20table%20reservation%20widget%20incomplete%20for%20events%3B%20OTA-style%20discovery%20risk%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://sansmaran.in/ while looking at banquet businesses in New Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book Room / Check Availability button, so guests go to Booking.com instead
+• Table reservation widget incomplete for events
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Sansmaran Banquet &amp; Fine Dine this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sansmaran.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book Room / Check Availability button, so guests go to Booking.com instead
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Sansmaran Banquet &amp; Fine Dine this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918652381977?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sansmaran.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Room%20/%20Check%20Availability%20button%2C%20so%20guests%20go%20to%20Booking.com%20instead%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sansmaranfinedine@gmail.com?subject=Sansmaran%20Banquet%20%26%20Fine%20Dine%3A%20I%20checked%20sansmaran.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//sansmaran.in/%20while%20looking%20at%20banquet%20businesses%20in%20New%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Room%20/%20Check%20Availability%20button%2C%20so%20guests%20go%20to%20Booking.com%20instead%0A%E2%80%A2%20Table%20reservation%20widget%20incomplete%20for%20events%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -5807,15 +8762,49 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004891376?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20The%20Spa%20Vashi%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Amateur%20HTML%20site%20with%20typos%20%28%27Tuseday%27%2C%20%27availbale%27%29%2C%20copyright%20year%202032%2C%20keyword-stuffed%20footer%2C%20hours%20listed%20as%2010%3A00%E2%80%9311%3A00%20%28looks%20broken%29%2C%20Gmail%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20The%20Spa%20Vashi%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>The Spa Vashi: I checked thespavashi.in</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>mailto:thespa.vashi@gmail.com?subject=The%20Spa%20Vashi%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20The%20Spa%20Vashi.%0A%0ASpecific%20issues%20I%20found%3A%0AAmateur%20HTML%20site%20with%20typos%20%28%27Tuseday%27%2C%20%27availbale%27%29%2C%20copyright%20year%202032%2C%20keyword-stuffed%20footer%2C%20hours%20listed%20as%2010%3A00%E2%80%9311%3A00%20%28looks%20broken%29%2C%20Gmail%20contact%0A%0ASpa%20buyers%20judge%20hygiene/professionalism%20from%20the%20site%3B%20redesign%20would%20reduce%20no-shows%20and%20spam%20enquiries.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20The%20Spa%20Vashi%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://thespavashi.in/ while looking at salon businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for The Spa Vashi this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thespavashi.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for The Spa Vashi this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919004891376?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thespavashi.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Spa%20Vashi%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>mailto:thespa.vashi@gmail.com?subject=The%20Spa%20Vashi%3A%20I%20checked%20thespavashi.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//thespavashi.in/%20while%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20Spa%20Vashi%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
         <is>
           <t>https://thespavashi.in/contact.html</t>
         </is>
@@ -5871,11 +8860,48 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919987360631?text=Hi%20Surabhi%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Surabhi%20Clinic%20%28Woman%20%26%20Child%29%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Wix-style%20dated%20multi-specialty%20brochure%20site%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Surabhi%20Clinic%20%28Woman%20%26%20Child%29%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>Dr. Surabhi Clinic (Woman &amp; Child): I checked www.gynecclinic.com</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Dear Surabhi,
+I opened https://www.gynecclinic.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site is a basic Wix brochure page — it doesn't look like a serious local brand
+• The pages look dated and thin — visitors don't get enough proof to call
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Dr. Surabhi Clinic (Woman &amp; Child) this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Hi Surabhi,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.gynecclinic.com/) and a couple of things stood out:
+• The site is a basic Wix brochure page — it doesn't look like a serious local brand
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Dr. Surabhi Clinic (Woman &amp; Child) this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919987360631?text=Hi%20Surabhi%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.gynecclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Surabhi%20Clinic%20%28Woman%20%26%20Child%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
         <is>
           <t>https://www.gynecclinic.com/</t>
         </is>
@@ -5931,11 +8957,48 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919136053699?text=Hi%20Sahana%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Rainbow%20Nursing%20Home%20%28Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Email%20shown%20as%20broken%20string%20%27nursinghomerainbow.com%27%20%28missing%20%40%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Rainbow%20Nursing%20Home%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>Rainbow Nursing Home: I checked www.rainbownursinghome.com</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>Dear Sahana,
+I opened https://www.rainbownursinghome.com/ while looking at small hospital businesses in Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• Email shown as broken string 'nursinghomerainbow.com' (missing @)
+• Doctor booking CTAs inconsistent (Dr. Sahana Shetty vs Hegde)
+• The pages look dated and thin — visitors don't get enough proof to call
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Rainbow Nursing Home this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sahana,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.rainbownursinghome.com/) and a couple of things stood out:
+• Email shown as broken string 'nursinghomerainbow.com' (missing @)
+• Doctor booking CTAs inconsistent (Dr. Sahana Shetty vs Hegde)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Rainbow Nursing Home this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919136053699?text=Hi%20Sahana%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.rainbownursinghome.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Email%20shown%20as%20broken%20string%20%27nursinghomerainbow.com%27%20%28missing%20%40%29%0A%E2%80%A2%20Doctor%20booking%20CTAs%20inconsistent%20%28Dr.%20Sahana%20Shetty%20vs%20Hegde%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Rainbow%20Nursing%20Home%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
         <is>
           <t>https://www.rainbownursinghome.com/</t>
         </is>
@@ -5991,11 +9054,48 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919920549676?text=Hi%20Neelesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Smile%20Evolve%20Dental%20Clinic%20%28Vashi%20/%20Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Older%20multi-location%20layout%20with%20dense%20text%20blocks%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Smile%20Evolve%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>Smile Evolve Dental Clinic: I checked www.smileevolve.com</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Dear Neelesh,
+I opened https://www.smileevolve.com/ while looking at dental businesses in Vashi / Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• Older multi-location layout with dense text blocks
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• Appointment flow is form/callback heavy rather than modern online booking
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Smile Evolve Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Hi Neelesh,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smileevolve.com/) and a couple of things stood out:
+• Older multi-location layout with dense text blocks
+• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Smile Evolve Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919920549676?text=Hi%20Neelesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smileevolve.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Older%20multi-location%20layout%20with%20dense%20text%20blocks%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Evolve%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
         <is>
           <t>https://www.smileevolve.com/</t>
         </is>
@@ -6051,11 +9151,45 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652366868?text=Hi%20Niyanta%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Antarachna%20Interiors%20%28CBD%20Belapur%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Spelling%20inconsistency%20%28Antarchana/Antarachna%29%2C%20unfinished%20service%20blurbs%2C%20sparse%20portfolio%2C%20weak%20contact/CTA%20structure%20for%20Belapur%20office%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Antarachna%20Interiors%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>Antarachna Interiors: I checked antarachnainteriors.com</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>Dear Niyanta,
+I opened https://antarachnainteriors.com/ while looking at interior design businesses in CBD Belapur, Navi Mumbai.
+Here's what a customer would notice today:
+• Unfinished / dummy text is still visible on the live site
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for Antarachna Interiors this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Hi Niyanta,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://antarachnainteriors.com/) and a couple of things stood out:
+• Unfinished / dummy text is still visible on the live site
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for Antarachna Interiors this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918652366868?text=Hi%20Niyanta%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//antarachnainteriors.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Antarachna%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>https://antarachnainteriors.com/about/</t>
         </is>
@@ -6107,11 +9241,48 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919820465370?text=Hi%20Parth%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Casa%20Dentique%20%28Seawoods%29%20and%20noticed%3A%20Email%20obscured/not%20clearly%20published%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Casa%20Dentique%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>Casa Dentique: I checked casadentique.com</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>Dear Parth,
+I opened https://casadentique.com/ while looking at dental businesses in Seawoods.
+Here's what a customer would notice today:
+• Email obscured/not clearly published
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• Mixed dental + hair transplant messaging dilutes focus
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Casa Dentique this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Hi Parth,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://casadentique.com/) and a couple of things stood out:
+• Email obscured/not clearly published
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Casa Dentique this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919820465370?text=Hi%20Parth%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//casadentique.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Email%20obscured/not%20clearly%20published%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Casa%20Dentique%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
         <is>
           <t>batch02_dental_research.json</t>
         </is>
@@ -6167,11 +9338,47 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919920186010?text=Hi%20Manisha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Anjani%20Maternity%20%26%20Nursing%20Home%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20No%20email%20listed%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Anjani%20Maternity%20%26%20Nursing%20Home%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>Anjani Maternity &amp; Nursing Home: I checked www.anjanimaternityhome.com</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>Dear Manisha,
+I opened https://www.anjanimaternityhome.com/ while looking at small hospital businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+• Otherwise cleaner than peers but still weak online appointment/ops tooling
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Anjani Maternity &amp; Nursing Home this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Hi Manisha,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.anjanimaternityhome.com/) and a couple of things stood out:
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+• Otherwise cleaner than peers but still weak online appointment/ops tooling
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Anjani Maternity &amp; Nursing Home this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919920186010?text=Hi%20Manisha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.anjanimaternityhome.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%E2%80%A2%20Otherwise%20cleaner%20than%20peers%20but%20still%20weak%20online%20appointment/ops%20tooling%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Anjani%20Maternity%20%26%20Nursing%20Home%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
         <is>
           <t>https://www.anjanimaternityhome.com/</t>
         </is>
@@ -6227,11 +9434,48 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919594545737?text=Hi%20Abhilash%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Bombay%20Diner%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20SEO%20content/brochure%20site%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Bombay%20Diner%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>Bombay Diner: I checked bombaydiner.in</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>Dear Abhilash,
+I opened https://bombaydiner.in/ while looking at restaurant businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• No online reservation, menu ordering, or clear enquiry CRM
+• Phone-heavy conversion
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Bombay Diner this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Hi Abhilash,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://bombaydiner.in/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• No online reservation, menu ordering, or clear enquiry CRM
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Bombay Diner this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919594545737?text=Hi%20Abhilash%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//bombaydiner.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20No%20online%20reservation%2C%20menu%20ordering%2C%20or%20clear%20enquiry%20CRM%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Bombay%20Diner%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
         <is>
           <t>https://bombaydiner.in/</t>
         </is>
@@ -6287,11 +9531,48 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917020902230?text=Hi%20Sumedh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20DentisTree%20Dental%20Clinic%20%28Ulwe%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Localo/landing-style%20site%20feels%20temporary%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20DentisTree%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>DentisTree Dental Clinic: I checked ulwedentist.localo.site</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>Dear Sumedh,
+I opened https://ulwedentist.localo.site/ while looking at dental businesses in Ulwe, Navi Mumbai.
+Here's what a customer would notice today:
+• Localo/landing-style site feels temporary
+• Weak brand trust vs owned .in domain
+• Booking still call-first
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for DentisTree Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sumedh,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ulwedentist.localo.site/) and a couple of things stood out:
+• Localo/landing-style site feels temporary
+• Weak brand trust vs owned .in domain
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for DentisTree Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917020902230?text=Hi%20Sumedh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ulwedentist.localo.site/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Localo/landing-style%20site%20feels%20temporary%0A%E2%80%A2%20Weak%20brand%20trust%20vs%20owned%20.in%20domain%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20DentisTree%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
         <is>
           <t>https://ulwedentist.localo.site/</t>
         </is>
@@ -6347,11 +9628,48 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917984558946?text=Hi%20Neha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Ekdantam%20Dental%20Clinic%20%28Kopar%20Khairane%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Offer-heavy%20homepage%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Ekdantam%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>Ekdantam Dental Clinic: I checked www.ekdantamdental.in</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>Dear Neha,
+I opened https://www.ekdantamdental.in/ while looking at dental businesses in Kopar Khairane, Navi Mumbai.
+Here's what a customer would notice today:
+• Offer-heavy homepage
+• Booking still call-centric
+• Conversion UX not sharp for implant/aligner high tickets
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Ekdantam Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Hi Neha,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.ekdantamdental.in/) and a couple of things stood out:
+• Offer-heavy homepage
+• Booking still call-centric
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Ekdantam Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917984558946?text=Hi%20Neha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.ekdantamdental.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Offer-heavy%20homepage%0A%E2%80%A2%20Booking%20still%20call-centric%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ekdantam%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
         <is>
           <t>https://www.ekdantamdental.in/</t>
         </is>
@@ -6407,11 +9725,48 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919819964488?text=Hi%20Harshada%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20The%20Dentalle%20%28Seawoods%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Newer%20clinic%20site%20is%20brochure-light%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20The%20Dentalle%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>The Dentalle: I checked thedentalle.com</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>Dear Harshada,
+I opened https://thedentalle.com/ while looking at dental businesses in Seawoods, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak online booking CTA
+• Limited trust/portfolio structure for Seawoods catchment
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for The Dentalle this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Hi Harshada,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thedentalle.com/) and a couple of things stood out:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak online booking CTA
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for The Dentalle this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919819964488?text=Hi%20Harshada%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thedentalle.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20online%20booking%20CTA%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dentalle%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
         <is>
           <t>https://thedentalle.com/</t>
         </is>
@@ -6467,11 +9822,47 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919326695614?text=Hi%20Neeraj%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr.%20Neeraj%27s%20Dental%20Clinic%20and%20Implant%20Centre%20%28Ulwe%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Call-now%20heavy%20booking%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr.%20Neeraj%27s%20Dental%20Clinic%20and%20Implant%20Centre%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>Dr. Neeraj's Dental Clinic and Implant Centre: I checked drneerajdental.in</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Dear Neeraj,
+I opened https://drneerajdental.in/ while looking at dental businesses in Ulwe, Navi Mumbai.
+Here's what a customer would notice today:
+• Call-now heavy booking
+• Weak structured appointment path for Ulwe growth corridor implant demand
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Dr. Neeraj's Dental Clinic and Implant Centre this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Hi Neeraj,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drneerajdental.in/) and a couple of things stood out:
+• Call-now heavy booking
+• Weak structured appointment path for Ulwe growth corridor implant demand
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Dr. Neeraj's Dental Clinic and Implant Centre this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919326695614?text=Hi%20Neeraj%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drneerajdental.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Call-now%20heavy%20booking%0A%E2%80%A2%20Weak%20structured%20appointment%20path%20for%20Ulwe%20growth%20corridor%20implant%20demand%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Neeraj%27s%20Dental%20Clinic%20and%20Implant%20Centre%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
         <is>
           <t>https://drneerajdental.in/</t>
         </is>
@@ -6527,11 +9918,47 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917021216053?text=Hi%20Jyoti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20The%20Physio%20Remedies%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Clinic%20listing%20presence%20stronger%20than%20conversion-led%20owned%20site%20UX%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20The%20Physio%20Remedies%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>The Physio Remedies: I checked www.physioremedies.org</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Dear Jyoti,
+I opened https://www.physioremedies.org/ while looking at physiotherapy businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Clinic listing presence stronger than conversion-led owned site UX
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for The Physio Remedies this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jyoti,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.physioremedies.org/) and a couple of things stood out:
+• Clinic listing presence stronger than conversion-led owned site UX
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for The Physio Remedies this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917021216053?text=Hi%20Jyoti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.physioremedies.org/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Clinic%20listing%20presence%20stronger%20than%20conversion-led%20owned%20site%20UX%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Physio%20Remedies%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
         <is>
           <t>https://www.physioremedies.org/</t>
         </is>
@@ -6587,15 +10014,49 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918080207999?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Hotel%20Seashore%20Residency%20%28CBD%20Belapur%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20hotel%20template%20%28same%20stack%20as%20sibling%20properties%29%2C%20thin%20room%20differentiation%2C%20booking%20widget%20without%20OTA/rate%20integrity%20clarity%2C%20stock-style%20testimonials%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Hotel%20Seashore%20Residency%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hotel Seashore Residency: I checked hotelseashoreresidency.in</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>mailto:booking@hotelseashoreresidency.in?subject=Hotel%20Seashore%20Residency%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Hotel%20Seashore%20Residency.%0A%0ASpecific%20issues%20I%20found%3A%0AGeneric%20hotel%20template%20%28same%20stack%20as%20sibling%20properties%29%2C%20thin%20room%20differentiation%2C%20booking%20widget%20without%20OTA/rate%20integrity%20clarity%2C%20stock-style%20testimonials%0A%0APalm%20Beach%20Rd%20independents%20lose%20share%20to%20OTAs%20without%20a%20trustworthy%20direct-book%20site.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Hotel%20Seashore%20Residency%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://hotelseashoreresidency.in/ while looking at hotel businesses in CBD Belapur, Navi Mumbai.
+Here's what a customer would notice today:
+• Room/event booking still depends on OTAs instead of a simple booking form on your own site
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Hotel Seashore Residency this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotelseashoreresidency.in/) and a couple of things stood out:
+• Room/event booking still depends on OTAs instead of a simple booking form on your own site
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Hotel Seashore Residency this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918080207999?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotelseashoreresidency.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Room/event%20booking%20still%20depends%20on%20OTAs%20instead%20of%20a%20simple%20booking%20form%20on%20your%20own%20site%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Seashore%20Residency%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>mailto:booking@hotelseashoreresidency.in?subject=Hotel%20Seashore%20Residency%3A%20I%20checked%20hotelseashoreresidency.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//hotelseashoreresidency.in/%20while%20looking%20at%20hotel%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Room/event%20booking%20still%20depends%20on%20OTAs%20instead%20of%20a%20simple%20booking%20form%20on%20your%20own%20site%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Seashore%20Residency%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
         <is>
           <t>https://hotelseashoreresidency.in/</t>
         </is>
@@ -6651,11 +10112,45 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917359662682?text=Hi%20Kruti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20FuturistiQ%20Smiles%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Placeholder%20Lorem%20Ipsum%20content%20still%20visible%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20FuturistiQ%20Smiles%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>FuturistiQ Smiles: I checked futuristiqsmiles.in</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>Dear Kruti,
+I opened https://futuristiqsmiles.in/ while looking at dental businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Placeholder 'Lorem ipsum' dummy text is still visible on the site
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for FuturistiQ Smiles this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kruti,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://futuristiqsmiles.in/) and a couple of things stood out:
+• Placeholder 'Lorem ipsum' dummy text is still visible on the site
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for FuturistiQ Smiles this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917359662682?text=Hi%20Kruti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//futuristiqsmiles.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Placeholder%20%27Lorem%20ipsum%27%20dummy%20text%20is%20still%20visible%20on%20the%20site%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20FuturistiQ%20Smiles%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
         <is>
           <t>https://futuristiqsmiles.in/</t>
         </is>
@@ -6711,11 +10206,45 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919619055472?text=Hi%20Kanchan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Kanchan%20Kolge%20Interiors%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20No%20clear%20online%20booking/order%20path%20on%20homepage%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Kanchan%20Kolge%20Interiors%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>Kanchan Kolge Interiors: I checked kanchankolge.com</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Dear Kanchan,
+I opened https://kanchankolge.com/ while looking at interior design businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for Kanchan Kolge Interiors this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kanchan,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://kanchankolge.com/) and a couple of things stood out:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for Kanchan Kolge Interiors this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919619055472?text=Hi%20Kanchan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//kanchankolge.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Kanchan%20Kolge%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
         <is>
           <t>https://kanchankolge.com/</t>
         </is>
@@ -6767,11 +10296,47 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918484989838?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Khana%20Junction%20%28Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Long%20static%20menu%20dump%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Khana%20Junction%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>Khana Junction: I checked khanajunction.com</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://khanajunction.com/ while looking at restaurant businesses in Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• Long static menu dump
+• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Khana Junction this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://khanajunction.com/) and a couple of things stood out:
+• Long static menu dump
+• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Khana Junction this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918484989838?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//khanajunction.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Long%20static%20menu%20dump%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Khana%20Junction%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
         <is>
           <t>https://khanajunction.com/</t>
         </is>
@@ -6827,15 +10392,51 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919370528517?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Goa%20travel-agent%20registration%20shown%20valid%20only%20through%2031-Mar-2025%20%28stale%20credential%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>KonkanArabia Hospitality &amp; Holiday Group: I checked konkanarabiahospitalitygroup.com</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>mailto:bookings@konkanarabiahospitalitygroup.com?subject=KonkanArabia%20Hospitality%20%26%20Holiday%20Group%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group.%0A%0ASpecific%20issues%20I%20found%3A%0AGoa%20travel-agent%20registration%20shown%20valid%20only%20through%2031-Mar-2025%20%28stale%20credential%29%3B%20long%20domain%20%2B%20mixed%20email%20brands%20%28kahg.com%20/%20gmail%29%20reduce%20clarity%0A%0ADubai/group-tour%20buyers%20check%20credentials%20%E2%80%94%20stale%20certificates%20and%20mixed%20contact%20brands%20reduce%20conversion.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://konkanarabiahospitalitygroup.com/ while looking at travel agent businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• Goa travel-agent registration shown valid only through 31-Mar-2025 (stale credential)
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for KonkanArabia Hospitality &amp; Holiday Group this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://konkanarabiahospitalitygroup.com/) and a couple of things stood out:
+• Goa travel-agent registration shown valid only through 31-Mar-2025 (stale credential)
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for KonkanArabia Hospitality &amp; Holiday Group this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919370528517?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//konkanarabiahospitalitygroup.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Goa%20travel-agent%20registration%20shown%20valid%20only%20through%2031-Mar-2025%20%28stale%20credential%29%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>mailto:bookings@konkanarabiahospitalitygroup.com?subject=KonkanArabia%20Hospitality%20%26%20Holiday%20Group%3A%20I%20checked%20konkanarabiahospitalitygroup.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//konkanarabiahospitalitygroup.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Goa%20travel-agent%20registration%20shown%20valid%20only%20through%2031-Mar-2025%20%28stale%20credential%29%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
         <is>
           <t>https://konkanarabiahospitalitygroup.com/</t>
         </is>
@@ -6891,15 +10492,49 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919653613434?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20KV%20Design%20Studio%20%28Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20studio%20site%20%28Kamothe%20address%20thin%29%2C%20stock-style%20testimonials%2C%20little%20project%20photography%20depth%2C%20chat%20widget%20over%20structured%20quote%20flow%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20KV%20Design%20Studio%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>KV Design Studio: I checked kvdesignstudio.in</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@kvdesignstudio.in?subject=KV%20Design%20Studio%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20KV%20Design%20Studio.%0A%0ASpecific%20issues%20I%20found%3A%0AGeneric%20template%20studio%20site%20%28Kamothe%20address%20thin%29%2C%20stock-style%20testimonials%2C%20little%20project%20photography%20depth%2C%20chat%20widget%20over%20structured%20quote%20flow%0A%0APanvel/Kamothe%20new%20flats%20need%20a%20local%20portfolio%20site%20that%20converts%20site-visit%20requests.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20KV%20Design%20Studio%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://kvdesignstudio.in/ while looking at interior design businesses in Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like SEO/template pages rather than a real project portfolio
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for KV Design Studio this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://kvdesignstudio.in/) and a couple of things stood out:
+• The site looks like SEO/template pages rather than a real project portfolio
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for KV Design Studio this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919653613434?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//kvdesignstudio.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20KV%20Design%20Studio%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@kvdesignstudio.in?subject=KV%20Design%20Studio%3A%20I%20checked%20kvdesignstudio.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//kvdesignstudio.in/%20while%20looking%20at%20interior%20design%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20KV%20Design%20Studio%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
         <is>
           <t>https://kvdesignstudio.in/about-us/</t>
         </is>
@@ -6955,15 +10590,49 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919372770138?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Nerul%20Gymkhana%20%28Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20SEO-heavy%20brochure%20layout%2C%20Gmail%20as%20primary%20inbox%2C%20fragmented%20contact%20numbers%20across%20pages%2C%20weak%20online%20membership/enquiry%20path%20for%203500%2B%20member%20club%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Nerul%20Gymkhana%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Nerul Gymkhana: I checked nerulgymkhana.com</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>mailto:nerulgymkhana@gmail.com?subject=Nerul%20Gymkhana%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Nerul%20Gymkhana.%0A%0ASpecific%20issues%20I%20found%3A%0ASEO-heavy%20brochure%20layout%2C%20Gmail%20as%20primary%20inbox%2C%20fragmented%20contact%20numbers%20across%20pages%2C%20weak%20online%20membership/enquiry%20path%20for%203500%2B%20member%20club%0A%0AFamilies%20shortlist%20clubs%20online%3B%20a%20cleaner%20join/enquiry%20UX%20would%20reduce%20admin%20call%20load.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Nerul%20Gymkhana%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://nerulgymkhana.com/ while looking at gym businesses in Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Nerul Gymkhana this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://nerulgymkhana.com/) and a couple of things stood out:
+• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Nerul Gymkhana this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919372770138?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//nerulgymkhana.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Nerul%20Gymkhana%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>mailto:nerulgymkhana@gmail.com?subject=Nerul%20Gymkhana%3A%20I%20checked%20nerulgymkhana.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//nerulgymkhana.com/%20while%20looking%20at%20gym%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Nerul%20Gymkhana%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
         <is>
           <t>https://nerulgymkhana.com/</t>
         </is>
@@ -7015,15 +10684,52 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919323620423?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20%28Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Nerul Gymkhana Arena One Banquet &amp; Lawn: I checked nerulgymkhana.com/facilities/arenaone</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>mailto:nerulgymkhana@gmail.com?subject=Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20event%20booking%20buried%20under%20club/membership%20content%3B%20no%20dedicated%20banquet%20booking%20flow%3B%20phone-only%20for%20venue%20hire%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://nerulgymkhana.com/facilities/arenaone/ while looking at banquet businesses in Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Event booking buried under club/membership content
+• No dedicated banquet booking flow
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Nerul Gymkhana Arena One Banquet &amp; Lawn this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://nerulgymkhana.com/facilities/arenaone/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Event booking buried under club/membership content
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Nerul Gymkhana Arena One Banquet &amp; Lawn this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919323620423?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//nerulgymkhana.com/facilities/arenaone/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Event%20booking%20buried%20under%20club/membership%20content%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>mailto:nerulgymkhana@gmail.com?subject=Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%3A%20I%20checked%20nerulgymkhana.com/facilities/arenaone&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//nerulgymkhana.com/facilities/arenaone/%20while%20looking%20at%20banquet%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Event%20booking%20buried%20under%20club/membership%20content%0A%E2%80%A2%20No%20dedicated%20banquet%20booking%20flow%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -7079,15 +10785,51 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918879746848?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Bigfoot%20Holidays%20%28Navi%20Mumbai%29%20and%20noticed%3A%20Template%20placeholder%20phones%20%2801234567890%20/%2009876543210%29%20appear%20in%20source%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Bigfoot%20Holidays%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Bigfoot Holidays: I checked www.bigfootholidays.com</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>mailto:business@bigfootholidays.com?subject=Bigfoot%20Holidays%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Navi%20Mumbai%2C%20I%20looked%20at%20Bigfoot%20Holidays.%0A%0ASpecific%20issues%20I%20found%3A%0ATemplate%20placeholder%20phones%20%2801234567890%20/%2009876543210%29%20appear%20in%20source%3B%20CloudM%20placeholder%20emails%20present%3B%20contact%20page%20404%0A%0APlaceholder%20contact%20data%20destroys%20trust%20for%20holiday%20buyers%20%E2%80%94%20fixing%20this%20alone%20can%20unlock%20more%20quote%20requests.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Bigfoot%20Holidays%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.bigfootholidays.com/ while looking at travel agent businesses in Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• CloudM placeholder emails present
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Bigfoot Holidays this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.bigfootholidays.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• CloudM placeholder emails present
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Bigfoot Holidays this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918879746848?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.bigfootholidays.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20CloudM%20placeholder%20emails%20present%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Bigfoot%20Holidays%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>mailto:business@bigfootholidays.com?subject=Bigfoot%20Holidays%3A%20I%20checked%20www.bigfootholidays.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.bigfootholidays.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20CloudM%20placeholder%20emails%20present%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Bigfoot%20Holidays%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
         <is>
           <t>https://www.bigfootholidays.com/</t>
         </is>
@@ -7143,15 +10885,52 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917420935001?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Crown%20Logistic%20Packers%20and%20Movers%20%28Thane%20West%29%20and%20noticed%3A%20Heavy%20keyword%20repetition%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Crown%20Logistic%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Crown Logistic Packers and Movers: I checked crownlogisticsindia.co.in</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@crownlogisticsindia.co.in?subject=Crown%20Logistic%20Packers%20and%20Movers%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Thane%20West%2C%20I%20looked%20at%20Crown%20Logistic%20Packers%20and%20Movers.%0A%0ASpecific%20issues%20I%20found%3A%0AHeavy%20keyword%20repetition%3B%20quote%20form%20has%20typos%20%28%27Domestic%20Servoces%27%29%3B%20trust%20claims%20dense%20but%20design%20feels%20generic%20template%0A%0AThane%20movers%20compete%20on%20trust%20%E2%80%94%20a%20cleaner%20certified-brand%20site%20with%20a%20frictionless%20quote%20form%20lifts%20booked%20surveys.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Crown%20Logistic%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://crownlogisticsindia.co.in/ while looking at packers &amp; movers businesses in Thane West.
+Here's what a customer would notice today:
+• Heavy keyword repetition
+• There are typos on the homepage (e.g. 'Domestic Servoces') that look unprofessional
+• The site looks like a generic template rather than your brand
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Crown Logistic Packers and Movers this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://crownlogisticsindia.co.in/) and a couple of things stood out:
+• Heavy keyword repetition
+• There are typos on the homepage (e.g. 'Domestic Servoces') that look unprofessional
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Crown Logistic Packers and Movers this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917420935001?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//crownlogisticsindia.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Heavy%20keyword%20repetition%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Domestic%20Servoces%27%29%20that%20look%20unprofessional%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Crown%20Logistic%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@crownlogisticsindia.co.in?subject=Crown%20Logistic%20Packers%20and%20Movers%3A%20I%20checked%20crownlogisticsindia.co.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//crownlogisticsindia.co.in/%20while%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Thane%20West.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Heavy%20keyword%20repetition%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Domestic%20Servoces%27%29%20that%20look%20unprofessional%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Crown%20Logistic%20Packers%20and%20Movers%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
         <is>
           <t>https://crownlogisticsindia.co.in/</t>
         </is>
@@ -7207,15 +10986,52 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918879327184?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Henotic%20Diagnostics%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Overloaded%20booking%20form%20with%20enormous%20keyword-stuffed%20test%20dropdown%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Henotic%20Diagnostics%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Henotic Diagnostics: I checked henoticdiagnostics.com</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>mailto:henoticdiagnostics@gmail.com?subject=Henotic%20Diagnostics%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Henotic%20Diagnostics.%0A%0ASpecific%20issues%20I%20found%3A%0AOverloaded%20booking%20form%20with%20enormous%20keyword-stuffed%20test%20dropdown%3B%20Gmail%20contact%3B%20feels%20more%20SEO%20portal%20than%20clinic%20site%0A%0APatients%20abandon%20bloated%20booking%20UIs%20%E2%80%94%20a%20simpler%20appointment%20path%20converts%20more%20Kharghar%20scan/pathology%20traffic.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Henotic%20Diagnostics%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://henoticdiagnostics.com/ while looking at diagnostic lab businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Overloaded booking form with enormous keyword-stuffed test dropdown
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Feels more SEO portal than clinic site
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Henotic Diagnostics this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://henoticdiagnostics.com/) and a couple of things stood out:
+• Overloaded booking form with enormous keyword-stuffed test dropdown
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Henotic Diagnostics this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918879327184?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//henoticdiagnostics.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Overloaded%20booking%20form%20with%20enormous%20keyword-stuffed%20test%20dropdown%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Henotic%20Diagnostics%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>mailto:henoticdiagnostics@gmail.com?subject=Henotic%20Diagnostics%3A%20I%20checked%20henoticdiagnostics.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//henoticdiagnostics.com/%20while%20looking%20at%20diagnostic%20lab%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Overloaded%20booking%20form%20with%20enormous%20keyword-stuffed%20test%20dropdown%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Feels%20more%20SEO%20portal%20than%20clinic%20site%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Henotic%20Diagnostics%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
         <is>
           <t>https://henoticdiagnostics.com/</t>
         </is>
@@ -7267,15 +11083,52 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833810330?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Hotel%20Garden%20Panvel%20%28Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Rediffmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Hotel%20Garden%20Panvel%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hotel Garden Panvel: I checked hotelgardenpanvel.com</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>mailto:hotelg@rediffmail.com?subject=Hotel%20Garden%20Panvel%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Hotel%20Garden%20Panvel.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Rediffmail%20for%20business%20contact%3B%20outdated%20copy/grammar%3B%20stats%20counters%20show%200%3B%20no%20modern%20online%20booking%20engine%3B%20weak%20mobile%20conversion%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Hotel%20Garden%20Panvel%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://hotelgardenpanvel.com/ while looking at hotel businesses in Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• Uses Rediffmail for business contact
+• The pages look dated and thin — visitors don't get enough proof to call
+• Stats counters show 0
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Hotel Garden Panvel this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotelgardenpanvel.com/) and a couple of things stood out:
+• Uses Rediffmail for business contact
+• The pages look dated and thin — visitors don't get enough proof to call
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Hotel Garden Panvel this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919833810330?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotelgardenpanvel.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Uses%20Rediffmail%20for%20business%20contact%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Garden%20Panvel%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>mailto:hotelg@rediffmail.com?subject=Hotel%20Garden%20Panvel%3A%20I%20checked%20hotelgardenpanvel.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//hotelgardenpanvel.com/%20while%20looking%20at%20hotel%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Uses%20Rediffmail%20for%20business%20contact%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Stats%20counters%20show%200%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Garden%20Panvel%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -7331,15 +11184,52 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919322512390?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Kothari%20Packers%20and%20Movers%20%28Nerul%20/%20Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20City%20landing%20pages%20are%20repetitive%20SEO%20templates%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Kothari%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Kothari Packers and Movers: I checked kotharipackersandmovers.com</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@kotharipackersandmovers.com?subject=Kothari%20Packers%20and%20Movers%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Nerul%20/%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Kothari%20Packers%20and%20Movers.%0A%0ASpecific%20issues%20I%20found%3A%0ACity%20landing%20pages%20are%20repetitive%20SEO%20templates%3B%20typos%20%28%27Pakcers%27%29%3B%20weak%20differentiation%20vs%20dozens%20of%20similarly%20named%20competitors%0A%0AIn%20a%20scam-heavy%20category%2C%20clearer%20brand%20proof%20and%20a%20modern%20quote%20UX%20win%20more%20Nerul/Kharghar%20moves.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Kothari%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://kotharipackersandmovers.com/ while looking at packers &amp; movers businesses in Nerul / Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• There are typos on the homepage (e.g. 'Pakcers') that look unprofessional
+• Weak differentiation vs dozens of similarly named competitors
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Kothari Packers and Movers this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://kotharipackersandmovers.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• There are typos on the homepage (e.g. 'Pakcers') that look unprofessional
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Kothari Packers and Movers this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919322512390?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//kotharipackersandmovers.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Pakcers%27%29%20that%20look%20unprofessional%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Kothari%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@kotharipackersandmovers.com?subject=Kothari%20Packers%20and%20Movers%3A%20I%20checked%20kotharipackersandmovers.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//kotharipackersandmovers.com/%20while%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Nerul%20/%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Pakcers%27%29%20that%20look%20unprofessional%0A%E2%80%A2%20Weak%20differentiation%20vs%20dozens%20of%20similarly%20named%20competitors%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Kothari%20Packers%20and%20Movers%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
         <is>
           <t>https://kotharipackersandmovers.com/</t>
         </is>
@@ -7395,15 +11285,49 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918655177772?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Reliable%20Education%20Classes%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Long%20SEO%20essay%20pages%20with%20repetitive%20%27best%20coaching%27%20claims%2C%20Gmail%20contact%2C%20weak%20visual%20proof%20of%20Vashi%20centre%2C%20no%20batch%20calendar%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Reliable%20Education%20Classes%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Reliable Education Classes: I checked reliablejeeneet.in</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>mailto:reliableeducationclasses@gmail.com?subject=Reliable%20Education%20Classes%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Reliable%20Education%20Classes.%0A%0ASpecific%20issues%20I%20found%3A%0ALong%20SEO%20essay%20pages%20with%20repetitive%20%27best%20coaching%27%20claims%2C%20Gmail%20contact%2C%20weak%20visual%20proof%20of%20Vashi%20centre%2C%20no%20batch%20calendar%0A%0APartnership%20pitch%20with%20Masterclass%20needs%20a%20cleaner%20landing%20that%20books%20counselling%20slots.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Reliable%20Education%20Classes%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://reliablejeeneet.in/ while looking at coaching classes businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can share a free concept page for Reliable Education Classes this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://reliablejeeneet.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can send a free one-page concept for Reliable Education Classes this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918655177772?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//reliablejeeneet.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Reliable%20Education%20Classes%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>mailto:reliableeducationclasses@gmail.com?subject=Reliable%20Education%20Classes%3A%20I%20checked%20reliablejeeneet.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//reliablejeeneet.in/%20while%20looking%20at%20coaching%20classes%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Reliable%20Education%20Classes%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
         <is>
           <t>https://reliablejeeneet.in/</t>
         </is>
@@ -7459,15 +11383,51 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919222283333?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Shree%20Classes%20IIT%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Branch%20pages%20feel%20dated%20brochure-style%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Shree%20Classes%20IIT%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Shree Classes IIT: I checked shreeclassesiit.com</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@shreeclasses.co.in?subject=Shree%20Classes%20IIT%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Shree%20Classes%20IIT.%0A%0ASpecific%20issues%20I%20found%3A%0ABranch%20pages%20feel%20dated%20brochure-style%3B%20weak%20mobile%20CTA%20hierarchy%20for%20a%2035-year%20institute%20competing%20with%20modern%20EdTech%20sites%0A%0ALegacy%20coaching%20brands%20lose%20Google%20shortlists%20when%20the%20site%20looks%20older%20than%20the%20competitors%20parents%20compare%20them%20against.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Shree%20Classes%20IIT%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://shreeclassesiit.com/ while looking at coaching institute businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• The site is hard to use on a phone — it doesn't fit the screen properly
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can share a free concept page for Shree Classes IIT this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://shreeclassesiit.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• The site is hard to use on a phone — it doesn't fit the screen properly
+Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
+I can send a free one-page concept for Shree Classes IIT this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919222283333?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//shreeclassesiit.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Classes%20IIT%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@shreeclasses.co.in?subject=Shree%20Classes%20IIT%3A%20I%20checked%20shreeclassesiit.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//shreeclassesiit.com/%20while%20looking%20at%20coaching%20institute%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Shree%20Classes%20IIT%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
         <is>
           <t>https://shreeclassesiit.com/kharghar-branch/</t>
         </is>
@@ -7523,15 +11483,51 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918655635968?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Yello%20Salon%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Yello%20Salon%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Yello Salon: I checked www.yellosalon.in</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>mailto:yellosalon.vashi@gmail.com?subject=Yello%20Salon%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Yello%20Salon.%0A%0ASpecific%20issues%20I%20found%3A%0AGmail%20for%20business%20contact%3B%20limited%20conversion%20structure%20beyond%20basic%20contact%20block%20for%20a%20Sector%2017%20salon%20competing%20with%20Peacock/Lakme%0A%0AVashi%20salon%20competition%20is%20intense%20%E2%80%94%20a%20stronger%20online%20booking%20presence%20wins%20more%20same-day%20appointments.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Yello%20Salon%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.yellosalon.in/ while looking at salon businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Limited conversion structure beyond basic contact block for a Sector 17 salon competing with Peacock/Lakme
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Yello Salon this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.yellosalon.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Limited conversion structure beyond basic contact block for a Sector 17 salon competing with Peacock/Lakme
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Yello Salon this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918655635968?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.yellosalon.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Limited%20conversion%20structure%20beyond%20basic%20contact%20block%20for%20a%20Sector%2017%20salon%20competing%20with%20Peacock/Lakme%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Yello%20Salon%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>mailto:yellosalon.vashi@gmail.com?subject=Yello%20Salon%3A%20I%20checked%20www.yellosalon.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.yellosalon.in/%20while%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Limited%20conversion%20structure%20beyond%20basic%20contact%20block%20for%20a%20Sector%2017%20salon%20competing%20with%20Peacock/Lakme%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Yello%20Salon%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
         <is>
           <t>https://www.yellosalon.in/</t>
         </is>
@@ -7587,15 +11583,52 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919320079007?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20All%20India%20Cargo%20Packers%20and%20Movers%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20All%20India%20Cargo%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>All India Cargo Packers and Movers: I checked www.allindiapacker.in</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>mailto:sahu.allindia@gmail.com?subject=All%20India%20Cargo%20Packers%20and%20Movers%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20All%20India%20Cargo%20Packers%20and%20Movers.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20SEO-heavy%20multi-city%20pages%20feel%20spammy%3B%20weak%20trust%20UX%20for%20high-ticket%20moves%0A%0AKharghar%20base%20movers%20%E2%80%94%20cleaner%20brand%20site%20wins%20society%20shifts.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20All%20India%20Cargo%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.allindiapacker.in/ while looking at packers &amp; movers businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• SEO-heavy multi-city pages feel spammy
+• Weak trust UX for high-ticket moves
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for All India Cargo Packers and Movers this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.allindiapacker.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• SEO-heavy multi-city pages feel spammy
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for All India Cargo Packers and Movers this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919320079007?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.allindiapacker.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20multi-city%20pages%20feel%20spammy%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20All%20India%20Cargo%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>mailto:sahu.allindia@gmail.com?subject=All%20India%20Cargo%20Packers%20and%20Movers%3A%20I%20checked%20www.allindiapacker.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.allindiapacker.in/%20while%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20multi-city%20pages%20feel%20spammy%0A%E2%80%A2%20Weak%20trust%20UX%20for%20high-ticket%20moves%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20All%20India%20Cargo%20Packers%20and%20Movers%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
         <is>
           <t>https://www.allindiapacker.in/</t>
         </is>
@@ -7651,15 +11684,49 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919130307464?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Aristo%20Real%20Estate%20Consultants%20%28Seawoods%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Clunky%20multi-agency%20filter%20UI%2C%20thin%20property%20presentation%2C%20weak%20mobile%20browse%20for%20Nerul%E2%80%93Seawoods%E2%80%93Belapur%20inventory%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Aristo%20Real%20Estate%20Consultants%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Aristo Real Estate Consultants: I checked aristouniversal.com</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@aristouniversal.com?subject=Aristo%20Real%20Estate%20Consultants%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Aristo%20Real%20Estate%20Consultants.%0A%0ASpecific%20issues%20I%20found%3A%0AClunky%20multi-agency%20filter%20UI%2C%20thin%20property%20presentation%2C%20weak%20mobile%20browse%20for%20Nerul%E2%80%93Seawoods%E2%80%93Belapur%20inventory%0A%0AMulti-node%20brokerage%20needs%20a%20consumer-grade%20search%20experience%20to%20convert%20portal%20traffic.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Aristo%20Real%20Estate%20Consultants%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://aristouniversal.com/ while looking at real estate broker businesses in Seawoods, Navi Mumbai.
+Here's what a customer would notice today:
+• The site is hard to use on a phone — it doesn't fit the screen properly
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Aristo Real Estate Consultants this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://aristouniversal.com/) and a couple of things stood out:
+• The site is hard to use on a phone — it doesn't fit the screen properly
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Aristo Real Estate Consultants this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919130307464?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//aristouniversal.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Aristo%20Real%20Estate%20Consultants%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@aristouniversal.com?subject=Aristo%20Real%20Estate%20Consultants%3A%20I%20checked%20aristouniversal.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//aristouniversal.com/%20while%20looking%20at%20real%20estate%20broker%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Aristo%20Real%20Estate%20Consultants%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
         <is>
           <t>https://aristouniversal.com/</t>
         </is>
@@ -7715,15 +11782,51 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004680588?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Black%20Fitness%20Kharghar%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Black%20Fitness%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Black Fitness Kharghar: I checked blackfitness.co.in</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>mailto:blackfit.kharghar@gmail.com?subject=Black%20Fitness%20Kharghar%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Black%20Fitness%20Kharghar.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%3B%20No%20clear%20online%20booking/order%20path%20on%20homepage%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Black%20Fitness%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://blackfitness.co.in/ while looking at fitness businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Black Fitness Kharghar this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://blackfitness.co.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Black Fitness Kharghar this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919004680588?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//blackfitness.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Black%20Fitness%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>mailto:blackfit.kharghar@gmail.com?subject=Black%20Fitness%20Kharghar%3A%20I%20checked%20blackfitness.co.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//blackfitness.co.in/%20while%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Black%20Fitness%20Kharghar%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
         <is>
           <t>https://blackfitness.co.in/</t>
         </is>
@@ -7779,15 +11882,49 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919930022269?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Cynosure%20Studios%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Typo-heavy%20About%20copy%2C%20Gmail%20contact%2C%20thin%20booking%20path%20for%20a%2020-year%20studio%20claiming%20luxury/editorial%20work%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Cynosure%20Studios%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Cynosure Studios: I checked www.cynosurestudio.in</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>mailto:cynodigital4@gmail.com?subject=Cynosure%20Studios%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Cynosure%20Studios.%0A%0ASpecific%20issues%20I%20found%3A%0ATypo-heavy%20About%20copy%2C%20Gmail%20contact%2C%20thin%20booking%20path%20for%20a%2020-year%20studio%20claiming%20luxury/editorial%20work%0A%0AWedding/portrait%20clients%20hire%20from%20portfolio%20polish%3B%20site%20quality%20currently%20undercuts%20the%20studio%20claim.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Cynosure%20Studios%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.cynosurestudio.in/ while looking at photography studio businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
+I can share a free concept page for Cynosure Studios this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.cynosurestudio.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
+I can send a free one-page concept for Cynosure Studios this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919930022269?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.cynosurestudio.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Cynosure%20Studios%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>mailto:cynodigital4@gmail.com?subject=Cynosure%20Studios%3A%20I%20checked%20www.cynosurestudio.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.cynosurestudio.in/%20while%20looking%20at%20photography%20studio%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Cynosure%20Studios%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
         <is>
           <t>https://www.cynosurestudio.in/about</t>
         </is>
@@ -7843,15 +11980,51 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919892505538?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20DELECON%20Design%20Co.%20%28Mumbai%20/%20Navi%20Mumbai%20/%20Thane%29%20and%20noticed%3A%20Gmail%20as%20primary%20business%20email%20despite%20long%20operating%20history%20%28since%202008%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20DELECON%20Design%20Co.%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>DELECON Design Co.: I checked www.delecondesigns.com</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>mailto:delecondesigns@gmail.com?subject=DELECON%20Design%20Co.%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Mumbai%20/%20Navi%20Mumbai%20/%20Thane%2C%20I%20looked%20at%20DELECON%20Design%20Co..%0A%0ASpecific%20issues%20I%20found%3A%0AGmail%20as%20primary%20business%20email%20despite%20long%20operating%20history%20%28since%202008%29%3B%20SEO-heavy%20locality%20pages%20can%20feel%20spammy%0A%0AEstablished%20interior%20firms%20still%20lose%20trust%20using%20free%20email%20%E2%80%94%20branded%20site%20%2B%20CRM%20upgrades%20win%20higher-ticket%20RFQs.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20DELECON%20Design%20Co.%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.delecondesigns.com/ while looking at interior design businesses in Mumbai / Navi Mumbai / Thane.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• SEO-heavy locality pages can feel spammy
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for DELECON Design Co. this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.delecondesigns.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• SEO-heavy locality pages can feel spammy
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for DELECON Design Co. this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919892505538?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.delecondesigns.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20locality%20pages%20can%20feel%20spammy%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20DELECON%20Design%20Co.%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>mailto:delecondesigns@gmail.com?subject=DELECON%20Design%20Co.%3A%20I%20checked%20www.delecondesigns.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.delecondesigns.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Mumbai%20/%20Navi%20Mumbai%20/%20Thane.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20locality%20pages%20can%20feel%20spammy%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20DELECON%20Design%20Co.%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
         <is>
           <t>https://www.delecondesigns.com/</t>
         </is>
@@ -7907,15 +12080,52 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004270644?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Patkar%20Laboratory%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Very%20dated%20brochure%20site%20for%20a%20NABL%20lab%20since%201987%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Patkar%20Laboratory%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Patkar Laboratory: I checked patkarlaboratory.com</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>mailto:patkarlaboratory@gmail.com?subject=Patkar%20Laboratory%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Patkar%20Laboratory.%0A%0ASpecific%20issues%20I%20found%3A%0AVery%20dated%20brochure%20site%20for%20a%20NABL%20lab%20since%201987%3B%20Gmail%20as%20primary%20contact%3B%20weak%20home-collection%20/%20test%20booking%20UX%0A%0APatients%20now%20book%20labs%20online%20%E2%80%94%20an%20outdated%20Patkar%20site%20loses%20sample-collection%20enquiries%20to%20Metropolis/Lal%20Path.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Patkar%20Laboratory%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://patkarlaboratory.com/ while looking at diagnostic lab businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Weak home-collection / test booking UX
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Patkar Laboratory this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://patkarlaboratory.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Patkar Laboratory this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919004270644?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//patkarlaboratory.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Patkar%20Laboratory%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>mailto:patkarlaboratory@gmail.com?subject=Patkar%20Laboratory%3A%20I%20checked%20patkarlaboratory.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//patkarlaboratory.com/%20while%20looking%20at%20diagnostic%20lab%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Weak%20home-collection%20/%20test%20booking%20UX%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Patkar%20Laboratory%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
         <is>
           <t>https://patkarlaboratory.com/contact/</t>
         </is>
@@ -7971,15 +12181,52 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918104022721?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Pravi%20Labs%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Claims%20mix%20NABH/NABL/ICMR%20messaging%20that%20can%20confuse%20patients%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Pravi%20Labs%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Pravi Labs: I checked www.pravilabs.in</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>mailto:care@pravilabs.in?subject=Pravi%20Labs%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Pravi%20Labs.%0A%0ASpecific%20issues%20I%20found%3A%0AClaims%20mix%20NABH/NABL/ICMR%20messaging%20that%20can%20confuse%20patients%3B%20generic%20template%20layout%3B%20weak%20test-menu%20discoverability%0A%0AHome-collection%20labs%20win%20on%20clarity%20%E2%80%94%20a%20cleaner%20test%20catalogue%20%2B%20booking%20flow%20beats%20competitor%20aggregators.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Pravi%20Labs%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.pravilabs.in/ while looking at diagnostic lab businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• Claims mix NABH/NABL/ICMR messaging that can confuse patients
+• The site looks like a generic template rather than your brand
+• Weak test-menu discoverability
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Pravi Labs this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.pravilabs.in/) and a couple of things stood out:
+• Claims mix NABH/NABL/ICMR messaging that can confuse patients
+• The site looks like a generic template rather than your brand
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Pravi Labs this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918104022721?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.pravilabs.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Claims%20mix%20NABH/NABL/ICMR%20messaging%20that%20can%20confuse%20patients%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pravi%20Labs%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>mailto:care@pravilabs.in?subject=Pravi%20Labs%3A%20I%20checked%20www.pravilabs.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.pravilabs.in/%20while%20looking%20at%20diagnostic%20lab%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Claims%20mix%20NABH/NABL/ICMR%20messaging%20that%20can%20confuse%20patients%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20test-menu%20discoverability%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pravi%20Labs%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
         <is>
           <t>https://www.pravilabs.in/</t>
         </is>
@@ -8031,15 +12278,52 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917021474940?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Pushp%20Vatika%20Resort%20%26%20Lawns%20%28Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Stay%20booking%20widget%20present%20but%20banquet/wedding%20enquiry%20still%20phone-heavy%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Pushp%20Vatika%20Resort%20%26%20Lawns%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Pushp Vatika Resort &amp; Lawns: I checked pushpvatikapanvel.com</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>mailto:reservations@pushpvatikapanvel.com?subject=Pushp%20Vatika%20Resort%20%26%20Lawns%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Pushp%20Vatika%20Resort%20%26%20Lawns.%0A%0ASpecific%20issues%20I%20found%3A%0AStay%20booking%20widget%20present%20but%20banquet/wedding%20enquiry%20still%20phone-heavy%3B%20limited%20WhatsApp%20prominence%20on%20primary%20CTAs%3B%20content%20blog-heavy%20vs%20conversion%0A%0AA%20clearer%20website%20usually%20converts%20more%20calls%20into%20booked%20customers.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Pushp%20Vatika%20Resort%20%26%20Lawns%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://pushpvatikapanvel.com/ while looking at hotel businesses in Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• Stay booking widget present but banquet/wedding enquiry still phone-heavy
+• Limited WhatsApp prominence on primary CTAs
+• Content blog-heavy vs conversion
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Pushp Vatika Resort &amp; Lawns this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pushpvatikapanvel.com/) and a couple of things stood out:
+• Stay booking widget present but banquet/wedding enquiry still phone-heavy
+• Limited WhatsApp prominence on primary CTAs
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Pushp Vatika Resort &amp; Lawns this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917021474940?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pushpvatikapanvel.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Stay%20booking%20widget%20present%20but%20banquet/wedding%20enquiry%20still%20phone-heavy%0A%E2%80%A2%20Limited%20WhatsApp%20prominence%20on%20primary%20CTAs%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pushp%20Vatika%20Resort%20%26%20Lawns%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>mailto:reservations@pushpvatikapanvel.com?subject=Pushp%20Vatika%20Resort%20%26%20Lawns%3A%20I%20checked%20pushpvatikapanvel.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//pushpvatikapanvel.com/%20while%20looking%20at%20hotel%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Stay%20booking%20widget%20present%20but%20banquet/wedding%20enquiry%20still%20phone-heavy%0A%E2%80%A2%20Limited%20WhatsApp%20prominence%20on%20primary%20CTAs%0A%E2%80%A2%20Content%20blog-heavy%20vs%20conversion%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pushp%20Vatika%20Resort%20%26%20Lawns%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -8095,15 +12379,52 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919747054419?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20RC%20Interior%20Designers%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20RC%20Interior%20Designers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>RC Interior Designers: I checked rcinteriordesigners.com</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>mailto:nairc20@gmail.com?subject=RC%20Interior%20Designers%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20RC%20Interior%20Designers.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20SEO-heavy%20service%20pages%3B%20weak%20project-gallery%20conversion%20vs%20modern%20interior%20studios%0A%0A19%2B%20years%20Kharghar%20interiors%20%E2%80%94%20brand%20site%20should%20feel%20premium%2C%20not%20directory-like.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20RC%20Interior%20Designers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://rcinteriordesigners.com/ while looking at interior design businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• SEO-heavy service pages
+• Weak project-gallery conversion vs modern interior studios
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for RC Interior Designers this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://rcinteriordesigners.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• SEO-heavy service pages
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for RC Interior Designers this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919747054419?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//rcinteriordesigners.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20service%20pages%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20RC%20Interior%20Designers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>mailto:nairc20@gmail.com?subject=RC%20Interior%20Designers%3A%20I%20checked%20rcinteriordesigners.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//rcinteriordesigners.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20service%20pages%0A%E2%80%A2%20Weak%20project-gallery%20conversion%20vs%20modern%20interior%20studios%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20RC%20Interior%20Designers%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
         <is>
           <t>https://rcinteriordesigners.com/</t>
         </is>
@@ -8159,15 +12480,51 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918928780318?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sai%20Leela%20Banquet%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sai%20Leela%20Banquet%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Sai Leela Banquet: I checked saileelabanquet.com</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>mailto:saileelabanquet@gmail.com?subject=Sai%20Leela%20Banquet%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Sai%20Leela%20Banquet.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20catering-led%20venue%20site%20lacks%20modern%20package/enquiry%20conversion%20path%0A%0AKamala%20Catering%E2%80%93managed%20venue%20%E2%80%94%20package%20pages%20%2B%20enquiry%20CRM%20book%20more%20events.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Sai%20Leela%20Banquet%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://saileelabanquet.com/ while looking at banquet businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Catering-led venue site lacks modern package/enquiry conversion path
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Sai Leela Banquet this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://saileelabanquet.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Catering-led venue site lacks modern package/enquiry conversion path
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Sai Leela Banquet this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918928780318?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//saileelabanquet.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Catering-led%20venue%20site%20lacks%20modern%20package/enquiry%20conversion%20path%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sai%20Leela%20Banquet%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>mailto:saileelabanquet@gmail.com?subject=Sai%20Leela%20Banquet%3A%20I%20checked%20saileelabanquet.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//saileelabanquet.com/%20while%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Catering-led%20venue%20site%20lacks%20modern%20package/enquiry%20conversion%20path%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sai%20Leela%20Banquet%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
         <is>
           <t>https://saileelabanquet.com/</t>
         </is>
@@ -8223,15 +12580,52 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917506006007?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Tungsten%20Fitness%20Club%20%28Vashi%20/%20Ghansoli%20/%20Nerul%20/%20Sanpada%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Tungsten%20Fitness%20Club%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Tungsten Fitness Club: I checked tungstenfitness.in</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>mailto:tungstenfitnessclub@gmail.com?subject=Tungsten%20Fitness%20Club%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%20/%20Ghansoli%20/%20Nerul%20/%20Sanpada%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Tungsten%20Fitness%20Club.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20multi-branch%20info%20is%20hard%20to%20scan%3B%20weak%20lead%20capture%20vs%20membership-focused%20competitors%0A%0AA%20cleaner%20branch%20%2B%20membership%20site%20turns%20multi-location%20search%20traffic%20into%20booked%20trial%20sessions.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Tungsten%20Fitness%20Club%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://tungstenfitness.in/ while looking at gym businesses in Vashi / Ghansoli / Nerul / Sanpada, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Multi-branch info is hard to scan
+• Weak lead capture vs membership-focused competitors
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Tungsten Fitness Club this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://tungstenfitness.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• Multi-branch info is hard to scan
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Tungsten Fitness Club this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917506006007?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//tungstenfitness.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Multi-branch%20info%20is%20hard%20to%20scan%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Tungsten%20Fitness%20Club%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>mailto:tungstenfitnessclub@gmail.com?subject=Tungsten%20Fitness%20Club%3A%20I%20checked%20tungstenfitness.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//tungstenfitness.in/%20while%20looking%20at%20gym%20businesses%20in%20Vashi%20/%20Ghansoli%20/%20Nerul%20/%20Sanpada%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Multi-branch%20info%20is%20hard%20to%20scan%0A%E2%80%A2%20Weak%20lead%20capture%20vs%20membership-focused%20competitors%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Tungsten%20Fitness%20Club%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
         <is>
           <t>https://tungstenfitness.in/</t>
         </is>
@@ -8287,15 +12681,52 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918828388004?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Nakshatra%20Salon%20%26%20Academy%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Nakshatra%20Salon%20%26%20Academy%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Nakshatra Salon &amp; Academy: I checked nakshatrasalonandacademy.in</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>mailto:nakshatrasalonacademy@gmail.com?subject=Nakshatra%20Salon%20%26%20Academy%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Nakshatra%20Salon%20%26%20Academy.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20appointment%20is%20call-only%3B%20academy%20course%20enquiry%20UX%20thin%0A%0ASalon%20%2B%20academy%20dual%20revenue%20%E2%80%94%20booking%20%2B%20course%20CRM%20fills%20chairs%20and%20seats.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Nakshatra%20Salon%20%26%20Academy%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://nakshatrasalonandacademy.in/ while looking at salon businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+• The pages look dated and thin — visitors don't get enough proof to call
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Nakshatra Salon &amp; Academy this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://nakshatrasalonandacademy.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• There's no clear Book Appointment button — patients have to hunt for a phone number
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Nakshatra Salon &amp; Academy this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918828388004?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//nakshatrasalonandacademy.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Nakshatra%20Salon%20%26%20Academy%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>mailto:nakshatrasalonacademy@gmail.com?subject=Nakshatra%20Salon%20%26%20Academy%3A%20I%20checked%20nakshatrasalonandacademy.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//nakshatrasalonandacademy.in/%20while%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Nakshatra%20Salon%20%26%20Academy%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
         <is>
           <t>https://nakshatrasalonandacademy.in/</t>
         </is>
@@ -8351,15 +12782,52 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919324006006?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sky%20Banquet%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sky%20Banquet%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Sky Banquet: I checked skybanquet.in</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>mailto:skybanquetkharghar@gmail.com?subject=Sky%20Banquet%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Sky%20Banquet.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%3B%20thin%20banquet%20site%3B%20no%20clear%20date-availability%20enquiry%20UX%0A%0AKharghar%20banquet%20hall%20%E2%80%94%20event%20enquiry%20form%20wins%20wedding%20season%20leads.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Sky%20Banquet%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://skybanquet.in/ while looking at banquet businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+• No clear date-availability enquiry UX
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Sky Banquet this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://skybanquet.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The pages look dated and thin — visitors don't get enough proof to call
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Sky Banquet this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919324006006?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//skybanquet.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sky%20Banquet%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>mailto:skybanquetkharghar@gmail.com?subject=Sky%20Banquet%3A%20I%20checked%20skybanquet.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//skybanquet.in/%20while%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20No%20clear%20date-availability%20enquiry%20UX%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sky%20Banquet%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
         <is>
           <t>https://skybanquet.in/</t>
         </is>
@@ -8415,15 +12883,49 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967244434?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Caramel%20Bakery%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Caramel%20Bakery%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Caramel Bakery: I checked thecaramelbakery.in</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>mailto:caramelkharghar@gmail.com?subject=Caramel%20Bakery%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Caramel%20Bakery.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Caramel%20Bakery%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://thecaramelbakery.in/ while looking at bakery businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Caramel Bakery this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thecaramelbakery.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Caramel Bakery this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919967244434?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thecaramelbakery.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Caramel%20Bakery%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>mailto:caramelkharghar@gmail.com?subject=Caramel%20Bakery%3A%20I%20checked%20thecaramelbakery.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//thecaramelbakery.in/%20while%20looking%20at%20bakery%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Caramel%20Bakery%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
         <is>
           <t>https://thecaramelbakery.in/</t>
         </is>
@@ -8479,15 +12981,49 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591860677?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Dr%20Pols%20Dental%20Clinic%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Dr%20Pols%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Dr Pols Dental Clinic: I checked drpolsdentalclinic.com</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@drpolsdentalclinic.com?subject=Dr%20Pols%20Dental%20Clinic%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Dr%20Pols%20Dental%20Clinic.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Dr%20Pols%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://drpolsdentalclinic.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Dr Pols Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drpolsdentalclinic.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Dr Pols Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918591860677?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drpolsdentalclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Pols%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@drpolsdentalclinic.com?subject=Dr%20Pols%20Dental%20Clinic%3A%20I%20checked%20drpolsdentalclinic.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//drpolsdentalclinic.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr%20Pols%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
         <is>
           <t>https://drpolsdentalclinic.com/</t>
         </is>
@@ -8543,15 +13079,49 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918881784197?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Hotel%20Three%20Star%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Hotel%20Three%20Star%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hotel Three Star: I checked hotelthreestar.com</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>mailto:support@gmail.com?subject=Hotel%20Three%20Star%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Hotel%20Three%20Star.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Hotel%20Three%20Star%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://hotelthreestar.com/ while looking at hotel businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Hotel Three Star this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotelthreestar.com/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Hotel Three Star this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918881784197?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotelthreestar.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Three%20Star%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>mailto:support@gmail.com?subject=Hotel%20Three%20Star%3A%20I%20checked%20hotelthreestar.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//hotelthreestar.com/%20while%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Three%20Star%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
         <is>
           <t>https://hotelthreestar.com/</t>
         </is>
@@ -8607,15 +13177,52 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918898619371?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Travizia%20Tours%20and%20Travels%20%28Navi%20Mumbai%29%20and%20noticed%3A%20Copyright%20still%20shows%202016%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Travizia%20Tours%20and%20Travels%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Travizia Tours and Travels: I checked traviziaworld.com</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>mailto:admin@traviziaworld.com?subject=Travizia%20Tours%20and%20Travels%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Navi%20Mumbai%2C%20I%20looked%20at%20Travizia%20Tours%20and%20Travels.%0A%0ASpecific%20issues%20I%20found%3A%0ACopyright%20still%20shows%202016%3B%20dated%20brochure%20look%3B%20PDF%20brochure%20reliance%3B%20weak%20modern%20package%20UX%0A%0AA%202016-era%20travel%20site%20signals%20inactivity%20%E2%80%94%20a%20rebuild%20restores%20enquiry%20volume%20for%20domestic/international%20packages.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Travizia%20Tours%20and%20Travels%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://traviziaworld.com/ while looking at travel agent businesses in Navi Mumbai.
+Here's what a customer would notice today:
+• Copyright still shows 2016
+• The site looks like a generic template rather than your brand
+• Weak modern package UX
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Travizia Tours and Travels this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://traviziaworld.com/) and a couple of things stood out:
+• Copyright still shows 2016
+• The site looks like a generic template rather than your brand
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Travizia Tours and Travels this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918898619371?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//traviziaworld.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Copyright%20still%20shows%202016%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Travizia%20Tours%20and%20Travels%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>mailto:admin@traviziaworld.com?subject=Travizia%20Tours%20and%20Travels%3A%20I%20checked%20traviziaworld.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//traviziaworld.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Copyright%20still%20shows%202016%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20modern%20package%20UX%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Travizia%20Tours%20and%20Travels%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
         <is>
           <t>https://traviziaworld.com/</t>
         </is>
@@ -8671,15 +13278,49 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918400007765?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Unique%20Interior%20Decor%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Uses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Unique%20Interior%20Decor%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Unique Interior Decor: I checked uniqueinteriordecor.in</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>mailto:uniqueinteriorm@gmail.com?subject=Unique%20Interior%20Decor%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Unique%20Interior%20Decor.%0A%0ASpecific%20issues%20I%20found%3A%0AUses%20Gmail%20for%20business%20contact%20%28looks%20less%20professional%29%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Unique%20Interior%20Decor%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://uniqueinteriordecor.in/ while looking at interior design businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for Unique Interior Decor this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://uniqueinteriordecor.in/) and a couple of things stood out:
+• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for Unique Interior Decor this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918400007765?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//uniqueinteriordecor.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Unique%20Interior%20Decor%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>mailto:uniqueinteriorm@gmail.com?subject=Unique%20Interior%20Decor%3A%20I%20checked%20uniqueinteriordecor.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//uniqueinteriordecor.in/%20while%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Unique%20Interior%20Decor%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
         <is>
           <t>https://uniqueinteriordecor.in/</t>
         </is>
@@ -8731,11 +13372,48 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918369843353?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Eka%20Dental%20Care%20Seawoods%20%28Seawoods%20/%20Nerul%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Location%20page%20is%20thin%20and%20keyword-stuffed%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Eka%20Dental%20Care%20Seawoods%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M130" s="2" t="inlineStr"/>
+          <t>Eka Dental Care Seawoods: I checked ekadentalcare.com</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://ekadentalcare.com/ while looking at dental businesses in Seawoods / Nerul, Navi Mumbai.
+Here's what a customer would notice today:
+• The pages look dated and thin — visitors don't get enough proof to call
+• No doctor/owner profile on Seawoods page
+• No email or WhatsApp CTA visible
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Eka Dental Care Seawoods this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ekadentalcare.com/) and a couple of things stood out:
+• The pages look dated and thin — visitors don't get enough proof to call
+• No doctor/owner profile on Seawoods page
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Eka Dental Care Seawoods this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918369843353?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ekadentalcare.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20No%20doctor/owner%20profile%20on%20Seawoods%20page%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Eka%20Dental%20Care%20Seawoods%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr">
         <is>
           <t>https://ekadentalcare.com/dentist-in-sector-44-seawoods/</t>
         </is>
@@ -8791,15 +13469,52 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919167006010?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Khanna%20Travels%20%28Navi%20Mumbai%29%20and%20noticed%3A%20Email%20typo%20variant%20appears%20as%20bookings%40khannatravels.co%20in%20places%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Khanna%20Travels%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Khanna Travels: I checked khannatravels.com</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>mailto:bookings@khannatravels.com?subject=Khanna%20Travels%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Navi%20Mumbai%2C%20I%20looked%20at%20Khanna%20Travels.%0A%0ASpecific%20issues%20I%20found%3A%0AEmail%20typo%20variant%20appears%20as%20bookings%40khannatravels.co%20in%20places%3B%20Elementor-heavy%20page%20can%20feel%20cluttered%3B%20multiple%20phone%20numbers%20without%20clear%20primary%20sales%20line%0A%0AIATA%20agencies%20still%20lose%20leisure%20RFQs%20when%20the%20site%20feels%20noisy%20and%20the%20primary%20booking%20path%20is%20unclear.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Khanna%20Travels%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://khannatravels.com/ while looking at travel agent businesses in Navi Mumbai.
+Here's what a customer would notice today:
+• There are typos on the homepage that look unprofessional
+• The site looks like a generic template rather than your brand
+• Multiple phone numbers without clear primary sales line
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Khanna Travels this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://khannatravels.com/) and a couple of things stood out:
+• There are typos on the homepage that look unprofessional
+• The site looks like a generic template rather than your brand
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Khanna Travels this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919167006010?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//khannatravels.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20that%20look%20unprofessional%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Khanna%20Travels%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>mailto:bookings@khannatravels.com?subject=Khanna%20Travels%3A%20I%20checked%20khannatravels.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//khannatravels.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20that%20look%20unprofessional%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Multiple%20phone%20numbers%20without%20clear%20primary%20sales%20line%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Khanna%20Travels%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
         <is>
           <t>https://khannatravels.com/</t>
         </is>
@@ -8855,15 +13570,49 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917388887976?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Colour%20Spa%20%26%20Hammam%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Thin%20single-page%20spa%20site%20with%20limited%20treatment%20detail%2C%20weak%20booking%20form%20%28email%20capture%20only%29%2C%20little%20photography%20of%20rooms/therapists%20for%20a%20Hammam%20claim%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Colour%20Spa%20%26%20Hammam%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Colour Spa &amp; Hammam: I checked colourspa.co.in</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@colourspakh.com?subject=Colour%20Spa%20%26%20Hammam%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Colour%20Spa%20%26%20Hammam.%0A%0ASpecific%20issues%20I%20found%3A%0AThin%20single-page%20spa%20site%20with%20limited%20treatment%20detail%2C%20weak%20booking%20form%20%28email%20capture%20only%29%2C%20little%20photography%20of%20rooms/therapists%20for%20a%20Hammam%20claim%0A%0AHammam%20is%20a%20differentiator%E2%80%94better%20visuals%20and%20package%20booking%20would%20justify%20premium%20pricing.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Colour%20Spa%20%26%20Hammam%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://colourspa.co.in/ while looking at salon businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The pages look dated and thin — visitors don't get enough proof to call
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Colour Spa &amp; Hammam this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://colourspa.co.in/) and a couple of things stood out:
+• The pages look dated and thin — visitors don't get enough proof to call
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Colour Spa &amp; Hammam this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917388887976?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//colourspa.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Colour%20Spa%20%26%20Hammam%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@colourspakh.com?subject=Colour%20Spa%20%26%20Hammam%3A%20I%20checked%20colourspa.co.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//colourspa.co.in/%20while%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Colour%20Spa%20%26%20Hammam%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
         <is>
           <t>https://colourspa.co.in/</t>
         </is>
@@ -8919,15 +13668,52 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919769788777?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Krishnaay%20Pure%20Veg%20Restaurant%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20SEO-heavy%20brochure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Krishnaay%20Pure%20Veg%20Restaurant%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Krishnaay Pure Veg Restaurant: I checked www.krishnaay.com</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>mailto:contact@krishnaay.com?subject=Krishnaay%20Pure%20Veg%20Restaurant%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Krishnaay%20Pure%20Veg%20Restaurant.%0A%0ASpecific%20issues%20I%20found%3A%0ASEO-heavy%20brochure%3B%20address%20inconsistency%20across%20pages%3B%20reservation%20is%20form/phone%20only%2C%20no%20live%20booking%0A%0AFine-dine%20veg%20%2B%20banquet/corporate%20tables%20need%20a%20trustworthy%20booking%20%2B%20events%20enquiry%20funnel.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Krishnaay%20Pure%20Veg%20Restaurant%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://www.krishnaay.com/ while looking at restaurant businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• Address inconsistency across pages
+• Reservation is form/phone only, no live booking
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Krishnaay Pure Veg Restaurant this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.krishnaay.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• Address inconsistency across pages
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Krishnaay Pure Veg Restaurant this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919769788777?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.krishnaay.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Address%20inconsistency%20across%20pages%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Krishnaay%20Pure%20Veg%20Restaurant%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>mailto:contact@krishnaay.com?subject=Krishnaay%20Pure%20Veg%20Restaurant%3A%20I%20checked%20www.krishnaay.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.krishnaay.com/%20while%20looking%20at%20restaurant%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Address%20inconsistency%20across%20pages%0A%E2%80%A2%20Reservation%20is%20form/phone%20only%2C%20no%20live%20booking%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Krishnaay%20Pure%20Veg%20Restaurant%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
         <is>
           <t>https://www.krishnaay.com/contact</t>
         </is>
@@ -8983,15 +13769,49 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917475669291?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Equinox%20Fitness%20Kharghar%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20No%20clear%20online%20booking/order%20path%20on%20homepage%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Equinox%20Fitness%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Equinox Fitness Kharghar: I checked equinoxfitnessindia.com</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>mailto:support@equinoxfitnessclub.com?subject=Equinox%20Fitness%20Kharghar%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Equinox%20Fitness%20Kharghar.%0A%0ASpecific%20issues%20I%20found%3A%0ANo%20clear%20online%20booking/order%20path%20on%20homepage%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Equinox%20Fitness%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://equinoxfitnessindia.com/ while looking at fitness businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Equinox Fitness Kharghar this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://equinoxfitnessindia.com/) and a couple of things stood out:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Equinox Fitness Kharghar this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917475669291?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//equinoxfitnessindia.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Equinox%20Fitness%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>mailto:support@equinoxfitnessclub.com?subject=Equinox%20Fitness%20Kharghar%3A%20I%20checked%20equinoxfitnessindia.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//equinoxfitnessindia.com/%20while%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Equinox%20Fitness%20Kharghar%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
         <is>
           <t>https://equinoxfitnessindia.com/</t>
         </is>
@@ -9039,11 +13859,48 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833406722?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Hotel%20Khandesh%20%26%20Banquet%20%28New%20Panvel%20%28Khanda%20Colony%29%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Contact%20page%20is%20thin/image-heavy%20with%20weak%20structured%20contact%20details%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Hotel%20Khandesh%20%26%20Banquet%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M135" s="2" t="inlineStr"/>
+          <t>Hotel Khandesh &amp; Banquet: I checked hotelkhandesh.in</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://hotelkhandesh.in/ while looking at hotel businesses in New Panvel (Khanda Colony), Navi Mumbai.
+Here's what a customer would notice today:
+• The pages look dated and thin — visitors don't get enough proof to call
+• Booking path unclear (phone banner only)
+• The site looks like a generic template rather than your brand
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Hotel Khandesh &amp; Banquet this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotelkhandesh.in/) and a couple of things stood out:
+• The pages look dated and thin — visitors don't get enough proof to call
+• Booking path unclear (phone banner only)
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Hotel Khandesh &amp; Banquet this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919833406722?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotelkhandesh.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Booking%20path%20unclear%20%28phone%20banner%20only%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Khandesh%20%26%20Banquet%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -9099,15 +13956,49 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918369497873?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Treka%20Interiors%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20No%20clear%20online%20booking/order%20path%20on%20homepage%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Treka%20Interiors%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Treka Interiors: I checked trekainteriors.com</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@trekainteriors.com?subject=Treka%20Interiors%3A%20quick%20note%20on%20your%20website&amp;body=Hello%2C%0A%0AWhile%20reviewing%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20looked%20at%20Treka%20Interiors.%0A%0ASpecific%20issues%20I%20found%3A%0ANo%20clear%20online%20booking/order%20path%20on%20homepage%0A%0ACustomers%20shortlist%20on%20mobile%20first%20%E2%80%94%20a%20clearer%20booking/order%20site%20converts%20more%20enquiries%20into%20paid%20work.%0A%0AHappy%20to%20share%20a%20free%20concept%20for%20Treka%20Interiors%20this%20week%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>Hello,
+I opened https://trekainteriors.com/ while looking at interior design businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for Treka Interiors this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://trekainteriors.com/) and a couple of things stood out:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for Treka Interiors this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918369497873?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//trekainteriors.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Treka%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>mailto:info@trekainteriors.com?subject=Treka%20Interiors%3A%20I%20checked%20trekainteriors.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//trekainteriors.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Treka%20Interiors%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
         <is>
           <t>https://trekainteriors.com/</t>
         </is>
@@ -9159,11 +14050,48 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917506393366?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Vivastu%20Interiors%20%28Seawoods%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Testimonials%20still%20contain%20placeholder%20%27%5BInterior%20Designer%27s%20Name%5D%27%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Vivastu%20Interiors%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M137" s="2" t="inlineStr"/>
+          <t>Vivastu Interiors: I checked vivastuinteriors.com</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://vivastuinteriors.com/ while looking at interior design businesses in Seawoods, Navi Mumbai.
+Here's what a customer would notice today:
+• Testimonials still contain placeholder '[Interior Designer's Name]'
+• Process copy mentions Livspace booking amounts
+• Unfinished / dummy text is still visible on the live site
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can share a free concept page for Vivastu Interiors this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://vivastuinteriors.com/) and a couple of things stood out:
+• Testimonials still contain placeholder '[Interior Designer's Name]'
+• Process copy mentions Livspace booking amounts
+Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
+I can send a free one-page concept for Vivastu Interiors this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917506393366?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//vivastuinteriors.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Testimonials%20still%20contain%20placeholder%20%27%5BInterior%20Designer%27s%20Name%5D%27%0A%E2%80%A2%20Process%20copy%20mentions%20Livspace%20booking%20amounts%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Vivastu%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr">
         <is>
           <t>https://vivastuinteriors.com/</t>
         </is>
@@ -9215,11 +14143,47 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137764238?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Arise%20Gym%20%28Kharghar%29%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Branch%20page%20feels%20brochure-thin%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Arise%20Gym%20%28Kharghar%29%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M138" s="2" t="inlineStr"/>
+          <t>Arise Gym (Kharghar): I checked arisefitness.in/gym-at-kharghar</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://arisefitness.in/gym-at-kharghar/ while looking at gym businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• The site is hard to use on a phone — it doesn't fit the screen properly
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Arise Gym (Kharghar) this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://arisefitness.in/gym-at-kharghar/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• The site is hard to use on a phone — it doesn't fit the screen properly
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Arise Gym (Kharghar) this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919137764238?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//arisefitness.in/gym-at-kharghar/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Arise%20Gym%20%28Kharghar%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr">
         <is>
           <t>https://arisefitness.in/gym-at-kharghar/</t>
         </is>
@@ -9271,11 +14235,45 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919892302930?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Fantasy%20Salon%20and%20Spa%20Vashi%20Plaza%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Keyword-spam%20homepage%20%28phone%20repeated%20as%20H1%20banners%29%2C%20dated%202022%20copyright%2C%20no%20email%2C%20weak%20gallery/booking%20flow%2C%20SEO-first%20rather%20than%20conversion-first%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Fantasy%20Salon%20and%20Spa%20Vashi%20Plaza%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M139" s="2" t="inlineStr"/>
+          <t>Fantasy Salon and Spa Vashi Plaza: I checked www.fantasyspavashi.in</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://www.fantasyspavashi.in/ while looking at salon businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The copyright year on the site is old, so it looks abandoned
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Fantasy Salon and Spa Vashi Plaza this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.fantasyspavashi.in/) and a couple of things stood out:
+• The copyright year on the site is old, so it looks abandoned
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Fantasy Salon and Spa Vashi Plaza this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919892302930?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.fantasyspavashi.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Fantasy%20Salon%20and%20Spa%20Vashi%20Plaza%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr">
         <is>
           <t>https://www.fantasyspavashi.in/</t>
         </is>
@@ -9323,11 +14321,48 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919930856111?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Ramratan%20Aashiyana%20Beach%20Resort%20%28Ulwe%20/%20Uran%20side%20%28near%20Navi%20Mumbai%29%2C%20Panvel%20Taluka%29%20and%20noticed%3A%20Typos%20on%20homepage%20%28Welocme%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Ramratan%20Aashiyana%20Beach%20Resort%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M140" s="2" t="inlineStr"/>
+          <t>Ramratan Aashiyana Beach Resort: I checked www.ramratanaashiyanaresort.com</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://www.ramratanaashiyanaresort.com/ while looking at hotel businesses in Ulwe / Uran side (near Navi Mumbai), Panvel Taluka.
+Here's what a customer would notice today:
+• There are typos on the homepage that look unprofessional
+• Check-availability incomplete
+• Banquet pricing FAQ-only
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Ramratan Aashiyana Beach Resort this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.ramratanaashiyanaresort.com/) and a couple of things stood out:
+• There are typos on the homepage that look unprofessional
+• Check-availability incomplete
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Ramratan Aashiyana Beach Resort this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919930856111?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.ramratanaashiyanaresort.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20that%20look%20unprofessional%0A%E2%80%A2%20Check-availability%20incomplete%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ramratan%20Aashiyana%20Beach%20Resort%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -9379,11 +14414,45 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918169067671?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Blue%20Cross%20Vets%20Clinic%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Minimal%20Wix%20page%2C%20WhatsApp-text-only%20appointments%2C%20almost%20no%20service%20menu/doctor%20profile/emergency%20info%20despite%20advanced-clinic%20claim%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Blue%20Cross%20Vets%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M141" s="2" t="inlineStr"/>
+          <t>Blue Cross Vets Clinic: I checked www.bluecrossvetsclinic.com</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://www.bluecrossvetsclinic.com/ while looking at pet clinic businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site is a basic Wix brochure page — it doesn't look like a serious local brand
+People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
+I can share a free concept page for Blue Cross Vets Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.bluecrossvetsclinic.com/) and a couple of things stood out:
+• The site is a basic Wix brochure page — it doesn't look like a serious local brand
+People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
+I can send a free one-page concept for Blue Cross Vets Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918169067671?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.bluecrossvetsclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Blue%20Cross%20Vets%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr">
         <is>
           <t>https://www.bluecrossvetsclinic.com/</t>
         </is>
@@ -9431,11 +14500,48 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918369797500?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20FloDine%20Cruise%20/%20Cafe%20Relish%20%28CBD%20Belapur%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Outdated%20WordPress%20layout%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20FloDine%20Cruise%20/%20Cafe%20Relish%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M142" s="2" t="inlineStr"/>
+          <t>FloDine Cruise / Cafe Relish: I checked flodine.in/home</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://flodine.in/home/ while looking at restaurant businesses in CBD Belapur, Navi Mumbai.
+Here's what a customer would notice today:
+• The pages look dated and thin — visitors don't get enough proof to call
+• Cruise booking is enquiry-led not instant book
+• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for FloDine Cruise / Cafe Relish this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://flodine.in/home/) and a couple of things stood out:
+• The pages look dated and thin — visitors don't get enough proof to call
+• Cruise booking is enquiry-led not instant book
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for FloDine Cruise / Cafe Relish this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918369797500?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//flodine.in/home/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Cruise%20booking%20is%20enquiry-led%20not%20instant%20book%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20FloDine%20Cruise%20/%20Cafe%20Relish%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr">
         <is>
           <t>batch03_fnb_research.json</t>
         </is>
@@ -9487,11 +14593,47 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967442981?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Arise%20Gym%20Kharghar%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20structure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Arise%20Gym%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M143" s="2" t="inlineStr"/>
+          <t>Arise Gym Kharghar: I checked arisefitness.in/gym-at-kharghar</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://arisefitness.in/gym-at-kharghar/ while looking at fitness businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• Weak conversion hierarchy vs modern competitors
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Arise Gym Kharghar this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://arisefitness.in/gym-at-kharghar/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• Weak conversion hierarchy vs modern competitors
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Arise Gym Kharghar this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919967442981?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//arisefitness.in/gym-at-kharghar/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Arise%20Gym%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr">
         <is>
           <t>https://arisefitness.in/gym-at-kharghar/</t>
         </is>
@@ -9543,11 +14685,47 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919819816669?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Elements%20Dental%20Clinic%20%28Vashi%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20structure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Elements%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M144" s="2" t="inlineStr"/>
+          <t>Elements Dental Clinic: I checked elementsdentalclinic.com</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://elementsdentalclinic.com/ while looking at dental businesses in Vashi, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak conversion hierarchy vs modern competitors
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Elements Dental Clinic this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://elementsdentalclinic.com/) and a couple of things stood out:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak conversion hierarchy vs modern competitors
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Elements Dental Clinic this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919819816669?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//elementsdentalclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Elements%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr">
         <is>
           <t>https://elementsdentalclinic.com/</t>
         </is>
@@ -9599,11 +14777,47 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917506946301?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Healthcare%20Imaging%20Kharghar%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20structure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Healthcare%20Imaging%20Kharghar%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M145" s="2" t="inlineStr"/>
+          <t>Healthcare Imaging Kharghar: I checked healthcareimaging.co.in</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://healthcareimaging.co.in/ while looking at diagnostics businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• Weak conversion hierarchy vs modern competitors
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can share a free concept page for Healthcare Imaging Kharghar this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://healthcareimaging.co.in/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• Weak conversion hierarchy vs modern competitors
+Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
+I can send a free one-page concept for Healthcare Imaging Kharghar this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917506946301?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//healthcareimaging.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Healthcare%20Imaging%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
         <is>
           <t>https://healthcareimaging.co.in/</t>
         </is>
@@ -9655,11 +14869,47 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917842268427?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sunshine%20Dental%20Care%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Generic%20template%20structure%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sunshine%20Dental%20Care%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M146" s="2" t="inlineStr"/>
+          <t>Sunshine Dental Care: I checked www.sunshine-dentalcare.in</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://www.sunshine-dentalcare.in/ while looking at dental businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak conversion hierarchy vs modern competitors
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can share a free concept page for Sunshine Dental Care this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.sunshine-dentalcare.in/) and a couple of things stood out:
+• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• Weak conversion hierarchy vs modern competitors
+Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
+I can send a free one-page concept for Sunshine Dental Care this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/917842268427?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.sunshine-dentalcare.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sunshine%20Dental%20Care%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr">
         <is>
           <t>https://www.sunshine-dentalcare.in/</t>
         </is>
@@ -9711,11 +14961,45 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919699999081?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Namastey%20Salon%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Broken%20counters%20showing%200%20for%20years/branches/reviews%2C%20%27Lorem%20ipsum%27%20in%20Client%20Speaks%2C%20no%20online%20booking%2C%20franchise%20CTA%20without%20contact%20clarity%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Namastey%20Salon%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M147" s="2" t="inlineStr"/>
+          <t>Namastey Salon: I checked namasteysalon.com</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://namasteysalon.com/ while looking at salon businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• Placeholder 'Lorem ipsum' dummy text is still visible on the site
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can share a free concept page for Namastey Salon this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://namasteysalon.com/) and a couple of things stood out:
+• Placeholder 'Lorem ipsum' dummy text is still visible on the site
+People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
+I can send a free one-page concept for Namastey Salon this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919699999081?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//namasteysalon.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Placeholder%20%27Lorem%20ipsum%27%20dummy%20text%20is%20still%20visible%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Namastey%20Salon%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr">
         <is>
           <t>https://namasteysalon.com/contact-us/</t>
         </is>
@@ -9767,11 +15051,48 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918879694359?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Link%20India%20Packers%20and%20Movers%20%28Kharghar%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20SEO-domain%20style%20URL%20%28moversandpackerskharghar.in%29%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Link%20India%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M148" s="2" t="inlineStr"/>
+          <t>Link India Packers and Movers: I checked moversandpackerskharghar.in</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://moversandpackerskharghar.in/ while looking at packers &amp; movers businesses in Kharghar, Navi Mumbai.
+Here's what a customer would notice today:
+• SEO-domain style URL (moversandpackerskharghar.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+• Generic claims (256+ branches) hard to verify from site
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Link India Packers and Movers this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://moversandpackerskharghar.in/) and a couple of things stood out:
+• SEO-domain style URL (moversandpackerskharghar.in)
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Link India Packers and Movers this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918879694359?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//moversandpackerskharghar.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20SEO-domain%20style%20URL%20%28moversandpackerskharghar.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Link%20India%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
         <is>
           <t>https://moversandpackerskharghar.in/</t>
         </is>
@@ -9823,11 +15144,45 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919222223532?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Tricity%20Realty%20/%20Ganesh%20Real%20Estates%20%28Seawoods%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Dated%20HTML%20property%20pages%2C%20typos%20%28%27Ganesh%20Real%20Esates%27%29%2C%20sparse%20listing%20cards%2C%20phone-only%20contact%2C%20no%20structured%20enquiry%20CRM%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Tricity%20Realty%20/%20Ganesh%20Real%20Estates%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M149" s="2" t="inlineStr"/>
+          <t>Tricity Realty / Ganesh Real Estates: I checked ganeshrealestates.com</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://ganeshrealestates.com/ while looking at real estate broker businesses in Seawoods, Navi Mumbai.
+Here's what a customer would notice today:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can share a free concept page for Tricity Realty / Ganesh Real Estates this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ganeshrealestates.com/) and a couple of things stood out:
+• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
+I can send a free one-page concept for Tricity Realty / Ganesh Real Estates this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919222223532?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ganeshrealestates.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Tricity%20Realty%20/%20Ganesh%20Real%20Estates%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr">
         <is>
           <t>https://ganeshrealestates.com/tricity-realty.html</t>
         </is>
@@ -9879,11 +15234,48 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918877557773?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Sagar%20Palace%20%28New%20Panvel%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20Basic%20banquet%20brochure%20site%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Sagar%20Palace%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M150" s="2" t="inlineStr"/>
+          <t>Sagar Palace: I checked www.sagarpalace.com</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I opened https://www.sagarpalace.com/ while looking at banquet businesses in New Panvel, Navi Mumbai.
+Here's what a customer would notice today:
+• The site looks like a generic template rather than your brand
+• The pages look dated and thin — visitors don't get enough proof to call
+• Weak package/CTA hierarchy
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can share a free concept page for Sagar Palace this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.sagarpalace.com/) and a couple of things stood out:
+• The site looks like a generic template rather than your brand
+• The pages look dated and thin — visitors don't get enough proof to call
+Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
+I can send a free one-page concept for Sagar Palace this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918877557773?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.sagarpalace.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sagar%20Palace%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr">
         <is>
           <t>https://www.sagarpalace.com/</t>
         </is>
@@ -9935,11 +15327,47 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919167828676?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Cafe%20G%20G%20%28Kamothe%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20No%20owned%20website%20%E2%80%94%20only%20Zomato/Swiggy/ConnectTo%20directory%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Cafe%20G%20G%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M151" s="2" t="inlineStr"/>
+          <t>Cafe G G: no website of your own yet</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I searched for Cafe G G in Kamothe, Navi Mumbai — there's no owned website, only listings.
+Here's what a customer would notice today:
+• You don't have your own website — people only find you on Zomato/Swiggy/Google, so they order there instead of from you
+• Offers free home delivery by phone with no branded order path
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Cafe G G this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I searched for Cafe G G online and a couple of things stood out:
+• You don't have your own website — people only find you on Zomato/Swiggy/Google, so they order there instead of from you
+• Offers free home delivery by phone with no branded order path
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Cafe G G this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/919167828676?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20searched%20for%20Cafe%20G%20G%20online%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20You%20don%27t%20have%20your%20own%20website%20%E2%80%94%20people%20only%20find%20you%20on%20Zomato/Swiggy/Google%2C%20so%20they%20order%20there%20instead%20of%20from%20you%0A%E2%80%A2%20Offers%20free%20home%20delivery%20by%20phone%20with%20no%20branded%20order%20path%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Cafe%20G%20G%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr">
         <is>
           <t>https://www.connectto.in/business/cafe-gg-kamothe-navi-mumbai</t>
         </is>
@@ -9991,11 +15419,47 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918928666902?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20reviewed%20Communion%20Cafe%20%28CBD%20Belapur%2C%20Navi%20Mumbai%29%20and%20noticed%3A%20No%20owned%20website%20%E2%80%94%20only%20Zomato/Swiggy/District/Instagram%0A%0AI%20can%20share%20a%20free%20one-page%20redesign%20/%20ordering%20concept%20for%20Communion%20Cafe%20this%20week%20%E2%80%94%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
-        </is>
-      </c>
-      <c r="M152" s="2" t="inlineStr"/>
+          <t>Communion Cafe: no website of your own yet</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I searched for Communion Cafe in CBD Belapur, Navi Mumbai — there's no owned website, only listings.
+Here's what a customer would notice today:
+• You don't have your own website — people only find you on Zomato/Swiggy/Google, so they order there instead of from you
+• Premium community cafe with media buzz but no brand site for bookings/events
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can share a free concept page for Communion Cafe this week so it's clear what I'd change — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
       <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio. I searched for Communion Cafe online and a couple of things stood out:
+• You don't have your own website — people only find you on Zomato/Swiggy/Google, so they order there instead of from you
+• Premium community cafe with media buzz but no brand site for bookings/events
+Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
+I can send a free one-page concept for Communion Cafe this week so you can see the difference — no charge, no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>https://wa.me/918928666902?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20searched%20for%20Communion%20Cafe%20online%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20You%20don%27t%20have%20your%20own%20website%20%E2%80%94%20people%20only%20find%20you%20on%20Zomato/Swiggy/Google%2C%20so%20they%20order%20there%20instead%20of%20from%20you%0A%E2%80%A2%20Premium%20community%20cafe%20with%20media%20buzz%20but%20no%20brand%20site%20for%20bookings/events%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Communion%20Cafe%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr">
         <is>
           <t>public listings</t>
         </is>

--- a/leads/Genuine_NM_100_Clients.xlsx
+++ b/leads/Genuine_NM_100_Clients.xlsx
@@ -589,20 +589,20 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Harshis: I checked harshis.in</t>
+          <t>A quick, polite note on harshis.in</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Dear Renu,
-I opened https://harshis.in/ while looking at bakery businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• Your website sometimes opens an error page (I got a 500) instead of your homepage
-• Leftover template / fake contact details are still showing on the site — not your real number or email
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Harshis this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at bakery businesses in Kharghar, Navi Mumbai, I visited https://harshis.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• On one visit the homepage showed an error instead of opening normally (this can happen if the server is overloaded)
+• A leftover template contact still appears on the site (not your real number/email) — worth swapping for yours
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Harshis this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -613,11 +613,11 @@
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Hi Renu,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://harshis.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• Your website sometimes opens an error page (I got a 500) instead of your homepage
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Harshis this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Harshis and had a look at https://harshis.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• On one visit the homepage showed an error instead of opening normally (this can happen if the server is overloaded)
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Harshis this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -626,12 +626,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918779385489?text=Hi%20Renu%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//harshis.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Harshis%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918779385489?text=Hi%20Renu%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Harshis%20and%20had%20a%20look%20at%20https%3A//harshis.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20On%20one%20visit%20the%20homepage%20showed%20an%20error%20instead%20of%20opening%20normally%20%28this%20can%20happen%20if%20the%20server%20is%20overloaded%29%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Harshis%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>mailto:renugujari@gmail.com?subject=Harshis%3A%20I%20checked%20harshis.in&amp;body=Dear%20Renu%2C%0A%0AI%20opened%20https%3A//harshis.in/%20while%20looking%20at%20bakery%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20Leftover%20template%20/%20fake%20contact%20details%20are%20still%20showing%20on%20the%20site%20%E2%80%94%20not%20your%20real%20number%20or%20email%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Harshis%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:renugujari@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20harshis.in&amp;body=Dear%20Renu%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20bakery%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//harshis.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20On%20one%20visit%20the%20homepage%20showed%20an%20error%20instead%20of%20opening%20normally%20%28this%20can%20happen%20if%20the%20server%20is%20overloaded%29%0A%E2%80%A2%20A%20leftover%20template%20contact%20still%20appears%20on%20the%20site%20%28not%20your%20real%20number/email%29%20%E2%80%94%20worth%20swapping%20for%20yours%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Harshis%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -694,20 +694,20 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Pacific Diagnostics &amp; Multispeciality Dental Clinic: I checked pacificddk.com</t>
+          <t>A quick, polite note on pacificddk.com</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Dear Nikhil,
-I opened https://pacificddk.com/ while looking at dental businesses in Panvel, Navi Mumbai.
-Here's what a customer would notice today:
-• The copyright year on the site is old, so it looks abandoned
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Pacific Diagnostics &amp; Multispeciality Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Panvel, Navi Mumbai, I visited https://pacificddk.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Pacific Diagnostics &amp; Multispeciality Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -718,11 +718,11 @@
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Hi Nikhil,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pacificddk.com/) and a couple of things stood out:
-• The copyright year on the site is old, so it looks abandoned
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Pacific Diagnostics &amp; Multispeciality Dental Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Pacific Diagnostics &amp; Multispeciality Dental Clinic and had a look at https://pacificddk.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Pacific Diagnostics &amp; Multispeciality Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -731,12 +731,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917738334040?text=Hi%20Nikhil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pacificddk.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917738334040?text=Hi%20Nikhil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//pacificddk.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>mailto:pacificddk@gmail.com?subject=Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%3A%20I%20checked%20pacificddk.com&amp;body=Dear%20Nikhil%2C%0A%0AI%20opened%20https%3A//pacificddk.com/%20while%20looking%20at%20dental%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:pacificddk@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20pacificddk.com&amp;body=Dear%20Nikhil%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//pacificddk.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Pacific%20Diagnostics%20%26%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -799,20 +799,20 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Sparsh Superspeciality Hospital: I checked sparshhospital.in</t>
+          <t>A quick, polite note on sparshhospital.in</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Dear Rohit,
-I opened https://sparshhospital.in/ while looking at healthcare businesses in Panvel, Navi Mumbai.
-Here's what a customer would notice today:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• There are typos on the homepage (e.g. 'Confortable care') that look unprofessional
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Sparsh Superspeciality Hospital this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Panvel, Navi Mumbai, I visited https://sparshhospital.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• A couple of small spelling slips on the homepage (e.g. 'Confortable care') — easy to fix, and it helps first impressions
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Sparsh Superspeciality Hospital this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -823,11 +823,11 @@
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Hi Rohit,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sparshhospital.in/) and a couple of things stood out:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• There are typos on the homepage (e.g. 'Confortable care') that look unprofessional
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Sparsh Superspeciality Hospital this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Sparsh Superspeciality Hospital and had a look at https://sparshhospital.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• A couple of small spelling slips on the homepage (e.g. 'Confortable care') — easy to fix, and it helps first impressions
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Sparsh Superspeciality Hospital this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -836,12 +836,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919022759022?text=Hi%20Rohit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sparshhospital.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Confortable%20care%27%29%20that%20look%20unprofessional%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sparsh%20Superspeciality%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919022759022?text=Hi%20Rohit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sparsh%20Superspeciality%20Hospital%20and%20had%20a%20look%20at%20https%3A//sparshhospital.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Confortable%20care%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sparsh%20Superspeciality%20Hospital%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>mailto:sparsh.tpa@gmail.com?subject=Sparsh%20Superspeciality%20Hospital%3A%20I%20checked%20sparshhospital.in&amp;body=Dear%20Rohit%2C%0A%0AI%20opened%20https%3A//sparshhospital.in/%20while%20looking%20at%20healthcare%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Confortable%20care%27%29%20that%20look%20unprofessional%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sparsh%20Superspeciality%20Hospital%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sparsh.tpa@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20sparshhospital.in&amp;body=Dear%20Rohit%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//sparshhospital.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Confortable%20care%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Sparsh%20Superspeciality%20Hospital%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -904,20 +904,20 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Dr. Jagruti Skin and Hair Clinic: I checked drjagrutiskinclinic.com</t>
+          <t>A quick, polite note on drjagrutiskinclinic.com</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Dear Jagruti,
-I opened https://drjagrutiskinclinic.com/ while looking at healthcare businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Vashi, Navi Mumbai, I visited https://drjagrutiskinclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Two-location footer dilutes local Vashi focus
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr. Jagruti Skin and Hair Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr. Jagruti Skin and Hair Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -928,11 +928,11 @@
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Hi Jagruti,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drjagrutiskinclinic.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The site looks like a generic template rather than your brand
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr. Jagruti Skin and Hair Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Jagruti Skin and Hair Clinic and had a look at https://drjagrutiskinclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr. Jagruti Skin and Hair Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -941,12 +941,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917021761628?text=Hi%20Jagruti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drjagrutiskinclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917021761628?text=Hi%20Jagruti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20and%20had%20a%20look%20at%20https%3A//drjagrutiskinclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>mailto:drjagruti97@gmail.com?subject=Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%3A%20I%20checked%20drjagrutiskinclinic.com&amp;body=Dear%20Jagruti%2C%0A%0AI%20opened%20https%3A//drjagrutiskinclinic.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Two-location%20footer%20dilutes%20local%20Vashi%20focus%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:drjagruti97@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20drjagrutiskinclinic.com&amp;body=Dear%20Jagruti%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//drjagrutiskinclinic.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Two-location%20footer%20dilutes%20local%20Vashi%20focus%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Jagruti%20Skin%20and%20Hair%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1009,20 +1009,20 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Dr. Jairaj's Hospital: I checked drjairajshospital.com</t>
+          <t>A quick, polite note on drjairajshospital.com</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Dear Jatin,
-I opened https://drjairajshospital.com/ while looking at healthcare businesses in CBD Belapur, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in CBD Belapur, Navi Mumbai, I visited https://drjairajshospital.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Limited doctor detail
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr. Jairaj's Hospital this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr. Jairaj's Hospital this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1033,11 +1033,11 @@
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Hi Jatin,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drjairajshospital.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr. Jairaj's Hospital this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Jairaj's Hospital and had a look at https://drjairajshospital.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr. Jairaj's Hospital this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1046,12 +1046,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917045011188?text=Hi%20Jatin%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drjairajshospital.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jairaj%27s%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917045011188?text=Hi%20Jatin%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Jairaj%27s%20Hospital%20and%20had%20a%20look%20at%20https%3A//drjairajshospital.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jairaj%27s%20Hospital%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>mailto:jairajhospital@gmail.com?subject=Dr.%20Jairaj%27s%20Hospital%3A%20I%20checked%20drjairajshospital.com&amp;body=Dear%20Jatin%2C%0A%0AI%20opened%20https%3A//drjairajshospital.com/%20while%20looking%20at%20healthcare%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Limited%20doctor%20detail%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Jairaj%27s%20Hospital%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:jairajhospital@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20drjairajshospital.com&amp;body=Dear%20Jatin%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//drjairajshospital.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20Limited%20doctor%20detail%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Jairaj%27s%20Hospital%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Rita's Beauty Hub: I checked www.ritasbeautyhub.in</t>
+          <t>A quick, polite note on www.ritasbeautyhub.in</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Dear Rita,
-I opened https://www.ritasbeautyhub.in/ while looking at salon businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Kharghar, Navi Mumbai, I visited https://www.ritasbeautyhub.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • Old static multi-page HTML
 • Heavy keyword stuffing in title
-• There are typos on the homepage (e.g. 'Amonymous') that look unprofessional
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Rita's Beauty Hub this week so it's clear what I'd change — no obligation.
-Regards,
+• A couple of small spelling slips on the homepage (e.g. 'Amonymous') — easy to fix, and it helps first impressions
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Rita's Beauty Hub this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1138,11 +1138,11 @@
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Hi Rita,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.ritasbeautyhub.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Rita's Beauty Hub and had a look at https://www.ritasbeautyhub.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Old static multi-page HTML
 • Heavy keyword stuffing in title
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Rita's Beauty Hub this week so you can see the difference — no charge, no obligation.
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Rita's Beauty Hub this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1151,12 +1151,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918850610990?text=Hi%20Rita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.ritasbeautyhub.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Old%20static%20multi-page%20HTML%0A%E2%80%A2%20Heavy%20keyword%20stuffing%20in%20title%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Rita%27s%20Beauty%20Hub%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918850610990?text=Hi%20Rita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Rita%27s%20Beauty%20Hub%20and%20had%20a%20look%20at%20https%3A//www.ritasbeautyhub.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Old%20static%20multi-page%20HTML%0A%E2%80%A2%20Heavy%20keyword%20stuffing%20in%20title%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Rita%27s%20Beauty%20Hub%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>mailto:ritasbeautyhub@gmail.com?subject=Rita%27s%20Beauty%20Hub%3A%20I%20checked%20www.ritasbeautyhub.in&amp;body=Dear%20Rita%2C%0A%0AI%20opened%20https%3A//www.ritasbeautyhub.in/%20while%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Old%20static%20multi-page%20HTML%0A%E2%80%A2%20Heavy%20keyword%20stuffing%20in%20title%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Amonymous%27%29%20that%20look%20unprofessional%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Rita%27s%20Beauty%20Hub%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:ritasbeautyhub@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.ritasbeautyhub.in&amp;body=Dear%20Rita%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.ritasbeautyhub.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Old%20static%20multi-page%20HTML%0A%E2%80%A2%20Heavy%20keyword%20stuffing%20in%20title%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Amonymous%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Rita%27s%20Beauty%20Hub%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1215,20 +1215,20 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Sasane Dental Clinic: I checked sasanedental.com</t>
+          <t>A quick, polite note on sasanedental.com</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Dear Rutuparn,
-I opened https://sasanedental.com/ while looking at dental businesses in Panvel.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Panvel, I visited https://sasanedental.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
 • Dual-brand (Tooth Legacy) messaging can confuse
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Sasane Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Sasane Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1239,11 +1239,11 @@
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Hi Rutuparn,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sasanedental.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Sasane Dental Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Sasane Dental Clinic and had a look at https://sasanedental.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Sasane Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1252,12 +1252,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967661337?text=Hi%20Rutuparn%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sasanedental.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sasane%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919967661337?text=Hi%20Rutuparn%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sasane%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//sasanedental.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sasane%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>mailto:sasanedentalclinic@gmail.com?subject=Sasane%20Dental%20Clinic%3A%20I%20checked%20sasanedental.com&amp;body=Dear%20Rutuparn%2C%0A%0AI%20opened%20https%3A//sasanedental.com/%20while%20looking%20at%20dental%20businesses%20in%20Panvel.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20Dual-brand%20%28Tooth%20Legacy%29%20messaging%20can%20confuse%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sasane%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sasanedentalclinic@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20sasanedental.com&amp;body=Dear%20Rutuparn%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Panvel%2C%20I%20visited%20https%3A//sasanedental.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20Dual-brand%20%28Tooth%20Legacy%29%20messaging%20can%20confuse%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Sasane%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1316,20 +1316,20 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Dentkraft Dental Clinics: I checked dentkraftdentalclinics.com</t>
+          <t>A quick, polite note on dentkraftdentalclinics.com</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Dear Harshil,
-I opened https://dentkraftdentalclinics.com/ while looking at dental businesses in Kharghar.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Dentkraft Dental Clinics this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, I visited https://dentkraftdentalclinics.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Dentkraft Dental Clinics this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1340,11 +1340,11 @@
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Hi Harshil,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://dentkraftdentalclinics.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Dentkraft Dental Clinics this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dentkraft Dental Clinics and had a look at https://dentkraftdentalclinics.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Dentkraft Dental Clinics this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1353,12 +1353,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004120002?text=Hi%20Harshil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//dentkraftdentalclinics.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dentkraft%20Dental%20Clinics%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919004120002?text=Hi%20Harshil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dentkraft%20Dental%20Clinics%20and%20had%20a%20look%20at%20https%3A//dentkraftdentalclinics.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dentkraft%20Dental%20Clinics%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>mailto:dr.harshil@gmail.com?subject=Dentkraft%20Dental%20Clinics%3A%20I%20checked%20dentkraftdentalclinics.com&amp;body=Dear%20Harshil%2C%0A%0AI%20opened%20https%3A//dentkraftdentalclinics.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dentkraft%20Dental%20Clinics%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:dr.harshil@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20dentkraftdentalclinics.com&amp;body=Dear%20Harshil%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20I%20visited%20https%3A//dentkraftdentalclinics.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dentkraft%20Dental%20Clinics%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Dr. Bhandari's Dental Clinic &amp; Implant Centre: I checked drgbdentalclinic.com</t>
+          <t>A quick, polite note on drgbdentalclinic.com</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Dear Ganesh,
-I opened https://drgbdentalclinic.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, Navi Mumbai, I visited https://drgbdentalclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Contact form requires JavaScript and looks incomplete
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Dr. Bhandari's Dental Clinic &amp; Implant Centre this week so it's clear what I'd change — no obligation.
-Regards,
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Dr. Bhandari's Dental Clinic &amp; Implant Centre this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1445,11 +1445,11 @@
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Hi Ganesh,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drgbdentalclinic.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Bhandari's Dental Clinic &amp; Implant Centre and had a look at https://drgbdentalclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Contact form requires JavaScript and looks incomplete
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Dr. Bhandari's Dental Clinic &amp; Implant Centre this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Dr. Bhandari's Dental Clinic &amp; Implant Centre this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918108973790?text=Hi%20Ganesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drgbdentalclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Contact%20form%20requires%20JavaScript%20and%20looks%20incomplete%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918108973790?text=Hi%20Ganesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20and%20had%20a%20look%20at%20https%3A//drgbdentalclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Contact%20form%20requires%20JavaScript%20and%20looks%20incomplete%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>mailto:drbhandarisdentalclinic@gmail.com?subject=Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%3A%20I%20checked%20drgbdentalclinic.com&amp;body=Dear%20Ganesh%2C%0A%0AI%20opened%20https%3A//drgbdentalclinic.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Contact%20form%20requires%20JavaScript%20and%20looks%20incomplete%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:drbhandarisdentalclinic@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20drgbdentalclinic.com&amp;body=Dear%20Ganesh%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//drgbdentalclinic.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Contact%20form%20requires%20JavaScript%20and%20looks%20incomplete%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Bhandari%27s%20Dental%20Clinic%20%26%20Implant%20Centre%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Orosmyle Dental Clinic: I checked orosmyle.com</t>
+          <t>A quick, polite note on orosmyle.com</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Dear Amit,
-I opened https://orosmyle.com/ while looking at dental businesses in Kamothe.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Orosmyle Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kamothe, I visited https://orosmyle.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Orosmyle Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1546,11 +1546,11 @@
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Hi Amit,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://orosmyle.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Orosmyle Dental Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Orosmyle Dental Clinic and had a look at https://orosmyle.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Orosmyle Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1559,12 +1559,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919892850651?text=Hi%20Amit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//orosmyle.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Orosmyle%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919892850651?text=Hi%20Amit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Orosmyle%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//orosmyle.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Orosmyle%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>mailto:orosmyle@gmail.com?subject=Orosmyle%20Dental%20Clinic%3A%20I%20checked%20orosmyle.com&amp;body=Dear%20Amit%2C%0A%0AI%20opened%20https%3A//orosmyle.com/%20while%20looking%20at%20dental%20businesses%20in%20Kamothe.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Orosmyle%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:orosmyle@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20orosmyle.com&amp;body=Dear%20Amit%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kamothe%2C%20I%20visited%20https%3A//orosmyle.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Orosmyle%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1623,20 +1623,20 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Ratnakokan Restaurant: I checked ratnakokan.com</t>
+          <t>A quick, polite note on ratnakokan.com</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Dear Sanjay,
-I opened https://ratnakokan.com/ while looking at restaurant businesses in Sanpada, Navi Mumbai.
-Here's what a customer would notice today:
-• The pages look dated and thin — visitors don't get enough proof to call
-• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at restaurant businesses in Sanpada, Navi Mumbai, I visited https://ratnakokan.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+• There's no easy online order yet — a simple menu/checkout often keeps people from switching to Swiggy/Zomato
 • Multi-branch phones listed but weak conversion CTAs
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Ratnakokan Restaurant this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Ratnakokan Restaurant this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1647,11 +1647,11 @@
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Hi Sanjay,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ratnakokan.com/) and a couple of things stood out:
-• The pages look dated and thin — visitors don't get enough proof to call
-• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Ratnakokan Restaurant this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Ratnakokan Restaurant and had a look at https://ratnakokan.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+• There's no easy online order yet — a simple menu/checkout often keeps people from switching to Swiggy/Zomato
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Ratnakokan Restaurant this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1660,12 +1660,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917045859333?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ratnakokan.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ratnakokan%20Restaurant%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917045859333?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Ratnakokan%20Restaurant%20and%20had%20a%20look%20at%20https%3A//ratnakokan.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20There%27s%20no%20easy%20online%20order%20yet%20%E2%80%94%20a%20simple%20menu/checkout%20often%20keeps%20people%20from%20switching%20to%20Swiggy/Zomato%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Ratnakokan%20Restaurant%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>mailto:mail@ratnakokan.com?subject=Ratnakokan%20Restaurant%3A%20I%20checked%20ratnakokan.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20opened%20https%3A//ratnakokan.com/%20while%20looking%20at%20restaurant%20businesses%20in%20Sanpada%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%E2%80%A2%20Multi-branch%20phones%20listed%20but%20weak%20conversion%20CTAs%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Ratnakokan%20Restaurant%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:mail@ratnakokan.com?subject=A%20quick%2C%20polite%20note%20on%20ratnakokan.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20restaurant%20businesses%20in%20Sanpada%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//ratnakokan.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20There%27s%20no%20easy%20online%20order%20yet%20%E2%80%94%20a%20simple%20menu/checkout%20often%20keeps%20people%20from%20switching%20to%20Swiggy/Zomato%0A%E2%80%A2%20Multi-branch%20phones%20listed%20but%20weak%20conversion%20CTAs%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Ratnakokan%20Restaurant%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1724,20 +1724,20 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Sasane Dental / Tooth Legacy Dental &amp; Implant Center: I checked sasanedental.com/contact-us</t>
+          <t>A quick, polite note on sasanedental.com/contact-us</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Dear Rutuparn,
-I opened https://sasanedental.com/contact-us/ while looking at dental businesses in Panvel.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Panvel, I visited https://sasanedental.com/contact-us/.
+I wanted to share a few small observations, only in case they're helpful:
 • New Panvel brand nested under Old Panvel site
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Dual-location confusion
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Sasane Dental / Tooth Legacy Dental &amp; Implant Center this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Sasane Dental / Tooth Legacy Dental &amp; Implant Center this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1748,11 +1748,11 @@
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Hi Rutuparn,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sasanedental.com/contact-us/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Sasane Dental / Tooth Legacy Dental &amp; Implant Center and had a look at https://sasanedental.com/contact-us/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • New Panvel brand nested under Old Panvel site
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Sasane Dental / Tooth Legacy Dental &amp; Implant Center this week so you can see the difference — no charge, no obligation.
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Sasane Dental / Tooth Legacy Dental &amp; Implant Center this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1761,12 +1761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919021621337?text=Hi%20Rutuparn%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sasanedental.com/contact-us/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20New%20Panvel%20brand%20nested%20under%20Old%20Panvel%20site%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919021621337?text=Hi%20Rutuparn%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20and%20had%20a%20look%20at%20https%3A//sasanedental.com/contact-us/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20New%20Panvel%20brand%20nested%20under%20Old%20Panvel%20site%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>mailto:sasanedentalclinic@gmail.com?subject=Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%3A%20I%20checked%20sasanedental.com/contact-us&amp;body=Dear%20Rutuparn%2C%0A%0AI%20opened%20https%3A//sasanedental.com/contact-us/%20while%20looking%20at%20dental%20businesses%20in%20Panvel.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20New%20Panvel%20brand%20nested%20under%20Old%20Panvel%20site%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Dual-location%20confusion%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sasanedentalclinic@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20sasanedental.com/contact-us&amp;body=Dear%20Rutuparn%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Panvel%2C%20I%20visited%20https%3A//sasanedental.com/contact-us/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20New%20Panvel%20brand%20nested%20under%20Old%20Panvel%20site%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Dual-location%20confusion%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Sasane%20Dental%20/%20Tooth%20Legacy%20Dental%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,20 +1825,20 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Smile Please Super Speciality Dental Clinic (Nerul): I checked www.smiileplease.com/nerulbranch</t>
+          <t>A quick, polite note on www.smiileplease.com/nerulbranch</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Dear Sharad,
-I opened https://www.smiileplease.com/nerulbranch/ while looking at dental businesses in Nerul.
-Here's what a customer would notice today:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Smile Please Super Speciality Dental Clinic (Nerul) this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Nerul, I visited https://www.smiileplease.com/nerulbranch/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Smile Please Super Speciality Dental Clinic (Nerul) this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1849,11 +1849,11 @@
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Hi Sharad,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smiileplease.com/nerulbranch/) and a couple of things stood out:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Smile Please Super Speciality Dental Clinic (Nerul) this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Smile Please Super Speciality Dental Clinic (Nerul) and had a look at https://www.smiileplease.com/nerulbranch/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Smile Please Super Speciality Dental Clinic (Nerul) this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1862,12 +1862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137208535?text=Hi%20Sharad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smiileplease.com/nerulbranch/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919137208535?text=Hi%20Sharad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20and%20had%20a%20look%20at%20https%3A//www.smiileplease.com/nerulbranch/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>mailto:shharrad@gmail.com?subject=Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%3A%20I%20checked%20www.smiileplease.com/nerulbranch&amp;body=Dear%20Sharad%2C%0A%0AI%20opened%20https%3A//www.smiileplease.com/nerulbranch/%20while%20looking%20at%20dental%20businesses%20in%20Nerul.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:shharrad@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.smiileplease.com/nerulbranch&amp;body=Dear%20Sharad%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Nerul%2C%20I%20visited%20https%3A//www.smiileplease.com/nerulbranch/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Please%20Super%20Speciality%20Dental%20Clinic%20%28Nerul%29%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,18 +1930,18 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Yash A. Jain &amp; Associates: I checked www.cayashjain.com</t>
+          <t>A quick, polite note on www.cayashjain.com</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
           <t>Dear Yash,
-I opened https://www.cayashjain.com/ while looking at ca firm businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
-I can share a free concept page for Yash A. Jain &amp; Associates this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at ca firm businesses in Vashi, Navi Mumbai, I visited https://www.cayashjain.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+People who find you on Google usually decide in a few seconds whether to enquire. A clearer next step on the site often helps.
+If you'd like, I can share a free concept page for Yash A. Jain &amp; Associates this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -1952,10 +1952,10 @@
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Hi Yash,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.cayashjain.com/) and a couple of things stood out:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
-I can send a free one-page concept for Yash A. Jain &amp; Associates this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Yash A. Jain &amp; Associates and had a look at https://www.cayashjain.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+People who find you on Google usually decide in a few seconds whether to enquire. A clearer next step on the site often helps.
+If it would help, I can send a free one-page concept for Yash A. Jain &amp; Associates this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -1964,12 +1964,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967044547?text=Hi%20Yash%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.cayashjain.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Yash%20A.%20Jain%20%26%20Associates%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919967044547?text=Hi%20Yash%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Yash%20A.%20Jain%20%26%20Associates%20and%20had%20a%20look%20at%20https%3A//www.cayashjain.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APeople%20who%20find%20you%20on%20Google%20usually%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20A%20clearer%20next%20step%20on%20the%20site%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Yash%20A.%20Jain%20%26%20Associates%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>mailto:yjassociates12@gmail.com?subject=Yash%20A.%20Jain%20%26%20Associates%3A%20I%20checked%20www.cayashjain.com&amp;body=Dear%20Yash%2C%0A%0AI%20opened%20https%3A//www.cayashjain.com/%20while%20looking%20at%20ca%20firm%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Yash%20A.%20Jain%20%26%20Associates%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:yjassociates12@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.cayashjain.com&amp;body=Dear%20Yash%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20ca%20firm%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.cayashjain.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APeople%20who%20find%20you%20on%20Google%20usually%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20A%20clearer%20next%20step%20on%20the%20site%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Yash%20A.%20Jain%20%26%20Associates%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2028,20 +2028,20 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>ALLDENT Dental Clinic: I checked www.alldentcliniculwe.com</t>
+          <t>A quick, polite note on www.alldentcliniculwe.com</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Dear Monika,
-I opened https://www.alldentcliniculwe.com/ while looking at dental businesses in Ulwe.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The phone number is missing from the homepage — people can't call you from the first screen
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for ALLDENT Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Ulwe, I visited https://www.alldentcliniculwe.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The phone number isn't easy to spot on the first screen — putting it in the header usually helps
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for ALLDENT Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2052,11 +2052,11 @@
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Hi Monika,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.alldentcliniculwe.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The phone number is missing from the homepage — people can't call you from the first screen
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for ALLDENT Dental Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across ALLDENT Dental Clinic and had a look at https://www.alldentcliniculwe.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The phone number isn't easy to spot on the first screen — putting it in the header usually helps
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for ALLDENT Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2065,12 +2065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917304577281?text=Hi%20Monika%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.alldentcliniculwe.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20ALLDENT%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917304577281?text=Hi%20Monika%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20ALLDENT%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.alldentcliniculwe.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20phone%20number%20isn%27t%20easy%20to%20spot%20on%20the%20first%20screen%20%E2%80%94%20putting%20it%20in%20the%20header%20usually%20helps%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20ALLDENT%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>mailto:alldentulwe@gmail.com?subject=ALLDENT%20Dental%20Clinic%3A%20I%20checked%20www.alldentcliniculwe.com&amp;body=Dear%20Monika%2C%0A%0AI%20opened%20https%3A//www.alldentcliniculwe.com/%20while%20looking%20at%20dental%20businesses%20in%20Ulwe.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20ALLDENT%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:alldentulwe@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.alldentcliniculwe.com&amp;body=Dear%20Monika%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Ulwe%2C%20I%20visited%20https%3A//www.alldentcliniculwe.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20phone%20number%20isn%27t%20easy%20to%20spot%20on%20the%20first%20screen%20%E2%80%94%20putting%20it%20in%20the%20header%20usually%20helps%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20ALLDENT%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2133,19 +2133,19 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Avneesh Diagnostics &amp; Healthcare: I checked avneeshdiagnostics.com</t>
+          <t>A quick, polite note on avneeshdiagnostics.com</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Dear Sanjay,
-I opened https://avneeshdiagnostics.com/ while looking at diagnostics businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Avneesh Diagnostics &amp; Healthcare this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at diagnostics businesses in Kharghar, Navi Mumbai, I visited https://avneeshdiagnostics.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Avneesh Diagnostics &amp; Healthcare this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2156,11 +2156,11 @@
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Hi Sanjay,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://avneeshdiagnostics.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Avneesh Diagnostics &amp; Healthcare this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Avneesh Diagnostics &amp; Healthcare and had a look at https://avneeshdiagnostics.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Avneesh Diagnostics &amp; Healthcare this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2169,12 +2169,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917715888551?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//avneeshdiagnostics.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Avneesh%20Diagnostics%20%26%20Healthcare%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917715888551?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Avneesh%20Diagnostics%20%26%20Healthcare%20and%20had%20a%20look%20at%20https%3A//avneeshdiagnostics.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Avneesh%20Diagnostics%20%26%20Healthcare%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@avneeshdiagnostics.com?subject=Avneesh%20Diagnostics%20%26%20Healthcare%3A%20I%20checked%20avneeshdiagnostics.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20opened%20https%3A//avneeshdiagnostics.com/%20while%20looking%20at%20diagnostics%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Avneesh%20Diagnostics%20%26%20Healthcare%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@avneeshdiagnostics.com?subject=A%20quick%2C%20polite%20note%20on%20avneeshdiagnostics.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20diagnostics%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//avneeshdiagnostics.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Avneesh%20Diagnostics%20%26%20Healthcare%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2237,20 +2237,20 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>CoreGym Kharghar: I checked coregym.co.in/home</t>
+          <t>A quick, polite note on coregym.co.in/home</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Dear Govind,
-I opened https://coregym.co.in/home while looking at fitness businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The copyright year on the site is old, so it looks abandoned
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for CoreGym Kharghar this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at fitness businesses in Kharghar, Navi Mumbai, I visited https://coregym.co.in/home.
+I wanted to share a few small observations, only in case they're helpful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for CoreGym Kharghar this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2261,11 +2261,11 @@
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Hi Govind,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://coregym.co.in/home) and a couple of things stood out:
-• The copyright year on the site is old, so it looks abandoned
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for CoreGym Kharghar this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across CoreGym Kharghar and had a look at https://coregym.co.in/home. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for CoreGym Kharghar this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2274,12 +2274,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918433589999?text=Hi%20Govind%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//coregym.co.in/home%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20CoreGym%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918433589999?text=Hi%20Govind%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20CoreGym%20Kharghar%20and%20had%20a%20look%20at%20https%3A//coregym.co.in/home.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20CoreGym%20Kharghar%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>mailto:impallari@gmail.com?subject=CoreGym%20Kharghar%3A%20I%20checked%20coregym.co.in/home&amp;body=Dear%20Govind%2C%0A%0AI%20opened%20https%3A//coregym.co.in/home%20while%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20CoreGym%20Kharghar%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:impallari@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20coregym.co.in/home&amp;body=Dear%20Govind%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//coregym.co.in/home.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20CoreGym%20Kharghar%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2338,20 +2338,20 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Dr Belokar Dental Clinic and Implant Center: I checked drbelokars.com</t>
+          <t>A quick, polite note on drbelokars.com</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
           <t>Dear Belokar,
-I opened https://drbelokars.com/ while looking at dental businesses in Kharghar.
-Here's what a customer would notice today:
-• The copyright year on the site is old, so it looks abandoned
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, I visited https://drbelokars.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
 • Dense SEO keyword stuffing
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Dr Belokar Dental Clinic and Implant Center this week so it's clear what I'd change — no obligation.
-Regards,
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Dr Belokar Dental Clinic and Implant Center this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2362,11 +2362,11 @@
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Hi Belokar,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drbelokars.com/) and a couple of things stood out:
-• The copyright year on the site is old, so it looks abandoned
+I'm Vaibhav from DMC Creatives Studio. I came across Dr Belokar Dental Clinic and Implant Center and had a look at https://drbelokars.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
 • Dense SEO keyword stuffing
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Dr Belokar Dental Clinic and Implant Center this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Dr Belokar Dental Clinic and Implant Center this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919136298251?text=Hi%20Belokar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drbelokars.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20Dense%20SEO%20keyword%20stuffing%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919136298251?text=Hi%20Belokar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20and%20had%20a%20look%20at%20https%3A//drbelokars.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%E2%80%A2%20Dense%20SEO%20keyword%20stuffing%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>mailto:dentist@drbelokars.com?subject=Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%3A%20I%20checked%20drbelokars.com&amp;body=Dear%20Belokar%2C%0A%0AI%20opened%20https%3A//drbelokars.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20Dense%20SEO%20keyword%20stuffing%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:dentist@drbelokars.com?subject=A%20quick%2C%20polite%20note%20on%20drbelokars.com&amp;body=Dear%20Belokar%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20I%20visited%20https%3A//drbelokars.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%E2%80%A2%20Dense%20SEO%20keyword%20stuffing%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr%20Belokar%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2443,20 +2443,20 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic: I checked entvaishalisangole.com</t>
+          <t>A quick, polite note on entvaishalisangole.com</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>Dear Vaishali,
-I opened https://entvaishalisangole.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Kharghar, Navi Mumbai, I visited https://entvaishalisangole.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Copyright still shows 2023
 • Repeated generic treatment blurbs
-• There are typos on the homepage (e.g. 'Ontology Service') that look unprofessional
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+• A couple of small spelling slips on the homepage (e.g. 'Ontology Service') — easy to fix, and it helps first impressions
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2467,11 +2467,11 @@
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Hi Vaishali,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://entvaishalisangole.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic and had a look at https://entvaishalisangole.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Copyright still shows 2023
 • Repeated generic treatment blurbs
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr. Vaishali Sangole's ENT &amp; Vertigo Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2480,12 +2480,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967752407?text=Hi%20Vaishali%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//entvaishalisangole.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Copyright%20still%20shows%202023%0A%E2%80%A2%20Repeated%20generic%20treatment%20blurbs%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919967752407?text=Hi%20Vaishali%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20and%20had%20a%20look%20at%20https%3A//entvaishalisangole.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Copyright%20still%20shows%202023%0A%E2%80%A2%20Repeated%20generic%20treatment%20blurbs%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@vaishalisangole.com?subject=Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%3A%20I%20checked%20entvaishalisangole.com&amp;body=Dear%20Vaishali%2C%0A%0AI%20opened%20https%3A//entvaishalisangole.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Copyright%20still%20shows%202023%0A%E2%80%A2%20Repeated%20generic%20treatment%20blurbs%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Ontology%20Service%27%29%20that%20look%20unprofessional%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@vaishalisangole.com?subject=A%20quick%2C%20polite%20note%20on%20entvaishalisangole.com&amp;body=Dear%20Vaishali%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//entvaishalisangole.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Copyright%20still%20shows%202023%0A%E2%80%A2%20Repeated%20generic%20treatment%20blurbs%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Ontology%20Service%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Vaishali%20Sangole%27s%20ENT%20%26%20Vertigo%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2544,20 +2544,20 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Dr. Jairaj's Diagnostic Centre: I checked jairajdiagnostics.com</t>
+          <t>A quick, polite note on jairajdiagnostics.com</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened http://jairajdiagnostics.com/ while looking at diagnostics businesses in CBD Belapur / Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site still opens on HTTP (no lock/HTTPS), which browsers flag as not secure
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-• The site is hard to use on a phone — it doesn't fit the screen properly
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr. Jairaj's Diagnostic Centre this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at diagnostics businesses in CBD Belapur / Kharghar, Navi Mumbai, I visited http://jairajdiagnostics.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The site still opens without the browser lock (HTTPS). Adding it usually helps people feel safer sharing details
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+• On a phone the layout is a little tight — making it mobile-friendly usually helps a lot in Navi Mumbai
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr. Jairaj's Diagnostic Centre this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2568,11 +2568,11 @@
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (http://jairajdiagnostics.com/) and a couple of things stood out:
-• The site still opens on HTTP (no lock/HTTPS), which browsers flag as not secure
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr. Jairaj's Diagnostic Centre this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Jairaj's Diagnostic Centre and had a look at http://jairajdiagnostics.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The site still opens without the browser lock (HTTPS). Adding it usually helps people feel safer sharing details
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr. Jairaj's Diagnostic Centre this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967064548?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28http%3A//jairajdiagnostics.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20opens%20on%20HTTP%20%28no%20lock/HTTPS%29%2C%20which%20browsers%20flag%20as%20not%20secure%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jairaj%27s%20Diagnostic%20Centre%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919967064548?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Jairaj%27s%20Diagnostic%20Centre%20and%20had%20a%20look%20at%20http%3A//jairajdiagnostics.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20site%20still%20opens%20without%20the%20browser%20lock%20%28HTTPS%29.%20Adding%20it%20usually%20helps%20people%20feel%20safer%20sharing%20details%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Jairaj%27s%20Diagnostic%20Centre%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr"/>
@@ -2641,20 +2641,20 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The Dental House: I checked dentalhousemumbai.com</t>
+          <t>A quick, polite note on dentalhousemumbai.com</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Dear Harshvardhan,
-I opened https://dentalhousemumbai.com/ while looking at dental businesses in Kopar Khairane.
-Here's what a customer would notice today:
-• The copyright year on the site is old, so it looks abandoned
-• Reviews/text on the site show broken characters, so it looks unmaintained
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for The Dental House this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kopar Khairane, I visited https://dentalhousemumbai.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
+• A few reviews show broken characters; a quick text fix would make them easier to read
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for The Dental House this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2665,11 +2665,11 @@
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Hi Harshvardhan,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://dentalhousemumbai.com/) and a couple of things stood out:
-• The copyright year on the site is old, so it looks abandoned
-• Reviews/text on the site show broken characters, so it looks unmaintained
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for The Dental House this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across The Dental House and had a look at https://dentalhousemumbai.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
+• A few reviews show broken characters; a quick text fix would make them easier to read
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for The Dental House this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2678,12 +2678,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919619944888?text=Hi%20Harshvardhan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//dentalhousemumbai.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20Reviews/text%20on%20the%20site%20show%20broken%20characters%2C%20so%20it%20looks%20unmaintained%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20House%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919619944888?text=Hi%20Harshvardhan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20The%20Dental%20House%20and%20had%20a%20look%20at%20https%3A//dentalhousemumbai.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%E2%80%A2%20A%20few%20reviews%20show%20broken%20characters%3B%20a%20quick%20text%20fix%20would%20make%20them%20easier%20to%20read%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20House%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@dentalhousemumbai.com?subject=The%20Dental%20House%3A%20I%20checked%20dentalhousemumbai.com&amp;body=Dear%20Harshvardhan%2C%0A%0AI%20opened%20https%3A//dentalhousemumbai.com/%20while%20looking%20at%20dental%20businesses%20in%20Kopar%20Khairane.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%E2%80%A2%20Reviews/text%20on%20the%20site%20show%20broken%20characters%2C%20so%20it%20looks%20unmaintained%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20Dental%20House%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@dentalhousemumbai.com?subject=A%20quick%2C%20polite%20note%20on%20dentalhousemumbai.com&amp;body=Dear%20Harshvardhan%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kopar%20Khairane%2C%20I%20visited%20https%3A//dentalhousemumbai.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%E2%80%A2%20A%20few%20reviews%20show%20broken%20characters%3B%20a%20quick%20text%20fix%20would%20make%20them%20easier%20to%20read%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20The%20Dental%20House%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Travellers World: I checked travellersworld.co.in</t>
+          <t>A quick, polite note on travellersworld.co.in</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Dear Sohil,
-I opened https://travellersworld.co.in/ while looking at travel agent businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The pages look dated and thin — visitors don't get enough proof to call
-• Old offers are still live on the site (one still says valid till 2012) — it looks abandoned
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at travel agent businesses in Vashi, Navi Mumbai, I visited https://travellersworld.co.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+• An older offer is still showing (one still says valid till 2012) — updating it would make the page feel current
 • Table-based 2010s layout
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Travellers World this week so it's clear what I'd change — no obligation.
-Regards,
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Travellers World this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2770,11 +2770,11 @@
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Hi Sohil,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://travellersworld.co.in/) and a couple of things stood out:
-• The pages look dated and thin — visitors don't get enough proof to call
-• Old offers are still live on the site (one still says valid till 2012) — it looks abandoned
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Travellers World this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Travellers World and had a look at https://travellersworld.co.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+• An older offer is still showing (one still says valid till 2012) — updating it would make the page feel current
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Travellers World this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2783,12 +2783,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919323464302?text=Hi%20Sohil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//travellersworld.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Old%20offers%20are%20still%20live%20on%20the%20site%20%28one%20still%20says%20valid%20till%202012%29%20%E2%80%94%20it%20looks%20abandoned%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Travellers%20World%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919323464302?text=Hi%20Sohil%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Travellers%20World%20and%20had%20a%20look%20at%20https%3A//travellersworld.co.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20An%20older%20offer%20is%20still%20showing%20%28one%20still%20says%20valid%20till%202012%29%20%E2%80%94%20updating%20it%20would%20make%20the%20page%20feel%20current%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Travellers%20World%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>mailto:sohilthakkar123@gmail.com?subject=Travellers%20World%3A%20I%20checked%20travellersworld.co.in&amp;body=Dear%20Sohil%2C%0A%0AI%20opened%20https%3A//travellersworld.co.in/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Old%20offers%20are%20still%20live%20on%20the%20site%20%28one%20still%20says%20valid%20till%202012%29%20%E2%80%94%20it%20looks%20abandoned%0A%E2%80%A2%20Table-based%202010s%20layout%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Travellers%20World%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sohilthakkar123@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20travellersworld.co.in&amp;body=Dear%20Sohil%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//travellersworld.co.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20An%20older%20offer%20is%20still%20showing%20%28one%20still%20says%20valid%20till%202012%29%20%E2%80%94%20updating%20it%20would%20make%20the%20page%20feel%20current%0A%E2%80%A2%20Table-based%202010s%20layout%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Travellers%20World%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2851,18 +2851,18 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Pranali Bane Interior Design's: I checked pranalibaneinteriordesign.com</t>
+          <t>A quick, polite note on pranalibaneinteriordesign.com</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Dear Pranali,
-I opened https://pranalibaneinteriordesign.com/ while looking at interior design businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like SEO/template pages rather than a real project portfolio
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for Pranali Bane Interior Design's this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Kharghar, Navi Mumbai, I visited https://pranalibaneinteriordesign.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages feel a little generic; a stronger project gallery would better show your actual work
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for Pranali Bane Interior Design's this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2873,10 +2873,10 @@
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Hi Pranali,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pranalibaneinteriordesign.com/) and a couple of things stood out:
-• The site looks like SEO/template pages rather than a real project portfolio
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for Pranali Bane Interior Design's this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Pranali Bane Interior Design's and had a look at https://pranalibaneinteriordesign.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages feel a little generic; a stronger project gallery would better show your actual work
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for Pranali Bane Interior Design's this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2885,12 +2885,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591828081?text=Hi%20Pranali%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pranalibaneinteriordesign.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pranali%20Bane%20Interior%20Design%27s%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918591828081?text=Hi%20Pranali%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Pranali%20Bane%20Interior%20Design%27s%20and%20had%20a%20look%20at%20https%3A//pranalibaneinteriordesign.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20feel%20a%20little%20generic%3B%20a%20stronger%20project%20gallery%20would%20better%20show%20your%20actual%20work%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Pranali%20Bane%20Interior%20Design%27s%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>mailto:Pb.design@zohomail.in?subject=Pranali%20Bane%20Interior%20Design%27s%3A%20I%20checked%20pranalibaneinteriordesign.com&amp;body=Dear%20Pranali%2C%0A%0AI%20opened%20https%3A//pranalibaneinteriordesign.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pranali%20Bane%20Interior%20Design%27s%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:Pb.design@zohomail.in?subject=A%20quick%2C%20polite%20note%20on%20pranalibaneinteriordesign.com&amp;body=Dear%20Pranali%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//pranalibaneinteriordesign.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20pages%20feel%20a%20little%20generic%3B%20a%20stronger%20project%20gallery%20would%20better%20show%20your%20actual%20work%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Pranali%20Bane%20Interior%20Design%27s%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2953,20 +2953,20 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Ramp Salon &amp; Academy: I checked www.rampsalonandacademy.com</t>
+          <t>A quick, polite note on www.rampsalonandacademy.com</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Dear Rita,
-I opened https://www.rampsalonandacademy.com/ while looking at salon businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Kharghar, Navi Mumbai, I visited https://www.rampsalonandacademy.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • SEO-stuffed duplicate service blocks
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Hours listed oddly as Mon-Fri only while salon likely needs weekend booking clarity
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Ramp Salon &amp; Academy this week so it's clear what I'd change — no obligation.
-Regards,
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Ramp Salon &amp; Academy this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -2977,11 +2977,11 @@
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>Hi Rita,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.rampsalonandacademy.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Ramp Salon &amp; Academy and had a look at https://www.rampsalonandacademy.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • SEO-stuffed duplicate service blocks
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Ramp Salon &amp; Academy this week so you can see the difference — no charge, no obligation.
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Ramp Salon &amp; Academy this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -2990,12 +2990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591365551?text=Hi%20Rita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.rampsalonandacademy.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20SEO-stuffed%20duplicate%20service%20blocks%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ramp%20Salon%20%26%20Academy%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918591365551?text=Hi%20Rita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Ramp%20Salon%20%26%20Academy%20and%20had%20a%20look%20at%20https%3A//www.rampsalonandacademy.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20SEO-stuffed%20duplicate%20service%20blocks%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Ramp%20Salon%20%26%20Academy%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>mailto:rampsalonacademy@gmail.com?subject=Ramp%20Salon%20%26%20Academy%3A%20I%20checked%20www.rampsalonandacademy.com&amp;body=Dear%20Rita%2C%0A%0AI%20opened%20https%3A//www.rampsalonandacademy.com/%20while%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20SEO-stuffed%20duplicate%20service%20blocks%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Hours%20listed%20oddly%20as%20Mon-Fri%20only%20while%20salon%20likely%20needs%20weekend%20booking%20clarity%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Ramp%20Salon%20%26%20Academy%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:rampsalonacademy@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.rampsalonandacademy.com&amp;body=Dear%20Rita%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.rampsalonandacademy.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20SEO-stuffed%20duplicate%20service%20blocks%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Hours%20listed%20oddly%20as%20Mon-Fri%20only%20while%20salon%20likely%20needs%20weekend%20booking%20clarity%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Ramp%20Salon%20%26%20Academy%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3058,20 +3058,20 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Peacock Salon: I checked peacocksalon.in</t>
+          <t>A quick, polite note on peacocksalon.in</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Dear Priti,
-I opened https://peacocksalon.in/ while looking at salon businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The site still has leftover template branding that isn't yours
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Vashi, Navi Mumbai, I visited https://peacocksalon.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• A little leftover template branding is still showing — replacing it with your own name/logo is a quick win
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
 • Product ratings show 0
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Peacock Salon this week so it's clear what I'd change — no obligation.
-Regards,
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Peacock Salon this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3082,11 +3082,11 @@
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>Hi Priti,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://peacocksalon.in/) and a couple of things stood out:
-• The site still has leftover template branding that isn't yours
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Peacock Salon this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Peacock Salon and had a look at https://peacocksalon.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A little leftover template branding is still showing — replacing it with your own name/logo is a quick win
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Peacock Salon this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3095,12 +3095,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919324774567?text=Hi%20Priti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//peacocksalon.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20has%20leftover%20template%20branding%20that%20isn%27t%20yours%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Peacock%20Salon%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919324774567?text=Hi%20Priti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Peacock%20Salon%20and%20had%20a%20look%20at%20https%3A//peacocksalon.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20little%20leftover%20template%20branding%20is%20still%20showing%20%E2%80%94%20replacing%20it%20with%20your%20own%20name/logo%20is%20a%20quick%20win%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Peacock%20Salon%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>mailto:vashi.peacock@gmail.com?subject=Peacock%20Salon%3A%20I%20checked%20peacocksalon.in&amp;body=Dear%20Priti%2C%0A%0AI%20opened%20https%3A//peacocksalon.in/%20while%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20still%20has%20leftover%20template%20branding%20that%20isn%27t%20yours%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20Product%20ratings%20show%200%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Peacock%20Salon%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:vashi.peacock@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20peacocksalon.in&amp;body=Dear%20Priti%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//peacocksalon.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20little%20leftover%20template%20branding%20is%20still%20showing%20%E2%80%94%20replacing%20it%20with%20your%20own%20name/logo%20is%20a%20quick%20win%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20Product%20ratings%20show%200%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Peacock%20Salon%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3163,18 +3163,18 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SLK Foundation Guest House: I checked www.slkfoundation.in/guest-house</t>
+          <t>A quick, polite note on www.slkfoundation.in/guest-house</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Dear Pankaj,
-I opened https://www.slkfoundation.in/guest-house/ while looking at hotel businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for SLK Foundation Guest House this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in Kharghar, Navi Mumbai, I visited https://www.slkfoundation.in/guest-house/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for SLK Foundation Guest House this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3185,10 +3185,10 @@
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>Hi Pankaj,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.slkfoundation.in/guest-house/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for SLK Foundation Guest House this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across SLK Foundation Guest House and had a look at https://www.slkfoundation.in/guest-house/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for SLK Foundation Guest House this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3197,12 +3197,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919035010503?text=Hi%20Pankaj%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.slkfoundation.in/guest-house/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20SLK%20Foundation%20Guest%20House%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919035010503?text=Hi%20Pankaj%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20SLK%20Foundation%20Guest%20House%20and%20had%20a%20look%20at%20https%3A//www.slkfoundation.in/guest-house/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20SLK%20Foundation%20Guest%20House%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>mailto:slkfoundation.in@gmail.com?subject=SLK%20Foundation%20Guest%20House%3A%20I%20checked%20www.slkfoundation.in/guest-house&amp;body=Dear%20Pankaj%2C%0A%0AI%20opened%20https%3A//www.slkfoundation.in/guest-house/%20while%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20SLK%20Foundation%20Guest%20House%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:slkfoundation.in@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.slkfoundation.in/guest-house&amp;body=Dear%20Pankaj%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.slkfoundation.in/guest-house/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20SLK%20Foundation%20Guest%20House%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3261,20 +3261,20 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Splendid Smiles Dental Clinic &amp; Implant Center: I checked www.splendidsmilesdentalclinic.com</t>
+          <t>A quick, polite note on www.splendidsmilesdentalclinic.com</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Dear Gunjan,
-I opened https://www.splendidsmilesdentalclinic.com/ while looking at dental businesses in Kopar Khairane.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kopar Khairane, I visited https://www.splendidsmilesdentalclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Multiple phone numbers across pages (9137777030 / 9930562407) create confusion
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Limited local content depth
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Splendid Smiles Dental Clinic &amp; Implant Center this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Splendid Smiles Dental Clinic &amp; Implant Center this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3285,11 +3285,11 @@
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>Hi Gunjan,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.splendidsmilesdentalclinic.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Splendid Smiles Dental Clinic &amp; Implant Center and had a look at https://www.splendidsmilesdentalclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Multiple phone numbers across pages (9137777030 / 9930562407) create confusion
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Splendid Smiles Dental Clinic &amp; Implant Center this week so you can see the difference — no charge, no obligation.
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Splendid Smiles Dental Clinic &amp; Implant Center this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3298,12 +3298,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137777030?text=Hi%20Gunjan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.splendidsmilesdentalclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Multiple%20phone%20numbers%20across%20pages%20%289137777030%20/%209930562407%29%20create%20confusion%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919137777030?text=Hi%20Gunjan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20and%20had%20a%20look%20at%20https%3A//www.splendidsmilesdentalclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Multiple%20phone%20numbers%20across%20pages%20%289137777030%20/%209930562407%29%20create%20confusion%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>mailto:help@splendidsmilesdentalclinic.com?subject=Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%3A%20I%20checked%20www.splendidsmilesdentalclinic.com&amp;body=Dear%20Gunjan%2C%0A%0AI%20opened%20https%3A//www.splendidsmilesdentalclinic.com/%20while%20looking%20at%20dental%20businesses%20in%20Kopar%20Khairane.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Multiple%20phone%20numbers%20across%20pages%20%289137777030%20/%209930562407%29%20create%20confusion%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Limited%20local%20content%20depth%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:help@splendidsmilesdentalclinic.com?subject=A%20quick%2C%20polite%20note%20on%20www.splendidsmilesdentalclinic.com&amp;body=Dear%20Gunjan%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kopar%20Khairane%2C%20I%20visited%20https%3A//www.splendidsmilesdentalclinic.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Multiple%20phone%20numbers%20across%20pages%20%289137777030%20/%209930562407%29%20create%20confusion%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20Limited%20local%20content%20depth%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Splendid%20Smiles%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3366,20 +3366,20 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Veer Multispecialty Hospital: I checked veericupanvel.com</t>
+          <t>A quick, polite note on veericupanvel.com</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Dear Tejas,
-I opened https://veericupanvel.com/ while looking at healthcare businesses in Panvel (Khanda Colony), Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Panvel (Khanda Colony), Navi Mumbai, I visited https://veericupanvel.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Broken English/placeholder copy
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Duplicate specialty sections
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Veer Multispecialty Hospital this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Veer Multispecialty Hospital this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3390,11 +3390,11 @@
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Hi Tejas,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://veericupanvel.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Veer Multispecialty Hospital and had a look at https://veericupanvel.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Broken English/placeholder copy
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Veer Multispecialty Hospital this week so you can see the difference — no charge, no obligation.
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Veer Multispecialty Hospital this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917208390300?text=Hi%20Tejas%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//veericupanvel.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Broken%20English/placeholder%20copy%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Veer%20Multispecialty%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917208390300?text=Hi%20Tejas%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Veer%20Multispecialty%20Hospital%20and%20had%20a%20look%20at%20https%3A//veericupanvel.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Broken%20English/placeholder%20copy%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Veer%20Multispecialty%20Hospital%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>mailto:veerhospital50@gmail.com?subject=Veer%20Multispecialty%20Hospital%3A%20I%20checked%20veericupanvel.com&amp;body=Dear%20Tejas%2C%0A%0AI%20opened%20https%3A//veericupanvel.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Panvel%20%28Khanda%20Colony%29%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Broken%20English/placeholder%20copy%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Duplicate%20specialty%20sections%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Veer%20Multispecialty%20Hospital%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:veerhospital50@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20veericupanvel.com&amp;body=Dear%20Tejas%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20Panvel%20%28Khanda%20Colony%29%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//veericupanvel.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Broken%20English/placeholder%20copy%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Duplicate%20specialty%20sections%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Veer%20Multispecialty%20Hospital%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Alpha Study: I checked alphagogy.com</t>
+          <t>A quick, polite note on alphagogy.com</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Dear Husain,
-I opened https://alphagogy.com/ while looking at education businesses in Nerul, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can share a free concept page for Alpha Study this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at education businesses in Nerul, Navi Mumbai, I visited https://alphagogy.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If you'd like, I can share a free concept page for Alpha Study this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3494,11 +3494,11 @@
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Hi Husain,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://alphagogy.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can send a free one-page concept for Alpha Study this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Alpha Study and had a look at https://alphagogy.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If it would help, I can send a free one-page concept for Alpha Study this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919326674310?text=Hi%20Husain%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//alphagogy.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Alpha%20Study%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919326674310?text=Hi%20Husain%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Alpha%20Study%20and%20had%20a%20look%20at%20https%3A//alphagogy.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Alpha%20Study%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>mailto:alphastudy.nerul@gmail.com?subject=Alpha%20Study%3A%20I%20checked%20alphagogy.com&amp;body=Dear%20Husain%2C%0A%0AI%20opened%20https%3A//alphagogy.com/%20while%20looking%20at%20education%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Alpha%20Study%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:alphastudy.nerul@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20alphagogy.com&amp;body=Dear%20Husain%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20education%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//alphagogy.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Alpha%20Study%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3575,20 +3575,20 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Cure Dental Clinic (Dr. Sweta Alapuria): I checked www.drswetaalapuria.com</t>
+          <t>A quick, polite note on www.drswetaalapuria.com</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Dear Sweta,
-I opened https://www.drswetaalapuria.com/ while looking at dental businesses in Airoli, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book Appointment button — patients have to hunt for a phone number
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Cure Dental Clinic (Dr. Sweta Alapuria) this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Airoli, Navi Mumbai, I visited https://www.drswetaalapuria.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Cure Dental Clinic (Dr. Sweta Alapuria) this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3599,11 +3599,11 @@
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>Hi Sweta,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.drswetaalapuria.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book Appointment button — patients have to hunt for a phone number
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Cure Dental Clinic (Dr. Sweta Alapuria) this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Cure Dental Clinic (Dr. Sweta Alapuria) and had a look at https://www.drswetaalapuria.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Cure Dental Clinic (Dr. Sweta Alapuria) this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3612,12 +3612,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919699356306?text=Hi%20Sweta%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.drswetaalapuria.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919699356306?text=Hi%20Sweta%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20and%20had%20a%20look%20at%20https%3A//www.drswetaalapuria.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Book%20Appointment%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20patients%20%28many%20currently%20have%20to%20look%20for%20a%20number%29%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>mailto:shweta.doc.2207@gmail.com?subject=Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%3A%20I%20checked%20www.drswetaalapuria.com&amp;body=Dear%20Sweta%2C%0A%0AI%20opened%20https%3A//www.drswetaalapuria.com/%20while%20looking%20at%20dental%20businesses%20in%20Airoli%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:shweta.doc.2207@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.drswetaalapuria.com&amp;body=Dear%20Sweta%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Airoli%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.drswetaalapuria.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Book%20Appointment%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20patients%20%28many%20currently%20have%20to%20look%20for%20a%20number%29%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Cure%20Dental%20Clinic%20%28Dr.%20Sweta%20Alapuria%29%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3680,20 +3680,20 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Dr. Nandini's Skin and Hair Care Clinic: I checked www.drnandiniskincare.com</t>
+          <t>A quick, polite note on www.drnandiniskincare.com</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Dear Nandini,
-I opened https://www.drnandiniskincare.com/ while looking at dermatology businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dermatology businesses in Kharghar, Navi Mumbai, I visited https://www.drnandiniskincare.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Laser/cosmetology booking path not conversion-sharp
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr. Nandini's Skin and Hair Care Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr. Nandini's Skin and Hair Care Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3704,11 +3704,11 @@
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>Hi Nandini,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.drnandiniskincare.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr. Nandini's Skin and Hair Care Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Nandini's Skin and Hair Care Clinic and had a look at https://www.drnandiniskincare.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr. Nandini's Skin and Hair Care Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3717,12 +3717,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919869369029?text=Hi%20Nandini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.drnandiniskincare.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919869369029?text=Hi%20Nandini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.drnandiniskincare.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>mailto:drnandinisskinhaircare@gmail.com?subject=Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%3A%20I%20checked%20www.drnandiniskincare.com&amp;body=Dear%20Nandini%2C%0A%0AI%20opened%20https%3A//www.drnandiniskincare.com/%20while%20looking%20at%20dermatology%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Laser/cosmetology%20booking%20path%20not%20conversion-sharp%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:drnandinisskinhaircare@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.drnandiniskincare.com&amp;body=Dear%20Nandini%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dermatology%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.drnandiniskincare.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20Laser/cosmetology%20booking%20path%20not%20conversion-sharp%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Nandini%27s%20Skin%20and%20Hair%20Care%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3781,20 +3781,20 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Kokan Swad Seawoods: I checked kokanswad.restaurant/branches/seawoods</t>
+          <t>A quick, polite note on kokanswad.restaurant/branches/seawoods</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Dear Nitin,
-I opened https://kokanswad.restaurant/branches/seawoods/ while looking at restaurant businesses in Seawoods, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at restaurant businesses in Seawoods, Navi Mumbai, I visited https://kokanswad.restaurant/branches/seawoods/.
+I wanted to share a few small observations, only in case they're helpful:
 • Enquiry-form led (no direct online order on branch page)
 • Multi-outlet brand site dilutes local conversion
 • WhatsApp present but secondary to form
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Kokan Swad Seawoods this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Kokan Swad Seawoods this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3805,11 +3805,11 @@
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>Hi Nitin,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://kokanswad.restaurant/branches/seawoods/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Kokan Swad Seawoods and had a look at https://kokanswad.restaurant/branches/seawoods/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Enquiry-form led (no direct online order on branch page)
 • Multi-outlet brand site dilutes local conversion
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Kokan Swad Seawoods this week so you can see the difference — no charge, no obligation.
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Kokan Swad Seawoods this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3818,12 +3818,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919324303057?text=Hi%20Nitin%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//kokanswad.restaurant/branches/seawoods/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Enquiry-form%20led%20%28no%20direct%20online%20order%20on%20branch%20page%29%0A%E2%80%A2%20Multi-outlet%20brand%20site%20dilutes%20local%20conversion%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Kokan%20Swad%20Seawoods%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919324303057?text=Hi%20Nitin%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Kokan%20Swad%20Seawoods%20and%20had%20a%20look%20at%20https%3A//kokanswad.restaurant/branches/seawoods/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Enquiry-form%20led%20%28no%20direct%20online%20order%20on%20branch%20page%29%0A%E2%80%A2%20Multi-outlet%20brand%20site%20dilutes%20local%20conversion%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Kokan%20Swad%20Seawoods%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>mailto:sales@kokanswad.restaurant?subject=Kokan%20Swad%20Seawoods%3A%20I%20checked%20kokanswad.restaurant/branches/seawoods&amp;body=Dear%20Nitin%2C%0A%0AI%20opened%20https%3A//kokanswad.restaurant/branches/seawoods/%20while%20looking%20at%20restaurant%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Enquiry-form%20led%20%28no%20direct%20online%20order%20on%20branch%20page%29%0A%E2%80%A2%20Multi-outlet%20brand%20site%20dilutes%20local%20conversion%0A%E2%80%A2%20WhatsApp%20present%20but%20secondary%20to%20form%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Kokan%20Swad%20Seawoods%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sales@kokanswad.restaurant?subject=A%20quick%2C%20polite%20note%20on%20kokanswad.restaurant/branches/seawoods&amp;body=Dear%20Nitin%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20restaurant%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//kokanswad.restaurant/branches/seawoods/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Enquiry-form%20led%20%28no%20direct%20online%20order%20on%20branch%20page%29%0A%E2%80%A2%20Multi-outlet%20brand%20site%20dilutes%20local%20conversion%0A%E2%80%A2%20WhatsApp%20present%20but%20secondary%20to%20form%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Kokan%20Swad%20Seawoods%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -3886,20 +3886,20 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Mahesh Pade &amp; Associates: I checked www.maheshpade.com</t>
+          <t>A quick, polite note on www.maheshpade.com</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Dear Mahesh,
-I opened https://www.maheshpade.com/ while looking at interior design businesses in Nerul / Seawoods, Navi Mumbai.
-Here's what a customer would notice today:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• The site looks like SEO/template pages rather than a real project portfolio
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Nerul / Seawoods, Navi Mumbai, I visited https://www.maheshpade.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• The pages feel a little generic; a stronger project gallery would better show your actual work
 • Weak project-case presentation for a studio since 2003
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for Mahesh Pade &amp; Associates this week so it's clear what I'd change — no obligation.
-Regards,
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for Mahesh Pade &amp; Associates this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -3910,11 +3910,11 @@
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Hi Mahesh,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.maheshpade.com/) and a couple of things stood out:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• The site looks like SEO/template pages rather than a real project portfolio
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for Mahesh Pade &amp; Associates this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Mahesh Pade &amp; Associates and had a look at https://www.maheshpade.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• The pages feel a little generic; a stronger project gallery would better show your actual work
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for Mahesh Pade &amp; Associates this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -3923,12 +3923,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919820536312?text=Hi%20Mahesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.maheshpade.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Mahesh%20Pade%20%26%20Associates%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919820536312?text=Hi%20Mahesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Mahesh%20Pade%20%26%20Associates%20and%20had%20a%20look%20at%20https%3A//www.maheshpade.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20The%20pages%20feel%20a%20little%20generic%3B%20a%20stronger%20project%20gallery%20would%20better%20show%20your%20actual%20work%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Mahesh%20Pade%20%26%20Associates%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@maheshpade.com?subject=Mahesh%20Pade%20%26%20Associates%3A%20I%20checked%20www.maheshpade.com&amp;body=Dear%20Mahesh%2C%0A%0AI%20opened%20https%3A//www.maheshpade.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Nerul%20/%20Seawoods%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%E2%80%A2%20Weak%20project-case%20presentation%20for%20a%20studio%20since%202003%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Mahesh%20Pade%20%26%20Associates%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@maheshpade.com?subject=A%20quick%2C%20polite%20note%20on%20www.maheshpade.com&amp;body=Dear%20Mahesh%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20interior%20design%20businesses%20in%20Nerul%20/%20Seawoods%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.maheshpade.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20The%20pages%20feel%20a%20little%20generic%3B%20a%20stronger%20project%20gallery%20would%20better%20show%20your%20actual%20work%0A%E2%80%A2%20Weak%20project-case%20presentation%20for%20a%20studio%20since%202003%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Mahesh%20Pade%20%26%20Associates%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -3987,20 +3987,20 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Moi Doughssier: I checked www.moidoughssier.com</t>
+          <t>A quick, polite note on www.moidoughssier.com</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Dear Nafisa,
-I opened https://www.moidoughssier.com/ while looking at bakery businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The site still pushes people to Swiggy/Zomato instead of letting them order/book with you directly
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at bakery businesses in Vashi, Navi Mumbai, I visited https://www.moidoughssier.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• Ordering currently points people to Swiggy/Zomato — a direct order option on your own site can keep more of the margin
 • Custom cakes WhatsApp-only
 • Site is strong but reservation/table booking for cafe seating is weak
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Moi Doughssier this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Moi Doughssier this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4011,11 +4011,11 @@
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>Hi Nafisa,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.moidoughssier.com/) and a couple of things stood out:
-• The site still pushes people to Swiggy/Zomato instead of letting them order/book with you directly
+I'm Vaibhav from DMC Creatives Studio. I came across Moi Doughssier and had a look at https://www.moidoughssier.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• Ordering currently points people to Swiggy/Zomato — a direct order option on your own site can keep more of the margin
 • Custom cakes WhatsApp-only
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Moi Doughssier this week so you can see the difference — no charge, no obligation.
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Moi Doughssier this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4024,12 +4024,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919867113900?text=Hi%20Nafisa%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.moidoughssier.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20pushes%20people%20to%20Swiggy/Zomato%20instead%20of%20letting%20them%20order/book%20with%20you%20directly%0A%E2%80%A2%20Custom%20cakes%20WhatsApp-only%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Moi%20Doughssier%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919867113900?text=Hi%20Nafisa%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Moi%20Doughssier%20and%20had%20a%20look%20at%20https%3A//www.moidoughssier.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Ordering%20currently%20points%20people%20to%20Swiggy/Zomato%20%E2%80%94%20a%20direct%20order%20option%20on%20your%20own%20site%20can%20keep%20more%20of%20the%20margin%0A%E2%80%A2%20Custom%20cakes%20WhatsApp-only%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Moi%20Doughssier%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>mailto:nafisa@moidoughssier.com?subject=Moi%20Doughssier%3A%20I%20checked%20www.moidoughssier.com&amp;body=Dear%20Nafisa%2C%0A%0AI%20opened%20https%3A//www.moidoughssier.com/%20while%20looking%20at%20bakery%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20still%20pushes%20people%20to%20Swiggy/Zomato%20instead%20of%20letting%20them%20order/book%20with%20you%20directly%0A%E2%80%A2%20Custom%20cakes%20WhatsApp-only%0A%E2%80%A2%20Site%20is%20strong%20but%20reservation/table%20booking%20for%20cafe%20seating%20is%20weak%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Moi%20Doughssier%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:nafisa@moidoughssier.com?subject=A%20quick%2C%20polite%20note%20on%20www.moidoughssier.com&amp;body=Dear%20Nafisa%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20bakery%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.moidoughssier.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Ordering%20currently%20points%20people%20to%20Swiggy/Zomato%20%E2%80%94%20a%20direct%20order%20option%20on%20your%20own%20site%20can%20keep%20more%20of%20the%20margin%0A%E2%80%A2%20Custom%20cakes%20WhatsApp-only%0A%E2%80%A2%20Site%20is%20strong%20but%20reservation/table%20booking%20for%20cafe%20seating%20is%20weak%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Moi%20Doughssier%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4092,19 +4092,19 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Panikar's Centre for Advanced Dentistry: I checked www.panikarsdentistry.com</t>
+          <t>A quick, polite note on www.panikarsdentistry.com</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Dear Sreekumar,
-I opened https://www.panikarsdentistry.com/ while looking at dental businesses in Sanpada, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Sanpada, Navi Mumbai, I visited https://www.panikarsdentistry.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Award messaging strong but appointment path is call-heavy vs modern implant clinics
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Panikar's Centre for Advanced Dentistry this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Panikar's Centre for Advanced Dentistry this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4115,11 +4115,11 @@
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>Hi Sreekumar,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.panikarsdentistry.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across Panikar's Centre for Advanced Dentistry and had a look at https://www.panikarsdentistry.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Award messaging strong but appointment path is call-heavy vs modern implant clinics
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Panikar's Centre for Advanced Dentistry this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Panikar's Centre for Advanced Dentistry this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4128,12 +4128,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004366342?text=Hi%20Sreekumar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.panikarsdentistry.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Award%20messaging%20strong%20but%20appointment%20path%20is%20call-heavy%20vs%20modern%20implant%20clinics%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919004366342?text=Hi%20Sreekumar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20and%20had%20a%20look%20at%20https%3A//www.panikarsdentistry.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Award%20messaging%20strong%20but%20appointment%20path%20is%20call-heavy%20vs%20modern%20implant%20clinics%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>mailto:panikarsdentistry@gmail.com?subject=Panikar%27s%20Centre%20for%20Advanced%20Dentistry%3A%20I%20checked%20www.panikarsdentistry.com&amp;body=Dear%20Sreekumar%2C%0A%0AI%20opened%20https%3A//www.panikarsdentistry.com/%20while%20looking%20at%20dental%20businesses%20in%20Sanpada%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Award%20messaging%20strong%20but%20appointment%20path%20is%20call-heavy%20vs%20modern%20implant%20clinics%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:panikarsdentistry@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.panikarsdentistry.com&amp;body=Dear%20Sreekumar%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Sanpada%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.panikarsdentistry.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Award%20messaging%20strong%20but%20appointment%20path%20is%20call-heavy%20vs%20modern%20implant%20clinics%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Panikar%27s%20Centre%20for%20Advanced%20Dentistry%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4196,18 +4196,18 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Sai Saya Principal Consultants: I checked saisayaprincipalconsultant.com</t>
+          <t>A quick, polite note on saisayaprincipalconsultant.com</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Dear Sudip,
-I opened https://saisayaprincipalconsultant.com/ while looking at real estate broker businesses in Airoli, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Sai Saya Principal Consultants this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at real estate broker businesses in Airoli, Navi Mumbai, I visited https://saisayaprincipalconsultant.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Sai Saya Principal Consultants this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4218,10 +4218,10 @@
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>Hi Sudip,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://saisayaprincipalconsultant.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Sai Saya Principal Consultants this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Sai Saya Principal Consultants and had a look at https://saisayaprincipalconsultant.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Sai Saya Principal Consultants this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4230,12 +4230,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919322268989?text=Hi%20Sudip%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//saisayaprincipalconsultant.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sai%20Saya%20Principal%20Consultants%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919322268989?text=Hi%20Sudip%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sai%20Saya%20Principal%20Consultants%20and%20had%20a%20look%20at%20https%3A//saisayaprincipalconsultant.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sai%20Saya%20Principal%20Consultants%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>mailto:saisaya89@gmail.com?subject=Sai%20Saya%20Principal%20Consultants%3A%20I%20checked%20saisayaprincipalconsultant.com&amp;body=Dear%20Sudip%2C%0A%0AI%20opened%20https%3A//saisayaprincipalconsultant.com/%20while%20looking%20at%20real%20estate%20broker%20businesses%20in%20Airoli%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sai%20Saya%20Principal%20Consultants%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:saisaya89@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20saisayaprincipalconsultant.com&amp;body=Dear%20Sudip%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20real%20estate%20broker%20businesses%20in%20Airoli%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//saisayaprincipalconsultant.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Sai%20Saya%20Principal%20Consultants%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4294,20 +4294,20 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SK Smile Dental Clinic and Implant Center: I checked sksmiledental.com</t>
+          <t>A quick, polite note on sksmiledental.com</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Dear Satish,
-I opened https://sksmiledental.com/ while looking at dental businesses in Airoli.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Airoli, I visited https://sksmiledental.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Generic WordPress look
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for SK Smile Dental Clinic and Implant Center this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for SK Smile Dental Clinic and Implant Center this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4318,11 +4318,11 @@
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>Hi Satish,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sksmiledental.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for SK Smile Dental Clinic and Implant Center this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across SK Smile Dental Clinic and Implant Center and had a look at https://sksmiledental.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for SK Smile Dental Clinic and Implant Center this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918291883844?text=Hi%20Satish%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sksmiledental.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918291883844?text=Hi%20Satish%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20and%20had%20a%20look%20at%20https%3A//sksmiledental.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>mailto:sksmiledental@gmail.com?subject=SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%3A%20I%20checked%20sksmiledental.com&amp;body=Dear%20Satish%2C%0A%0AI%20opened%20https%3A//sksmiledental.com/%20while%20looking%20at%20dental%20businesses%20in%20Airoli.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Generic%20WordPress%20look%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sksmiledental@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20sksmiledental.com&amp;body=Dear%20Satish%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Airoli%2C%20I%20visited%20https%3A//sksmiledental.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20Generic%20WordPress%20look%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20SK%20Smile%20Dental%20Clinic%20and%20Implant%20Center%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4399,19 +4399,19 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Skin Science Clinic: I checked skinsciencemumbai.com</t>
+          <t>A quick, polite note on skinsciencemumbai.com</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Dear Kiran,
-I opened https://skinsciencemumbai.com/ while looking at dermatology businesses in Nerul, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dermatology businesses in Nerul, Navi Mumbai, I visited https://skinsciencemumbai.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Aesthetic clinic booking can be sharper for Seawoods/Nerul high ARPU treatments
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Skin Science Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Skin Science Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4422,11 +4422,11 @@
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>Hi Kiran,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://skinsciencemumbai.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across Skin Science Clinic and had a look at https://skinsciencemumbai.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Aesthetic clinic booking can be sharper for Seawoods/Nerul high ARPU treatments
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Skin Science Clinic this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Skin Science Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917777005606?text=Hi%20Kiran%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//skinsciencemumbai.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Aesthetic%20clinic%20booking%20can%20be%20sharper%20for%20Seawoods/Nerul%20high%20ARPU%20treatments%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Skin%20Science%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917777005606?text=Hi%20Kiran%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Skin%20Science%20Clinic%20and%20had%20a%20look%20at%20https%3A//skinsciencemumbai.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Aesthetic%20clinic%20booking%20can%20be%20sharper%20for%20Seawoods/Nerul%20high%20ARPU%20treatments%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Skin%20Science%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>mailto:skinscienceclinics@gmail.com?subject=Skin%20Science%20Clinic%3A%20I%20checked%20skinsciencemumbai.com&amp;body=Dear%20Kiran%2C%0A%0AI%20opened%20https%3A//skinsciencemumbai.com/%20while%20looking%20at%20dermatology%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Aesthetic%20clinic%20booking%20can%20be%20sharper%20for%20Seawoods/Nerul%20high%20ARPU%20treatments%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Skin%20Science%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:skinscienceclinics@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20skinsciencemumbai.com&amp;body=Dear%20Kiran%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dermatology%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//skinsciencemumbai.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Aesthetic%20clinic%20booking%20can%20be%20sharper%20for%20Seawoods/Nerul%20high%20ARPU%20treatments%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Skin%20Science%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4499,20 +4499,20 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Smile Care Dental Clinic &amp; Implant Center: I checked www.smilecareairoli.com</t>
+          <t>A quick, polite note on www.smilecareairoli.com</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
           <t>Dear Umesh,
-I opened https://www.smilecareairoli.com/ while looking at dental businesses in Airoli.
-Here's what a customer would notice today:
-• The public email on the site is a Yahoo address — that looks dated to customers
-• The phone number is missing from the homepage — people can't call you from the first screen
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Smile Care Dental Clinic &amp; Implant Center this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Airoli, I visited https://www.smilecareairoli.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Yahoo address — a branded company email usually feels more current
+• The phone number isn't easy to spot on the first screen — putting it in the header usually helps
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Smile Care Dental Clinic &amp; Implant Center this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4523,11 +4523,11 @@
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>Hi Umesh,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smilecareairoli.com/) and a couple of things stood out:
-• The public email on the site is a Yahoo address — that looks dated to customers
-• The phone number is missing from the homepage — people can't call you from the first screen
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Smile Care Dental Clinic &amp; Implant Center this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Smile Care Dental Clinic &amp; Implant Center and had a look at https://www.smilecareairoli.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Yahoo address — a branded company email usually feels more current
+• The phone number isn't easy to spot on the first screen — putting it in the header usually helps
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Smile Care Dental Clinic &amp; Implant Center this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652628813?text=Hi%20Umesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smilecareairoli.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Yahoo%20address%20%E2%80%94%20that%20looks%20dated%20to%20customers%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918652628813?text=Hi%20Umesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20and%20had%20a%20look%20at%20https%3A//www.smilecareairoli.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Yahoo%20address%20%E2%80%94%20a%20branded%20company%20email%20usually%20feels%20more%20current%0A%E2%80%A2%20The%20phone%20number%20isn%27t%20easy%20to%20spot%20on%20the%20first%20screen%20%E2%80%94%20putting%20it%20in%20the%20header%20usually%20helps%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>mailto:smilecaredentalclinic@yahoo.com?subject=Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%3A%20I%20checked%20www.smilecareairoli.com&amp;body=Dear%20Umesh%2C%0A%0AI%20opened%20https%3A//www.smilecareairoli.com/%20while%20looking%20at%20dental%20businesses%20in%20Airoli.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Yahoo%20address%20%E2%80%94%20that%20looks%20dated%20to%20customers%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:smilecaredentalclinic@yahoo.com?subject=A%20quick%2C%20polite%20note%20on%20www.smilecareairoli.com&amp;body=Dear%20Umesh%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Airoli%2C%20I%20visited%20https%3A//www.smilecareairoli.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Yahoo%20address%20%E2%80%94%20a%20branded%20company%20email%20usually%20feels%20more%20current%0A%E2%80%A2%20The%20phone%20number%20isn%27t%20easy%20to%20spot%20on%20the%20first%20screen%20%E2%80%94%20putting%20it%20in%20the%20header%20usually%20helps%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Care%20Dental%20Clinic%20%26%20Implant%20Center%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4600,19 +4600,19 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Smilekraft Dental Clinic: I checked www.smilekraftclinic.com</t>
+          <t>A quick, polite note on www.smilekraftclinic.com</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
           <t>Dear Vinothini,
-I opened https://www.smilekraftclinic.com/ while looking at dental businesses in Seawoods.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Seawoods, I visited https://www.smilekraftclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Long-form SEO page density
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Smilekraft Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Smilekraft Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4623,11 +4623,11 @@
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>Hi Vinothini,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smilekraftclinic.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across Smilekraft Dental Clinic and had a look at https://www.smilekraftclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Long-form SEO page density
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Smilekraft Dental Clinic this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Smilekraft Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4636,12 +4636,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919869912382?text=Hi%20Vinothini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smilekraftclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Long-form%20SEO%20page%20density%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smilekraft%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919869912382?text=Hi%20Vinothini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Smilekraft%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.smilekraftclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Long-form%20SEO%20page%20density%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Smilekraft%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>mailto:smilekraftclinic@gmail.com?subject=Smilekraft%20Dental%20Clinic%3A%20I%20checked%20www.smilekraftclinic.com&amp;body=Dear%20Vinothini%2C%0A%0AI%20opened%20https%3A//www.smilekraftclinic.com/%20while%20looking%20at%20dental%20businesses%20in%20Seawoods.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Long-form%20SEO%20page%20density%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Smilekraft%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:smilekraftclinic@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.smilekraftclinic.com&amp;body=Dear%20Vinothini%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Seawoods%2C%20I%20visited%20https%3A//www.smilekraftclinic.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Long-form%20SEO%20page%20density%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Smilekraft%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4704,20 +4704,20 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The Ashtanga Institute of Yoga &amp; Naturopathy: I checked theashtangainstitute.com</t>
+          <t>A quick, polite note on theashtangainstitute.com</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
           <t>Dear Sandeep,
-I opened https://theashtangainstitute.com/ while looking at gym businesses in Airoli, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• The pages look dated and thin — visitors don't get enough proof to call
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for The Ashtanga Institute of Yoga &amp; Naturopathy this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at gym businesses in Airoli, Navi Mumbai, I visited https://theashtangainstitute.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for The Ashtanga Institute of Yoga &amp; Naturopathy this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4728,11 +4728,11 @@
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>Hi Sandeep,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://theashtangainstitute.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for The Ashtanga Institute of Yoga &amp; Naturopathy this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across The Ashtanga Institute of Yoga &amp; Naturopathy and had a look at https://theashtangainstitute.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for The Ashtanga Institute of Yoga &amp; Naturopathy this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4741,12 +4741,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967485808?text=Hi%20Sandeep%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//theashtangainstitute.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919967485808?text=Hi%20Sandeep%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20and%20had%20a%20look%20at%20https%3A//theashtangainstitute.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>mailto:theashtangainstitute@gmail.com?subject=The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%3A%20I%20checked%20theashtangainstitute.com&amp;body=Dear%20Sandeep%2C%0A%0AI%20opened%20https%3A//theashtangainstitute.com/%20while%20looking%20at%20gym%20businesses%20in%20Airoli%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:theashtangainstitute@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20theashtangainstitute.com&amp;body=Dear%20Sandeep%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20gym%20businesses%20in%20Airoli%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//theashtangainstitute.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20The%20Ashtanga%20Institute%20of%20Yoga%20%26%20Naturopathy%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4809,19 +4809,19 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Aaroh Academy: I checked aarohacademy.com</t>
+          <t>A quick, polite note on aarohacademy.com</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Dear Shalini,
-I opened https://aarohacademy.com/ while looking at education businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at education businesses in Kharghar, Navi Mumbai, I visited https://aarohacademy.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak conversion hierarchy vs modern competitors
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can share a free concept page for Aaroh Academy this week so it's clear what I'd change — no obligation.
-Regards,
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If you'd like, I can share a free concept page for Aaroh Academy this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4832,11 +4832,11 @@
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>Hi Shalini,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://aarohacademy.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
+I'm Vaibhav from DMC Creatives Studio. I came across Aaroh Academy and had a look at https://aarohacademy.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak conversion hierarchy vs modern competitors
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can send a free one-page concept for Aaroh Academy this week so you can see the difference — no charge, no obligation.
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If it would help, I can send a free one-page concept for Aaroh Academy this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4845,12 +4845,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919867063446?text=Hi%20Shalini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//aarohacademy.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Aaroh%20Academy%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919867063446?text=Hi%20Shalini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Aaroh%20Academy%20and%20had%20a%20look%20at%20https%3A//aarohacademy.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Aaroh%20Academy%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@aarohacademy.com?subject=Aaroh%20Academy%3A%20I%20checked%20aarohacademy.com&amp;body=Dear%20Shalini%2C%0A%0AI%20opened%20https%3A//aarohacademy.com/%20while%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Aaroh%20Academy%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@aarohacademy.com?subject=A%20quick%2C%20polite%20note%20on%20aarohacademy.com&amp;body=Dear%20Shalini%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//aarohacademy.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Aaroh%20Academy%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4913,19 +4913,19 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Meritorious Tutorials: I checked meritorious.co.in</t>
+          <t>A quick, polite note on meritorious.co.in</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
           <t>Dear Ashok,
-I opened https://meritorious.co.in/ while looking at education businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at education businesses in Kharghar, Navi Mumbai, I visited https://meritorious.co.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak conversion hierarchy vs modern competitors
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can share a free concept page for Meritorious Tutorials this week so it's clear what I'd change — no obligation.
-Regards,
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If you'd like, I can share a free concept page for Meritorious Tutorials this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4936,11 +4936,11 @@
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>Hi Ashok,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://meritorious.co.in/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
+I'm Vaibhav from DMC Creatives Studio. I came across Meritorious Tutorials and had a look at https://meritorious.co.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak conversion hierarchy vs modern competitors
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can send a free one-page concept for Meritorious Tutorials this week so you can see the difference — no charge, no obligation.
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If it would help, I can send a free one-page concept for Meritorious Tutorials this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -4949,12 +4949,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004229269?text=Hi%20Ashok%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//meritorious.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Meritorious%20Tutorials%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919004229269?text=Hi%20Ashok%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Meritorious%20Tutorials%20and%20had%20a%20look%20at%20https%3A//meritorious.co.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Meritorious%20Tutorials%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@meritorious.co.in?subject=Meritorious%20Tutorials%3A%20I%20checked%20meritorious.co.in&amp;body=Dear%20Ashok%2C%0A%0AI%20opened%20https%3A//meritorious.co.in/%20while%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Meritorious%20Tutorials%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@meritorious.co.in?subject=A%20quick%2C%20polite%20note%20on%20meritorious.co.in&amp;body=Dear%20Ashok%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//meritorious.co.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Meritorious%20Tutorials%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5017,19 +5017,19 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Ora Care Dental Studio: I checked oracaredentalstudio.com</t>
+          <t>A quick, polite note on oracaredentalstudio.com</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Dear Prerna,
-I opened https://oracaredentalstudio.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, Navi Mumbai, I visited https://oracaredentalstudio.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak conversion hierarchy vs modern competitors
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Ora Care Dental Studio this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Ora Care Dental Studio this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5040,11 +5040,11 @@
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>Hi Prerna,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://oracaredentalstudio.com/) and a couple of things stood out:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I'm Vaibhav from DMC Creatives Studio. I came across Ora Care Dental Studio and had a look at https://oracaredentalstudio.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak conversion hierarchy vs modern competitors
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Ora Care Dental Studio this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Ora Care Dental Studio this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5053,12 +5053,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917875617480?text=Hi%20Prerna%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//oracaredentalstudio.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ora%20Care%20Dental%20Studio%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917875617480?text=Hi%20Prerna%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Ora%20Care%20Dental%20Studio%20and%20had%20a%20look%20at%20https%3A//oracaredentalstudio.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Ora%20Care%20Dental%20Studio%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>mailto:your@email.com?subject=Ora%20Care%20Dental%20Studio%3A%20I%20checked%20oracaredentalstudio.com&amp;body=Dear%20Prerna%2C%0A%0AI%20opened%20https%3A//oracaredentalstudio.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Ora%20Care%20Dental%20Studio%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:your@email.com?subject=A%20quick%2C%20polite%20note%20on%20oracaredentalstudio.com&amp;body=Dear%20Prerna%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//oracaredentalstudio.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Ora%20Care%20Dental%20Studio%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5117,20 +5117,20 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Ratnakokan Seawoods: I checked ratnakokan.com</t>
+          <t>A quick, polite note on ratnakokan.com</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
           <t>Dear Sanjay,
-I opened https://ratnakokan.com/ while looking at restaurant businesses in Seawoods, Navi Mumbai.
-Here's what a customer would notice today:
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at restaurant businesses in Seawoods, Navi Mumbai, I visited https://ratnakokan.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • No branch-specific menu/order flow
-• There's no Order Online / Book a table button on the homepage
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Ratnakokan Seawoods this week so it's clear what I'd change — no obligation.
-Regards,
+• An Order Online or Book a table button on the homepage would make it easier for people who are ready to buy
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Ratnakokan Seawoods this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5141,11 +5141,11 @@
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>Hi Sanjay,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ratnakokan.com/) and a couple of things stood out:
-• The pages look dated and thin — visitors don't get enough proof to call
+I'm Vaibhav from DMC Creatives Studio. I came across Ratnakokan Seawoods and had a look at https://ratnakokan.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • No branch-specific menu/order flow
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Ratnakokan Seawoods this week so you can see the difference — no charge, no obligation.
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Ratnakokan Seawoods this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5154,12 +5154,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833862548?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ratnakokan.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20No%20branch-specific%20menu/order%20flow%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ratnakokan%20Seawoods%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919833862548?text=Hi%20Sanjay%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Ratnakokan%20Seawoods%20and%20had%20a%20look%20at%20https%3A//ratnakokan.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20No%20branch-specific%20menu/order%20flow%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Ratnakokan%20Seawoods%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>mailto:mail@ratnakokan.com?subject=Ratnakokan%20Seawoods%3A%20I%20checked%20ratnakokan.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20opened%20https%3A//ratnakokan.com/%20while%20looking%20at%20restaurant%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20No%20branch-specific%20menu/order%20flow%0A%E2%80%A2%20There%27s%20no%20Order%20Online%20/%20Book%20a%20table%20button%20on%20the%20homepage%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Ratnakokan%20Seawoods%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:mail@ratnakokan.com?subject=A%20quick%2C%20polite%20note%20on%20ratnakokan.com&amp;body=Dear%20Sanjay%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20restaurant%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//ratnakokan.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20No%20branch-specific%20menu/order%20flow%0A%E2%80%A2%20An%20Order%20Online%20or%20Book%20a%20table%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20are%20ready%20to%20buy%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Ratnakokan%20Seawoods%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5218,20 +5218,20 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Smile Matters Multispeciality Dental Clinic: I checked smilemattersgroup.com</t>
+          <t>A quick, polite note on smilemattersgroup.com</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
           <t>Dear Prasad,
-I opened https://smilemattersgroup.com/ while looking at dental businesses in Kharghar.
-Here's what a customer would notice today:
-• Your website sometimes opens an error page (I got a 500) instead of your homepage
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, I visited https://smilemattersgroup.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• On one visit the homepage showed an error instead of opening normally (this can happen if the server is overloaded)
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Booking depends mainly on phone/WhatsApp
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Smile Matters Multispeciality Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Smile Matters Multispeciality Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5242,11 +5242,11 @@
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>Hi Prasad,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://smilemattersgroup.com/) and a couple of things stood out:
-• Your website sometimes opens an error page (I got a 500) instead of your homepage
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Smile Matters Multispeciality Dental Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Smile Matters Multispeciality Dental Clinic and had a look at https://smilemattersgroup.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• On one visit the homepage showed an error instead of opening normally (this can happen if the server is overloaded)
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Smile Matters Multispeciality Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5255,12 +5255,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918850192774?text=Hi%20Prasad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//smilemattersgroup.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918850192774?text=Hi%20Prasad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//smilemattersgroup.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20On%20one%20visit%20the%20homepage%20showed%20an%20error%20instead%20of%20opening%20normally%20%28this%20can%20happen%20if%20the%20server%20is%20overloaded%29%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>mailto:drprasad@smilemattersgroup.com?subject=Smile%20Matters%20Multispeciality%20Dental%20Clinic%3A%20I%20checked%20smilemattersgroup.com&amp;body=Dear%20Prasad%2C%0A%0AI%20opened%20https%3A//smilemattersgroup.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Booking%20depends%20mainly%20on%20phone/WhatsApp%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:drprasad@smilemattersgroup.com?subject=A%20quick%2C%20polite%20note%20on%20smilemattersgroup.com&amp;body=Dear%20Prasad%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20I%20visited%20https%3A//smilemattersgroup.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20On%20one%20visit%20the%20homepage%20showed%20an%20error%20instead%20of%20opening%20normally%20%28this%20can%20happen%20if%20the%20server%20is%20overloaded%29%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20Booking%20depends%20mainly%20on%20phone/WhatsApp%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Smile%20Matters%20Multispeciality%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5323,18 +5323,18 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Agrawal Diagnostics Center Ulwe: I checked agrawaldiagnosticsulwe.com</t>
+          <t>A quick, polite note on agrawaldiagnosticsulwe.com</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Dear Anup,
-I opened https://agrawaldiagnosticsulwe.com/ while looking at diagnostics businesses in Ulwe, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Agrawal Diagnostics Center Ulwe this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at diagnostics businesses in Ulwe, Navi Mumbai, I visited https://agrawaldiagnosticsulwe.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Agrawal Diagnostics Center Ulwe this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5345,10 +5345,10 @@
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>Hi Anup,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://agrawaldiagnosticsulwe.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Agrawal Diagnostics Center Ulwe this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Agrawal Diagnostics Center Ulwe and had a look at https://agrawaldiagnosticsulwe.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Agrawal Diagnostics Center Ulwe this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5357,12 +5357,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918928785788?text=Hi%20Anup%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//agrawaldiagnosticsulwe.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Agrawal%20Diagnostics%20Center%20Ulwe%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918928785788?text=Hi%20Anup%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Agrawal%20Diagnostics%20Center%20Ulwe%20and%20had%20a%20look%20at%20https%3A//agrawaldiagnosticsulwe.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Agrawal%20Diagnostics%20Center%20Ulwe%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>mailto:anup3356@gmail.com?subject=Agrawal%20Diagnostics%20Center%20Ulwe%3A%20I%20checked%20agrawaldiagnosticsulwe.com&amp;body=Dear%20Anup%2C%0A%0AI%20opened%20https%3A//agrawaldiagnosticsulwe.com/%20while%20looking%20at%20diagnostics%20businesses%20in%20Ulwe%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Agrawal%20Diagnostics%20Center%20Ulwe%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:anup3356@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20agrawaldiagnosticsulwe.com&amp;body=Dear%20Anup%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20diagnostics%20businesses%20in%20Ulwe%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//agrawaldiagnosticsulwe.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Agrawal%20Diagnostics%20Center%20Ulwe%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5425,18 +5425,18 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Dr. Janugade Ayurvedic Clinic: I checked www.drjanugades.com</t>
+          <t>A quick, polite note on www.drjanugades.com</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
           <t>Dear Archana,
-I opened https://www.drjanugades.com/ while looking at healthcare businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr. Janugade Ayurvedic Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Vashi, Navi Mumbai, I visited https://www.drjanugades.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr. Janugade Ayurvedic Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5447,10 +5447,10 @@
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>Hi Archana,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.drjanugades.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr. Janugade Ayurvedic Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Janugade Ayurvedic Clinic and had a look at https://www.drjanugades.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr. Janugade Ayurvedic Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5459,12 +5459,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918823529411?text=Hi%20Archana%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.drjanugades.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Janugade%20Ayurvedic%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918823529411?text=Hi%20Archana%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Janugade%20Ayurvedic%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.drjanugades.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Janugade%20Ayurvedic%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>mailto:drjanugades@gmail.com?subject=Dr.%20Janugade%20Ayurvedic%20Clinic%3A%20I%20checked%20www.drjanugades.com&amp;body=Dear%20Archana%2C%0A%0AI%20opened%20https%3A//www.drjanugades.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Janugade%20Ayurvedic%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:drjanugades@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.drjanugades.com&amp;body=Dear%20Archana%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.drjanugades.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Janugade%20Ayurvedic%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5527,18 +5527,18 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Dr. Sambhaji Patil Skin Care Clinic: I checked drsambhajipatil.com</t>
+          <t>A quick, polite note on drsambhajipatil.com</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
           <t>Dear Sambhaji,
-I opened https://drsambhajipatil.com/ while looking at healthcare businesses in Nerul / Panvel, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr. Sambhaji Patil Skin Care Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Nerul / Panvel, Navi Mumbai, I visited https://drsambhajipatil.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr. Sambhaji Patil Skin Care Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5549,10 +5549,10 @@
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>Hi Sambhaji,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drsambhajipatil.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr. Sambhaji Patil Skin Care Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Sambhaji Patil Skin Care Clinic and had a look at https://drsambhajipatil.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr. Sambhaji Patil Skin Care Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591420077?text=Hi%20Sambhaji%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drsambhajipatil.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918591420077?text=Hi%20Sambhaji%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20and%20had%20a%20look%20at%20https%3A//drsambhajipatil.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>mailto:drsambhajipatil.com@gmail.com?subject=Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%3A%20I%20checked%20drsambhajipatil.com&amp;body=Dear%20Sambhaji%2C%0A%0AI%20opened%20https%3A//drsambhajipatil.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Nerul%20/%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:drsambhajipatil.com@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20drsambhajipatil.com&amp;body=Dear%20Sambhaji%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20Nerul%20/%20Panvel%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//drsambhajipatil.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr.%20Sambhaji%20Patil%20Skin%20Care%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5621,20 +5621,20 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Nakhawa Garden Restaurant: I checked nakhawagardenrestaurant.com</t>
+          <t>A quick, polite note on nakhawagardenrestaurant.com</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://nakhawagardenrestaurant.com/ while looking at restaurant businesses in Panvel (Shirdhon), Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at restaurant businesses in Panvel (Shirdhon), Navi Mumbai, I visited https://nakhawagardenrestaurant.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• There's no easy online order yet — a simple menu/checkout often keeps people from switching to Swiggy/Zomato
 • Contact-led site with limited WhatsApp CTA prominence
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Nakhawa Garden Restaurant this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Nakhawa Garden Restaurant this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5645,11 +5645,11 @@
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://nakhawagardenrestaurant.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Nakhawa Garden Restaurant this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Nakhawa Garden Restaurant and had a look at https://nakhawagardenrestaurant.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• There's no easy online order yet — a simple menu/checkout often keeps people from switching to Swiggy/Zomato
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Nakhawa Garden Restaurant this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5658,12 +5658,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591971009?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//nakhawagardenrestaurant.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Nakhawa%20Garden%20Restaurant%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918591971009?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Nakhawa%20Garden%20Restaurant%20and%20had%20a%20look%20at%20https%3A//nakhawagardenrestaurant.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20There%27s%20no%20easy%20online%20order%20yet%20%E2%80%94%20a%20simple%20menu/checkout%20often%20keeps%20people%20from%20switching%20to%20Swiggy/Zomato%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Nakhawa%20Garden%20Restaurant%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>mailto:nakhawa1009@gmail.com?subject=Nakhawa%20Garden%20Restaurant%3A%20I%20checked%20nakhawagardenrestaurant.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//nakhawagardenrestaurant.com/%20while%20looking%20at%20restaurant%20businesses%20in%20Panvel%20%28Shirdhon%29%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%E2%80%A2%20Contact-led%20site%20with%20limited%20WhatsApp%20CTA%20prominence%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Nakhawa%20Garden%20Restaurant%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:nakhawa1009@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20nakhawagardenrestaurant.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20restaurant%20businesses%20in%20Panvel%20%28Shirdhon%29%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//nakhawagardenrestaurant.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20There%27s%20no%20easy%20online%20order%20yet%20%E2%80%94%20a%20simple%20menu/checkout%20often%20keeps%20people%20from%20switching%20to%20Swiggy/Zomato%0A%E2%80%A2%20Contact-led%20site%20with%20limited%20WhatsApp%20CTA%20prominence%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Nakhawa%20Garden%20Restaurant%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -5726,18 +5726,18 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The Dental Studio Kharghar: I checked thedentalstudiokharghar.com</t>
+          <t>A quick, polite note on thedentalstudiokharghar.com</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
           <t>Dear Himmat,
-I opened https://thedentalstudiokharghar.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for The Dental Studio Kharghar this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, Navi Mumbai, I visited https://thedentalstudiokharghar.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for The Dental Studio Kharghar this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5748,10 +5748,10 @@
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Hi Himmat,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thedentalstudiokharghar.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for The Dental Studio Kharghar this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across The Dental Studio Kharghar and had a look at https://thedentalstudiokharghar.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for The Dental Studio Kharghar this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5760,12 +5760,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918989255544?text=Hi%20Himmat%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thedentalstudiokharghar.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20Studio%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918989255544?text=Hi%20Himmat%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20The%20Dental%20Studio%20Kharghar%20and%20had%20a%20look%20at%20https%3A//thedentalstudiokharghar.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20Studio%20Kharghar%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>mailto:anands9@gmail.com?subject=The%20Dental%20Studio%20Kharghar%3A%20I%20checked%20thedentalstudiokharghar.com&amp;body=Dear%20Himmat%2C%0A%0AI%20opened%20https%3A//thedentalstudiokharghar.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20Dental%20Studio%20Kharghar%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:anands9@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20thedentalstudiokharghar.com&amp;body=Dear%20Himmat%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//thedentalstudiokharghar.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20The%20Dental%20Studio%20Kharghar%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5828,18 +5828,18 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>The TOOTH Clinic: I checked thetoothclinickharghar.co.in</t>
+          <t>A quick, polite note on thetoothclinickharghar.co.in</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Dear Bhavna,
-I opened https://thetoothclinickharghar.co.in/ while looking at dental businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for The TOOTH Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, Navi Mumbai, I visited https://thetoothclinickharghar.co.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for The TOOTH Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5850,10 +5850,10 @@
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>Hi Bhavna,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thetoothclinickharghar.co.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for The TOOTH Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across The TOOTH Clinic and had a look at https://thetoothclinickharghar.co.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for The TOOTH Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5862,12 +5862,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919930050434?text=Hi%20Bhavna%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thetoothclinickharghar.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20TOOTH%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919930050434?text=Hi%20Bhavna%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20The%20TOOTH%20Clinic%20and%20had%20a%20look%20at%20https%3A//thetoothclinickharghar.co.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20The%20TOOTH%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>mailto:thetoothclinic.kharghar@gmail.com?subject=The%20TOOTH%20Clinic%3A%20I%20checked%20thetoothclinickharghar.co.in&amp;body=Dear%20Bhavna%2C%0A%0AI%20opened%20https%3A//thetoothclinickharghar.co.in/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20TOOTH%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:thetoothclinic.kharghar@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20thetoothclinickharghar.co.in&amp;body=Dear%20Bhavna%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//thetoothclinickharghar.co.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20The%20TOOTH%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -5926,20 +5926,20 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Samarth Nethralaya: I checked samarthnethralaya.com</t>
+          <t>A quick, polite note on samarthnethralaya.com</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
           <t>Dear Archis,
-I opened https://samarthnethralaya.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Kharghar, Navi Mumbai, I visited https://samarthnethralaya.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • No clear public email
 • Booking form forwards to WhatsApp rather than integrated scheduling
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Samarth Nethralaya this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Samarth Nethralaya this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -5950,11 +5950,11 @@
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>Hi Archis,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://samarthnethralaya.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
+I'm Vaibhav from DMC Creatives Studio. I came across Samarth Nethralaya and had a look at https://samarthnethralaya.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • No clear public email
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Samarth Nethralaya this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Samarth Nethralaya this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -5963,7 +5963,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652458337?text=Hi%20Archis%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//samarthnethralaya.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20No%20clear%20public%20email%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Samarth%20Nethralaya%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918652458337?text=Hi%20Archis%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Samarth%20Nethralaya%20and%20had%20a%20look%20at%20https%3A//samarthnethralaya.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20No%20clear%20public%20email%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Samarth%20Nethralaya%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr"/>
@@ -6023,20 +6023,20 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Art of Smiles by Citizen Dental Clinic: I checked www.artofsmiles.in</t>
+          <t>A quick, polite note on www.artofsmiles.in</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
           <t>Dear Anand,
-I opened https://www.artofsmiles.in/ while looking at dental businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The site is a basic Wix brochure page — it doesn't look like a serious local brand
-• The site still has leftover template branding that isn't yours
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Art of Smiles by Citizen Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Vashi, Navi Mumbai, I visited https://www.artofsmiles.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The site still has a simple builder look; a cleaner custom layout would better match your brand
+• A little leftover template branding is still showing — replacing it with your own name/logo is a quick win
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Art of Smiles by Citizen Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6047,11 +6047,11 @@
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>Hi Anand,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.artofsmiles.in/) and a couple of things stood out:
-• The site is a basic Wix brochure page — it doesn't look like a serious local brand
-• The site still has leftover template branding that isn't yours
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Art of Smiles by Citizen Dental Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Art of Smiles by Citizen Dental Clinic and had a look at https://www.artofsmiles.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The site still has a simple builder look; a cleaner custom layout would better match your brand
+• A little leftover template branding is still showing — replacing it with your own name/logo is a quick win
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Art of Smiles by Citizen Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6060,7 +6060,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919167550145?text=Hi%20Anand%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.artofsmiles.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%E2%80%A2%20The%20site%20still%20has%20leftover%20template%20branding%20that%20isn%27t%20yours%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Art%20of%20Smiles%20by%20Citizen%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919167550145?text=Hi%20Anand%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Art%20of%20Smiles%20by%20Citizen%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.artofsmiles.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20site%20still%20has%20a%20simple%20builder%20look%3B%20a%20cleaner%20custom%20layout%20would%20better%20match%20your%20brand%0A%E2%80%A2%20A%20little%20leftover%20template%20branding%20is%20still%20showing%20%E2%80%94%20replacing%20it%20with%20your%20own%20name/logo%20is%20a%20quick%20win%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Art%20of%20Smiles%20by%20Citizen%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr"/>
@@ -6124,18 +6124,18 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>J B Patel &amp; Associates: I checked www.jbpassociates.in</t>
+          <t>A quick, polite note on www.jbpassociates.in</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.jbpassociates.in/ while looking at ca firm businesses in CBD Belapur, Navi Mumbai.
-Here's what a customer would notice today:
-• The site is a basic Wix brochure page — it doesn't look like a serious local brand
-People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
-I can share a free concept page for J B Patel &amp; Associates this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at ca firm businesses in CBD Belapur, Navi Mumbai, I visited https://www.jbpassociates.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The site still has a simple builder look; a cleaner custom layout would better match your brand
+People who find you on Google usually decide in a few seconds whether to enquire. A clearer next step on the site often helps.
+If you'd like, I can share a free concept page for J B Patel &amp; Associates this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6146,10 +6146,10 @@
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.jbpassociates.in/) and a couple of things stood out:
-• The site is a basic Wix brochure page — it doesn't look like a serious local brand
-People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
-I can send a free one-page concept for J B Patel &amp; Associates this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across J B Patel &amp; Associates and had a look at https://www.jbpassociates.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The site still has a simple builder look; a cleaner custom layout would better match your brand
+People who find you on Google usually decide in a few seconds whether to enquire. A clearer next step on the site often helps.
+If it would help, I can send a free one-page concept for J B Patel &amp; Associates this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6158,12 +6158,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919167980919?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.jbpassociates.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20J%20B%20Patel%20%26%20Associates%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919167980919?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20J%20B%20Patel%20%26%20Associates%20and%20had%20a%20look%20at%20https%3A//www.jbpassociates.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20site%20still%20has%20a%20simple%20builder%20look%3B%20a%20cleaner%20custom%20layout%20would%20better%20match%20your%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20usually%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20A%20clearer%20next%20step%20on%20the%20site%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20J%20B%20Patel%20%26%20Associates%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>mailto:tax@jbpassociates.in?subject=J%20B%20Patel%20%26%20Associates%3A%20I%20checked%20www.jbpassociates.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.jbpassociates.in/%20while%20looking%20at%20ca%20firm%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20J%20B%20Patel%20%26%20Associates%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:tax@jbpassociates.in?subject=A%20quick%2C%20polite%20note%20on%20www.jbpassociates.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20ca%20firm%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.jbpassociates.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20site%20still%20has%20a%20simple%20builder%20look%3B%20a%20cleaner%20custom%20layout%20would%20better%20match%20your%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20usually%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20A%20clearer%20next%20step%20on%20the%20site%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20J%20B%20Patel%20%26%20Associates%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6226,19 +6226,19 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>VAC IIT JEE NEET (Vidyotama Ashram Classes): I checked vaciit.com</t>
+          <t>A quick, polite note on vaciit.com</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
           <t>Dear Vinayak,
-I opened https://vaciit.com/ while looking at coaching institute businesses in Kharghar / Belapur / Nerul, Navi Mumbai.
-Here's what a customer would notice today:
-• Unfinished / dummy text is still visible on the live site
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at coaching institute businesses in Kharghar / Belapur / Nerul, Navi Mumbai, I visited https://vaciit.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A small bit of unfinished / sample text is still visible — easy to tidy up
 • Founder name inconsistency (Prasad vs Yadav)
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can share a free concept page for VAC IIT JEE NEET (Vidyotama Ashram Classes) this week so it's clear what I'd change — no obligation.
-Regards,
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If you'd like, I can share a free concept page for VAC IIT JEE NEET (Vidyotama Ashram Classes) this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6249,11 +6249,11 @@
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>Hi Vinayak,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://vaciit.com/) and a couple of things stood out:
-• Unfinished / dummy text is still visible on the live site
+I'm Vaibhav from DMC Creatives Studio. I came across VAC IIT JEE NEET (Vidyotama Ashram Classes) and had a look at https://vaciit.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A small bit of unfinished / sample text is still visible — easy to tidy up
 • Founder name inconsistency (Prasad vs Yadav)
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can send a free one-page concept for VAC IIT JEE NEET (Vidyotama Ashram Classes) this week so you can see the difference — no charge, no obligation.
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If it would help, I can send a free one-page concept for VAC IIT JEE NEET (Vidyotama Ashram Classes) this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917903370914?text=Hi%20Vinayak%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//vaciit.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%E2%80%A2%20Founder%20name%20inconsistency%20%28Prasad%20vs%20Yadav%29%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917903370914?text=Hi%20Vinayak%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20and%20had%20a%20look%20at%20https%3A//vaciit.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20small%20bit%20of%20unfinished%20/%20sample%20text%20is%20still%20visible%20%E2%80%94%20easy%20to%20tidy%20up%0A%E2%80%A2%20Founder%20name%20inconsistency%20%28Prasad%20vs%20Yadav%29%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@vaciit.com?subject=VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%3A%20I%20checked%20vaciit.com&amp;body=Dear%20Vinayak%2C%0A%0AI%20opened%20https%3A//vaciit.com/%20while%20looking%20at%20coaching%20institute%20businesses%20in%20Kharghar%20/%20Belapur%20/%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%E2%80%A2%20Founder%20name%20inconsistency%20%28Prasad%20vs%20Yadav%29%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@vaciit.com?subject=A%20quick%2C%20polite%20note%20on%20vaciit.com&amp;body=Dear%20Vinayak%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20coaching%20institute%20businesses%20in%20Kharghar%20/%20Belapur%20/%20Nerul%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//vaciit.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20small%20bit%20of%20unfinished%20/%20sample%20text%20is%20still%20visible%20%E2%80%94%20easy%20to%20tidy%20up%0A%E2%80%A2%20Founder%20name%20inconsistency%20%28Prasad%20vs%20Yadav%29%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20VAC%20IIT%20JEE%20NEET%20%28Vidyotama%20Ashram%20Classes%29%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6330,20 +6330,20 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Yuvani Aesthetic Clinic: I checked www.yuvaniaestheticclinic.com</t>
+          <t>A quick, polite note on www.yuvaniaestheticclinic.com</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Dear Nandita,
-I opened https://www.yuvaniaestheticclinic.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• Reviews/text on the site show broken characters, so it looks unmaintained
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Kharghar, Navi Mumbai, I visited https://www.yuvaniaestheticclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A few reviews show broken characters; a quick text fix would make them easier to read
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Limited structured online booking
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Yuvani Aesthetic Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Yuvani Aesthetic Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6354,11 +6354,11 @@
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>Hi Nandita,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.yuvaniaestheticclinic.com/) and a couple of things stood out:
-• Reviews/text on the site show broken characters, so it looks unmaintained
-• The site looks like a generic template rather than your brand
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Yuvani Aesthetic Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Yuvani Aesthetic Clinic and had a look at https://www.yuvaniaestheticclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A few reviews show broken characters; a quick text fix would make them easier to read
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Yuvani Aesthetic Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6367,12 +6367,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917977585840?text=Hi%20Nandita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.yuvaniaestheticclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Reviews/text%20on%20the%20site%20show%20broken%20characters%2C%20so%20it%20looks%20unmaintained%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Yuvani%20Aesthetic%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917977585840?text=Hi%20Nandita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Yuvani%20Aesthetic%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.yuvaniaestheticclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20few%20reviews%20show%20broken%20characters%3B%20a%20quick%20text%20fix%20would%20make%20them%20easier%20to%20read%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Yuvani%20Aesthetic%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@yuvaniaestheticclinic.com?subject=Yuvani%20Aesthetic%20Clinic%3A%20I%20checked%20www.yuvaniaestheticclinic.com&amp;body=Dear%20Nandita%2C%0A%0AI%20opened%20https%3A//www.yuvaniaestheticclinic.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Reviews/text%20on%20the%20site%20show%20broken%20characters%2C%20so%20it%20looks%20unmaintained%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Limited%20structured%20online%20booking%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Yuvani%20Aesthetic%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@yuvaniaestheticclinic.com?subject=A%20quick%2C%20polite%20note%20on%20www.yuvaniaestheticclinic.com&amp;body=Dear%20Nandita%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.yuvaniaestheticclinic.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20few%20reviews%20show%20broken%20characters%3B%20a%20quick%20text%20fix%20would%20make%20them%20easier%20to%20read%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Limited%20structured%20online%20booking%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Yuvani%20Aesthetic%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6435,20 +6435,20 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Baking Magic: I checked bakingmagic.in</t>
+          <t>A quick, polite note on bakingmagic.in</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
           <t>Dear Nalini,
-I opened https://bakingmagic.in/ while looking at bakery businesses in CBD Belapur, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at bakery businesses in CBD Belapur, Navi Mumbai, I visited https://bakingmagic.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • Older WordPress catalogue
-• Social/Instagram links on the site are broken and don't open your real pages
+• The Instagram / Facebook links don't currently open your real pages — a small fix if you'd like people to follow you
 • Enquiry forms instead of modern checkout
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Baking Magic this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Baking Magic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6459,11 +6459,11 @@
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>Hi Nalini,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://bakingmagic.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Baking Magic and had a look at https://bakingmagic.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Older WordPress catalogue
-• Social/Instagram links on the site are broken and don't open your real pages
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Baking Magic this week so you can see the difference — no charge, no obligation.
+• The Instagram / Facebook links don't currently open your real pages — a small fix if you'd like people to follow you
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Baking Magic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919769619932?text=Hi%20Nalini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//bakingmagic.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Older%20WordPress%20catalogue%0A%E2%80%A2%20Social/Instagram%20links%20on%20the%20site%20are%20broken%20and%20don%27t%20open%20your%20real%20pages%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Baking%20Magic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919769619932?text=Hi%20Nalini%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Baking%20Magic%20and%20had%20a%20look%20at%20https%3A//bakingmagic.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Older%20WordPress%20catalogue%0A%E2%80%A2%20The%20Instagram%20/%20Facebook%20links%20don%27t%20currently%20open%20your%20real%20pages%20%E2%80%94%20a%20small%20fix%20if%20you%27d%20like%20people%20to%20follow%20you%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Baking%20Magic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@bakingmagic.in?subject=Baking%20Magic%3A%20I%20checked%20bakingmagic.in&amp;body=Dear%20Nalini%2C%0A%0AI%20opened%20https%3A//bakingmagic.in/%20while%20looking%20at%20bakery%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Older%20WordPress%20catalogue%0A%E2%80%A2%20Social/Instagram%20links%20on%20the%20site%20are%20broken%20and%20don%27t%20open%20your%20real%20pages%0A%E2%80%A2%20Enquiry%20forms%20instead%20of%20modern%20checkout%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Baking%20Magic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@bakingmagic.in?subject=A%20quick%2C%20polite%20note%20on%20bakingmagic.in&amp;body=Dear%20Nalini%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20bakery%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//bakingmagic.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Older%20WordPress%20catalogue%0A%E2%80%A2%20The%20Instagram%20/%20Facebook%20links%20don%27t%20currently%20open%20your%20real%20pages%20%E2%80%94%20a%20small%20fix%20if%20you%27d%20like%20people%20to%20follow%20you%0A%E2%80%A2%20Enquiry%20forms%20instead%20of%20modern%20checkout%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Baking%20Magic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6540,20 +6540,20 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Neeta's Royal Trips &amp; Holidays: I checked neetasroyalholidays.com</t>
+          <t>A quick, polite note on neetasroyalholidays.com</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
           <t>Dear Bharat,
-I opened https://neetasroyalholidays.com/ while looking at travel agent businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at travel agent businesses in Vashi, Navi Mumbai, I visited https://neetasroyalholidays.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Contact page is stronger than marketing pages — conversion hierarchy uneven
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Neeta's Royal Trips &amp; Holidays this week so it's clear what I'd change — no obligation.
-Regards,
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Neeta's Royal Trips &amp; Holidays this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6564,11 +6564,11 @@
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>Hi Bharat,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://neetasroyalholidays.com/) and a couple of things stood out:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• The pages look dated and thin — visitors don't get enough proof to call
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Neeta's Royal Trips &amp; Holidays this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Neeta's Royal Trips &amp; Holidays and had a look at https://neetasroyalholidays.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Neeta's Royal Trips &amp; Holidays this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919920402020?text=Hi%20Bharat%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//neetasroyalholidays.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919920402020?text=Hi%20Bharat%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20and%20had%20a%20look%20at%20https%3A//neetasroyalholidays.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@neetasroyalholidays.in?subject=Neeta%27s%20Royal%20Trips%20%26%20Holidays%3A%20I%20checked%20neetasroyalholidays.com&amp;body=Dear%20Bharat%2C%0A%0AI%20opened%20https%3A//neetasroyalholidays.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Contact%20page%20is%20stronger%20than%20marketing%20pages%20%E2%80%94%20conversion%20hierarchy%20uneven%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@neetasroyalholidays.in?subject=A%20quick%2C%20polite%20note%20on%20neetasroyalholidays.com&amp;body=Dear%20Bharat%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//neetasroyalholidays.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20Contact%20page%20is%20stronger%20than%20marketing%20pages%20%E2%80%94%20conversion%20hierarchy%20uneven%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Neeta%27s%20Royal%20Trips%20%26%20Holidays%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -6641,20 +6641,20 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Physio Matters Clinic &amp; Sports Rehab: I checked physiomatters.in</t>
+          <t>A quick, polite note on physiomatters.in</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
           <t>Dear Ruchita,
-I opened https://physiomatters.in/ while looking at healthcare businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Vashi, Navi Mumbai, I visited https://physiomatters.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • Cardio-pulmonary section uses irrelevant 'modern enterprises' copy
 • Repeated 'View More' UI clutter
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Physio Matters Clinic &amp; Sports Rehab this week so it's clear what I'd change — no obligation.
-Regards,
+• There isn't a visible business email yet, so some people may hesitate to write in
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Physio Matters Clinic &amp; Sports Rehab this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6665,11 +6665,11 @@
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>Hi Ruchita,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://physiomatters.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Physio Matters Clinic &amp; Sports Rehab and had a look at https://physiomatters.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Cardio-pulmonary section uses irrelevant 'modern enterprises' copy
 • Repeated 'View More' UI clutter
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Physio Matters Clinic &amp; Sports Rehab this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Physio Matters Clinic &amp; Sports Rehab this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6678,7 +6678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917304483530?text=Hi%20Ruchita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//physiomatters.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Cardio-pulmonary%20section%20uses%20irrelevant%20%27modern%20enterprises%27%20copy%0A%E2%80%A2%20Repeated%20%27View%20More%27%20UI%20clutter%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Physio%20Matters%20Clinic%20%26%20Sports%20Rehab%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917304483530?text=Hi%20Ruchita%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Physio%20Matters%20Clinic%20%26%20Sports%20Rehab%20and%20had%20a%20look%20at%20https%3A//physiomatters.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Cardio-pulmonary%20section%20uses%20irrelevant%20%27modern%20enterprises%27%20copy%0A%E2%80%A2%20Repeated%20%27View%20More%27%20UI%20clutter%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Physio%20Matters%20Clinic%20%26%20Sports%20Rehab%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr"/>
@@ -6742,18 +6742,18 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Perfect Tutorials: I checked www.perfecttutorials.in</t>
+          <t>A quick, polite note on www.perfecttutorials.in</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
           <t>Dear Vishal,
-I opened https://www.perfecttutorials.in/ while looking at education businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can share a free concept page for Perfect Tutorials this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at education businesses in Kharghar, Navi Mumbai, I visited https://www.perfecttutorials.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If you'd like, I can share a free concept page for Perfect Tutorials this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6764,10 +6764,10 @@
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>Hi Vishal,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.perfecttutorials.in/) and a couple of things stood out:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can send a free one-page concept for Perfect Tutorials this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Perfect Tutorials and had a look at https://www.perfecttutorials.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If it would help, I can send a free one-page concept for Perfect Tutorials this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6776,12 +6776,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919920230990?text=Hi%20Vishal%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.perfecttutorials.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Perfect%20Tutorials%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919920230990?text=Hi%20Vishal%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Perfect%20Tutorials%20and%20had%20a%20look%20at%20https%3A//www.perfecttutorials.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Perfect%20Tutorials%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>mailto:perfecttutorials@yahoo.in?subject=Perfect%20Tutorials%3A%20I%20checked%20www.perfecttutorials.in&amp;body=Dear%20Vishal%2C%0A%0AI%20opened%20https%3A//www.perfecttutorials.in/%20while%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Perfect%20Tutorials%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:perfecttutorials@yahoo.in?subject=A%20quick%2C%20polite%20note%20on%20www.perfecttutorials.in&amp;body=Dear%20Vishal%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20education%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.perfecttutorials.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Perfect%20Tutorials%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -6844,18 +6844,18 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Zellene Dental Care: I checked zellenedentalcare.com</t>
+          <t>A quick, polite note on zellenedentalcare.com</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Dear Avishkar,
-I opened https://zellenedentalcare.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• Leftover template / fake contact details are still showing on the site — not your real number or email
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Zellene Dental Care this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, Navi Mumbai, I visited https://zellenedentalcare.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A leftover template contact still appears on the site (not your real number/email) — worth swapping for yours
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Zellene Dental Care this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6866,10 +6866,10 @@
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>Hi Avishkar,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://zellenedentalcare.com/) and a couple of things stood out:
-• Leftover template / fake contact details are still showing on the site — not your real number or email
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Zellene Dental Care this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Zellene Dental Care and had a look at https://zellenedentalcare.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A leftover template contact still appears on the site (not your real number/email) — worth swapping for yours
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Zellene Dental Care this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6878,12 +6878,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591472142?text=Hi%20Avishkar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//zellenedentalcare.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Leftover%20template%20/%20fake%20contact%20details%20are%20still%20showing%20on%20the%20site%20%E2%80%94%20not%20your%20real%20number%20or%20email%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Zellene%20Dental%20Care%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918591472142?text=Hi%20Avishkar%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Zellene%20Dental%20Care%20and%20had%20a%20look%20at%20https%3A//zellenedentalcare.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20leftover%20template%20contact%20still%20appears%20on%20the%20site%20%28not%20your%20real%20number/email%29%20%E2%80%94%20worth%20swapping%20for%20yours%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Zellene%20Dental%20Care%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@zellenedentalcare.com?subject=Zellene%20Dental%20Care%3A%20I%20checked%20zellenedentalcare.com&amp;body=Dear%20Avishkar%2C%0A%0AI%20opened%20https%3A//zellenedentalcare.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Leftover%20template%20/%20fake%20contact%20details%20are%20still%20showing%20on%20the%20site%20%E2%80%94%20not%20your%20real%20number%20or%20email%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Zellene%20Dental%20Care%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@zellenedentalcare.com?subject=A%20quick%2C%20polite%20note%20on%20zellenedentalcare.com&amp;body=Dear%20Avishkar%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//zellenedentalcare.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20leftover%20template%20contact%20still%20appears%20on%20the%20site%20%28not%20your%20real%20number/email%29%20%E2%80%94%20worth%20swapping%20for%20yours%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Zellene%20Dental%20Care%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -6938,20 +6938,20 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Ardent Smiles: I checked www.ardentsmiles.in</t>
+          <t>A quick, polite note on www.ardentsmiles.in</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
           <t>Dear Vivek,
-I opened https://www.ardentsmiles.in/ while looking at dental businesses in Nerul.
-Here's what a customer would notice today:
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Nerul, I visited https://www.ardentsmiles.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• There isn't a visible business email yet, so some people may hesitate to write in
 • Emoji-heavy hero copy
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Ardent Smiles this week so it's clear what I'd change — no obligation.
-Regards,
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Ardent Smiles this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -6962,11 +6962,11 @@
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>Hi Vivek,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.ardentsmiles.in/) and a couple of things stood out:
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+I'm Vaibhav from DMC Creatives Studio. I came across Ardent Smiles and had a look at https://www.ardentsmiles.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• There isn't a visible business email yet, so some people may hesitate to write in
 • Emoji-heavy hero copy
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Ardent Smiles this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Ardent Smiles this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918097592505?text=Hi%20Vivek%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.ardentsmiles.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%E2%80%A2%20Emoji-heavy%20hero%20copy%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ardent%20Smiles%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918097592505?text=Hi%20Vivek%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Ardent%20Smiles%20and%20had%20a%20look%20at%20https%3A//www.ardentsmiles.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20There%20isn%27t%20a%20visible%20business%20email%20yet%2C%20so%20some%20people%20may%20hesitate%20to%20write%20in%0A%E2%80%A2%20Emoji-heavy%20hero%20copy%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Ardent%20Smiles%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr"/>
@@ -7035,18 +7035,18 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Gunjan Estate Consultant: I checked www.gunjanestate.com</t>
+          <t>A quick, polite note on www.gunjanestate.com</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
           <t>Dear Gunjan,
-I opened https://www.gunjanestate.com/ while looking at real estate broker businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Gunjan Estate Consultant this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at real estate broker businesses in Vashi, Navi Mumbai, I visited https://www.gunjanestate.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Gunjan Estate Consultant this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7057,10 +7057,10 @@
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>Hi Gunjan,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.gunjanestate.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Gunjan Estate Consultant this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Gunjan Estate Consultant and had a look at https://www.gunjanestate.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Gunjan Estate Consultant this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7069,7 +7069,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919820130065?text=Hi%20Gunjan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.gunjanestate.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Gunjan%20Estate%20Consultant%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919820130065?text=Hi%20Gunjan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Gunjan%20Estate%20Consultant%20and%20had%20a%20look%20at%20https%3A//www.gunjanestate.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Gunjan%20Estate%20Consultant%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr"/>
@@ -7125,20 +7125,20 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Mumbai Dental Care: I checked www.mumbaidentalcare.in</t>
+          <t>A quick, polite note on www.mumbaidentalcare.in</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
           <t>Dear Vaibhav,
-I opened https://www.mumbaidentalcare.in/ while looking at dental businesses in Ulwe.
-Here's what a customer would notice today:
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Ulwe, I visited https://www.mumbaidentalcare.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• There isn't a visible business email yet, so some people may hesitate to write in
 • Truncated service blurbs
 • Aggressive 'Fix teeth in 3 Days' marketing claims
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Mumbai Dental Care this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Mumbai Dental Care this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7149,11 +7149,11 @@
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>Hi Vaibhav,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.mumbaidentalcare.in/) and a couple of things stood out:
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+I'm Vaibhav from DMC Creatives Studio. I came across Mumbai Dental Care and had a look at https://www.mumbaidentalcare.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• There isn't a visible business email yet, so some people may hesitate to write in
 • Truncated service blurbs
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Mumbai Dental Care this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Mumbai Dental Care this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7162,7 +7162,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917304319909?text=Hi%20Vaibhav%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.mumbaidentalcare.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%E2%80%A2%20Truncated%20service%20blurbs%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Mumbai%20Dental%20Care%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917304319909?text=Hi%20Vaibhav%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Mumbai%20Dental%20Care%20and%20had%20a%20look%20at%20https%3A//www.mumbaidentalcare.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20There%20isn%27t%20a%20visible%20business%20email%20yet%2C%20so%20some%20people%20may%20hesitate%20to%20write%20in%0A%E2%80%A2%20Truncated%20service%20blurbs%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Mumbai%20Dental%20Care%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr"/>
@@ -7218,20 +7218,20 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Dhriti Dent 'O' Care and Implant Center: I checked dhritidentocare.com</t>
+          <t>A quick, polite note on dhritidentocare.com</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
           <t>Dear Kanchan,
-I opened https://dhritidentocare.com/ while looking at dental businesses in Kamothe.
-Here's what a customer would notice today:
-• Your website sometimes opens an error page (I got a 500) instead of your homepage
-• There are typos on the homepage that look unprofessional
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Dhriti Dent 'O' Care and Implant Center this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kamothe, I visited https://dhritidentocare.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• On one visit the homepage showed an error instead of opening normally (this can happen if the server is overloaded)
+• A couple of small spelling slips on the homepage — easy to fix, and it helps first impressions
+• There isn't a visible business email yet, so some people may hesitate to write in
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Dhriti Dent 'O' Care and Implant Center this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7242,11 +7242,11 @@
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>Hi Kanchan,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://dhritidentocare.com/) and a couple of things stood out:
-• Your website sometimes opens an error page (I got a 500) instead of your homepage
-• There are typos on the homepage that look unprofessional
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Dhriti Dent 'O' Care and Implant Center this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dhriti Dent 'O' Care and Implant Center and had a look at https://dhritidentocare.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• On one visit the homepage showed an error instead of opening normally (this can happen if the server is overloaded)
+• A couple of small spelling slips on the homepage — easy to fix, and it helps first impressions
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Dhriti Dent 'O' Care and Implant Center this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7255,7 +7255,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918356049763?text=Hi%20Kanchan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//dhritidentocare.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20that%20look%20unprofessional%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dhriti%20Dent%20%27O%27%20Care%20and%20Implant%20Center%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918356049763?text=Hi%20Kanchan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dhriti%20Dent%20%27O%27%20Care%20and%20Implant%20Center%20and%20had%20a%20look%20at%20https%3A//dhritidentocare.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20On%20one%20visit%20the%20homepage%20showed%20an%20error%20instead%20of%20opening%20normally%20%28this%20can%20happen%20if%20the%20server%20is%20overloaded%29%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dhriti%20Dent%20%27O%27%20Care%20and%20Implant%20Center%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr"/>
@@ -7311,20 +7311,20 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Lotus Dental Care Clinic: I checked lotusdentalcareclinic.com</t>
+          <t>A quick, polite note on lotusdentalcareclinic.com</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Dear Sonal,
-I opened https://lotusdentalcareclinic.com/ while looking at dental businesses in Vashi.
-Here's what a customer would notice today:
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-• The pages look dated and thin — visitors don't get enough proof to call
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Lotus Dental Care Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Vashi, I visited https://lotusdentalcareclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• There isn't a visible business email yet, so some people may hesitate to write in
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Lotus Dental Care Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7335,11 +7335,11 @@
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>Hi Sonal,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://lotusdentalcareclinic.com/) and a couple of things stood out:
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Lotus Dental Care Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Lotus Dental Care Clinic and had a look at https://lotusdentalcareclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• There isn't a visible business email yet, so some people may hesitate to write in
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Lotus Dental Care Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7348,7 +7348,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919987158061?text=Hi%20Sonal%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//lotusdentalcareclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Lotus%20Dental%20Care%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919987158061?text=Hi%20Sonal%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Lotus%20Dental%20Care%20Clinic%20and%20had%20a%20look%20at%20https%3A//lotusdentalcareclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20There%20isn%27t%20a%20visible%20business%20email%20yet%2C%20so%20some%20people%20may%20hesitate%20to%20write%20in%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Lotus%20Dental%20Care%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr"/>
@@ -7408,20 +7408,20 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Shree Datta Mohini Hospital: I checked sdmhospital.in</t>
+          <t>A quick, polite note on sdmhospital.in</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
           <t>Dear Purshottam,
-I opened https://sdmhospital.in/ while looking at healthcare businesses in Nerul, Navi Mumbai.
-Here's what a customer would notice today:
-• There are typos on the homepage (e.g. 'Weatlh of Experience') that look unprofessional
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Nerul, Navi Mumbai, I visited https://sdmhospital.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• A couple of small spelling slips on the homepage (e.g. 'Weatlh of Experience') — easy to fix, and it helps first impressions
 • No clear public email
 • Dense text-heavy design
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Shree Datta Mohini Hospital this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Shree Datta Mohini Hospital this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7432,11 +7432,11 @@
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>Hi Purshottam,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sdmhospital.in/) and a couple of things stood out:
-• There are typos on the homepage (e.g. 'Weatlh of Experience') that look unprofessional
+I'm Vaibhav from DMC Creatives Studio. I came across Shree Datta Mohini Hospital and had a look at https://sdmhospital.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A couple of small spelling slips on the homepage (e.g. 'Weatlh of Experience') — easy to fix, and it helps first impressions
 • No clear public email
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Shree Datta Mohini Hospital this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Shree Datta Mohini Hospital this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7445,7 +7445,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919769759944?text=Hi%20Purshottam%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sdmhospital.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Weatlh%20of%20Experience%27%29%20that%20look%20unprofessional%0A%E2%80%A2%20No%20clear%20public%20email%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Datta%20Mohini%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919769759944?text=Hi%20Purshottam%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Shree%20Datta%20Mohini%20Hospital%20and%20had%20a%20look%20at%20https%3A//sdmhospital.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Weatlh%20of%20Experience%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%E2%80%A2%20No%20clear%20public%20email%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Datta%20Mohini%20Hospital%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr"/>
@@ -7501,20 +7501,20 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Smile Avenue Dental Clinic: I checked smileavenueclinic.com</t>
+          <t>A quick, polite note on smileavenueclinic.com</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
           <t>Dear Amit,
-I opened https://smileavenueclinic.com/ while looking at dental businesses in Nerul.
-Here's what a customer would notice today:
-• The phone number is missing from the homepage — people can't call you from the first screen
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-• The site still sends patients to Practo to book, instead of capturing the appointment on your own page
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Smile Avenue Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Nerul, I visited https://smileavenueclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The phone number isn't easy to spot on the first screen — putting it in the header usually helps
+• There isn't a visible business email yet, so some people may hesitate to write in
+• Appointments currently go through Practo — a simple booking option on your own site can capture more patients directly
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Smile Avenue Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7525,11 +7525,11 @@
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>Hi Amit,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://smileavenueclinic.com/) and a couple of things stood out:
-• The phone number is missing from the homepage — people can't call you from the first screen
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Smile Avenue Dental Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Smile Avenue Dental Clinic and had a look at https://smileavenueclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The phone number isn't easy to spot on the first screen — putting it in the header usually helps
+• There isn't a visible business email yet, so some people may hesitate to write in
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Smile Avenue Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137267173?text=Hi%20Amit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//smileavenueclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20phone%20number%20is%20missing%20from%20the%20homepage%20%E2%80%94%20people%20can%27t%20call%20you%20from%20the%20first%20screen%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Avenue%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919137267173?text=Hi%20Amit%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Smile%20Avenue%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//smileavenueclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20phone%20number%20isn%27t%20easy%20to%20spot%20on%20the%20first%20screen%20%E2%80%94%20putting%20it%20in%20the%20header%20usually%20helps%0A%E2%80%A2%20There%20isn%27t%20a%20visible%20business%20email%20yet%2C%20so%20some%20people%20may%20hesitate%20to%20write%20in%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Avenue%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr"/>
@@ -7598,19 +7598,19 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The Dental Hut: I checked www.thedentalhut.com</t>
+          <t>A quick, polite note on www.thedentalhut.com</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
           <t>Dear Sunny,
-I opened https://www.thedentalhut.com/ while looking at dental businesses in Airoli, Navi Mumbai.
-Here's what a customer would notice today:
-• The site still sends patients to Practo to book, instead of capturing the appointment on your own page
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Airoli, Navi Mumbai, I visited https://www.thedentalhut.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• Appointments currently go through Practo — a simple booking option on your own site can capture more patients directly
 • Weak WhatsApp click-to-chat path for Airoli families
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for The Dental Hut this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for The Dental Hut this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7621,11 +7621,11 @@
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>Hi Sunny,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.thedentalhut.com/) and a couple of things stood out:
-• The site still sends patients to Practo to book, instead of capturing the appointment on your own page
+I'm Vaibhav from DMC Creatives Studio. I came across The Dental Hut and had a look at https://www.thedentalhut.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• Appointments currently go through Practo — a simple booking option on your own site can capture more patients directly
 • Weak WhatsApp click-to-chat path for Airoli families
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for The Dental Hut this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for The Dental Hut this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918451922257?text=Hi%20Sunny%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.thedentalhut.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20sends%20patients%20to%20Practo%20to%20book%2C%20instead%20of%20capturing%20the%20appointment%20on%20your%20own%20page%0A%E2%80%A2%20Weak%20WhatsApp%20click-to-chat%20path%20for%20Airoli%20families%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20Hut%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918451922257?text=Hi%20Sunny%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20The%20Dental%20Hut%20and%20had%20a%20look%20at%20https%3A//www.thedentalhut.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Appointments%20currently%20go%20through%20Practo%20%E2%80%94%20a%20simple%20booking%20option%20on%20your%20own%20site%20can%20capture%20more%20patients%20directly%0A%E2%80%A2%20Weak%20WhatsApp%20click-to-chat%20path%20for%20Airoli%20families%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dental%20Hut%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr"/>
@@ -7694,19 +7694,19 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Dr Pranav's Physiorehab Clinic: I checked pranavphysiorehab.in</t>
+          <t>A quick, polite note on pranavphysiorehab.in</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
           <t>Dear Pranav,
-I opened https://pranavphysiorehab.in/ while looking at physiotherapy businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at physiotherapy businesses in Kharghar, Navi Mumbai, I visited https://pranavphysiorehab.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • Appointment path is phone/WhatsApp/form heavy
 • Home-visit booking CTA not sharp enough for multi-node Navi Mumbai demand
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr Pranav's Physiorehab Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr Pranav's Physiorehab Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7717,11 +7717,11 @@
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>Hi Pranav,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pranavphysiorehab.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Dr Pranav's Physiorehab Clinic and had a look at https://pranavphysiorehab.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Appointment path is phone/WhatsApp/form heavy
 • Home-visit booking CTA not sharp enough for multi-node Navi Mumbai demand
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr Pranav's Physiorehab Clinic this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr Pranav's Physiorehab Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7730,7 +7730,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833857855?text=Hi%20Pranav%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pranavphysiorehab.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Appointment%20path%20is%20phone/WhatsApp/form%20heavy%0A%E2%80%A2%20Home-visit%20booking%20CTA%20not%20sharp%20enough%20for%20multi-node%20Navi%20Mumbai%20demand%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Pranav%27s%20Physiorehab%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919833857855?text=Hi%20Pranav%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr%20Pranav%27s%20Physiorehab%20Clinic%20and%20had%20a%20look%20at%20https%3A//pranavphysiorehab.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Appointment%20path%20is%20phone/WhatsApp/form%20heavy%0A%E2%80%A2%20Home-visit%20booking%20CTA%20not%20sharp%20enough%20for%20multi-node%20Navi%20Mumbai%20demand%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Pranav%27s%20Physiorehab%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr"/>
@@ -7790,20 +7790,20 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Manasi Shirke Interiors: I checked www.manasishirke.com</t>
+          <t>A quick, polite note on www.manasishirke.com</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Dear Manasi,
-I opened https://www.manasishirke.com/ while looking at interior design businesses in Navi Mumbai.
-Here's what a customer would notice today:
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-• The pages look dated and thin — visitors don't get enough proof to call
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for Manasi Shirke Interiors this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Navi Mumbai, I visited https://www.manasishirke.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• There isn't a visible business email yet, so some people may hesitate to write in
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for Manasi Shirke Interiors this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7814,11 +7814,11 @@
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>Hi Manasi,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.manasishirke.com/) and a couple of things stood out:
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for Manasi Shirke Interiors this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Manasi Shirke Interiors and had a look at https://www.manasishirke.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• There isn't a visible business email yet, so some people may hesitate to write in
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for Manasi Shirke Interiors this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7827,7 +7827,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833831389?text=Hi%20Manasi%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.manasishirke.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Manasi%20Shirke%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919833831389?text=Hi%20Manasi%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Manasi%20Shirke%20Interiors%20and%20had%20a%20look%20at%20https%3A//www.manasishirke.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20There%20isn%27t%20a%20visible%20business%20email%20yet%2C%20so%20some%20people%20may%20hesitate%20to%20write%20in%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Manasi%20Shirke%20Interiors%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr"/>
@@ -7883,20 +7883,20 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Shree Samarth Dental Clinic and Implant Centre: I checked shreesamarthdental.com</t>
+          <t>A quick, polite note on shreesamarthdental.com</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
           <t>Dear Anuradha,
-I opened https://shreesamarthdental.com/ while looking at dental businesses in Belapur.
-Here's what a customer would notice today:
-• Your website sometimes opens an error page (I got a 500) instead of your homepage
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Shree Samarth Dental Clinic and Implant Centre this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Belapur, I visited https://shreesamarthdental.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• On one visit the homepage showed an error instead of opening normally (this can happen if the server is overloaded)
+• There isn't a visible business email yet, so some people may hesitate to write in
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Shree Samarth Dental Clinic and Implant Centre this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -7907,11 +7907,11 @@
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>Hi Anuradha,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://shreesamarthdental.com/) and a couple of things stood out:
-• Your website sometimes opens an error page (I got a 500) instead of your homepage
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Shree Samarth Dental Clinic and Implant Centre this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Shree Samarth Dental Clinic and Implant Centre and had a look at https://shreesamarthdental.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• On one visit the homepage showed an error instead of opening normally (this can happen if the server is overloaded)
+• There isn't a visible business email yet, so some people may hesitate to write in
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Shree Samarth Dental Clinic and Implant Centre this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137814191?text=Hi%20Anuradha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//shreesamarthdental.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Your%20website%20sometimes%20opens%20an%20error%20page%20%28I%20got%20a%20500%29%20instead%20of%20your%20homepage%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Samarth%20Dental%20Clinic%20and%20Implant%20Centre%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919137814191?text=Hi%20Anuradha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Shree%20Samarth%20Dental%20Clinic%20and%20Implant%20Centre%20and%20had%20a%20look%20at%20https%3A//shreesamarthdental.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20On%20one%20visit%20the%20homepage%20showed%20an%20error%20instead%20of%20opening%20normally%20%28this%20can%20happen%20if%20the%20server%20is%20overloaded%29%0A%E2%80%A2%20There%20isn%27t%20a%20visible%20business%20email%20yet%2C%20so%20some%20people%20may%20hesitate%20to%20write%20in%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Samarth%20Dental%20Clinic%20and%20Implant%20Centre%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr"/>
@@ -7980,19 +7980,19 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Smile Please Dental Clinic: I checked www.smiileplease.com</t>
+          <t>A quick, polite note on www.smiileplease.com</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
           <t>Dear Sharad,
-I opened https://www.smiileplease.com/ while looking at dental businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Vashi, Navi Mumbai, I visited https://www.smiileplease.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak conversion hierarchy vs modern competitors
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Smile Please Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Smile Please Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8003,11 +8003,11 @@
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>Hi Sharad,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smiileplease.com/) and a couple of things stood out:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I'm Vaibhav from DMC Creatives Studio. I came across Smile Please Dental Clinic and had a look at https://www.smiileplease.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak conversion hierarchy vs modern competitors
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Smile Please Dental Clinic this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Smile Please Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8016,7 +8016,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919019607843?text=Hi%20Sharad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smiileplease.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Please%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919019607843?text=Hi%20Sharad%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Smile%20Please%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.smiileplease.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Please%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr"/>
@@ -8076,18 +8076,18 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Opal Spa &amp; Salon Nerul: I checked opalspanerul.com</t>
+          <t>A quick, polite note on opalspanerul.com</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://opalspanerul.com/ while looking at salon businesses in Nerul, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Opal Spa &amp; Salon Nerul this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Nerul, Navi Mumbai, I visited https://opalspanerul.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Opal Spa &amp; Salon Nerul this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8098,10 +8098,10 @@
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://opalspanerul.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Opal Spa &amp; Salon Nerul this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Opal Spa &amp; Salon Nerul and had a look at https://opalspanerul.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Opal Spa &amp; Salon Nerul this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917304917886?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//opalspanerul.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Opal%20Spa%20%26%20Salon%20Nerul%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917304917886?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Opal%20Spa%20%26%20Salon%20Nerul%20and%20had%20a%20look%20at%20https%3A//opalspanerul.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Opal%20Spa%20%26%20Salon%20Nerul%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>mailto:opalspanerul2024@gmail.com?subject=Opal%20Spa%20%26%20Salon%20Nerul%3A%20I%20checked%20opalspanerul.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//opalspanerul.com/%20while%20looking%20at%20salon%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Opal%20Spa%20%26%20Salon%20Nerul%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:opalspanerul2024@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20opalspanerul.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20salon%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//opalspanerul.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Opal%20Spa%20%26%20Salon%20Nerul%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8170,20 +8170,20 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Sarovar Annexe: I checked www.sarovarannexe.com</t>
+          <t>A quick, polite note on www.sarovarannexe.com</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.sarovarannexe.com/ while looking at banquet businesses in Kamothe, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The site looks like a generic template rather than your brand
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Sarovar Annexe this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at banquet businesses in Kamothe, Navi Mumbai, I visited https://www.sarovarannexe.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Sarovar Annexe this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8194,11 +8194,11 @@
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.sarovarannexe.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The site looks like a generic template rather than your brand
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Sarovar Annexe this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Sarovar Annexe and had a look at https://www.sarovarannexe.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Sarovar Annexe this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8207,12 +8207,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918422012171?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.sarovarannexe.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sarovar%20Annexe%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918422012171?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sarovar%20Annexe%20and%20had%20a%20look%20at%20https%3A//www.sarovarannexe.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sarovar%20Annexe%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>mailto:sarovarannexe@gmail.com?subject=Sarovar%20Annexe%3A%20I%20checked%20www.sarovarannexe.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.sarovarannexe.com/%20while%20looking%20at%20banquet%20businesses%20in%20Kamothe%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sarovar%20Annexe%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sarovarannexe@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.sarovarannexe.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20banquet%20businesses%20in%20Kamothe%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.sarovarannexe.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Sarovar%20Annexe%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -8271,18 +8271,18 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Dhruvatan Guest House: I checked dhruvatanguesthouse.com</t>
+          <t>A quick, polite note on dhruvatanguesthouse.com</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened http://dhruvatanguesthouse.com/ while looking at hotel businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site still opens on HTTP (no lock/HTTPS), which browsers flag as not secure
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Dhruvatan Guest House this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in Kharghar, Navi Mumbai, I visited http://dhruvatanguesthouse.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The site still opens without the browser lock (HTTPS). Adding it usually helps people feel safer sharing details
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Dhruvatan Guest House this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8293,10 +8293,10 @@
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (http://dhruvatanguesthouse.com/) and a couple of things stood out:
-• The site still opens on HTTP (no lock/HTTPS), which browsers flag as not secure
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Dhruvatan Guest House this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dhruvatan Guest House and had a look at http://dhruvatanguesthouse.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The site still opens without the browser lock (HTTPS). Adding it usually helps people feel safer sharing details
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Dhruvatan Guest House this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8305,12 +8305,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919930810218?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28http%3A//dhruvatanguesthouse.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20still%20opens%20on%20HTTP%20%28no%20lock/HTTPS%29%2C%20which%20browsers%20flag%20as%20not%20secure%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dhruvatan%20Guest%20House%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919930810218?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dhruvatan%20Guest%20House%20and%20had%20a%20look%20at%20http%3A//dhruvatanguesthouse.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20site%20still%20opens%20without%20the%20browser%20lock%20%28HTTPS%29.%20Adding%20it%20usually%20helps%20people%20feel%20safer%20sharing%20details%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dhruvatan%20Guest%20House%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@dhruvatanguesthouse.com?subject=Dhruvatan%20Guest%20House%3A%20I%20checked%20dhruvatanguesthouse.com&amp;body=Hello%2C%0A%0AI%20opened%20http%3A//dhruvatanguesthouse.com/%20while%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20still%20opens%20on%20HTTP%20%28no%20lock/HTTPS%29%2C%20which%20browsers%20flag%20as%20not%20secure%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dhruvatan%20Guest%20House%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@dhruvatanguesthouse.com?subject=A%20quick%2C%20polite%20note%20on%20dhruvatanguesthouse.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20http%3A//dhruvatanguesthouse.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20site%20still%20opens%20without%20the%20browser%20lock%20%28HTTPS%29.%20Adding%20it%20usually%20helps%20people%20feel%20safer%20sharing%20details%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dhruvatan%20Guest%20House%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -8369,20 +8369,20 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Kharghar Multispeciality Hospital: I checked khargharhospital.com</t>
+          <t>A quick, polite note on khargharhospital.com</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://khargharhospital.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The footer still shows leftover website-builder / agency watermarks
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Kharghar, Navi Mumbai, I visited https://khargharhospital.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The footer still shows a website-builder credit — removing it is a small polish
 • Service list is a long form dropdown
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Kharghar Multispeciality Hospital this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Kharghar Multispeciality Hospital this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8393,11 +8393,11 @@
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://khargharhospital.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The footer still shows leftover website-builder / agency watermarks
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Kharghar Multispeciality Hospital this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Kharghar Multispeciality Hospital and had a look at https://khargharhospital.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The footer still shows a website-builder credit — removing it is a small polish
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Kharghar Multispeciality Hospital this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919594810508?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//khargharhospital.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20footer%20still%20shows%20leftover%20website-builder%20/%20agency%20watermarks%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Kharghar%20Multispeciality%20Hospital%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919594810508?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Kharghar%20Multispeciality%20Hospital%20and%20had%20a%20look%20at%20https%3A//khargharhospital.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20footer%20still%20shows%20a%20website-builder%20credit%20%E2%80%94%20removing%20it%20is%20a%20small%20polish%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Kharghar%20Multispeciality%20Hospital%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>mailto:khargharhospital@gmail.com?subject=Kharghar%20Multispeciality%20Hospital%3A%20I%20checked%20khargharhospital.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//khargharhospital.com/%20while%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20footer%20still%20shows%20leftover%20website-builder%20/%20agency%20watermarks%0A%E2%80%A2%20Service%20list%20is%20a%20long%20form%20dropdown%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Kharghar%20Multispeciality%20Hospital%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:khargharhospital@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20khargharhospital.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20healthcare%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//khargharhospital.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20footer%20still%20shows%20a%20website-builder%20credit%20%E2%80%94%20removing%20it%20is%20a%20small%20polish%0A%E2%80%A2%20Service%20list%20is%20a%20long%20form%20dropdown%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Kharghar%20Multispeciality%20Hospital%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -8470,18 +8470,18 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Hotel Lavish Villa: I checked hotellavishvilla.com</t>
+          <t>A quick, polite note on hotellavishvilla.com</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://hotellavishvilla.com/ while looking at hotel businesses in CBD Belapur, Navi Mumbai.
-Here's what a customer would notice today:
-• Unfinished / dummy text is still visible on the live site
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Hotel Lavish Villa this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in CBD Belapur, Navi Mumbai, I visited https://hotellavishvilla.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A small bit of unfinished / sample text is still visible — easy to tidy up
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Hotel Lavish Villa this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8492,10 +8492,10 @@
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotellavishvilla.com/) and a couple of things stood out:
-• Unfinished / dummy text is still visible on the live site
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Hotel Lavish Villa this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Hotel Lavish Villa and had a look at https://hotellavishvilla.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A small bit of unfinished / sample text is still visible — easy to tidy up
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Hotel Lavish Villa this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8504,12 +8504,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652109924?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotellavishvilla.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Lavish%20Villa%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918652109924?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Hotel%20Lavish%20Villa%20and%20had%20a%20look%20at%20https%3A//hotellavishvilla.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20small%20bit%20of%20unfinished%20/%20sample%20text%20is%20still%20visible%20%E2%80%94%20easy%20to%20tidy%20up%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Lavish%20Villa%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>mailto:enquiryhotellavishvilla@gmail.com?subject=Hotel%20Lavish%20Villa%3A%20I%20checked%20hotellavishvilla.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//hotellavishvilla.com/%20while%20looking%20at%20hotel%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Lavish%20Villa%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:enquiryhotellavishvilla@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20hotellavishvilla.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20hotel%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//hotellavishvilla.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20small%20bit%20of%20unfinished%20/%20sample%20text%20is%20still%20visible%20%E2%80%94%20easy%20to%20tidy%20up%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Lavish%20Villa%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -8564,20 +8564,20 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Pacific Banquets: I checked pacificbanquets.co.in</t>
+          <t>A quick, polite note on pacificbanquets.co.in</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://pacificbanquets.co.in/ while looking at banquet businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book Room / Check Availability button, so guests go to Booking.com instead
-• The pages look dated and thin — visitors don't get enough proof to call
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Pacific Banquets this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at banquet businesses in Kharghar, Navi Mumbai, I visited https://pacificbanquets.co.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A simple Check Availability / Book button would help guests book with you instead of going to Booking.com
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Pacific Banquets this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8588,11 +8588,11 @@
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pacificbanquets.co.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book Room / Check Availability button, so guests go to Booking.com instead
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Pacific Banquets this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Pacific Banquets and had a look at https://pacificbanquets.co.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A simple Check Availability / Book button would help guests book with you instead of going to Booking.com
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Pacific Banquets this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8601,12 +8601,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918080610202?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pacificbanquets.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Room%20/%20Check%20Availability%20button%2C%20so%20guests%20go%20to%20Booking.com%20instead%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pacific%20Banquets%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918080610202?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Pacific%20Banquets%20and%20had%20a%20look%20at%20https%3A//pacificbanquets.co.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20simple%20Check%20Availability%20/%20Book%20button%20would%20help%20guests%20book%20with%20you%20instead%20of%20going%20to%20Booking.com%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Pacific%20Banquets%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>mailto:pacificbanquets@gmail.com?subject=Pacific%20Banquets%3A%20I%20checked%20pacificbanquets.co.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//pacificbanquets.co.in/%20while%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Room%20/%20Check%20Availability%20button%2C%20so%20guests%20go%20to%20Booking.com%20instead%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pacific%20Banquets%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:pacificbanquets@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20pacificbanquets.co.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//pacificbanquets.co.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20simple%20Check%20Availability%20/%20Book%20button%20would%20help%20guests%20book%20with%20you%20instead%20of%20going%20to%20Booking.com%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Pacific%20Banquets%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -8661,20 +8661,20 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Sansmaran Banquet &amp; Fine Dine: I checked sansmaran.in</t>
+          <t>A quick, polite note on sansmaran.in</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://sansmaran.in/ while looking at banquet businesses in New Panvel, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book Room / Check Availability button, so guests go to Booking.com instead
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at banquet businesses in New Panvel, Navi Mumbai, I visited https://sansmaran.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A simple Check Availability / Book button would help guests book with you instead of going to Booking.com
 • Table reservation widget incomplete for events
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Sansmaran Banquet &amp; Fine Dine this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Sansmaran Banquet &amp; Fine Dine this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8685,11 +8685,11 @@
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://sansmaran.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book Room / Check Availability button, so guests go to Booking.com instead
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Sansmaran Banquet &amp; Fine Dine this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Sansmaran Banquet &amp; Fine Dine and had a look at https://sansmaran.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A simple Check Availability / Book button would help guests book with you instead of going to Booking.com
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Sansmaran Banquet &amp; Fine Dine this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8698,12 +8698,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652381977?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//sansmaran.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Room%20/%20Check%20Availability%20button%2C%20so%20guests%20go%20to%20Booking.com%20instead%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918652381977?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20and%20had%20a%20look%20at%20https%3A//sansmaran.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20simple%20Check%20Availability%20/%20Book%20button%20would%20help%20guests%20book%20with%20you%20instead%20of%20going%20to%20Booking.com%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>mailto:sansmaranfinedine@gmail.com?subject=Sansmaran%20Banquet%20%26%20Fine%20Dine%3A%20I%20checked%20sansmaran.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//sansmaran.in/%20while%20looking%20at%20banquet%20businesses%20in%20New%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Room%20/%20Check%20Availability%20button%2C%20so%20guests%20go%20to%20Booking.com%20instead%0A%E2%80%A2%20Table%20reservation%20widget%20incomplete%20for%20events%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sansmaranfinedine@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20sansmaran.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20banquet%20businesses%20in%20New%20Panvel%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//sansmaran.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20simple%20Check%20Availability%20/%20Book%20button%20would%20help%20guests%20book%20with%20you%20instead%20of%20going%20to%20Booking.com%0A%E2%80%A2%20Table%20reservation%20widget%20incomplete%20for%20events%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Sansmaran%20Banquet%20%26%20Fine%20Dine%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -8762,18 +8762,18 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>The Spa Vashi: I checked thespavashi.in</t>
+          <t>A quick, polite note on thespavashi.in</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://thespavashi.in/ while looking at salon businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for The Spa Vashi this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Vashi, Navi Mumbai, I visited https://thespavashi.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for The Spa Vashi this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8784,10 +8784,10 @@
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thespavashi.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for The Spa Vashi this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across The Spa Vashi and had a look at https://thespavashi.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for The Spa Vashi this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8796,12 +8796,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004891376?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thespavashi.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Spa%20Vashi%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919004891376?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20The%20Spa%20Vashi%20and%20had%20a%20look%20at%20https%3A//thespavashi.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Spa%20Vashi%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>mailto:thespa.vashi@gmail.com?subject=The%20Spa%20Vashi%3A%20I%20checked%20thespavashi.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//thespavashi.in/%20while%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20The%20Spa%20Vashi%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:thespa.vashi@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20thespavashi.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//thespavashi.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20The%20Spa%20Vashi%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -8860,20 +8860,20 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Dr. Surabhi Clinic (Woman &amp; Child): I checked www.gynecclinic.com</t>
+          <t>A quick, polite note on www.gynecclinic.com</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
           <t>Dear Surabhi,
-I opened https://www.gynecclinic.com/ while looking at healthcare businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site is a basic Wix brochure page — it doesn't look like a serious local brand
-• The pages look dated and thin — visitors don't get enough proof to call
-• There's no clear Book Appointment button — patients have to hunt for a phone number
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Dr. Surabhi Clinic (Woman &amp; Child) this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at healthcare businesses in Kharghar, Navi Mumbai, I visited https://www.gynecclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The site still has a simple builder look; a cleaner custom layout would better match your brand
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Dr. Surabhi Clinic (Woman &amp; Child) this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8884,11 +8884,11 @@
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>Hi Surabhi,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.gynecclinic.com/) and a couple of things stood out:
-• The site is a basic Wix brochure page — it doesn't look like a serious local brand
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Dr. Surabhi Clinic (Woman &amp; Child) this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Surabhi Clinic (Woman &amp; Child) and had a look at https://www.gynecclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The site still has a simple builder look; a cleaner custom layout would better match your brand
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Dr. Surabhi Clinic (Woman &amp; Child) this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8897,7 +8897,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919987360631?text=Hi%20Surabhi%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.gynecclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Surabhi%20Clinic%20%28Woman%20%26%20Child%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919987360631?text=Hi%20Surabhi%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Surabhi%20Clinic%20%28Woman%20%26%20Child%29%20and%20had%20a%20look%20at%20https%3A//www.gynecclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20site%20still%20has%20a%20simple%20builder%20look%3B%20a%20cleaner%20custom%20layout%20would%20better%20match%20your%20brand%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Surabhi%20Clinic%20%28Woman%20%26%20Child%29%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr"/>
@@ -8957,20 +8957,20 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Rainbow Nursing Home: I checked www.rainbownursinghome.com</t>
+          <t>A quick, polite note on www.rainbownursinghome.com</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
           <t>Dear Sahana,
-I opened https://www.rainbownursinghome.com/ while looking at small hospital businesses in Nerul, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at small hospital businesses in Nerul, Navi Mumbai, I visited https://www.rainbownursinghome.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Email shown as broken string 'nursinghomerainbow.com' (missing @)
 • Doctor booking CTAs inconsistent (Dr. Sahana Shetty vs Hegde)
-• The pages look dated and thin — visitors don't get enough proof to call
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Rainbow Nursing Home this week so it's clear what I'd change — no obligation.
-Regards,
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Rainbow Nursing Home this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -8981,11 +8981,11 @@
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Hi Sahana,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.rainbownursinghome.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Rainbow Nursing Home and had a look at https://www.rainbownursinghome.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Email shown as broken string 'nursinghomerainbow.com' (missing @)
 • Doctor booking CTAs inconsistent (Dr. Sahana Shetty vs Hegde)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Rainbow Nursing Home this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Rainbow Nursing Home this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -8994,7 +8994,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919136053699?text=Hi%20Sahana%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.rainbownursinghome.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Email%20shown%20as%20broken%20string%20%27nursinghomerainbow.com%27%20%28missing%20%40%29%0A%E2%80%A2%20Doctor%20booking%20CTAs%20inconsistent%20%28Dr.%20Sahana%20Shetty%20vs%20Hegde%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Rainbow%20Nursing%20Home%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919136053699?text=Hi%20Sahana%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Rainbow%20Nursing%20Home%20and%20had%20a%20look%20at%20https%3A//www.rainbownursinghome.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Email%20shown%20as%20broken%20string%20%27nursinghomerainbow.com%27%20%28missing%20%40%29%0A%E2%80%A2%20Doctor%20booking%20CTAs%20inconsistent%20%28Dr.%20Sahana%20Shetty%20vs%20Hegde%29%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Rainbow%20Nursing%20Home%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr"/>
@@ -9054,20 +9054,20 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Smile Evolve Dental Clinic: I checked www.smileevolve.com</t>
+          <t>A quick, polite note on www.smileevolve.com</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
           <t>Dear Neelesh,
-I opened https://www.smileevolve.com/ while looking at dental businesses in Vashi / Panvel, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Vashi / Panvel, Navi Mumbai, I visited https://www.smileevolve.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Older multi-location layout with dense text blocks
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
+• There isn't a visible business email yet, so some people may hesitate to write in
 • Appointment flow is form/callback heavy rather than modern online booking
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Smile Evolve Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Smile Evolve Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9078,11 +9078,11 @@
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>Hi Neelesh,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.smileevolve.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Smile Evolve Dental Clinic and had a look at https://www.smileevolve.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Older multi-location layout with dense text blocks
-• There's no business email listed on the site, so serious enquiries have nowhere professional to write
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Smile Evolve Dental Clinic this week so you can see the difference — no charge, no obligation.
+• There isn't a visible business email yet, so some people may hesitate to write in
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Smile Evolve Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9091,7 +9091,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919920549676?text=Hi%20Neelesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.smileevolve.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Older%20multi-location%20layout%20with%20dense%20text%20blocks%0A%E2%80%A2%20There%27s%20no%20business%20email%20listed%20on%20the%20site%2C%20so%20serious%20enquiries%20have%20nowhere%20professional%20to%20write%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Evolve%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919920549676?text=Hi%20Neelesh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Smile%20Evolve%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.smileevolve.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Older%20multi-location%20layout%20with%20dense%20text%20blocks%0A%E2%80%A2%20There%20isn%27t%20a%20visible%20business%20email%20yet%2C%20so%20some%20people%20may%20hesitate%20to%20write%20in%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Smile%20Evolve%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr"/>
@@ -9151,18 +9151,18 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Antarachna Interiors: I checked antarachnainteriors.com</t>
+          <t>A quick, polite note on antarachnainteriors.com</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
           <t>Dear Niyanta,
-I opened https://antarachnainteriors.com/ while looking at interior design businesses in CBD Belapur, Navi Mumbai.
-Here's what a customer would notice today:
-• Unfinished / dummy text is still visible on the live site
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for Antarachna Interiors this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in CBD Belapur, Navi Mumbai, I visited https://antarachnainteriors.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A small bit of unfinished / sample text is still visible — easy to tidy up
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for Antarachna Interiors this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9173,10 +9173,10 @@
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>Hi Niyanta,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://antarachnainteriors.com/) and a couple of things stood out:
-• Unfinished / dummy text is still visible on the live site
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for Antarachna Interiors this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Antarachna Interiors and had a look at https://antarachnainteriors.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A small bit of unfinished / sample text is still visible — easy to tidy up
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for Antarachna Interiors this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9185,7 +9185,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918652366868?text=Hi%20Niyanta%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//antarachnainteriors.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Unfinished%20/%20dummy%20text%20is%20still%20visible%20on%20the%20live%20site%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Antarachna%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918652366868?text=Hi%20Niyanta%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Antarachna%20Interiors%20and%20had%20a%20look%20at%20https%3A//antarachnainteriors.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20small%20bit%20of%20unfinished%20/%20sample%20text%20is%20still%20visible%20%E2%80%94%20easy%20to%20tidy%20up%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Antarachna%20Interiors%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr"/>
@@ -9241,20 +9241,20 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Casa Dentique: I checked casadentique.com</t>
+          <t>A quick, polite note on casadentique.com</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Dear Parth,
-I opened https://casadentique.com/ while looking at dental businesses in Seawoods.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Seawoods, I visited https://casadentique.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Email obscured/not clearly published
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
 • Mixed dental + hair transplant messaging dilutes focus
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Casa Dentique this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Casa Dentique this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9265,11 +9265,11 @@
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>Hi Parth,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://casadentique.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Casa Dentique and had a look at https://casadentique.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Email obscured/not clearly published
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Casa Dentique this week so you can see the difference — no charge, no obligation.
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Casa Dentique this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9278,7 +9278,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919820465370?text=Hi%20Parth%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//casadentique.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Email%20obscured/not%20clearly%20published%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Casa%20Dentique%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919820465370?text=Hi%20Parth%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Casa%20Dentique%20and%20had%20a%20look%20at%20https%3A//casadentique.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Email%20obscured/not%20clearly%20published%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Casa%20Dentique%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr"/>
@@ -9338,19 +9338,19 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Anjani Maternity &amp; Nursing Home: I checked www.anjanimaternityhome.com</t>
+          <t>A quick, polite note on www.anjanimaternityhome.com</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
           <t>Dear Manisha,
-I opened https://www.anjanimaternityhome.com/ while looking at small hospital businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• There's no clear Book Appointment button — patients have to hunt for a phone number
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at small hospital businesses in Kharghar, Navi Mumbai, I visited https://www.anjanimaternityhome.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
 • Otherwise cleaner than peers but still weak online appointment/ops tooling
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Anjani Maternity &amp; Nursing Home this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Anjani Maternity &amp; Nursing Home this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9361,11 +9361,11 @@
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>Hi Manisha,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.anjanimaternityhome.com/) and a couple of things stood out:
-• There's no clear Book Appointment button — patients have to hunt for a phone number
+I'm Vaibhav from DMC Creatives Studio. I came across Anjani Maternity &amp; Nursing Home and had a look at https://www.anjanimaternityhome.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
 • Otherwise cleaner than peers but still weak online appointment/ops tooling
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Anjani Maternity &amp; Nursing Home this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Anjani Maternity &amp; Nursing Home this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9374,7 +9374,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919920186010?text=Hi%20Manisha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.anjanimaternityhome.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%E2%80%A2%20Otherwise%20cleaner%20than%20peers%20but%20still%20weak%20online%20appointment/ops%20tooling%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Anjani%20Maternity%20%26%20Nursing%20Home%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919920186010?text=Hi%20Manisha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Anjani%20Maternity%20%26%20Nursing%20Home%20and%20had%20a%20look%20at%20https%3A//www.anjanimaternityhome.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20clear%20Book%20Appointment%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20patients%20%28many%20currently%20have%20to%20look%20for%20a%20number%29%0A%E2%80%A2%20Otherwise%20cleaner%20than%20peers%20but%20still%20weak%20online%20appointment/ops%20tooling%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Anjani%20Maternity%20%26%20Nursing%20Home%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr"/>
@@ -9434,20 +9434,20 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Bombay Diner: I checked bombaydiner.in</t>
+          <t>A quick, polite note on bombaydiner.in</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
           <t>Dear Abhilash,
-I opened https://bombaydiner.in/ while looking at restaurant businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at restaurant businesses in Kharghar, Navi Mumbai, I visited https://bombaydiner.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • No online reservation, menu ordering, or clear enquiry CRM
 • Phone-heavy conversion
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Bombay Diner this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Bombay Diner this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9458,11 +9458,11 @@
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>Hi Abhilash,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://bombaydiner.in/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
+I'm Vaibhav from DMC Creatives Studio. I came across Bombay Diner and had a look at https://bombaydiner.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • No online reservation, menu ordering, or clear enquiry CRM
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Bombay Diner this week so you can see the difference — no charge, no obligation.
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Bombay Diner this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919594545737?text=Hi%20Abhilash%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//bombaydiner.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20No%20online%20reservation%2C%20menu%20ordering%2C%20or%20clear%20enquiry%20CRM%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Bombay%20Diner%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919594545737?text=Hi%20Abhilash%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Bombay%20Diner%20and%20had%20a%20look%20at%20https%3A//bombaydiner.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20No%20online%20reservation%2C%20menu%20ordering%2C%20or%20clear%20enquiry%20CRM%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Bombay%20Diner%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr"/>
@@ -9531,20 +9531,20 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>DentisTree Dental Clinic: I checked ulwedentist.localo.site</t>
+          <t>A quick, polite note on ulwedentist.localo.site</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
           <t>Dear Sumedh,
-I opened https://ulwedentist.localo.site/ while looking at dental businesses in Ulwe, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Ulwe, Navi Mumbai, I visited https://ulwedentist.localo.site/.
+I wanted to share a few small observations, only in case they're helpful:
 • Localo/landing-style site feels temporary
 • Weak brand trust vs owned .in domain
 • Booking still call-first
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for DentisTree Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for DentisTree Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9555,11 +9555,11 @@
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Hi Sumedh,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ulwedentist.localo.site/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across DentisTree Dental Clinic and had a look at https://ulwedentist.localo.site/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Localo/landing-style site feels temporary
 • Weak brand trust vs owned .in domain
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for DentisTree Dental Clinic this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for DentisTree Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9568,7 +9568,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917020902230?text=Hi%20Sumedh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ulwedentist.localo.site/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Localo/landing-style%20site%20feels%20temporary%0A%E2%80%A2%20Weak%20brand%20trust%20vs%20owned%20.in%20domain%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20DentisTree%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917020902230?text=Hi%20Sumedh%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20DentisTree%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//ulwedentist.localo.site/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Localo/landing-style%20site%20feels%20temporary%0A%E2%80%A2%20Weak%20brand%20trust%20vs%20owned%20.in%20domain%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20DentisTree%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr"/>
@@ -9628,20 +9628,20 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Ekdantam Dental Clinic: I checked www.ekdantamdental.in</t>
+          <t>A quick, polite note on www.ekdantamdental.in</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
           <t>Dear Neha,
-I opened https://www.ekdantamdental.in/ while looking at dental businesses in Kopar Khairane, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kopar Khairane, Navi Mumbai, I visited https://www.ekdantamdental.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • Offer-heavy homepage
 • Booking still call-centric
 • Conversion UX not sharp for implant/aligner high tickets
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Ekdantam Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Ekdantam Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9652,11 +9652,11 @@
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>Hi Neha,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.ekdantamdental.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Ekdantam Dental Clinic and had a look at https://www.ekdantamdental.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Offer-heavy homepage
 • Booking still call-centric
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Ekdantam Dental Clinic this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Ekdantam Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917984558946?text=Hi%20Neha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.ekdantamdental.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Offer-heavy%20homepage%0A%E2%80%A2%20Booking%20still%20call-centric%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ekdantam%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917984558946?text=Hi%20Neha%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Ekdantam%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.ekdantamdental.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Offer-heavy%20homepage%0A%E2%80%A2%20Booking%20still%20call-centric%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Ekdantam%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr"/>
@@ -9725,20 +9725,20 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>The Dentalle: I checked thedentalle.com</t>
+          <t>A quick, polite note on thedentalle.com</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Dear Harshada,
-I opened https://thedentalle.com/ while looking at dental businesses in Seawoods, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Seawoods, Navi Mumbai, I visited https://thedentalle.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak online booking CTA
 • Limited trust/portfolio structure for Seawoods catchment
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for The Dentalle this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for The Dentalle this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9749,11 +9749,11 @@
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>Hi Harshada,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thedentalle.com/) and a couple of things stood out:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I'm Vaibhav from DMC Creatives Studio. I came across The Dentalle and had a look at https://thedentalle.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak online booking CTA
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for The Dentalle this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for The Dentalle this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9762,7 +9762,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919819964488?text=Hi%20Harshada%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thedentalle.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20online%20booking%20CTA%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dentalle%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919819964488?text=Hi%20Harshada%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20The%20Dentalle%20and%20had%20a%20look%20at%20https%3A//thedentalle.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20Weak%20online%20booking%20CTA%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Dentalle%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr"/>
@@ -9822,19 +9822,19 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Dr. Neeraj's Dental Clinic and Implant Centre: I checked drneerajdental.in</t>
+          <t>A quick, polite note on drneerajdental.in</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
           <t>Dear Neeraj,
-I opened https://drneerajdental.in/ while looking at dental businesses in Ulwe, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Ulwe, Navi Mumbai, I visited https://drneerajdental.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • Call-now heavy booking
 • Weak structured appointment path for Ulwe growth corridor implant demand
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Dr. Neeraj's Dental Clinic and Implant Centre this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Dr. Neeraj's Dental Clinic and Implant Centre this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9845,11 +9845,11 @@
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>Hi Neeraj,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drneerajdental.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Dr. Neeraj's Dental Clinic and Implant Centre and had a look at https://drneerajdental.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Call-now heavy booking
 • Weak structured appointment path for Ulwe growth corridor implant demand
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Dr. Neeraj's Dental Clinic and Implant Centre this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Dr. Neeraj's Dental Clinic and Implant Centre this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9858,7 +9858,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919326695614?text=Hi%20Neeraj%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drneerajdental.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Call-now%20heavy%20booking%0A%E2%80%A2%20Weak%20structured%20appointment%20path%20for%20Ulwe%20growth%20corridor%20implant%20demand%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Neeraj%27s%20Dental%20Clinic%20and%20Implant%20Centre%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919326695614?text=Hi%20Neeraj%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr.%20Neeraj%27s%20Dental%20Clinic%20and%20Implant%20Centre%20and%20had%20a%20look%20at%20https%3A//drneerajdental.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Call-now%20heavy%20booking%0A%E2%80%A2%20Weak%20structured%20appointment%20path%20for%20Ulwe%20growth%20corridor%20implant%20demand%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr.%20Neeraj%27s%20Dental%20Clinic%20and%20Implant%20Centre%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr"/>
@@ -9918,19 +9918,19 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>The Physio Remedies: I checked www.physioremedies.org</t>
+          <t>A quick, polite note on www.physioremedies.org</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
           <t>Dear Jyoti,
-I opened https://www.physioremedies.org/ while looking at physiotherapy businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at physiotherapy businesses in Kharghar, Navi Mumbai, I visited https://www.physioremedies.org/.
+I wanted to share a few small observations, only in case they're helpful:
 • Clinic listing presence stronger than conversion-led owned site UX
-• There's no clear Book Appointment button — patients have to hunt for a phone number
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for The Physio Remedies this week so it's clear what I'd change — no obligation.
-Regards,
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for The Physio Remedies this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -9941,11 +9941,11 @@
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>Hi Jyoti,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.physioremedies.org/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across The Physio Remedies and had a look at https://www.physioremedies.org/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Clinic listing presence stronger than conversion-led owned site UX
-• There's no clear Book Appointment button — patients have to hunt for a phone number
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for The Physio Remedies this week so you can see the difference — no charge, no obligation.
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for The Physio Remedies this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -9954,7 +9954,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917021216053?text=Hi%20Jyoti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.physioremedies.org/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Clinic%20listing%20presence%20stronger%20than%20conversion-led%20owned%20site%20UX%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Physio%20Remedies%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917021216053?text=Hi%20Jyoti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20The%20Physio%20Remedies%20and%20had%20a%20look%20at%20https%3A//www.physioremedies.org/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Clinic%20listing%20presence%20stronger%20than%20conversion-led%20owned%20site%20UX%0A%E2%80%A2%20A%20clear%20Book%20Appointment%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20patients%20%28many%20currently%20have%20to%20look%20for%20a%20number%29%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20The%20Physio%20Remedies%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr"/>
@@ -10014,18 +10014,18 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Hotel Seashore Residency: I checked hotelseashoreresidency.in</t>
+          <t>A quick, polite note on hotelseashoreresidency.in</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://hotelseashoreresidency.in/ while looking at hotel businesses in CBD Belapur, Navi Mumbai.
-Here's what a customer would notice today:
-• Room/event booking still depends on OTAs instead of a simple booking form on your own site
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Hotel Seashore Residency this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in CBD Belapur, Navi Mumbai, I visited https://hotelseashoreresidency.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• Bookings still go through listing sites — a short form on your own page can help guests book with you directly
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Hotel Seashore Residency this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10036,10 +10036,10 @@
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotelseashoreresidency.in/) and a couple of things stood out:
-• Room/event booking still depends on OTAs instead of a simple booking form on your own site
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Hotel Seashore Residency this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Hotel Seashore Residency and had a look at https://hotelseashoreresidency.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• Bookings still go through listing sites — a short form on your own page can help guests book with you directly
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Hotel Seashore Residency this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10048,12 +10048,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918080207999?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotelseashoreresidency.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Room/event%20booking%20still%20depends%20on%20OTAs%20instead%20of%20a%20simple%20booking%20form%20on%20your%20own%20site%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Seashore%20Residency%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918080207999?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Hotel%20Seashore%20Residency%20and%20had%20a%20look%20at%20https%3A//hotelseashoreresidency.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Bookings%20still%20go%20through%20listing%20sites%20%E2%80%94%20a%20short%20form%20on%20your%20own%20page%20can%20help%20guests%20book%20with%20you%20directly%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Seashore%20Residency%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>mailto:booking@hotelseashoreresidency.in?subject=Hotel%20Seashore%20Residency%3A%20I%20checked%20hotelseashoreresidency.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//hotelseashoreresidency.in/%20while%20looking%20at%20hotel%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Room/event%20booking%20still%20depends%20on%20OTAs%20instead%20of%20a%20simple%20booking%20form%20on%20your%20own%20site%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Seashore%20Residency%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:booking@hotelseashoreresidency.in?subject=A%20quick%2C%20polite%20note%20on%20hotelseashoreresidency.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20hotel%20businesses%20in%20CBD%20Belapur%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//hotelseashoreresidency.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Bookings%20still%20go%20through%20listing%20sites%20%E2%80%94%20a%20short%20form%20on%20your%20own%20page%20can%20help%20guests%20book%20with%20you%20directly%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Seashore%20Residency%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -10112,18 +10112,18 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>FuturistiQ Smiles: I checked futuristiqsmiles.in</t>
+          <t>A quick, polite note on futuristiqsmiles.in</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
           <t>Dear Kruti,
-I opened https://futuristiqsmiles.in/ while looking at dental businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• Placeholder 'Lorem ipsum' dummy text is still visible on the site
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for FuturistiQ Smiles this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, Navi Mumbai, I visited https://futuristiqsmiles.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• A little placeholder text is still visible — easy to replace with your own copy
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for FuturistiQ Smiles this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10134,10 +10134,10 @@
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Hi Kruti,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://futuristiqsmiles.in/) and a couple of things stood out:
-• Placeholder 'Lorem ipsum' dummy text is still visible on the site
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for FuturistiQ Smiles this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across FuturistiQ Smiles and had a look at https://futuristiqsmiles.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A little placeholder text is still visible — easy to replace with your own copy
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for FuturistiQ Smiles this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10146,7 +10146,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917359662682?text=Hi%20Kruti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//futuristiqsmiles.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Placeholder%20%27Lorem%20ipsum%27%20dummy%20text%20is%20still%20visible%20on%20the%20site%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20FuturistiQ%20Smiles%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917359662682?text=Hi%20Kruti%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20FuturistiQ%20Smiles%20and%20had%20a%20look%20at%20https%3A//futuristiqsmiles.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20little%20placeholder%20text%20is%20still%20visible%20%E2%80%94%20easy%20to%20replace%20with%20your%20own%20copy%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20FuturistiQ%20Smiles%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr"/>
@@ -10206,18 +10206,18 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Kanchan Kolge Interiors: I checked kanchankolge.com</t>
+          <t>A quick, polite note on kanchankolge.com</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
           <t>Dear Kanchan,
-I opened https://kanchankolge.com/ while looking at interior design businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for Kanchan Kolge Interiors this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Vashi, Navi Mumbai, I visited https://kanchankolge.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for Kanchan Kolge Interiors this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10228,10 +10228,10 @@
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>Hi Kanchan,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://kanchankolge.com/) and a couple of things stood out:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for Kanchan Kolge Interiors this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Kanchan Kolge Interiors and had a look at https://kanchankolge.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for Kanchan Kolge Interiors this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10240,7 +10240,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919619055472?text=Hi%20Kanchan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//kanchankolge.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Kanchan%20Kolge%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919619055472?text=Hi%20Kanchan%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Kanchan%20Kolge%20Interiors%20and%20had%20a%20look%20at%20https%3A//kanchankolge.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Kanchan%20Kolge%20Interiors%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr"/>
@@ -10296,19 +10296,19 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Khana Junction: I checked khanajunction.com</t>
+          <t>A quick, polite note on khanajunction.com</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://khanajunction.com/ while looking at restaurant businesses in Panvel, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at restaurant businesses in Panvel, Navi Mumbai, I visited https://khanajunction.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Long static menu dump
-• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Khana Junction this week so it's clear what I'd change — no obligation.
-Regards,
+• There's no easy online order yet — a simple menu/checkout often keeps people from switching to Swiggy/Zomato
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Khana Junction this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10319,11 +10319,11 @@
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://khanajunction.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Khana Junction and had a look at https://khanajunction.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Long static menu dump
-• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Khana Junction this week so you can see the difference — no charge, no obligation.
+• There's no easy online order yet — a simple menu/checkout often keeps people from switching to Swiggy/Zomato
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Khana Junction this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10332,7 +10332,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918484989838?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//khanajunction.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Long%20static%20menu%20dump%0A%E2%80%A2%20There%27s%20no%20proper%20online%20order/menu%20checkout%20%E2%80%94%20people%20bounce%20to%20Swiggy/Zomato%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Khana%20Junction%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918484989838?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Khana%20Junction%20and%20had%20a%20look%20at%20https%3A//khanajunction.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Long%20static%20menu%20dump%0A%E2%80%A2%20There%27s%20no%20easy%20online%20order%20yet%20%E2%80%94%20a%20simple%20menu/checkout%20often%20keeps%20people%20from%20switching%20to%20Swiggy/Zomato%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Khana%20Junction%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr"/>
@@ -10392,19 +10392,19 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>KonkanArabia Hospitality &amp; Holiday Group: I checked konkanarabiahospitalitygroup.com</t>
+          <t>A quick, polite note on konkanarabiahospitalitygroup.com</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://konkanarabiahospitalitygroup.com/ while looking at travel agent businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at travel agent businesses in Vashi, Navi Mumbai, I visited https://konkanarabiahospitalitygroup.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Goa travel-agent registration shown valid only through 31-Mar-2025 (stale credential)
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for KonkanArabia Hospitality &amp; Holiday Group this week so it's clear what I'd change — no obligation.
-Regards,
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for KonkanArabia Hospitality &amp; Holiday Group this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10415,11 +10415,11 @@
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://konkanarabiahospitalitygroup.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across KonkanArabia Hospitality &amp; Holiday Group and had a look at https://konkanarabiahospitalitygroup.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Goa travel-agent registration shown valid only through 31-Mar-2025 (stale credential)
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for KonkanArabia Hospitality &amp; Holiday Group this week so you can see the difference — no charge, no obligation.
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for KonkanArabia Hospitality &amp; Holiday Group this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10428,12 +10428,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919370528517?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//konkanarabiahospitalitygroup.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Goa%20travel-agent%20registration%20shown%20valid%20only%20through%2031-Mar-2025%20%28stale%20credential%29%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919370528517?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20and%20had%20a%20look%20at%20https%3A//konkanarabiahospitalitygroup.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Goa%20travel-agent%20registration%20shown%20valid%20only%20through%2031-Mar-2025%20%28stale%20credential%29%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>mailto:bookings@konkanarabiahospitalitygroup.com?subject=KonkanArabia%20Hospitality%20%26%20Holiday%20Group%3A%20I%20checked%20konkanarabiahospitalitygroup.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//konkanarabiahospitalitygroup.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Goa%20travel-agent%20registration%20shown%20valid%20only%20through%2031-Mar-2025%20%28stale%20credential%29%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:bookings@konkanarabiahospitalitygroup.com?subject=A%20quick%2C%20polite%20note%20on%20konkanarabiahospitalitygroup.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20travel%20agent%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//konkanarabiahospitalitygroup.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Goa%20travel-agent%20registration%20shown%20valid%20only%20through%2031-Mar-2025%20%28stale%20credential%29%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20KonkanArabia%20Hospitality%20%26%20Holiday%20Group%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -10492,18 +10492,18 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>KV Design Studio: I checked kvdesignstudio.in</t>
+          <t>A quick, polite note on kvdesignstudio.in</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://kvdesignstudio.in/ while looking at interior design businesses in Panvel, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like SEO/template pages rather than a real project portfolio
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for KV Design Studio this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Panvel, Navi Mumbai, I visited https://kvdesignstudio.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages feel a little generic; a stronger project gallery would better show your actual work
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for KV Design Studio this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10514,10 +10514,10 @@
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://kvdesignstudio.in/) and a couple of things stood out:
-• The site looks like SEO/template pages rather than a real project portfolio
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for KV Design Studio this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across KV Design Studio and had a look at https://kvdesignstudio.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages feel a little generic; a stronger project gallery would better show your actual work
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for KV Design Studio this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10526,12 +10526,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919653613434?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//kvdesignstudio.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20KV%20Design%20Studio%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919653613434?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20KV%20Design%20Studio%20and%20had%20a%20look%20at%20https%3A//kvdesignstudio.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20feel%20a%20little%20generic%3B%20a%20stronger%20project%20gallery%20would%20better%20show%20your%20actual%20work%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20KV%20Design%20Studio%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@kvdesignstudio.in?subject=KV%20Design%20Studio%3A%20I%20checked%20kvdesignstudio.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//kvdesignstudio.in/%20while%20looking%20at%20interior%20design%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20SEO/template%20pages%20rather%20than%20a%20real%20project%20portfolio%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20KV%20Design%20Studio%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@kvdesignstudio.in?subject=A%20quick%2C%20polite%20note%20on%20kvdesignstudio.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20interior%20design%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//kvdesignstudio.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20pages%20feel%20a%20little%20generic%3B%20a%20stronger%20project%20gallery%20would%20better%20show%20your%20actual%20work%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20KV%20Design%20Studio%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -10590,18 +10590,18 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Nerul Gymkhana: I checked nerulgymkhana.com</t>
+          <t>A quick, polite note on nerulgymkhana.com</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://nerulgymkhana.com/ while looking at gym businesses in Nerul, Navi Mumbai.
-Here's what a customer would notice today:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Nerul Gymkhana this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at gym businesses in Nerul, Navi Mumbai, I visited https://nerulgymkhana.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Nerul Gymkhana this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10612,10 +10612,10 @@
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://nerulgymkhana.com/) and a couple of things stood out:
-• Homepage numbers/stats are stuck at 0 (looks unfinished to visitors)
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Nerul Gymkhana this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Nerul Gymkhana and had a look at https://nerulgymkhana.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A few numbers on the homepage still show 0 — visitors may think the page is still being set up
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Nerul Gymkhana this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10624,12 +10624,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919372770138?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//nerulgymkhana.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Nerul%20Gymkhana%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919372770138?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Nerul%20Gymkhana%20and%20had%20a%20look%20at%20https%3A//nerulgymkhana.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Nerul%20Gymkhana%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>mailto:nerulgymkhana@gmail.com?subject=Nerul%20Gymkhana%3A%20I%20checked%20nerulgymkhana.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//nerulgymkhana.com/%20while%20looking%20at%20gym%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Homepage%20numbers/stats%20are%20stuck%20at%200%20%28looks%20unfinished%20to%20visitors%29%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Nerul%20Gymkhana%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:nerulgymkhana@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20nerulgymkhana.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20gym%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//nerulgymkhana.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20few%20numbers%20on%20the%20homepage%20still%20show%200%20%E2%80%94%20visitors%20may%20think%20the%20page%20is%20still%20being%20set%20up%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Nerul%20Gymkhana%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -10684,20 +10684,20 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Nerul Gymkhana Arena One Banquet &amp; Lawn: I checked nerulgymkhana.com/facilities/arenaone</t>
+          <t>A quick, polite note on nerulgymkhana.com/facilities/arenaone</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://nerulgymkhana.com/facilities/arenaone/ while looking at banquet businesses in Nerul, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at banquet businesses in Nerul, Navi Mumbai, I visited https://nerulgymkhana.com/facilities/arenaone/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Event booking buried under club/membership content
 • No dedicated banquet booking flow
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Nerul Gymkhana Arena One Banquet &amp; Lawn this week so it's clear what I'd change — no obligation.
-Regards,
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Nerul Gymkhana Arena One Banquet &amp; Lawn this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10708,11 +10708,11 @@
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://nerulgymkhana.com/facilities/arenaone/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across Nerul Gymkhana Arena One Banquet &amp; Lawn and had a look at https://nerulgymkhana.com/facilities/arenaone/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Event booking buried under club/membership content
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Nerul Gymkhana Arena One Banquet &amp; Lawn this week so you can see the difference — no charge, no obligation.
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Nerul Gymkhana Arena One Banquet &amp; Lawn this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10721,12 +10721,12 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919323620423?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//nerulgymkhana.com/facilities/arenaone/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Event%20booking%20buried%20under%20club/membership%20content%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919323620423?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20and%20had%20a%20look%20at%20https%3A//nerulgymkhana.com/facilities/arenaone/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Event%20booking%20buried%20under%20club/membership%20content%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>mailto:nerulgymkhana@gmail.com?subject=Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%3A%20I%20checked%20nerulgymkhana.com/facilities/arenaone&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//nerulgymkhana.com/facilities/arenaone/%20while%20looking%20at%20banquet%20businesses%20in%20Nerul%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Event%20booking%20buried%20under%20club/membership%20content%0A%E2%80%A2%20No%20dedicated%20banquet%20booking%20flow%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:nerulgymkhana@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20nerulgymkhana.com/facilities/arenaone&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20banquet%20businesses%20in%20Nerul%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//nerulgymkhana.com/facilities/arenaone/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Event%20booking%20buried%20under%20club/membership%20content%0A%E2%80%A2%20No%20dedicated%20banquet%20booking%20flow%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Nerul%20Gymkhana%20Arena%20One%20Banquet%20%26%20Lawn%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -10785,19 +10785,19 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Bigfoot Holidays: I checked www.bigfootholidays.com</t>
+          <t>A quick, polite note on www.bigfootholidays.com</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.bigfootholidays.com/ while looking at travel agent businesses in Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at travel agent businesses in Navi Mumbai, I visited https://www.bigfootholidays.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • CloudM placeholder emails present
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Bigfoot Holidays this week so it's clear what I'd change — no obligation.
-Regards,
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Bigfoot Holidays this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10808,11 +10808,11 @@
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.bigfootholidays.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
+I'm Vaibhav from DMC Creatives Studio. I came across Bigfoot Holidays and had a look at https://www.bigfootholidays.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • CloudM placeholder emails present
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Bigfoot Holidays this week so you can see the difference — no charge, no obligation.
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Bigfoot Holidays this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10821,12 +10821,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918879746848?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.bigfootholidays.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20CloudM%20placeholder%20emails%20present%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Bigfoot%20Holidays%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918879746848?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Bigfoot%20Holidays%20and%20had%20a%20look%20at%20https%3A//www.bigfootholidays.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20CloudM%20placeholder%20emails%20present%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Bigfoot%20Holidays%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>mailto:business@bigfootholidays.com?subject=Bigfoot%20Holidays%3A%20I%20checked%20www.bigfootholidays.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.bigfootholidays.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20CloudM%20placeholder%20emails%20present%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Bigfoot%20Holidays%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:business@bigfootholidays.com?subject=A%20quick%2C%20polite%20note%20on%20www.bigfootholidays.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.bigfootholidays.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20CloudM%20placeholder%20emails%20present%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Bigfoot%20Holidays%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -10885,20 +10885,20 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Crown Logistic Packers and Movers: I checked crownlogisticsindia.co.in</t>
+          <t>A quick, polite note on crownlogisticsindia.co.in</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://crownlogisticsindia.co.in/ while looking at packers &amp; movers businesses in Thane West.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at packers &amp; movers businesses in Thane West, I visited https://crownlogisticsindia.co.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • Heavy keyword repetition
-• There are typos on the homepage (e.g. 'Domestic Servoces') that look unprofessional
-• The site looks like a generic template rather than your brand
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Crown Logistic Packers and Movers this week so it's clear what I'd change — no obligation.
-Regards,
+• A couple of small spelling slips on the homepage (e.g. 'Domestic Servoces') — easy to fix, and it helps first impressions
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Crown Logistic Packers and Movers this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -10909,11 +10909,11 @@
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://crownlogisticsindia.co.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Crown Logistic Packers and Movers and had a look at https://crownlogisticsindia.co.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Heavy keyword repetition
-• There are typos on the homepage (e.g. 'Domestic Servoces') that look unprofessional
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Crown Logistic Packers and Movers this week so you can see the difference — no charge, no obligation.
+• A couple of small spelling slips on the homepage (e.g. 'Domestic Servoces') — easy to fix, and it helps first impressions
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Crown Logistic Packers and Movers this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917420935001?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//crownlogisticsindia.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Heavy%20keyword%20repetition%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Domestic%20Servoces%27%29%20that%20look%20unprofessional%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Crown%20Logistic%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917420935001?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Crown%20Logistic%20Packers%20and%20Movers%20and%20had%20a%20look%20at%20https%3A//crownlogisticsindia.co.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Heavy%20keyword%20repetition%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Domestic%20Servoces%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Crown%20Logistic%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@crownlogisticsindia.co.in?subject=Crown%20Logistic%20Packers%20and%20Movers%3A%20I%20checked%20crownlogisticsindia.co.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//crownlogisticsindia.co.in/%20while%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Thane%20West.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Heavy%20keyword%20repetition%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Domestic%20Servoces%27%29%20that%20look%20unprofessional%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Crown%20Logistic%20Packers%20and%20Movers%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@crownlogisticsindia.co.in?subject=A%20quick%2C%20polite%20note%20on%20crownlogisticsindia.co.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Thane%20West%2C%20I%20visited%20https%3A//crownlogisticsindia.co.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Heavy%20keyword%20repetition%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Domestic%20Servoces%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Crown%20Logistic%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -10986,20 +10986,20 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Henotic Diagnostics: I checked henoticdiagnostics.com</t>
+          <t>A quick, polite note on henoticdiagnostics.com</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://henoticdiagnostics.com/ while looking at diagnostic lab businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at diagnostic lab businesses in Kharghar, Navi Mumbai, I visited https://henoticdiagnostics.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Overloaded booking form with enormous keyword-stuffed test dropdown
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Feels more SEO portal than clinic site
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Henotic Diagnostics this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Henotic Diagnostics this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11010,11 +11010,11 @@
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://henoticdiagnostics.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Henotic Diagnostics and had a look at https://henoticdiagnostics.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Overloaded booking form with enormous keyword-stuffed test dropdown
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Henotic Diagnostics this week so you can see the difference — no charge, no obligation.
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Henotic Diagnostics this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11023,12 +11023,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918879327184?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//henoticdiagnostics.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Overloaded%20booking%20form%20with%20enormous%20keyword-stuffed%20test%20dropdown%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Henotic%20Diagnostics%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918879327184?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Henotic%20Diagnostics%20and%20had%20a%20look%20at%20https%3A//henoticdiagnostics.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Overloaded%20booking%20form%20with%20enormous%20keyword-stuffed%20test%20dropdown%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Henotic%20Diagnostics%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>mailto:henoticdiagnostics@gmail.com?subject=Henotic%20Diagnostics%3A%20I%20checked%20henoticdiagnostics.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//henoticdiagnostics.com/%20while%20looking%20at%20diagnostic%20lab%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Overloaded%20booking%20form%20with%20enormous%20keyword-stuffed%20test%20dropdown%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Feels%20more%20SEO%20portal%20than%20clinic%20site%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Henotic%20Diagnostics%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:henoticdiagnostics@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20henoticdiagnostics.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20diagnostic%20lab%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//henoticdiagnostics.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Overloaded%20booking%20form%20with%20enormous%20keyword-stuffed%20test%20dropdown%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Feels%20more%20SEO%20portal%20than%20clinic%20site%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Henotic%20Diagnostics%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -11083,20 +11083,20 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Hotel Garden Panvel: I checked hotelgardenpanvel.com</t>
+          <t>A quick, polite note on hotelgardenpanvel.com</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://hotelgardenpanvel.com/ while looking at hotel businesses in Panvel, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in Panvel, Navi Mumbai, I visited https://hotelgardenpanvel.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Uses Rediffmail for business contact
-• The pages look dated and thin — visitors don't get enough proof to call
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Stats counters show 0
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Hotel Garden Panvel this week so it's clear what I'd change — no obligation.
-Regards,
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Hotel Garden Panvel this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11107,11 +11107,11 @@
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotelgardenpanvel.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Hotel Garden Panvel and had a look at https://hotelgardenpanvel.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Uses Rediffmail for business contact
-• The pages look dated and thin — visitors don't get enough proof to call
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Hotel Garden Panvel this week so you can see the difference — no charge, no obligation.
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Hotel Garden Panvel this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11120,12 +11120,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833810330?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotelgardenpanvel.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Uses%20Rediffmail%20for%20business%20contact%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Garden%20Panvel%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919833810330?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Hotel%20Garden%20Panvel%20and%20had%20a%20look%20at%20https%3A//hotelgardenpanvel.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Uses%20Rediffmail%20for%20business%20contact%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Garden%20Panvel%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>mailto:hotelg@rediffmail.com?subject=Hotel%20Garden%20Panvel%3A%20I%20checked%20hotelgardenpanvel.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//hotelgardenpanvel.com/%20while%20looking%20at%20hotel%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Uses%20Rediffmail%20for%20business%20contact%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Stats%20counters%20show%200%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Garden%20Panvel%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:hotelg@rediffmail.com?subject=A%20quick%2C%20polite%20note%20on%20hotelgardenpanvel.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20hotel%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//hotelgardenpanvel.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Uses%20Rediffmail%20for%20business%20contact%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20Stats%20counters%20show%200%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Garden%20Panvel%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -11184,20 +11184,20 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Kothari Packers and Movers: I checked kotharipackersandmovers.com</t>
+          <t>A quick, polite note on kotharipackersandmovers.com</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://kotharipackersandmovers.com/ while looking at packers &amp; movers businesses in Nerul / Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
-• There are typos on the homepage (e.g. 'Pakcers') that look unprofessional
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at packers &amp; movers businesses in Nerul / Kharghar, Navi Mumbai, I visited https://kotharipackersandmovers.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• A couple of small spelling slips on the homepage (e.g. 'Pakcers') — easy to fix, and it helps first impressions
 • Weak differentiation vs dozens of similarly named competitors
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Kothari Packers and Movers this week so it's clear what I'd change — no obligation.
-Regards,
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Kothari Packers and Movers this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11208,11 +11208,11 @@
       <c r="N108" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://kotharipackersandmovers.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
-• There are typos on the homepage (e.g. 'Pakcers') that look unprofessional
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Kothari Packers and Movers this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Kothari Packers and Movers and had a look at https://kotharipackersandmovers.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• A couple of small spelling slips on the homepage (e.g. 'Pakcers') — easy to fix, and it helps first impressions
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Kothari Packers and Movers this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11221,12 +11221,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919322512390?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//kotharipackersandmovers.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Pakcers%27%29%20that%20look%20unprofessional%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Kothari%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919322512390?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Kothari%20Packers%20and%20Movers%20and%20had%20a%20look%20at%20https%3A//kotharipackersandmovers.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Pakcers%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Kothari%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@kotharipackersandmovers.com?subject=Kothari%20Packers%20and%20Movers%3A%20I%20checked%20kotharipackersandmovers.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//kotharipackersandmovers.com/%20while%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Nerul%20/%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20%28e.g.%20%27Pakcers%27%29%20that%20look%20unprofessional%0A%E2%80%A2%20Weak%20differentiation%20vs%20dozens%20of%20similarly%20named%20competitors%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Kothari%20Packers%20and%20Movers%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@kotharipackersandmovers.com?subject=A%20quick%2C%20polite%20note%20on%20kotharipackersandmovers.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Nerul%20/%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//kotharipackersandmovers.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%28e.g.%20%27Pakcers%27%29%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%E2%80%A2%20Weak%20differentiation%20vs%20dozens%20of%20similarly%20named%20competitors%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Kothari%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -11285,18 +11285,18 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Reliable Education Classes: I checked reliablejeeneet.in</t>
+          <t>A quick, polite note on reliablejeeneet.in</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://reliablejeeneet.in/ while looking at coaching classes businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can share a free concept page for Reliable Education Classes this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at coaching classes businesses in Vashi, Navi Mumbai, I visited https://reliablejeeneet.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If you'd like, I can share a free concept page for Reliable Education Classes this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11307,10 +11307,10 @@
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://reliablejeeneet.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can send a free one-page concept for Reliable Education Classes this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Reliable Education Classes and had a look at https://reliablejeeneet.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If it would help, I can send a free one-page concept for Reliable Education Classes this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11319,12 +11319,12 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918655177772?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//reliablejeeneet.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Reliable%20Education%20Classes%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918655177772?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Reliable%20Education%20Classes%20and%20had%20a%20look%20at%20https%3A//reliablejeeneet.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Reliable%20Education%20Classes%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>mailto:reliableeducationclasses@gmail.com?subject=Reliable%20Education%20Classes%3A%20I%20checked%20reliablejeeneet.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//reliablejeeneet.in/%20while%20looking%20at%20coaching%20classes%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Reliable%20Education%20Classes%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:reliableeducationclasses@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20reliablejeeneet.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20coaching%20classes%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//reliablejeeneet.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Reliable%20Education%20Classes%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -11383,19 +11383,19 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Shree Classes IIT: I checked shreeclassesiit.com</t>
+          <t>A quick, polite note on shreeclassesiit.com</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://shreeclassesiit.com/ while looking at coaching institute businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
-• The site is hard to use on a phone — it doesn't fit the screen properly
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can share a free concept page for Shree Classes IIT this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at coaching institute businesses in Kharghar, Navi Mumbai, I visited https://shreeclassesiit.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• On a phone the layout is a little tight — making it mobile-friendly usually helps a lot in Navi Mumbai
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If you'd like, I can share a free concept page for Shree Classes IIT this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11406,11 +11406,11 @@
       <c r="N110" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://shreeclassesiit.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
-• The site is hard to use on a phone — it doesn't fit the screen properly
-Parents compare institutes online. A demo-class / admission form on the site captures the enquiry before they call someone else.
-I can send a free one-page concept for Shree Classes IIT this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Shree Classes IIT and had a look at https://shreeclassesiit.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• On a phone the layout is a little tight — making it mobile-friendly usually helps a lot in Navi Mumbai
+Parents compare institutes online first. A simple demo-class / enquiry form often captures the interest while it's warm.
+If it would help, I can send a free one-page concept for Shree Classes IIT this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11419,12 +11419,12 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919222283333?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//shreeclassesiit.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Classes%20IIT%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919222283333?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Shree%20Classes%20IIT%20and%20had%20a%20look%20at%20https%3A//shreeclassesiit.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20On%20a%20phone%20the%20layout%20is%20a%20little%20tight%20%E2%80%94%20making%20it%20mobile-friendly%20usually%20helps%20a%20lot%20in%20Navi%20Mumbai%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Shree%20Classes%20IIT%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@shreeclasses.co.in?subject=Shree%20Classes%20IIT%3A%20I%20checked%20shreeclassesiit.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//shreeclassesiit.com/%20while%20looking%20at%20coaching%20institute%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0AParents%20compare%20institutes%20online.%20A%20demo-class%20/%20admission%20form%20on%20the%20site%20captures%20the%20enquiry%20before%20they%20call%20someone%20else.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Shree%20Classes%20IIT%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@shreeclasses.co.in?subject=A%20quick%2C%20polite%20note%20on%20shreeclassesiit.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20coaching%20institute%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//shreeclassesiit.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20On%20a%20phone%20the%20layout%20is%20a%20little%20tight%20%E2%80%94%20making%20it%20mobile-friendly%20usually%20helps%20a%20lot%20in%20Navi%20Mumbai%0A%0AParents%20compare%20institutes%20online%20first.%20A%20simple%20demo-class%20/%20enquiry%20form%20often%20captures%20the%20interest%20while%20it%27s%20warm.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Shree%20Classes%20IIT%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -11483,19 +11483,19 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Yello Salon: I checked www.yellosalon.in</t>
+          <t>A quick, polite note on www.yellosalon.in</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.yellosalon.in/ while looking at salon businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Vashi, Navi Mumbai, I visited https://www.yellosalon.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Limited conversion structure beyond basic contact block for a Sector 17 salon competing with Peacock/Lakme
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Yello Salon this week so it's clear what I'd change — no obligation.
-Regards,
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Yello Salon this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11506,11 +11506,11 @@
       <c r="N111" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.yellosalon.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across Yello Salon and had a look at https://www.yellosalon.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Limited conversion structure beyond basic contact block for a Sector 17 salon competing with Peacock/Lakme
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Yello Salon this week so you can see the difference — no charge, no obligation.
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Yello Salon this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11519,12 +11519,12 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918655635968?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.yellosalon.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Limited%20conversion%20structure%20beyond%20basic%20contact%20block%20for%20a%20Sector%2017%20salon%20competing%20with%20Peacock/Lakme%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Yello%20Salon%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918655635968?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Yello%20Salon%20and%20had%20a%20look%20at%20https%3A//www.yellosalon.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Limited%20conversion%20structure%20beyond%20basic%20contact%20block%20for%20a%20Sector%2017%20salon%20competing%20with%20Peacock/Lakme%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Yello%20Salon%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>mailto:yellosalon.vashi@gmail.com?subject=Yello%20Salon%3A%20I%20checked%20www.yellosalon.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.yellosalon.in/%20while%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Limited%20conversion%20structure%20beyond%20basic%20contact%20block%20for%20a%20Sector%2017%20salon%20competing%20with%20Peacock/Lakme%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Yello%20Salon%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:yellosalon.vashi@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.yellosalon.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20salon%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.yellosalon.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Limited%20conversion%20structure%20beyond%20basic%20contact%20block%20for%20a%20Sector%2017%20salon%20competing%20with%20Peacock/Lakme%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Yello%20Salon%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -11583,20 +11583,20 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>All India Cargo Packers and Movers: I checked www.allindiapacker.in</t>
+          <t>A quick, polite note on www.allindiapacker.in</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.allindiapacker.in/ while looking at packers &amp; movers businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at packers &amp; movers businesses in Kharghar, Navi Mumbai, I visited https://www.allindiapacker.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • SEO-heavy multi-city pages feel spammy
 • Weak trust UX for high-ticket moves
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for All India Cargo Packers and Movers this week so it's clear what I'd change — no obligation.
-Regards,
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for All India Cargo Packers and Movers this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11607,11 +11607,11 @@
       <c r="N112" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.allindiapacker.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across All India Cargo Packers and Movers and had a look at https://www.allindiapacker.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • SEO-heavy multi-city pages feel spammy
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for All India Cargo Packers and Movers this week so you can see the difference — no charge, no obligation.
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for All India Cargo Packers and Movers this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11620,12 +11620,12 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919320079007?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.allindiapacker.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20multi-city%20pages%20feel%20spammy%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20All%20India%20Cargo%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919320079007?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20All%20India%20Cargo%20Packers%20and%20Movers%20and%20had%20a%20look%20at%20https%3A//www.allindiapacker.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20SEO-heavy%20multi-city%20pages%20feel%20spammy%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20All%20India%20Cargo%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>mailto:sahu.allindia@gmail.com?subject=All%20India%20Cargo%20Packers%20and%20Movers%3A%20I%20checked%20www.allindiapacker.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.allindiapacker.in/%20while%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20multi-city%20pages%20feel%20spammy%0A%E2%80%A2%20Weak%20trust%20UX%20for%20high-ticket%20moves%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20All%20India%20Cargo%20Packers%20and%20Movers%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:sahu.allindia@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.allindiapacker.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20packers%20%26%20movers%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.allindiapacker.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20SEO-heavy%20multi-city%20pages%20feel%20spammy%0A%E2%80%A2%20Weak%20trust%20UX%20for%20high-ticket%20moves%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20All%20India%20Cargo%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -11684,18 +11684,18 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Aristo Real Estate Consultants: I checked aristouniversal.com</t>
+          <t>A quick, polite note on aristouniversal.com</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://aristouniversal.com/ while looking at real estate broker businesses in Seawoods, Navi Mumbai.
-Here's what a customer would notice today:
-• The site is hard to use on a phone — it doesn't fit the screen properly
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Aristo Real Estate Consultants this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at real estate broker businesses in Seawoods, Navi Mumbai, I visited https://aristouniversal.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• On a phone the layout is a little tight — making it mobile-friendly usually helps a lot in Navi Mumbai
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Aristo Real Estate Consultants this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11706,10 +11706,10 @@
       <c r="N113" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://aristouniversal.com/) and a couple of things stood out:
-• The site is hard to use on a phone — it doesn't fit the screen properly
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Aristo Real Estate Consultants this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Aristo Real Estate Consultants and had a look at https://aristouniversal.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• On a phone the layout is a little tight — making it mobile-friendly usually helps a lot in Navi Mumbai
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Aristo Real Estate Consultants this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11718,12 +11718,12 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919130307464?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//aristouniversal.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Aristo%20Real%20Estate%20Consultants%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919130307464?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Aristo%20Real%20Estate%20Consultants%20and%20had%20a%20look%20at%20https%3A//aristouniversal.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20On%20a%20phone%20the%20layout%20is%20a%20little%20tight%20%E2%80%94%20making%20it%20mobile-friendly%20usually%20helps%20a%20lot%20in%20Navi%20Mumbai%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Aristo%20Real%20Estate%20Consultants%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@aristouniversal.com?subject=Aristo%20Real%20Estate%20Consultants%3A%20I%20checked%20aristouniversal.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//aristouniversal.com/%20while%20looking%20at%20real%20estate%20broker%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Aristo%20Real%20Estate%20Consultants%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@aristouniversal.com?subject=A%20quick%2C%20polite%20note%20on%20aristouniversal.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20real%20estate%20broker%20businesses%20in%20Seawoods%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//aristouniversal.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20On%20a%20phone%20the%20layout%20is%20a%20little%20tight%20%E2%80%94%20making%20it%20mobile-friendly%20usually%20helps%20a%20lot%20in%20Navi%20Mumbai%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Aristo%20Real%20Estate%20Consultants%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -11782,19 +11782,19 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Black Fitness Kharghar: I checked blackfitness.co.in</t>
+          <t>A quick, polite note on blackfitness.co.in</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://blackfitness.co.in/ while looking at fitness businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Black Fitness Kharghar this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at fitness businesses in Kharghar, Navi Mumbai, I visited https://blackfitness.co.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Black Fitness Kharghar this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11805,11 +11805,11 @@
       <c r="N114" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://blackfitness.co.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Black Fitness Kharghar this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Black Fitness Kharghar and had a look at https://blackfitness.co.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Black Fitness Kharghar this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11818,12 +11818,12 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004680588?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//blackfitness.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Black%20Fitness%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919004680588?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Black%20Fitness%20Kharghar%20and%20had%20a%20look%20at%20https%3A//blackfitness.co.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Black%20Fitness%20Kharghar%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>mailto:blackfit.kharghar@gmail.com?subject=Black%20Fitness%20Kharghar%3A%20I%20checked%20blackfitness.co.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//blackfitness.co.in/%20while%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Black%20Fitness%20Kharghar%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:blackfit.kharghar@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20blackfitness.co.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//blackfitness.co.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Black%20Fitness%20Kharghar%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -11882,18 +11882,18 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Cynosure Studios: I checked www.cynosurestudio.in</t>
+          <t>A quick, polite note on www.cynosurestudio.in</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.cynosurestudio.in/ while looking at photography studio businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
-I can share a free concept page for Cynosure Studios this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at photography studio businesses in Kharghar, Navi Mumbai, I visited https://www.cynosurestudio.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+People who find you on Google usually decide in a few seconds whether to enquire. A clearer next step on the site often helps.
+If you'd like, I can share a free concept page for Cynosure Studios this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -11904,10 +11904,10 @@
       <c r="N115" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.cynosurestudio.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
-I can send a free one-page concept for Cynosure Studios this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Cynosure Studios and had a look at https://www.cynosurestudio.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+People who find you on Google usually decide in a few seconds whether to enquire. A clearer next step on the site often helps.
+If it would help, I can send a free one-page concept for Cynosure Studios this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -11916,12 +11916,12 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919930022269?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.cynosurestudio.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Cynosure%20Studios%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919930022269?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Cynosure%20Studios%20and%20had%20a%20look%20at%20https%3A//www.cynosurestudio.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APeople%20who%20find%20you%20on%20Google%20usually%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20A%20clearer%20next%20step%20on%20the%20site%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Cynosure%20Studios%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>mailto:cynodigital4@gmail.com?subject=Cynosure%20Studios%3A%20I%20checked%20www.cynosurestudio.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.cynosurestudio.in/%20while%20looking%20at%20photography%20studio%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Cynosure%20Studios%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:cynodigital4@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.cynosurestudio.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20photography%20studio%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.cynosurestudio.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APeople%20who%20find%20you%20on%20Google%20usually%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20A%20clearer%20next%20step%20on%20the%20site%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Cynosure%20Studios%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -11980,19 +11980,19 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>DELECON Design Co.: I checked www.delecondesigns.com</t>
+          <t>A quick, polite note on www.delecondesigns.com</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.delecondesigns.com/ while looking at interior design businesses in Mumbai / Navi Mumbai / Thane.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Mumbai / Navi Mumbai / Thane, I visited https://www.delecondesigns.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • SEO-heavy locality pages can feel spammy
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for DELECON Design Co. this week so it's clear what I'd change — no obligation.
-Regards,
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for DELECON Design Co. this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12003,11 +12003,11 @@
       <c r="N116" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.delecondesigns.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across DELECON Design Co. and had a look at https://www.delecondesigns.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • SEO-heavy locality pages can feel spammy
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for DELECON Design Co. this week so you can see the difference — no charge, no obligation.
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for DELECON Design Co. this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12016,12 +12016,12 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919892505538?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.delecondesigns.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20locality%20pages%20can%20feel%20spammy%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20DELECON%20Design%20Co.%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919892505538?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20DELECON%20Design%20Co.%20and%20had%20a%20look%20at%20https%3A//www.delecondesigns.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20SEO-heavy%20locality%20pages%20can%20feel%20spammy%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20DELECON%20Design%20Co.%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>mailto:delecondesigns@gmail.com?subject=DELECON%20Design%20Co.%3A%20I%20checked%20www.delecondesigns.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.delecondesigns.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Mumbai%20/%20Navi%20Mumbai%20/%20Thane.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20locality%20pages%20can%20feel%20spammy%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20DELECON%20Design%20Co.%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:delecondesigns@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20www.delecondesigns.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20interior%20design%20businesses%20in%20Mumbai%20/%20Navi%20Mumbai%20/%20Thane%2C%20I%20visited%20https%3A//www.delecondesigns.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20SEO-heavy%20locality%20pages%20can%20feel%20spammy%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20DELECON%20Design%20Co.%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -12080,20 +12080,20 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>Patkar Laboratory: I checked patkarlaboratory.com</t>
+          <t>A quick, polite note on patkarlaboratory.com</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://patkarlaboratory.com/ while looking at diagnostic lab businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at diagnostic lab businesses in Vashi, Navi Mumbai, I visited https://patkarlaboratory.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Weak home-collection / test booking UX
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Patkar Laboratory this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Patkar Laboratory this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12104,11 +12104,11 @@
       <c r="N117" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://patkarlaboratory.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Patkar Laboratory this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Patkar Laboratory and had a look at https://patkarlaboratory.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Patkar Laboratory this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12117,12 +12117,12 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919004270644?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//patkarlaboratory.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Patkar%20Laboratory%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919004270644?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Patkar%20Laboratory%20and%20had%20a%20look%20at%20https%3A//patkarlaboratory.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Patkar%20Laboratory%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>mailto:patkarlaboratory@gmail.com?subject=Patkar%20Laboratory%3A%20I%20checked%20patkarlaboratory.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//patkarlaboratory.com/%20while%20looking%20at%20diagnostic%20lab%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Weak%20home-collection%20/%20test%20booking%20UX%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Patkar%20Laboratory%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:patkarlaboratory@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20patkarlaboratory.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20diagnostic%20lab%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//patkarlaboratory.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Weak%20home-collection%20/%20test%20booking%20UX%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Patkar%20Laboratory%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -12181,20 +12181,20 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Pravi Labs: I checked www.pravilabs.in</t>
+          <t>A quick, polite note on www.pravilabs.in</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.pravilabs.in/ while looking at diagnostic lab businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at diagnostic lab businesses in Vashi, Navi Mumbai, I visited https://www.pravilabs.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • Claims mix NABH/NABL/ICMR messaging that can confuse patients
-• The site looks like a generic template rather than your brand
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak test-menu discoverability
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Pravi Labs this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Pravi Labs this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12205,11 +12205,11 @@
       <c r="N118" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.pravilabs.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Pravi Labs and had a look at https://www.pravilabs.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Claims mix NABH/NABL/ICMR messaging that can confuse patients
-• The site looks like a generic template rather than your brand
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Pravi Labs this week so you can see the difference — no charge, no obligation.
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Pravi Labs this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12218,12 +12218,12 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918104022721?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.pravilabs.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Claims%20mix%20NABH/NABL/ICMR%20messaging%20that%20can%20confuse%20patients%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pravi%20Labs%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918104022721?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Pravi%20Labs%20and%20had%20a%20look%20at%20https%3A//www.pravilabs.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Claims%20mix%20NABH/NABL/ICMR%20messaging%20that%20can%20confuse%20patients%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Pravi%20Labs%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>mailto:care@pravilabs.in?subject=Pravi%20Labs%3A%20I%20checked%20www.pravilabs.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.pravilabs.in/%20while%20looking%20at%20diagnostic%20lab%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Claims%20mix%20NABH/NABL/ICMR%20messaging%20that%20can%20confuse%20patients%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20test-menu%20discoverability%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pravi%20Labs%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:care@pravilabs.in?subject=A%20quick%2C%20polite%20note%20on%20www.pravilabs.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20diagnostic%20lab%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.pravilabs.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Claims%20mix%20NABH/NABL/ICMR%20messaging%20that%20can%20confuse%20patients%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Weak%20test-menu%20discoverability%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Pravi%20Labs%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -12278,20 +12278,20 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Pushp Vatika Resort &amp; Lawns: I checked pushpvatikapanvel.com</t>
+          <t>A quick, polite note on pushpvatikapanvel.com</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://pushpvatikapanvel.com/ while looking at hotel businesses in Panvel, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in Panvel, Navi Mumbai, I visited https://pushpvatikapanvel.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Stay booking widget present but banquet/wedding enquiry still phone-heavy
 • Limited WhatsApp prominence on primary CTAs
 • Content blog-heavy vs conversion
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Pushp Vatika Resort &amp; Lawns this week so it's clear what I'd change — no obligation.
-Regards,
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Pushp Vatika Resort &amp; Lawns this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12302,11 +12302,11 @@
       <c r="N119" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://pushpvatikapanvel.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Pushp Vatika Resort &amp; Lawns and had a look at https://pushpvatikapanvel.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Stay booking widget present but banquet/wedding enquiry still phone-heavy
 • Limited WhatsApp prominence on primary CTAs
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Pushp Vatika Resort &amp; Lawns this week so you can see the difference — no charge, no obligation.
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Pushp Vatika Resort &amp; Lawns this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12315,12 +12315,12 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917021474940?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//pushpvatikapanvel.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Stay%20booking%20widget%20present%20but%20banquet/wedding%20enquiry%20still%20phone-heavy%0A%E2%80%A2%20Limited%20WhatsApp%20prominence%20on%20primary%20CTAs%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Pushp%20Vatika%20Resort%20%26%20Lawns%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917021474940?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Pushp%20Vatika%20Resort%20%26%20Lawns%20and%20had%20a%20look%20at%20https%3A//pushpvatikapanvel.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Stay%20booking%20widget%20present%20but%20banquet/wedding%20enquiry%20still%20phone-heavy%0A%E2%80%A2%20Limited%20WhatsApp%20prominence%20on%20primary%20CTAs%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Pushp%20Vatika%20Resort%20%26%20Lawns%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>mailto:reservations@pushpvatikapanvel.com?subject=Pushp%20Vatika%20Resort%20%26%20Lawns%3A%20I%20checked%20pushpvatikapanvel.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//pushpvatikapanvel.com/%20while%20looking%20at%20hotel%20businesses%20in%20Panvel%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Stay%20booking%20widget%20present%20but%20banquet/wedding%20enquiry%20still%20phone-heavy%0A%E2%80%A2%20Limited%20WhatsApp%20prominence%20on%20primary%20CTAs%0A%E2%80%A2%20Content%20blog-heavy%20vs%20conversion%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Pushp%20Vatika%20Resort%20%26%20Lawns%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:reservations@pushpvatikapanvel.com?subject=A%20quick%2C%20polite%20note%20on%20pushpvatikapanvel.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20hotel%20businesses%20in%20Panvel%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//pushpvatikapanvel.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Stay%20booking%20widget%20present%20but%20banquet/wedding%20enquiry%20still%20phone-heavy%0A%E2%80%A2%20Limited%20WhatsApp%20prominence%20on%20primary%20CTAs%0A%E2%80%A2%20Content%20blog-heavy%20vs%20conversion%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Pushp%20Vatika%20Resort%20%26%20Lawns%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -12379,20 +12379,20 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>RC Interior Designers: I checked rcinteriordesigners.com</t>
+          <t>A quick, polite note on rcinteriordesigners.com</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://rcinteriordesigners.com/ while looking at interior design businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Kharghar, Navi Mumbai, I visited https://rcinteriordesigners.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • SEO-heavy service pages
 • Weak project-gallery conversion vs modern interior studios
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for RC Interior Designers this week so it's clear what I'd change — no obligation.
-Regards,
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for RC Interior Designers this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12403,11 +12403,11 @@
       <c r="N120" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://rcinteriordesigners.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across RC Interior Designers and had a look at https://rcinteriordesigners.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • SEO-heavy service pages
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for RC Interior Designers this week so you can see the difference — no charge, no obligation.
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for RC Interior Designers this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12416,12 +12416,12 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919747054419?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//rcinteriordesigners.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20service%20pages%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20RC%20Interior%20Designers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919747054419?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20RC%20Interior%20Designers%20and%20had%20a%20look%20at%20https%3A//rcinteriordesigners.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20SEO-heavy%20service%20pages%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20RC%20Interior%20Designers%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>mailto:nairc20@gmail.com?subject=RC%20Interior%20Designers%3A%20I%20checked%20rcinteriordesigners.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//rcinteriordesigners.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20SEO-heavy%20service%20pages%0A%E2%80%A2%20Weak%20project-gallery%20conversion%20vs%20modern%20interior%20studios%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20RC%20Interior%20Designers%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:nairc20@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20rcinteriordesigners.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//rcinteriordesigners.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20SEO-heavy%20service%20pages%0A%E2%80%A2%20Weak%20project-gallery%20conversion%20vs%20modern%20interior%20studios%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20RC%20Interior%20Designers%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -12480,19 +12480,19 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Sai Leela Banquet: I checked saileelabanquet.com</t>
+          <t>A quick, polite note on saileelabanquet.com</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://saileelabanquet.com/ while looking at banquet businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at banquet businesses in Kharghar, Navi Mumbai, I visited https://saileelabanquet.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Catering-led venue site lacks modern package/enquiry conversion path
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Sai Leela Banquet this week so it's clear what I'd change — no obligation.
-Regards,
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Sai Leela Banquet this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12503,11 +12503,11 @@
       <c r="N121" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://saileelabanquet.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across Sai Leela Banquet and had a look at https://saileelabanquet.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Catering-led venue site lacks modern package/enquiry conversion path
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Sai Leela Banquet this week so you can see the difference — no charge, no obligation.
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Sai Leela Banquet this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918928780318?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//saileelabanquet.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Catering-led%20venue%20site%20lacks%20modern%20package/enquiry%20conversion%20path%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sai%20Leela%20Banquet%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918928780318?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sai%20Leela%20Banquet%20and%20had%20a%20look%20at%20https%3A//saileelabanquet.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Catering-led%20venue%20site%20lacks%20modern%20package/enquiry%20conversion%20path%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sai%20Leela%20Banquet%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>mailto:saileelabanquet@gmail.com?subject=Sai%20Leela%20Banquet%3A%20I%20checked%20saileelabanquet.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//saileelabanquet.com/%20while%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Catering-led%20venue%20site%20lacks%20modern%20package/enquiry%20conversion%20path%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sai%20Leela%20Banquet%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:saileelabanquet@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20saileelabanquet.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//saileelabanquet.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Catering-led%20venue%20site%20lacks%20modern%20package/enquiry%20conversion%20path%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Sai%20Leela%20Banquet%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -12580,20 +12580,20 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Tungsten Fitness Club: I checked tungstenfitness.in</t>
+          <t>A quick, polite note on tungstenfitness.in</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://tungstenfitness.in/ while looking at gym businesses in Vashi / Ghansoli / Nerul / Sanpada, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at gym businesses in Vashi / Ghansoli / Nerul / Sanpada, Navi Mumbai, I visited https://tungstenfitness.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Multi-branch info is hard to scan
 • Weak lead capture vs membership-focused competitors
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Tungsten Fitness Club this week so it's clear what I'd change — no obligation.
-Regards,
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Tungsten Fitness Club this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12604,11 +12604,11 @@
       <c r="N122" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://tungstenfitness.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
+I'm Vaibhav from DMC Creatives Studio. I came across Tungsten Fitness Club and had a look at https://tungstenfitness.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
 • Multi-branch info is hard to scan
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Tungsten Fitness Club this week so you can see the difference — no charge, no obligation.
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Tungsten Fitness Club this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917506006007?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//tungstenfitness.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Multi-branch%20info%20is%20hard%20to%20scan%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Tungsten%20Fitness%20Club%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917506006007?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Tungsten%20Fitness%20Club%20and%20had%20a%20look%20at%20https%3A//tungstenfitness.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Multi-branch%20info%20is%20hard%20to%20scan%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Tungsten%20Fitness%20Club%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>mailto:tungstenfitnessclub@gmail.com?subject=Tungsten%20Fitness%20Club%3A%20I%20checked%20tungstenfitness.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//tungstenfitness.in/%20while%20looking%20at%20gym%20businesses%20in%20Vashi%20/%20Ghansoli%20/%20Nerul%20/%20Sanpada%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20Multi-branch%20info%20is%20hard%20to%20scan%0A%E2%80%A2%20Weak%20lead%20capture%20vs%20membership-focused%20competitors%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Tungsten%20Fitness%20Club%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:tungstenfitnessclub@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20tungstenfitness.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20gym%20businesses%20in%20Vashi%20/%20Ghansoli%20/%20Nerul%20/%20Sanpada%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//tungstenfitness.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20Multi-branch%20info%20is%20hard%20to%20scan%0A%E2%80%A2%20Weak%20lead%20capture%20vs%20membership-focused%20competitors%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Tungsten%20Fitness%20Club%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -12681,20 +12681,20 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Nakshatra Salon &amp; Academy: I checked nakshatrasalonandacademy.in</t>
+          <t>A quick, polite note on nakshatrasalonandacademy.in</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://nakshatrasalonandacademy.in/ while looking at salon businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book Appointment button — patients have to hunt for a phone number
-• The pages look dated and thin — visitors don't get enough proof to call
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Nakshatra Salon &amp; Academy this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Kharghar, Navi Mumbai, I visited https://nakshatrasalonandacademy.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Nakshatra Salon &amp; Academy this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12705,11 +12705,11 @@
       <c r="N123" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://nakshatrasalonandacademy.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• There's no clear Book Appointment button — patients have to hunt for a phone number
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Nakshatra Salon &amp; Academy this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Nakshatra Salon &amp; Academy and had a look at https://nakshatrasalonandacademy.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• A clear Book Appointment button on the homepage would make it easier for patients (many currently have to look for a number)
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Nakshatra Salon &amp; Academy this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12718,12 +12718,12 @@
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918828388004?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//nakshatrasalonandacademy.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Nakshatra%20Salon%20%26%20Academy%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918828388004?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Nakshatra%20Salon%20%26%20Academy%20and%20had%20a%20look%20at%20https%3A//nakshatrasalonandacademy.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Book%20Appointment%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20patients%20%28many%20currently%20have%20to%20look%20for%20a%20number%29%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Nakshatra%20Salon%20%26%20Academy%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>mailto:nakshatrasalonacademy@gmail.com?subject=Nakshatra%20Salon%20%26%20Academy%3A%20I%20checked%20nakshatrasalonandacademy.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//nakshatrasalonandacademy.in/%20while%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20Appointment%20button%20%E2%80%94%20patients%20have%20to%20hunt%20for%20a%20phone%20number%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Nakshatra%20Salon%20%26%20Academy%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:nakshatrasalonacademy@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20nakshatrasalonandacademy.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//nakshatrasalonandacademy.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20A%20clear%20Book%20Appointment%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20patients%20%28many%20currently%20have%20to%20look%20for%20a%20number%29%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Nakshatra%20Salon%20%26%20Academy%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -12782,20 +12782,20 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Sky Banquet: I checked skybanquet.in</t>
+          <t>A quick, polite note on skybanquet.in</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://skybanquet.in/ while looking at banquet businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at banquet businesses in Kharghar, Navi Mumbai, I visited https://skybanquet.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • No clear date-availability enquiry UX
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Sky Banquet this week so it's clear what I'd change — no obligation.
-Regards,
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Sky Banquet this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12806,11 +12806,11 @@
       <c r="N124" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://skybanquet.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-• The pages look dated and thin — visitors don't get enough proof to call
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Sky Banquet this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Sky Banquet and had a look at https://skybanquet.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Sky Banquet this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12819,12 +12819,12 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919324006006?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//skybanquet.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sky%20Banquet%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919324006006?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sky%20Banquet%20and%20had%20a%20look%20at%20https%3A//skybanquet.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sky%20Banquet%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>mailto:skybanquetkharghar@gmail.com?subject=Sky%20Banquet%3A%20I%20checked%20skybanquet.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//skybanquet.in/%20while%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20No%20clear%20date-availability%20enquiry%20UX%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Sky%20Banquet%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:skybanquetkharghar@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20skybanquet.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20banquet%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//skybanquet.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20No%20clear%20date-availability%20enquiry%20UX%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Sky%20Banquet%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -12883,18 +12883,18 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Caramel Bakery: I checked thecaramelbakery.in</t>
+          <t>A quick, polite note on thecaramelbakery.in</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://thecaramelbakery.in/ while looking at bakery businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Caramel Bakery this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at bakery businesses in Kharghar, Navi Mumbai, I visited https://thecaramelbakery.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Caramel Bakery this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -12905,10 +12905,10 @@
       <c r="N125" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://thecaramelbakery.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Caramel Bakery this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Caramel Bakery and had a look at https://thecaramelbakery.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Caramel Bakery this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -12917,12 +12917,12 @@
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967244434?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//thecaramelbakery.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Caramel%20Bakery%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919967244434?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Caramel%20Bakery%20and%20had%20a%20look%20at%20https%3A//thecaramelbakery.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Caramel%20Bakery%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>mailto:caramelkharghar@gmail.com?subject=Caramel%20Bakery%3A%20I%20checked%20thecaramelbakery.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//thecaramelbakery.in/%20while%20looking%20at%20bakery%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Caramel%20Bakery%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:caramelkharghar@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20thecaramelbakery.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20bakery%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//thecaramelbakery.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Caramel%20Bakery%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -12981,18 +12981,18 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Dr Pols Dental Clinic: I checked drpolsdentalclinic.com</t>
+          <t>A quick, polite note on drpolsdentalclinic.com</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://drpolsdentalclinic.com/ while looking at dental businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Dr Pols Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, Navi Mumbai, I visited https://drpolsdentalclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Dr Pols Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13003,10 +13003,10 @@
       <c r="N126" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://drpolsdentalclinic.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Dr Pols Dental Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Dr Pols Dental Clinic and had a look at https://drpolsdentalclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Dr Pols Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13015,12 +13015,12 @@
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918591860677?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//drpolsdentalclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Pols%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918591860677?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Dr%20Pols%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//drpolsdentalclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Dr%20Pols%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@drpolsdentalclinic.com?subject=Dr%20Pols%20Dental%20Clinic%3A%20I%20checked%20drpolsdentalclinic.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//drpolsdentalclinic.com/%20while%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Dr%20Pols%20Dental%20Clinic%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@drpolsdentalclinic.com?subject=A%20quick%2C%20polite%20note%20on%20drpolsdentalclinic.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20dental%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//drpolsdentalclinic.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Dr%20Pols%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -13079,18 +13079,18 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Hotel Three Star: I checked hotelthreestar.com</t>
+          <t>A quick, polite note on hotelthreestar.com</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://hotelthreestar.com/ while looking at hotel businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Hotel Three Star this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in Kharghar, Navi Mumbai, I visited https://hotelthreestar.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Hotel Three Star this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13101,10 +13101,10 @@
       <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotelthreestar.com/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Hotel Three Star this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Hotel Three Star and had a look at https://hotelthreestar.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Hotel Three Star this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13113,12 +13113,12 @@
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918881784197?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotelthreestar.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Three%20Star%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918881784197?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Hotel%20Three%20Star%20and%20had%20a%20look%20at%20https%3A//hotelthreestar.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Three%20Star%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>mailto:support@gmail.com?subject=Hotel%20Three%20Star%3A%20I%20checked%20hotelthreestar.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//hotelthreestar.com/%20while%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Three%20Star%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:support@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20hotelthreestar.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20hotel%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//hotelthreestar.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Hotel%20Three%20Star%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -13177,20 +13177,20 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Travizia Tours and Travels: I checked traviziaworld.com</t>
+          <t>A quick, polite note on traviziaworld.com</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://traviziaworld.com/ while looking at travel agent businesses in Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at travel agent businesses in Navi Mumbai, I visited https://traviziaworld.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Copyright still shows 2016
-• The site looks like a generic template rather than your brand
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak modern package UX
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Travizia Tours and Travels this week so it's clear what I'd change — no obligation.
-Regards,
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Travizia Tours and Travels this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13201,11 +13201,11 @@
       <c r="N128" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://traviziaworld.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Travizia Tours and Travels and had a look at https://traviziaworld.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Copyright still shows 2016
-• The site looks like a generic template rather than your brand
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Travizia Tours and Travels this week so you can see the difference — no charge, no obligation.
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Travizia Tours and Travels this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13214,12 +13214,12 @@
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918898619371?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//traviziaworld.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Copyright%20still%20shows%202016%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Travizia%20Tours%20and%20Travels%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918898619371?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Travizia%20Tours%20and%20Travels%20and%20had%20a%20look%20at%20https%3A//traviziaworld.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Copyright%20still%20shows%202016%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Travizia%20Tours%20and%20Travels%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>mailto:admin@traviziaworld.com?subject=Travizia%20Tours%20and%20Travels%3A%20I%20checked%20traviziaworld.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//traviziaworld.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20Copyright%20still%20shows%202016%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20modern%20package%20UX%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Travizia%20Tours%20and%20Travels%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:admin@traviziaworld.com?subject=A%20quick%2C%20polite%20note%20on%20traviziaworld.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai%2C%20I%20visited%20https%3A//traviziaworld.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20Copyright%20still%20shows%202016%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Weak%20modern%20package%20UX%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Travizia%20Tours%20and%20Travels%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -13278,18 +13278,18 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Unique Interior Decor: I checked uniqueinteriordecor.in</t>
+          <t>A quick, polite note on uniqueinteriordecor.in</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://uniqueinteriordecor.in/ while looking at interior design businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for Unique Interior Decor this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Kharghar, Navi Mumbai, I visited https://uniqueinteriordecor.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for Unique Interior Decor this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13300,10 +13300,10 @@
       <c r="N129" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://uniqueinteriordecor.in/) and a couple of things stood out:
-• The public email on the site is a Gmail address, not a company email (e.g. info@yourbrand.in)
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for Unique Interior Decor this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Unique Interior Decor and had a look at https://uniqueinteriordecor.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The public email is a Gmail address — a simple branded email (like info@yourbrand.in) often feels more professional
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for Unique Interior Decor this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13312,12 +13312,12 @@
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918400007765?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//uniqueinteriordecor.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Unique%20Interior%20Decor%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918400007765?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Unique%20Interior%20Decor%20and%20had%20a%20look%20at%20https%3A//uniqueinteriordecor.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Unique%20Interior%20Decor%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>mailto:uniqueinteriorm@gmail.com?subject=Unique%20Interior%20Decor%3A%20I%20checked%20uniqueinteriordecor.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//uniqueinteriordecor.in/%20while%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20public%20email%20on%20the%20site%20is%20a%20Gmail%20address%2C%20not%20a%20company%20email%20%28e.g.%20info%40yourbrand.in%29%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Unique%20Interior%20Decor%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:uniqueinteriorm@gmail.com?subject=A%20quick%2C%20polite%20note%20on%20uniqueinteriordecor.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//uniqueinteriordecor.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20public%20email%20is%20a%20Gmail%20address%20%E2%80%94%20a%20simple%20branded%20email%20%28like%20info%40yourbrand.in%29%20often%20feels%20more%20professional%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Unique%20Interior%20Decor%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -13372,20 +13372,20 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Eka Dental Care Seawoods: I checked ekadentalcare.com</t>
+          <t>A quick, polite note on ekadentalcare.com</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://ekadentalcare.com/ while looking at dental businesses in Seawoods / Nerul, Navi Mumbai.
-Here's what a customer would notice today:
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Seawoods / Nerul, Navi Mumbai, I visited https://ekadentalcare.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • No doctor/owner profile on Seawoods page
 • No email or WhatsApp CTA visible
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Eka Dental Care Seawoods this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Eka Dental Care Seawoods this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13396,11 +13396,11 @@
       <c r="N130" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ekadentalcare.com/) and a couple of things stood out:
-• The pages look dated and thin — visitors don't get enough proof to call
+I'm Vaibhav from DMC Creatives Studio. I came across Eka Dental Care Seawoods and had a look at https://ekadentalcare.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • No doctor/owner profile on Seawoods page
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Eka Dental Care Seawoods this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Eka Dental Care Seawoods this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13409,7 +13409,7 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918369843353?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ekadentalcare.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20No%20doctor/owner%20profile%20on%20Seawoods%20page%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Eka%20Dental%20Care%20Seawoods%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918369843353?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Eka%20Dental%20Care%20Seawoods%20and%20had%20a%20look%20at%20https%3A//ekadentalcare.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20No%20doctor/owner%20profile%20on%20Seawoods%20page%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Eka%20Dental%20Care%20Seawoods%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr"/>
@@ -13469,20 +13469,20 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Khanna Travels: I checked khannatravels.com</t>
+          <t>A quick, polite note on khannatravels.com</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://khannatravels.com/ while looking at travel agent businesses in Navi Mumbai.
-Here's what a customer would notice today:
-• There are typos on the homepage that look unprofessional
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at travel agent businesses in Navi Mumbai, I visited https://khannatravels.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A couple of small spelling slips on the homepage — easy to fix, and it helps first impressions
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Multiple phone numbers without clear primary sales line
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Khanna Travels this week so it's clear what I'd change — no obligation.
-Regards,
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Khanna Travels this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13493,11 +13493,11 @@
       <c r="N131" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://khannatravels.com/) and a couple of things stood out:
-• There are typos on the homepage that look unprofessional
-• The site looks like a generic template rather than your brand
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Khanna Travels this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Khanna Travels and had a look at https://khannatravels.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A couple of small spelling slips on the homepage — easy to fix, and it helps first impressions
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Khanna Travels this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13506,12 +13506,12 @@
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919167006010?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//khannatravels.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20that%20look%20unprofessional%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Khanna%20Travels%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919167006010?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Khanna%20Travels%20and%20had%20a%20look%20at%20https%3A//khannatravels.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Khanna%20Travels%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>mailto:bookings@khannatravels.com?subject=Khanna%20Travels%3A%20I%20checked%20khannatravels.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//khannatravels.com/%20while%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20that%20look%20unprofessional%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Multiple%20phone%20numbers%20without%20clear%20primary%20sales%20line%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Khanna%20Travels%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:bookings@khannatravels.com?subject=A%20quick%2C%20polite%20note%20on%20khannatravels.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20travel%20agent%20businesses%20in%20Navi%20Mumbai%2C%20I%20visited%20https%3A//khannatravels.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Multiple%20phone%20numbers%20without%20clear%20primary%20sales%20line%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Khanna%20Travels%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -13570,18 +13570,18 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Colour Spa &amp; Hammam: I checked colourspa.co.in</t>
+          <t>A quick, polite note on colourspa.co.in</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://colourspa.co.in/ while looking at salon businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The pages look dated and thin — visitors don't get enough proof to call
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Colour Spa &amp; Hammam this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Kharghar, Navi Mumbai, I visited https://colourspa.co.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Colour Spa &amp; Hammam this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13592,10 +13592,10 @@
       <c r="N132" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://colourspa.co.in/) and a couple of things stood out:
-• The pages look dated and thin — visitors don't get enough proof to call
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Colour Spa &amp; Hammam this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Colour Spa &amp; Hammam and had a look at https://colourspa.co.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Colour Spa &amp; Hammam this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13604,12 +13604,12 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917388887976?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//colourspa.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Colour%20Spa%20%26%20Hammam%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917388887976?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Colour%20Spa%20%26%20Hammam%20and%20had%20a%20look%20at%20https%3A//colourspa.co.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Colour%20Spa%20%26%20Hammam%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@colourspakh.com?subject=Colour%20Spa%20%26%20Hammam%3A%20I%20checked%20colourspa.co.in&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//colourspa.co.in/%20while%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Colour%20Spa%20%26%20Hammam%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@colourspakh.com?subject=A%20quick%2C%20polite%20note%20on%20colourspa.co.in&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20salon%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//colourspa.co.in/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Colour%20Spa%20%26%20Hammam%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -13668,20 +13668,20 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Krishnaay Pure Veg Restaurant: I checked www.krishnaay.com</t>
+          <t>A quick, polite note on www.krishnaay.com</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.krishnaay.com/ while looking at restaurant businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at restaurant businesses in Vashi, Navi Mumbai, I visited https://www.krishnaay.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Address inconsistency across pages
 • Reservation is form/phone only, no live booking
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Krishnaay Pure Veg Restaurant this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Krishnaay Pure Veg Restaurant this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13692,11 +13692,11 @@
       <c r="N133" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.krishnaay.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
+I'm Vaibhav from DMC Creatives Studio. I came across Krishnaay Pure Veg Restaurant and had a look at https://www.krishnaay.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Address inconsistency across pages
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Krishnaay Pure Veg Restaurant this week so you can see the difference — no charge, no obligation.
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Krishnaay Pure Veg Restaurant this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13705,12 +13705,12 @@
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919769788777?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.krishnaay.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Address%20inconsistency%20across%20pages%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Krishnaay%20Pure%20Veg%20Restaurant%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919769788777?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Krishnaay%20Pure%20Veg%20Restaurant%20and%20had%20a%20look%20at%20https%3A//www.krishnaay.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Address%20inconsistency%20across%20pages%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Krishnaay%20Pure%20Veg%20Restaurant%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>mailto:contact@krishnaay.com?subject=Krishnaay%20Pure%20Veg%20Restaurant%3A%20I%20checked%20www.krishnaay.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//www.krishnaay.com/%20while%20looking%20at%20restaurant%20businesses%20in%20Vashi%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Address%20inconsistency%20across%20pages%0A%E2%80%A2%20Reservation%20is%20form/phone%20only%2C%20no%20live%20booking%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Krishnaay%20Pure%20Veg%20Restaurant%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:contact@krishnaay.com?subject=A%20quick%2C%20polite%20note%20on%20www.krishnaay.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20restaurant%20businesses%20in%20Vashi%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//www.krishnaay.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Address%20inconsistency%20across%20pages%0A%E2%80%A2%20Reservation%20is%20form/phone%20only%2C%20no%20live%20booking%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Krishnaay%20Pure%20Veg%20Restaurant%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -13769,18 +13769,18 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Equinox Fitness Kharghar: I checked equinoxfitnessindia.com</t>
+          <t>A quick, polite note on equinoxfitnessindia.com</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://equinoxfitnessindia.com/ while looking at fitness businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Equinox Fitness Kharghar this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at fitness businesses in Kharghar, Navi Mumbai, I visited https://equinoxfitnessindia.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Equinox Fitness Kharghar this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13791,10 +13791,10 @@
       <c r="N134" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://equinoxfitnessindia.com/) and a couple of things stood out:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Equinox Fitness Kharghar this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Equinox Fitness Kharghar and had a look at https://equinoxfitnessindia.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Equinox Fitness Kharghar this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917475669291?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//equinoxfitnessindia.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Equinox%20Fitness%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917475669291?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Equinox%20Fitness%20Kharghar%20and%20had%20a%20look%20at%20https%3A//equinoxfitnessindia.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Equinox%20Fitness%20Kharghar%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>mailto:support@equinoxfitnessclub.com?subject=Equinox%20Fitness%20Kharghar%3A%20I%20checked%20equinoxfitnessindia.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//equinoxfitnessindia.com/%20while%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Equinox%20Fitness%20Kharghar%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:support@equinoxfitnessclub.com?subject=A%20quick%2C%20polite%20note%20on%20equinoxfitnessindia.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20fitness%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//equinoxfitnessindia.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Equinox%20Fitness%20Kharghar%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -13859,20 +13859,20 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Hotel Khandesh &amp; Banquet: I checked hotelkhandesh.in</t>
+          <t>A quick, polite note on hotelkhandesh.in</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://hotelkhandesh.in/ while looking at hotel businesses in New Panvel (Khanda Colony), Navi Mumbai.
-Here's what a customer would notice today:
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in New Panvel (Khanda Colony), Navi Mumbai, I visited https://hotelkhandesh.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Booking path unclear (phone banner only)
-• The site looks like a generic template rather than your brand
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Hotel Khandesh &amp; Banquet this week so it's clear what I'd change — no obligation.
-Regards,
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Hotel Khandesh &amp; Banquet this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13883,11 +13883,11 @@
       <c r="N135" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://hotelkhandesh.in/) and a couple of things stood out:
-• The pages look dated and thin — visitors don't get enough proof to call
+I'm Vaibhav from DMC Creatives Studio. I came across Hotel Khandesh &amp; Banquet and had a look at https://hotelkhandesh.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Booking path unclear (phone banner only)
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Hotel Khandesh &amp; Banquet this week so you can see the difference — no charge, no obligation.
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Hotel Khandesh &amp; Banquet this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13896,7 +13896,7 @@
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919833406722?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//hotelkhandesh.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Booking%20path%20unclear%20%28phone%20banner%20only%29%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Khandesh%20%26%20Banquet%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919833406722?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Hotel%20Khandesh%20%26%20Banquet%20and%20had%20a%20look%20at%20https%3A//hotelkhandesh.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20Booking%20path%20unclear%20%28phone%20banner%20only%29%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Hotel%20Khandesh%20%26%20Banquet%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr"/>
@@ -13956,18 +13956,18 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Treka Interiors: I checked trekainteriors.com</t>
+          <t>A quick, polite note on trekainteriors.com</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://trekainteriors.com/ while looking at interior design businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for Treka Interiors this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Kharghar, Navi Mumbai, I visited https://trekainteriors.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for Treka Interiors this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -13978,10 +13978,10 @@
       <c r="N136" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://trekainteriors.com/) and a couple of things stood out:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for Treka Interiors this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Treka Interiors and had a look at https://trekainteriors.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for Treka Interiors this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -13990,12 +13990,12 @@
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918369497873?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//trekainteriors.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Treka%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918369497873?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Treka%20Interiors%20and%20had%20a%20look%20at%20https%3A//trekainteriors.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Treka%20Interiors%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>mailto:info@trekainteriors.com?subject=Treka%20Interiors%3A%20I%20checked%20trekainteriors.com&amp;body=Hello%2C%0A%0AI%20opened%20https%3A//trekainteriors.com/%20while%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai.%0A%0AHere%27s%20what%20a%20customer%20would%20notice%20today%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20share%20a%20free%20concept%20page%20for%20Treka%20Interiors%20this%20week%20so%20it%27s%20clear%20what%20I%27d%20change%20%E2%80%94%20no%20obligation.%0A%0ARegards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>mailto:info@trekainteriors.com?subject=A%20quick%2C%20polite%20note%20on%20trekainteriors.com&amp;body=Hello%2C%0A%0AI%20hope%20you%27re%20well.%20I%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20While%20looking%20at%20interior%20design%20businesses%20in%20Kharghar%2C%20Navi%20Mumbai%2C%20I%20visited%20https%3A//trekainteriors.com/.%0A%0AI%20wanted%20to%20share%20a%20few%20small%20observations%2C%20only%20in%20case%20they%27re%20helpful%3A%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20you%27d%20like%2C%20I%20can%20share%20a%20free%20concept%20page%20for%20Treka%20Interiors%20this%20week%20so%20you%20can%20see%20what%20a%20clearer%20version%20might%20look%20like.%20No%20obligation%20at%20all.%0A%0AWarm%20regards%2C%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Ahello%40dmcstudio.in%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -14050,20 +14050,20 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Vivastu Interiors: I checked vivastuinteriors.com</t>
+          <t>A quick, polite note on vivastuinteriors.com</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://vivastuinteriors.com/ while looking at interior design businesses in Seawoods, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at interior design businesses in Seawoods, Navi Mumbai, I visited https://vivastuinteriors.com/.
+I wanted to share a few small observations, only in case they're helpful:
 • Testimonials still contain placeholder '[Interior Designer's Name]'
 • Process copy mentions Livspace booking amounts
-• Unfinished / dummy text is still visible on the live site
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can share a free concept page for Vivastu Interiors this week so it's clear what I'd change — no obligation.
-Regards,
+• A small bit of unfinished / sample text is still visible — easy to tidy up
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If you'd like, I can share a free concept page for Vivastu Interiors this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14074,11 +14074,11 @@
       <c r="N137" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://vivastuinteriors.com/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Vivastu Interiors and had a look at https://vivastuinteriors.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • Testimonials still contain placeholder '[Interior Designer's Name]'
 • Process copy mentions Livspace booking amounts
-Homeowners shortlist 3 designers from Google. A clear project gallery + quote form gets the site visit.
-I can send a free one-page concept for Vivastu Interiors this week so you can see the difference — no charge, no obligation.
+Homeowners usually shortlist 2–3 designers from Google. A clear project gallery and quote form often wins the site visit.
+If it would help, I can send a free one-page concept for Vivastu Interiors this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14087,7 +14087,7 @@
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917506393366?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//vivastuinteriors.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Testimonials%20still%20contain%20placeholder%20%27%5BInterior%20Designer%27s%20Name%5D%27%0A%E2%80%A2%20Process%20copy%20mentions%20Livspace%20booking%20amounts%0A%0AHomeowners%20shortlist%203%20designers%20from%20Google.%20A%20clear%20project%20gallery%20%2B%20quote%20form%20gets%20the%20site%20visit.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Vivastu%20Interiors%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917506393366?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Vivastu%20Interiors%20and%20had%20a%20look%20at%20https%3A//vivastuinteriors.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Testimonials%20still%20contain%20placeholder%20%27%5BInterior%20Designer%27s%20Name%5D%27%0A%E2%80%A2%20Process%20copy%20mentions%20Livspace%20booking%20amounts%0A%0AHomeowners%20usually%20shortlist%202%E2%80%933%20designers%20from%20Google.%20A%20clear%20project%20gallery%20and%20quote%20form%20often%20wins%20the%20site%20visit.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Vivastu%20Interiors%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr"/>
@@ -14143,19 +14143,19 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Arise Gym (Kharghar): I checked arisefitness.in/gym-at-kharghar</t>
+          <t>A quick, polite note on arisefitness.in/gym-at-kharghar</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://arisefitness.in/gym-at-kharghar/ while looking at gym businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
-• The site is hard to use on a phone — it doesn't fit the screen properly
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Arise Gym (Kharghar) this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at gym businesses in Kharghar, Navi Mumbai, I visited https://arisefitness.in/gym-at-kharghar/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• On a phone the layout is a little tight — making it mobile-friendly usually helps a lot in Navi Mumbai
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Arise Gym (Kharghar) this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14166,11 +14166,11 @@
       <c r="N138" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://arisefitness.in/gym-at-kharghar/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
-• The site is hard to use on a phone — it doesn't fit the screen properly
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Arise Gym (Kharghar) this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Arise Gym (Kharghar) and had a look at https://arisefitness.in/gym-at-kharghar/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• On a phone the layout is a little tight — making it mobile-friendly usually helps a lot in Navi Mumbai
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Arise Gym (Kharghar) this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14179,7 +14179,7 @@
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919137764238?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//arisefitness.in/gym-at-kharghar/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20site%20is%20hard%20to%20use%20on%20a%20phone%20%E2%80%94%20it%20doesn%27t%20fit%20the%20screen%20properly%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Arise%20Gym%20%28Kharghar%29%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919137764238?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Arise%20Gym%20%28Kharghar%29%20and%20had%20a%20look%20at%20https%3A//arisefitness.in/gym-at-kharghar/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20On%20a%20phone%20the%20layout%20is%20a%20little%20tight%20%E2%80%94%20making%20it%20mobile-friendly%20usually%20helps%20a%20lot%20in%20Navi%20Mumbai%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Arise%20Gym%20%28Kharghar%29%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr"/>
@@ -14235,18 +14235,18 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>Fantasy Salon and Spa Vashi Plaza: I checked www.fantasyspavashi.in</t>
+          <t>A quick, polite note on www.fantasyspavashi.in</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.fantasyspavashi.in/ while looking at salon businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The copyright year on the site is old, so it looks abandoned
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Fantasy Salon and Spa Vashi Plaza this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Vashi, Navi Mumbai, I visited https://www.fantasyspavashi.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Fantasy Salon and Spa Vashi Plaza this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14257,10 +14257,10 @@
       <c r="N139" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.fantasyspavashi.in/) and a couple of things stood out:
-• The copyright year on the site is old, so it looks abandoned
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Fantasy Salon and Spa Vashi Plaza this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Fantasy Salon and Spa Vashi Plaza and had a look at https://www.fantasyspavashi.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The copyright year looks a little old, so some visitors may assume the site hasn't been updated recently
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Fantasy Salon and Spa Vashi Plaza this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14269,7 +14269,7 @@
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919892302930?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.fantasyspavashi.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20copyright%20year%20on%20the%20site%20is%20old%2C%20so%20it%20looks%20abandoned%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Fantasy%20Salon%20and%20Spa%20Vashi%20Plaza%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919892302930?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Fantasy%20Salon%20and%20Spa%20Vashi%20Plaza%20and%20had%20a%20look%20at%20https%3A//www.fantasyspavashi.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20copyright%20year%20looks%20a%20little%20old%2C%20so%20some%20visitors%20may%20assume%20the%20site%20hasn%27t%20been%20updated%20recently%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Fantasy%20Salon%20and%20Spa%20Vashi%20Plaza%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr"/>
@@ -14321,20 +14321,20 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Ramratan Aashiyana Beach Resort: I checked www.ramratanaashiyanaresort.com</t>
+          <t>A quick, polite note on www.ramratanaashiyanaresort.com</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.ramratanaashiyanaresort.com/ while looking at hotel businesses in Ulwe / Uran side (near Navi Mumbai), Panvel Taluka.
-Here's what a customer would notice today:
-• There are typos on the homepage that look unprofessional
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at hotel businesses in Ulwe / Uran side (near Navi Mumbai), Panvel Taluka, I visited https://www.ramratanaashiyanaresort.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A couple of small spelling slips on the homepage — easy to fix, and it helps first impressions
 • Check-availability incomplete
 • Banquet pricing FAQ-only
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Ramratan Aashiyana Beach Resort this week so it's clear what I'd change — no obligation.
-Regards,
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Ramratan Aashiyana Beach Resort this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14345,11 +14345,11 @@
       <c r="N140" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.ramratanaashiyanaresort.com/) and a couple of things stood out:
-• There are typos on the homepage that look unprofessional
+I'm Vaibhav from DMC Creatives Studio. I came across Ramratan Aashiyana Beach Resort and had a look at https://www.ramratanaashiyanaresort.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A couple of small spelling slips on the homepage — easy to fix, and it helps first impressions
 • Check-availability incomplete
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Ramratan Aashiyana Beach Resort this week so you can see the difference — no charge, no obligation.
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Ramratan Aashiyana Beach Resort this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14358,7 +14358,7 @@
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919930856111?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.ramratanaashiyanaresort.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%20are%20typos%20on%20the%20homepage%20that%20look%20unprofessional%0A%E2%80%A2%20Check-availability%20incomplete%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Ramratan%20Aashiyana%20Beach%20Resort%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919930856111?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Ramratan%20Aashiyana%20Beach%20Resort%20and%20had%20a%20look%20at%20https%3A//www.ramratanaashiyanaresort.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20couple%20of%20small%20spelling%20slips%20on%20the%20homepage%20%E2%80%94%20easy%20to%20fix%2C%20and%20it%20helps%20first%20impressions%0A%E2%80%A2%20Check-availability%20incomplete%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Ramratan%20Aashiyana%20Beach%20Resort%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr"/>
@@ -14414,18 +14414,18 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Blue Cross Vets Clinic: I checked www.bluecrossvetsclinic.com</t>
+          <t>A quick, polite note on www.bluecrossvetsclinic.com</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.bluecrossvetsclinic.com/ while looking at pet clinic businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site is a basic Wix brochure page — it doesn't look like a serious local brand
-People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
-I can share a free concept page for Blue Cross Vets Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at pet clinic businesses in Kharghar, Navi Mumbai, I visited https://www.bluecrossvetsclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The site still has a simple builder look; a cleaner custom layout would better match your brand
+People who find you on Google usually decide in a few seconds whether to enquire. A clearer next step on the site often helps.
+If you'd like, I can share a free concept page for Blue Cross Vets Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14436,10 +14436,10 @@
       <c r="N141" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.bluecrossvetsclinic.com/) and a couple of things stood out:
-• The site is a basic Wix brochure page — it doesn't look like a serious local brand
-People who find you on Google decide in a few seconds whether to enquire. The site should make that one tap, not a hunt.
-I can send a free one-page concept for Blue Cross Vets Clinic this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Blue Cross Vets Clinic and had a look at https://www.bluecrossvetsclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The site still has a simple builder look; a cleaner custom layout would better match your brand
+People who find you on Google usually decide in a few seconds whether to enquire. A clearer next step on the site often helps.
+If it would help, I can send a free one-page concept for Blue Cross Vets Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14448,7 +14448,7 @@
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918169067671?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.bluecrossvetsclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20is%20a%20basic%20Wix%20brochure%20page%20%E2%80%94%20it%20doesn%27t%20look%20like%20a%20serious%20local%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20The%20site%20should%20make%20that%20one%20tap%2C%20not%20a%20hunt.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Blue%20Cross%20Vets%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918169067671?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Blue%20Cross%20Vets%20Clinic%20and%20had%20a%20look%20at%20https%3A//www.bluecrossvetsclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20site%20still%20has%20a%20simple%20builder%20look%3B%20a%20cleaner%20custom%20layout%20would%20better%20match%20your%20brand%0A%0APeople%20who%20find%20you%20on%20Google%20usually%20decide%20in%20a%20few%20seconds%20whether%20to%20enquire.%20A%20clearer%20next%20step%20on%20the%20site%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Blue%20Cross%20Vets%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P141" s="2" t="inlineStr"/>
@@ -14500,20 +14500,20 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>FloDine Cruise / Cafe Relish: I checked flodine.in/home</t>
+          <t>A quick, polite note on flodine.in/home</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://flodine.in/home/ while looking at restaurant businesses in CBD Belapur, Navi Mumbai.
-Here's what a customer would notice today:
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at restaurant businesses in CBD Belapur, Navi Mumbai, I visited https://flodine.in/home/.
+I wanted to share a few small observations, only in case they're helpful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Cruise booking is enquiry-led not instant book
-• There's no proper online order/menu checkout — people bounce to Swiggy/Zomato
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for FloDine Cruise / Cafe Relish this week so it's clear what I'd change — no obligation.
-Regards,
+• There's no easy online order yet — a simple menu/checkout often keeps people from switching to Swiggy/Zomato
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for FloDine Cruise / Cafe Relish this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14524,11 +14524,11 @@
       <c r="N142" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://flodine.in/home/) and a couple of things stood out:
-• The pages look dated and thin — visitors don't get enough proof to call
+I'm Vaibhav from DMC Creatives Studio. I came across FloDine Cruise / Cafe Relish and had a look at https://flodine.in/home/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Cruise booking is enquiry-led not instant book
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for FloDine Cruise / Cafe Relish this week so you can see the difference — no charge, no obligation.
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for FloDine Cruise / Cafe Relish this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14537,7 +14537,7 @@
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918369797500?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//flodine.in/home/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%E2%80%A2%20Cruise%20booking%20is%20enquiry-led%20not%20instant%20book%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20FloDine%20Cruise%20/%20Cafe%20Relish%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918369797500?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20FloDine%20Cruise%20/%20Cafe%20Relish%20and%20had%20a%20look%20at%20https%3A//flodine.in/home/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%E2%80%A2%20Cruise%20booking%20is%20enquiry-led%20not%20instant%20book%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20FloDine%20Cruise%20/%20Cafe%20Relish%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr"/>
@@ -14593,19 +14593,19 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Arise Gym Kharghar: I checked arisefitness.in/gym-at-kharghar</t>
+          <t>A quick, polite note on arisefitness.in/gym-at-kharghar</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://arisefitness.in/gym-at-kharghar/ while looking at fitness businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at fitness businesses in Kharghar, Navi Mumbai, I visited https://arisefitness.in/gym-at-kharghar/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak conversion hierarchy vs modern competitors
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Arise Gym Kharghar this week so it's clear what I'd change — no obligation.
-Regards,
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Arise Gym Kharghar this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14616,11 +14616,11 @@
       <c r="N143" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://arisefitness.in/gym-at-kharghar/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
+I'm Vaibhav from DMC Creatives Studio. I came across Arise Gym Kharghar and had a look at https://arisefitness.in/gym-at-kharghar/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak conversion hierarchy vs modern competitors
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Arise Gym Kharghar this week so you can see the difference — no charge, no obligation.
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Arise Gym Kharghar this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14629,7 +14629,7 @@
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919967442981?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//arisefitness.in/gym-at-kharghar/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Arise%20Gym%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919967442981?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Arise%20Gym%20Kharghar%20and%20had%20a%20look%20at%20https%3A//arisefitness.in/gym-at-kharghar/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Arise%20Gym%20Kharghar%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr"/>
@@ -14685,19 +14685,19 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Elements Dental Clinic: I checked elementsdentalclinic.com</t>
+          <t>A quick, polite note on elementsdentalclinic.com</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://elementsdentalclinic.com/ while looking at dental businesses in Vashi, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Vashi, Navi Mumbai, I visited https://elementsdentalclinic.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak conversion hierarchy vs modern competitors
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Elements Dental Clinic this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Elements Dental Clinic this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14708,11 +14708,11 @@
       <c r="N144" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://elementsdentalclinic.com/) and a couple of things stood out:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I'm Vaibhav from DMC Creatives Studio. I came across Elements Dental Clinic and had a look at https://elementsdentalclinic.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak conversion hierarchy vs modern competitors
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Elements Dental Clinic this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Elements Dental Clinic this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14721,7 +14721,7 @@
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919819816669?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//elementsdentalclinic.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Elements%20Dental%20Clinic%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919819816669?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Elements%20Dental%20Clinic%20and%20had%20a%20look%20at%20https%3A//elementsdentalclinic.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Elements%20Dental%20Clinic%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr"/>
@@ -14777,19 +14777,19 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Kharghar: I checked healthcareimaging.co.in</t>
+          <t>A quick, polite note on healthcareimaging.co.in</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://healthcareimaging.co.in/ while looking at diagnostics businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at diagnostics businesses in Kharghar, Navi Mumbai, I visited https://healthcareimaging.co.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak conversion hierarchy vs modern competitors
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can share a free concept page for Healthcare Imaging Kharghar this week so it's clear what I'd change — no obligation.
-Regards,
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If you'd like, I can share a free concept page for Healthcare Imaging Kharghar this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14800,11 +14800,11 @@
       <c r="N145" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://healthcareimaging.co.in/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
+I'm Vaibhav from DMC Creatives Studio. I came across Healthcare Imaging Kharghar and had a look at https://healthcareimaging.co.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
 • Weak conversion hierarchy vs modern competitors
-Patients compare clinics on their phone before they call. A clearer booking page usually wins the appointment.
-I can send a free one-page concept for Healthcare Imaging Kharghar this week so you can see the difference — no charge, no obligation.
+Most patients compare clinics on their phone before they call. A clearer booking page often makes that choice easier.
+If it would help, I can send a free one-page concept for Healthcare Imaging Kharghar this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14813,7 +14813,7 @@
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917506946301?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//healthcareimaging.co.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20usually%20wins%20the%20appointment.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Healthcare%20Imaging%20Kharghar%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917506946301?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Healthcare%20Imaging%20Kharghar%20and%20had%20a%20look%20at%20https%3A//healthcareimaging.co.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0AMost%20patients%20compare%20clinics%20on%20their%20phone%20before%20they%20call.%20A%20clearer%20booking%20page%20often%20makes%20that%20choice%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Healthcare%20Imaging%20Kharghar%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr"/>
@@ -14869,19 +14869,19 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Dental Care: I checked www.sunshine-dentalcare.in</t>
+          <t>A quick, polite note on www.sunshine-dentalcare.in</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.sunshine-dentalcare.in/ while looking at dental businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at dental businesses in Kharghar, Navi Mumbai, I visited https://www.sunshine-dentalcare.in/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak conversion hierarchy vs modern competitors
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can share a free concept page for Sunshine Dental Care this week so it's clear what I'd change — no obligation.
-Regards,
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If you'd like, I can share a free concept page for Sunshine Dental Care this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14892,11 +14892,11 @@
       <c r="N146" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.sunshine-dentalcare.in/) and a couple of things stood out:
-• The site looks like a generic clinic template — not a brand patients would trust over a nearby competitor
+I'm Vaibhav from DMC Creatives Studio. I came across Sunshine Dental Care and had a look at https://www.sunshine-dentalcare.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels like a standard clinic template — a more personal look usually helps patients choose you
 • Weak conversion hierarchy vs modern competitors
-Patients Google a dentist, open 2–3 sites, and book the one that looks easiest. Right now yours makes them call and wait.
-I can send a free one-page concept for Sunshine Dental Care this week so you can see the difference — no charge, no obligation.
+Patients usually open 2–3 dentist sites on their phone and book the one that feels easiest. A clearer booking path often helps.
+If it would help, I can send a free one-page concept for Sunshine Dental Care this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14905,7 +14905,7 @@
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/917842268427?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.sunshine-dentalcare.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20clinic%20template%20%E2%80%94%20not%20a%20brand%20patients%20would%20trust%20over%20a%20nearby%20competitor%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20Google%20a%20dentist%2C%20open%202%E2%80%933%20sites%2C%20and%20book%20the%20one%20that%20looks%20easiest.%20Right%20now%20yours%20makes%20them%20call%20and%20wait.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sunshine%20Dental%20Care%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/917842268427?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sunshine%20Dental%20Care%20and%20had%20a%20look%20at%20https%3A//www.sunshine-dentalcare.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20like%20a%20standard%20clinic%20template%20%E2%80%94%20a%20more%20personal%20look%20usually%20helps%20patients%20choose%20you%0A%E2%80%A2%20Weak%20conversion%20hierarchy%20vs%20modern%20competitors%0A%0APatients%20usually%20open%202%E2%80%933%20dentist%20sites%20on%20their%20phone%20and%20book%20the%20one%20that%20feels%20easiest.%20A%20clearer%20booking%20path%20often%20helps.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sunshine%20Dental%20Care%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr"/>
@@ -14961,18 +14961,18 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Namastey Salon: I checked namasteysalon.com</t>
+          <t>A quick, polite note on namasteysalon.com</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://namasteysalon.com/ while looking at salon businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
-• Placeholder 'Lorem ipsum' dummy text is still visible on the site
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can share a free concept page for Namastey Salon this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at salon businesses in Kharghar, Navi Mumbai, I visited https://namasteysalon.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A little placeholder text is still visible — easy to replace with your own copy
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If you'd like, I can share a free concept page for Namastey Salon this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -14983,10 +14983,10 @@
       <c r="N147" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://namasteysalon.com/) and a couple of things stood out:
-• Placeholder 'Lorem ipsum' dummy text is still visible on the site
-People decide memberships/appointments from the phone. If trial/booking isn't obvious, they join the competitor who made it easy.
-I can send a free one-page concept for Namastey Salon this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Namastey Salon and had a look at https://namasteysalon.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A little placeholder text is still visible — easy to replace with your own copy
+People often decide trial/memberships from their phone. A simple booking button usually makes that easier.
+If it would help, I can send a free one-page concept for Namastey Salon this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -14995,7 +14995,7 @@
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919699999081?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//namasteysalon.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20Placeholder%20%27Lorem%20ipsum%27%20dummy%20text%20is%20still%20visible%20on%20the%20site%0A%0APeople%20decide%20memberships/appointments%20from%20the%20phone.%20If%20trial/booking%20isn%27t%20obvious%2C%20they%20join%20the%20competitor%20who%20made%20it%20easy.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Namastey%20Salon%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919699999081?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Namastey%20Salon%20and%20had%20a%20look%20at%20https%3A//namasteysalon.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20little%20placeholder%20text%20is%20still%20visible%20%E2%80%94%20easy%20to%20replace%20with%20your%20own%20copy%0A%0APeople%20often%20decide%20trial/memberships%20from%20their%20phone.%20A%20simple%20booking%20button%20usually%20makes%20that%20easier.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Namastey%20Salon%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr"/>
@@ -15051,20 +15051,20 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Link India Packers and Movers: I checked moversandpackerskharghar.in</t>
+          <t>A quick, polite note on moversandpackerskharghar.in</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://moversandpackerskharghar.in/ while looking at packers &amp; movers businesses in Kharghar, Navi Mumbai.
-Here's what a customer would notice today:
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at packers &amp; movers businesses in Kharghar, Navi Mumbai, I visited https://moversandpackerskharghar.in/.
+I wanted to share a few small observations, only in case they're helpful:
 • SEO-domain style URL (moversandpackerskharghar.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
 • Generic claims (256+ branches) hard to verify from site
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Link India Packers and Movers this week so it's clear what I'd change — no obligation.
-Regards,
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Link India Packers and Movers this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -15075,11 +15075,11 @@
       <c r="N148" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://moversandpackerskharghar.in/) and a couple of things stood out:
+I'm Vaibhav from DMC Creatives Studio. I came across Link India Packers and Movers and had a look at https://moversandpackerskharghar.in/. Hope you don't mind me sharing a couple of small observations — only if useful:
 • SEO-domain style URL (moversandpackerskharghar.in)
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Link India Packers and Movers this week so you can see the difference — no charge, no obligation.
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Link India Packers and Movers this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -15088,7 +15088,7 @@
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918879694359?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//moversandpackerskharghar.in/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20SEO-domain%20style%20URL%20%28moversandpackerskharghar.in%29%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Link%20India%20Packers%20and%20Movers%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918879694359?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Link%20India%20Packers%20and%20Movers%20and%20had%20a%20look%20at%20https%3A//moversandpackerskharghar.in/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20SEO-domain%20style%20URL%20%28moversandpackerskharghar.in%29%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Link%20India%20Packers%20and%20Movers%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr"/>
@@ -15144,18 +15144,18 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Tricity Realty / Ganesh Real Estates: I checked ganeshrealestates.com</t>
+          <t>A quick, polite note on ganeshrealestates.com</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://ganeshrealestates.com/ while looking at real estate broker businesses in Seawoods, Navi Mumbai.
-Here's what a customer would notice today:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can share a free concept page for Tricity Realty / Ganesh Real Estates this week so it's clear what I'd change — no obligation.
-Regards,
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at real estate broker businesses in Seawoods, Navi Mumbai, I visited https://ganeshrealestates.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If you'd like, I can share a free concept page for Tricity Realty / Ganesh Real Estates this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -15166,10 +15166,10 @@
       <c r="N149" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://ganeshrealestates.com/) and a couple of things stood out:
-• There's no clear Book / Enquire button — visitors have to call instead of converting on the site
-High-ticket buyers want a trustworthy site with a quote form — directory pages make them hesitate.
-I can send a free one-page concept for Tricity Realty / Ganesh Real Estates this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Tricity Realty / Ganesh Real Estates and had a look at https://ganeshrealestates.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• A clear Enquire / Book button on the homepage would make it easier for people who don't want to call first
+For this kind of work, people like a clear, trustworthy site with an easy way to ask for a quote.
+If it would help, I can send a free one-page concept for Tricity Realty / Ganesh Real Estates this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -15178,7 +15178,7 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919222223532?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//ganeshrealestates.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20There%27s%20no%20clear%20Book%20/%20Enquire%20button%20%E2%80%94%20visitors%20have%20to%20call%20instead%20of%20converting%20on%20the%20site%0A%0AHigh-ticket%20buyers%20want%20a%20trustworthy%20site%20with%20a%20quote%20form%20%E2%80%94%20directory%20pages%20make%20them%20hesitate.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Tricity%20Realty%20/%20Ganesh%20Real%20Estates%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919222223532?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Tricity%20Realty%20/%20Ganesh%20Real%20Estates%20and%20had%20a%20look%20at%20https%3A//ganeshrealestates.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20A%20clear%20Enquire%20/%20Book%20button%20on%20the%20homepage%20would%20make%20it%20easier%20for%20people%20who%20don%27t%20want%20to%20call%20first%0A%0AFor%20this%20kind%20of%20work%2C%20people%20like%20a%20clear%2C%20trustworthy%20site%20with%20an%20easy%20way%20to%20ask%20for%20a%20quote.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Tricity%20Realty%20/%20Ganesh%20Real%20Estates%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr"/>
@@ -15234,20 +15234,20 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Sagar Palace: I checked www.sagarpalace.com</t>
+          <t>A quick, polite note on www.sagarpalace.com</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I opened https://www.sagarpalace.com/ while looking at banquet businesses in New Panvel, Navi Mumbai.
-Here's what a customer would notice today:
-• The site looks like a generic template rather than your brand
-• The pages look dated and thin — visitors don't get enough proof to call
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. While looking at banquet businesses in New Panvel, Navi Mumbai, I visited https://www.sagarpalace.com/.
+I wanted to share a few small observations, only in case they're helpful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
 • Weak package/CTA hierarchy
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can share a free concept page for Sagar Palace this week so it's clear what I'd change — no obligation.
-Regards,
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If you'd like, I can share a free concept page for Sagar Palace this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -15258,11 +15258,11 @@
       <c r="N150" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I opened your website (https://www.sagarpalace.com/) and a couple of things stood out:
-• The site looks like a generic template rather than your brand
-• The pages look dated and thin — visitors don't get enough proof to call
-Guests who land on your site should be able to check dates and book. If they can't, they pay Booking.com instead of you.
-I can send a free one-page concept for Sagar Palace this week so you can see the difference — no charge, no obligation.
+I'm Vaibhav from DMC Creatives Studio. I came across Sagar Palace and had a look at https://www.sagarpalace.com/. Hope you don't mind me sharing a couple of small observations — only if useful:
+• The layout still feels a little template-like — a more personal look would better reflect your brand
+• The pages are a little light on detail — a bit more proof (photos, services, reviews) usually helps people feel ready to call
+Guests who land on your site often want to check dates quickly. Making that easy can bring more direct bookings.
+If it would help, I can send a free one-page concept for Sagar Palace this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -15271,7 +15271,7 @@
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918877557773?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20opened%20your%20website%20%28https%3A//www.sagarpalace.com/%29%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20The%20site%20looks%20like%20a%20generic%20template%20rather%20than%20your%20brand%0A%E2%80%A2%20The%20pages%20look%20dated%20and%20thin%20%E2%80%94%20visitors%20don%27t%20get%20enough%20proof%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20should%20be%20able%20to%20check%20dates%20and%20book.%20If%20they%20can%27t%2C%20they%20pay%20Booking.com%20instead%20of%20you.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Sagar%20Palace%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918877557773?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Sagar%20Palace%20and%20had%20a%20look%20at%20https%3A//www.sagarpalace.com/.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20The%20layout%20still%20feels%20a%20little%20template-like%20%E2%80%94%20a%20more%20personal%20look%20would%20better%20reflect%20your%20brand%0A%E2%80%A2%20The%20pages%20are%20a%20little%20light%20on%20detail%20%E2%80%94%20a%20bit%20more%20proof%20%28photos%2C%20services%2C%20reviews%29%20usually%20helps%20people%20feel%20ready%20to%20call%0A%0AGuests%20who%20land%20on%20your%20site%20often%20want%20to%20check%20dates%20quickly.%20Making%20that%20easy%20can%20bring%20more%20direct%20bookings.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Sagar%20Palace%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr"/>
@@ -15327,19 +15327,19 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Cafe G G: no website of your own yet</t>
+          <t>A quick note for Cafe G G</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I searched for Cafe G G in Kamothe, Navi Mumbai — there's no owned website, only listings.
-Here's what a customer would notice today:
-• You don't have your own website — people only find you on Zomato/Swiggy/Google, so they order there instead of from you
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. I came across Cafe G G in Kamothe, Navi Mumbai — most of the online presence right now is through listings rather than a site of your own.
+I wanted to share a few small observations, only in case they're helpful:
+• Most people currently find you on listings (Google / Zomato / Swiggy) rather than a site of your own
 • Offers free home delivery by phone with no branded order path
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Cafe G G this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Cafe G G this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -15350,11 +15350,11 @@
       <c r="N151" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I searched for Cafe G G online and a couple of things stood out:
-• You don't have your own website — people only find you on Zomato/Swiggy/Google, so they order there instead of from you
+I'm Vaibhav from DMC Creatives Studio. I came across Cafe G G while looking at local businesses. Hope you don't mind me sharing a couple of small observations — only if useful:
+• Most people currently find you on listings (Google / Zomato / Swiggy) rather than a site of your own
 • Offers free home delivery by phone with no branded order path
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Cafe G G this week so you can see the difference — no charge, no obligation.
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Cafe G G this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -15363,7 +15363,7 @@
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/919167828676?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20searched%20for%20Cafe%20G%20G%20online%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20You%20don%27t%20have%20your%20own%20website%20%E2%80%94%20people%20only%20find%20you%20on%20Zomato/Swiggy/Google%2C%20so%20they%20order%20there%20instead%20of%20from%20you%0A%E2%80%A2%20Offers%20free%20home%20delivery%20by%20phone%20with%20no%20branded%20order%20path%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Cafe%20G%20G%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/919167828676?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Cafe%20G%20G%20while%20looking%20at%20local%20businesses.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Most%20people%20currently%20find%20you%20on%20listings%20%28Google%20/%20Zomato%20/%20Swiggy%29%20rather%20than%20a%20site%20of%20your%20own%0A%E2%80%A2%20Offers%20free%20home%20delivery%20by%20phone%20with%20no%20branded%20order%20path%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Cafe%20G%20G%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr"/>
@@ -15419,19 +15419,19 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Communion Cafe: no website of your own yet</t>
+          <t>A quick note for Communion Cafe</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I searched for Communion Cafe in CBD Belapur, Navi Mumbai — there's no owned website, only listings.
-Here's what a customer would notice today:
-• You don't have your own website — people only find you on Zomato/Swiggy/Google, so they order there instead of from you
+I hope you're well. I'm Vaibhav from DMC Creatives Studio. I came across Communion Cafe in CBD Belapur, Navi Mumbai — most of the online presence right now is through listings rather than a site of your own.
+I wanted to share a few small observations, only in case they're helpful:
+• Most people currently find you on listings (Google / Zomato / Swiggy) rather than a site of your own
 • Premium community cafe with media buzz but no brand site for bookings/events
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can share a free concept page for Communion Cafe this week so it's clear what I'd change — no obligation.
-Regards,
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If you'd like, I can share a free concept page for Communion Cafe this week so you can see what a clearer version might look like. No obligation at all.
+Warm regards,
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -15442,11 +15442,11 @@
       <c r="N152" s="2" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I searched for Communion Cafe online and a couple of things stood out:
-• You don't have your own website — people only find you on Zomato/Swiggy/Google, so they order there instead of from you
+I'm Vaibhav from DMC Creatives Studio. I came across Communion Cafe while looking at local businesses. Hope you don't mind me sharing a couple of small observations — only if useful:
+• Most people currently find you on listings (Google / Zomato / Swiggy) rather than a site of your own
 • Premium community cafe with media buzz but no brand site for bookings/events
-Hungry customers open your site to order or book a table. If that's hard, they go to Zomato/Swiggy and you lose the margin.
-I can send a free one-page concept for Communion Cafe this week so you can see the difference — no charge, no obligation.
+When someone is ready to order, they usually pick whichever option feels simplest. A clearer order/book path on your own site can help.
+If it would help, I can send a free one-page concept for Communion Cafe this week — no charge and no obligation, just so you can see the idea.
 Vaibhav Gurav
 DMC Creatives Studio
 www.dmcstudio.in
@@ -15455,7 +15455,7 @@
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>https://wa.me/918928666902?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20searched%20for%20Communion%20Cafe%20online%20and%20a%20couple%20of%20things%20stood%20out%3A%0A%E2%80%A2%20You%20don%27t%20have%20your%20own%20website%20%E2%80%94%20people%20only%20find%20you%20on%20Zomato/Swiggy/Google%2C%20so%20they%20order%20there%20instead%20of%20from%20you%0A%E2%80%A2%20Premium%20community%20cafe%20with%20media%20buzz%20but%20no%20brand%20site%20for%20bookings/events%0A%0AHungry%20customers%20open%20your%20site%20to%20order%20or%20book%20a%20table.%20If%20that%27s%20hard%2C%20they%20go%20to%20Zomato/Swiggy%20and%20you%20lose%20the%20margin.%0A%0AI%20can%20send%20a%20free%20one-page%20concept%20for%20Communion%20Cafe%20this%20week%20so%20you%20can%20see%20the%20difference%20%E2%80%94%20no%20charge%2C%20no%20obligation.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
+          <t>https://wa.me/918928666902?text=Hello%2C%0A%0AI%27m%20Vaibhav%20from%20DMC%20Creatives%20Studio.%20I%20came%20across%20Communion%20Cafe%20while%20looking%20at%20local%20businesses.%20Hope%20you%20don%27t%20mind%20me%20sharing%20a%20couple%20of%20small%20observations%20%E2%80%94%20only%20if%20useful%3A%0A%E2%80%A2%20Most%20people%20currently%20find%20you%20on%20listings%20%28Google%20/%20Zomato%20/%20Swiggy%29%20rather%20than%20a%20site%20of%20your%20own%0A%E2%80%A2%20Premium%20community%20cafe%20with%20media%20buzz%20but%20no%20brand%20site%20for%20bookings/events%0A%0AWhen%20someone%20is%20ready%20to%20order%2C%20they%20usually%20pick%20whichever%20option%20feels%20simplest.%20A%20clearer%20order/book%20path%20on%20your%20own%20site%20can%20help.%0A%0AIf%20it%20would%20help%2C%20I%20can%20send%20a%20free%20one-page%20concept%20for%20Communion%20Cafe%20this%20week%20%E2%80%94%20no%20charge%20and%20no%20obligation%2C%20just%20so%20you%20can%20see%20the%20idea.%0A%0AVaibhav%20Gurav%0ADMC%20Creatives%20Studio%0Awww.dmcstudio.in%0A%2B91%2083693%2061785</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr"/>
